--- a/artfynd/A 42607-2025 artfynd.xlsx
+++ b/artfynd/A 42607-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128740505</v>
+        <v>128738845</v>
       </c>
       <c r="B2" t="n">
-        <v>98610</v>
+        <v>86729</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219862</v>
+        <v>3762</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717182</v>
+        <v>716961</v>
       </c>
       <c r="R2" t="n">
-        <v>6374336</v>
+        <v>6374255</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,9 +743,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,44 +770,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128740514</v>
+        <v>128738831</v>
       </c>
       <c r="B3" t="n">
-        <v>86753</v>
+        <v>86972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3712</v>
+        <v>3767</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717295</v>
+        <v>717030</v>
       </c>
       <c r="R3" t="n">
-        <v>6374249</v>
+        <v>6374429</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -840,9 +850,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,44 +877,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128738854</v>
+        <v>128742256</v>
       </c>
       <c r="B4" t="n">
-        <v>86927</v>
+        <v>86972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716967</v>
+        <v>717053</v>
       </c>
       <c r="R4" t="n">
-        <v>6374338</v>
+        <v>6374253</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -937,50 +957,39 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128738845</v>
+        <v>128740514</v>
       </c>
       <c r="B5" t="n">
-        <v>86729</v>
+        <v>86753</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -988,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1012,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716961</v>
+        <v>717295</v>
       </c>
       <c r="R5" t="n">
-        <v>6374255</v>
+        <v>6374249</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1045,19 +1054,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1072,44 +1071,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128738831</v>
+        <v>128738854</v>
       </c>
       <c r="B6" t="n">
-        <v>86972</v>
+        <v>86927</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1119,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717030</v>
+        <v>716967</v>
       </c>
       <c r="R6" t="n">
-        <v>6374429</v>
+        <v>6374338</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1154,7 +1153,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1164,7 +1163,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,6 +1172,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1191,32 +1191,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128742256</v>
+        <v>128740505</v>
       </c>
       <c r="B7" t="n">
-        <v>86972</v>
+        <v>98613</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3767</v>
+        <v>219862</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717053</v>
+        <v>717182</v>
       </c>
       <c r="R7" t="n">
-        <v>6374253</v>
+        <v>6374336</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,12 +1276,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1386,32 +1386,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128738834</v>
+        <v>128738853</v>
       </c>
       <c r="B9" t="n">
-        <v>86972</v>
+        <v>86927</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716985</v>
+        <v>717033</v>
       </c>
       <c r="R9" t="n">
-        <v>6374341</v>
+        <v>6374425</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1475,6 +1475,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1493,7 +1494,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128738837</v>
+        <v>128738834</v>
       </c>
       <c r="B10" t="n">
         <v>86972</v>
@@ -1528,10 +1529,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717037</v>
+        <v>716985</v>
       </c>
       <c r="R10" t="n">
-        <v>6374236</v>
+        <v>6374341</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1563,7 +1564,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1573,7 +1574,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1600,32 +1601,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128738853</v>
+        <v>128742266</v>
       </c>
       <c r="B11" t="n">
-        <v>86927</v>
+        <v>86729</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1635,10 +1636,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>717033</v>
+        <v>717201</v>
       </c>
       <c r="R11" t="n">
-        <v>6374425</v>
+        <v>6374151</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1668,72 +1669,61 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128742266</v>
+        <v>128738837</v>
       </c>
       <c r="B12" t="n">
-        <v>86729</v>
+        <v>86972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1743,10 +1733,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>717201</v>
+        <v>717037</v>
       </c>
       <c r="R12" t="n">
-        <v>6374151</v>
+        <v>6374236</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,9 +1766,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1793,44 +1793,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128742285</v>
+        <v>128740482</v>
       </c>
       <c r="B13" t="n">
-        <v>86927</v>
+        <v>86972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716995</v>
+        <v>717057</v>
       </c>
       <c r="R13" t="n">
-        <v>6374141</v>
+        <v>6374457</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1884,67 +1884,63 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128742275</v>
+        <v>128740504</v>
       </c>
       <c r="B14" t="n">
-        <v>86878</v>
+        <v>98613</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6003296</v>
+        <v>219862</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716983</v>
+        <v>717091</v>
       </c>
       <c r="R14" t="n">
-        <v>6374138</v>
+        <v>6374400</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1979,62 +1975,56 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Kollekt taget för sekvensering av Martin Axegård.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128740504</v>
+        <v>128742285</v>
       </c>
       <c r="B15" t="n">
-        <v>98610</v>
+        <v>86927</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219862</v>
+        <v>6003295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2044,10 +2034,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>717091</v>
+        <v>716995</v>
       </c>
       <c r="R15" t="n">
-        <v>6374400</v>
+        <v>6374141</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2088,28 +2078,29 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128740482</v>
+        <v>128742275</v>
       </c>
       <c r="B16" t="n">
-        <v>86972</v>
+        <v>86878</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2117,34 +2108,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3767</v>
+        <v>6003296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Stor odörspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius mussivus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.) Melot</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>717057</v>
+        <v>716983</v>
       </c>
       <c r="R16" t="n">
-        <v>6374457</v>
+        <v>6374138</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2179,56 +2173,62 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Kollekt taget för sekvensering av Martin Axegård.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128738885</v>
+        <v>128738898</v>
       </c>
       <c r="B17" t="n">
-        <v>86775</v>
+        <v>86890</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>424</v>
+        <v>3674</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>717029</v>
+        <v>716960</v>
       </c>
       <c r="R17" t="n">
-        <v>6374326</v>
+        <v>6374150</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2310,32 +2310,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128738859</v>
+        <v>128738832</v>
       </c>
       <c r="B18" t="n">
-        <v>98622</v>
+        <v>86972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219874</v>
+        <v>3767</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716963</v>
+        <v>717000</v>
       </c>
       <c r="R18" t="n">
-        <v>6374082</v>
+        <v>6374409</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2417,32 +2417,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128738857</v>
+        <v>128738885</v>
       </c>
       <c r="B19" t="n">
-        <v>86927</v>
+        <v>86775</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>717049</v>
+        <v>717029</v>
       </c>
       <c r="R19" t="n">
-        <v>6374317</v>
+        <v>6374326</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2506,7 +2506,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2525,10 +2524,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128738898</v>
+        <v>128738859</v>
       </c>
       <c r="B20" t="n">
-        <v>86890</v>
+        <v>98625</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2536,21 +2535,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3674</v>
+        <v>219874</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2560,10 +2559,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>716960</v>
+        <v>716963</v>
       </c>
       <c r="R20" t="n">
-        <v>6374150</v>
+        <v>6374082</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2595,7 +2594,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2605,7 +2604,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2632,7 +2631,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128738856</v>
+        <v>128742286</v>
       </c>
       <c r="B21" t="n">
         <v>86927</v>
@@ -2667,10 +2666,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>716986</v>
+        <v>716970</v>
       </c>
       <c r="R21" t="n">
-        <v>6374339</v>
+        <v>6374097</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2700,19 +2699,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2728,12 +2717,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2838,32 +2827,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128738832</v>
+        <v>128738857</v>
       </c>
       <c r="B23" t="n">
-        <v>86972</v>
+        <v>86927</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2873,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>717000</v>
+        <v>717049</v>
       </c>
       <c r="R23" t="n">
-        <v>6374409</v>
+        <v>6374317</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2908,7 +2897,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2918,7 +2907,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2927,6 +2916,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2945,7 +2935,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128742286</v>
+        <v>128738856</v>
       </c>
       <c r="B24" t="n">
         <v>86927</v>
@@ -2980,10 +2970,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>716970</v>
+        <v>716986</v>
       </c>
       <c r="R24" t="n">
-        <v>6374097</v>
+        <v>6374339</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3013,9 +3003,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3031,19 +3031,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128740485</v>
+        <v>128742257</v>
       </c>
       <c r="B25" t="n">
         <v>86972</v>
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>717286</v>
+        <v>716992</v>
       </c>
       <c r="R25" t="n">
-        <v>6374251</v>
+        <v>6374120</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3128,19 +3128,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128742257</v>
+        <v>128740485</v>
       </c>
       <c r="B26" t="n">
         <v>86972</v>
@@ -3175,10 +3175,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>716992</v>
+        <v>717286</v>
       </c>
       <c r="R26" t="n">
-        <v>6374120</v>
+        <v>6374251</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,12 +3225,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128740489</v>
+        <v>128742273</v>
       </c>
       <c r="B28" t="n">
-        <v>90975</v>
+        <v>86903</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3345,21 +3345,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5741</v>
+        <v>1988</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>717220</v>
+        <v>717014</v>
       </c>
       <c r="R28" t="n">
-        <v>6374302</v>
+        <v>6374164</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3419,22 +3419,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128742273</v>
+        <v>128740489</v>
       </c>
       <c r="B29" t="n">
-        <v>86903</v>
+        <v>90975</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3442,21 +3442,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1988</v>
+        <v>5741</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>717014</v>
+        <v>717220</v>
       </c>
       <c r="R29" t="n">
-        <v>6374164</v>
+        <v>6374302</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3516,44 +3516,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128742283</v>
+        <v>128738846</v>
       </c>
       <c r="B30" t="n">
-        <v>86927</v>
+        <v>90975</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6003295</v>
+        <v>5741</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3563,10 +3563,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>717040</v>
+        <v>717037</v>
       </c>
       <c r="R30" t="n">
-        <v>6374195</v>
+        <v>6374226</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3596,62 +3596,71 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128742281</v>
+        <v>128738839</v>
       </c>
       <c r="B31" t="n">
-        <v>86927</v>
+        <v>86972</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3664,7 +3673,7 @@
         <v>717039</v>
       </c>
       <c r="R31" t="n">
-        <v>6374227</v>
+        <v>6374168</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3694,62 +3703,71 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128738839</v>
+        <v>128742283</v>
       </c>
       <c r="B32" t="n">
-        <v>86972</v>
+        <v>86927</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3759,10 +3777,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>717039</v>
+        <v>717040</v>
       </c>
       <c r="R32" t="n">
-        <v>6374168</v>
+        <v>6374195</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3792,71 +3810,62 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128738846</v>
+        <v>128742281</v>
       </c>
       <c r="B33" t="n">
-        <v>90975</v>
+        <v>86927</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5741</v>
+        <v>6003295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3866,10 +3875,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>717037</v>
+        <v>717039</v>
       </c>
       <c r="R33" t="n">
-        <v>6374226</v>
+        <v>6374227</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3899,39 +3908,30 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4035,10 +4035,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128742272</v>
+        <v>128742254</v>
       </c>
       <c r="B35" t="n">
-        <v>91001</v>
+        <v>86972</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4046,21 +4046,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5747</v>
+        <v>3767</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>717018</v>
+        <v>717285</v>
       </c>
       <c r="R35" t="n">
-        <v>6374179</v>
+        <v>6374272</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4132,10 +4132,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128742254</v>
+        <v>128742272</v>
       </c>
       <c r="B36" t="n">
-        <v>86972</v>
+        <v>91001</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4143,21 +4143,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3767</v>
+        <v>5747</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4167,10 +4167,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>717285</v>
+        <v>717018</v>
       </c>
       <c r="R36" t="n">
-        <v>6374272</v>
+        <v>6374179</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4327,7 +4327,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128740502</v>
+        <v>128740499</v>
       </c>
       <c r="B38" t="n">
         <v>86927</v>
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>717282</v>
+        <v>717145</v>
       </c>
       <c r="R38" t="n">
-        <v>6374266</v>
+        <v>6374308</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4425,7 +4425,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128740499</v>
+        <v>128740502</v>
       </c>
       <c r="B39" t="n">
         <v>86927</v>
@@ -4460,10 +4460,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>717145</v>
+        <v>717282</v>
       </c>
       <c r="R39" t="n">
-        <v>6374308</v>
+        <v>6374266</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4523,10 +4523,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128738858</v>
+        <v>128738866</v>
       </c>
       <c r="B40" t="n">
-        <v>86927</v>
+        <v>90208</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4534,21 +4534,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6003295</v>
+        <v>970</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4558,10 +4558,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>717003</v>
+        <v>717039</v>
       </c>
       <c r="R40" t="n">
-        <v>6374177</v>
+        <v>6374321</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4631,7 +4631,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128738900</v>
+        <v>128740521</v>
       </c>
       <c r="B41" t="n">
         <v>86890</v>
@@ -4666,10 +4666,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>716960</v>
+        <v>717216</v>
       </c>
       <c r="R41" t="n">
-        <v>6374079</v>
+        <v>6374357</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4699,19 +4699,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>09:09</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>09:09</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4726,19 +4716,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128740521</v>
+        <v>128738900</v>
       </c>
       <c r="B42" t="n">
         <v>86890</v>
@@ -4773,10 +4763,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>717216</v>
+        <v>716960</v>
       </c>
       <c r="R42" t="n">
-        <v>6374357</v>
+        <v>6374079</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4806,9 +4796,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4823,12 +4823,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4933,7 +4933,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128738897</v>
+        <v>128738858</v>
       </c>
       <c r="B44" t="n">
         <v>86927</v>
@@ -4968,10 +4968,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>717015</v>
+        <v>717003</v>
       </c>
       <c r="R44" t="n">
-        <v>6374144</v>
+        <v>6374177</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5041,10 +5041,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128738866</v>
+        <v>128738897</v>
       </c>
       <c r="B45" t="n">
-        <v>90208</v>
+        <v>86927</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5052,21 +5052,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>970</v>
+        <v>6003295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5076,10 +5076,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>717039</v>
+        <v>717015</v>
       </c>
       <c r="R45" t="n">
-        <v>6374321</v>
+        <v>6374144</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5252,32 +5252,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128738895</v>
+        <v>128740509</v>
       </c>
       <c r="B47" t="n">
-        <v>86927</v>
+        <v>86949</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5287,10 +5287,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>716974</v>
+        <v>717258</v>
       </c>
       <c r="R47" t="n">
-        <v>6374284</v>
+        <v>6374286</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5320,40 +5320,29 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5467,10 +5456,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128740509</v>
+        <v>128742259</v>
       </c>
       <c r="B49" t="n">
-        <v>86949</v>
+        <v>86972</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5478,21 +5467,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5502,10 +5491,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>717258</v>
+        <v>716980</v>
       </c>
       <c r="R49" t="n">
-        <v>6374286</v>
+        <v>6374067</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5552,19 +5541,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128742259</v>
+        <v>128738842</v>
       </c>
       <c r="B50" t="n">
         <v>86972</v>
@@ -5599,10 +5588,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>716980</v>
+        <v>716981</v>
       </c>
       <c r="R50" t="n">
-        <v>6374067</v>
+        <v>6374088</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5632,9 +5621,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5649,19 +5648,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128742268</v>
+        <v>128738895</v>
       </c>
       <c r="B51" t="n">
         <v>86927</v>
@@ -5696,10 +5695,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>717267</v>
+        <v>716974</v>
       </c>
       <c r="R51" t="n">
-        <v>6374322</v>
+        <v>6374284</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5729,9 +5728,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5747,19 +5756,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128742280</v>
+        <v>128742268</v>
       </c>
       <c r="B52" t="n">
         <v>86927</v>
@@ -5794,10 +5803,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>717058</v>
+        <v>717267</v>
       </c>
       <c r="R52" t="n">
-        <v>6374174</v>
+        <v>6374322</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5857,32 +5866,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128738842</v>
+        <v>128742280</v>
       </c>
       <c r="B53" t="n">
-        <v>86972</v>
+        <v>86927</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5892,10 +5901,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>716981</v>
+        <v>717058</v>
       </c>
       <c r="R53" t="n">
-        <v>6374088</v>
+        <v>6374174</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5925,71 +5934,62 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>09:31</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>09:31</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128738880</v>
+        <v>128738843</v>
       </c>
       <c r="B54" t="n">
-        <v>86753</v>
+        <v>86972</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3712</v>
+        <v>3767</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5999,10 +5999,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>716983</v>
+        <v>716967</v>
       </c>
       <c r="R54" t="n">
-        <v>6374266</v>
+        <v>6374084</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6071,32 +6071,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128738896</v>
+        <v>128738880</v>
       </c>
       <c r="B55" t="n">
-        <v>86927</v>
+        <v>86753</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6106,10 +6106,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>717038</v>
+        <v>716983</v>
       </c>
       <c r="R55" t="n">
-        <v>6374195</v>
+        <v>6374266</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6160,7 +6160,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6179,32 +6178,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128742289</v>
+        <v>128738838</v>
       </c>
       <c r="B56" t="n">
-        <v>86927</v>
+        <v>86972</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6214,10 +6213,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>716965</v>
+        <v>717020</v>
       </c>
       <c r="R56" t="n">
-        <v>6374079</v>
+        <v>6374199</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6247,37 +6246,46 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128742269</v>
+        <v>128738896</v>
       </c>
       <c r="B57" t="n">
         <v>86927</v>
@@ -6312,10 +6320,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>717186</v>
+        <v>717038</v>
       </c>
       <c r="R57" t="n">
-        <v>6374129</v>
+        <v>6374195</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6345,9 +6353,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6363,19 +6381,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128742279</v>
+        <v>128742289</v>
       </c>
       <c r="B58" t="n">
         <v>86927</v>
@@ -6410,10 +6428,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>717013</v>
+        <v>716965</v>
       </c>
       <c r="R58" t="n">
-        <v>6374176</v>
+        <v>6374079</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6473,7 +6491,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128742288</v>
+        <v>128742269</v>
       </c>
       <c r="B59" t="n">
         <v>86927</v>
@@ -6508,10 +6526,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>716995</v>
+        <v>717186</v>
       </c>
       <c r="R59" t="n">
-        <v>6374147</v>
+        <v>6374129</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6571,32 +6589,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128738843</v>
+        <v>128742279</v>
       </c>
       <c r="B60" t="n">
-        <v>86972</v>
+        <v>86927</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6606,10 +6624,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>716967</v>
+        <v>717013</v>
       </c>
       <c r="R60" t="n">
-        <v>6374084</v>
+        <v>6374176</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6639,71 +6657,62 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128738838</v>
+        <v>128742288</v>
       </c>
       <c r="B61" t="n">
-        <v>86972</v>
+        <v>86927</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6713,10 +6722,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>717020</v>
+        <v>716995</v>
       </c>
       <c r="R61" t="n">
-        <v>6374199</v>
+        <v>6374147</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6746,39 +6755,30 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7186,32 +7186,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128738886</v>
+        <v>128738893</v>
       </c>
       <c r="B66" t="n">
-        <v>86775</v>
+        <v>86927</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7221,10 +7221,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>716990</v>
+        <v>717000</v>
       </c>
       <c r="R66" t="n">
-        <v>6374260</v>
+        <v>6374121</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7275,6 +7275,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7293,32 +7294,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128742263</v>
+        <v>128738841</v>
       </c>
       <c r="B67" t="n">
-        <v>90975</v>
+        <v>86972</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5741</v>
+        <v>3767</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7328,10 +7329,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>717281</v>
+        <v>716992</v>
       </c>
       <c r="R67" t="n">
-        <v>6374199</v>
+        <v>6374116</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7361,9 +7362,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7378,19 +7389,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128742252</v>
+        <v>128738835</v>
       </c>
       <c r="B68" t="n">
         <v>86972</v>
@@ -7425,10 +7436,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>717146</v>
+        <v>716983</v>
       </c>
       <c r="R68" t="n">
-        <v>6374313</v>
+        <v>6374357</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7458,9 +7469,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7475,19 +7496,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128738841</v>
+        <v>128742252</v>
       </c>
       <c r="B69" t="n">
         <v>86972</v>
@@ -7522,10 +7543,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>716992</v>
+        <v>717146</v>
       </c>
       <c r="R69" t="n">
-        <v>6374116</v>
+        <v>6374313</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7555,19 +7576,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>09:50</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7582,44 +7593,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128738835</v>
+        <v>128740522</v>
       </c>
       <c r="B70" t="n">
-        <v>86972</v>
+        <v>86890</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7629,10 +7640,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>716983</v>
+        <v>717274</v>
       </c>
       <c r="R70" t="n">
-        <v>6374357</v>
+        <v>6374210</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7662,19 +7673,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>14:27</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7689,22 +7690,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128740522</v>
+        <v>128742263</v>
       </c>
       <c r="B71" t="n">
-        <v>86890</v>
+        <v>90975</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7712,21 +7713,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3674</v>
+        <v>5741</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7736,10 +7737,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>717274</v>
+        <v>717281</v>
       </c>
       <c r="R71" t="n">
-        <v>6374210</v>
+        <v>6374199</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7786,44 +7787,44 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128738893</v>
+        <v>128738886</v>
       </c>
       <c r="B72" t="n">
-        <v>86927</v>
+        <v>86775</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7833,10 +7834,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>717000</v>
+        <v>716990</v>
       </c>
       <c r="R72" t="n">
-        <v>6374121</v>
+        <v>6374260</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7868,7 +7869,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -7878,7 +7879,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7887,7 +7888,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8003,10 +8003,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128738884</v>
+        <v>128742255</v>
       </c>
       <c r="B74" t="n">
-        <v>86775</v>
+        <v>86972</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8014,21 +8014,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>424</v>
+        <v>3767</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8038,10 +8038,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>716969</v>
+        <v>717059</v>
       </c>
       <c r="R74" t="n">
-        <v>6374310</v>
+        <v>6374329</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8071,19 +8071,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>14:32</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8098,19 +8088,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128738867</v>
+        <v>128742276</v>
       </c>
       <c r="B75" t="n">
         <v>86949</v>
@@ -8145,10 +8135,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>717115</v>
+        <v>717269</v>
       </c>
       <c r="R75" t="n">
-        <v>6374297</v>
+        <v>6374317</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8178,19 +8168,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>13:35</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8205,44 +8185,44 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128738892</v>
+        <v>128738884</v>
       </c>
       <c r="B76" t="n">
-        <v>86927</v>
+        <v>86775</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8252,10 +8232,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>717037</v>
+        <v>716969</v>
       </c>
       <c r="R76" t="n">
-        <v>6374150</v>
+        <v>6374310</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8287,7 +8267,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8297,7 +8277,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8306,7 +8286,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8325,7 +8304,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128742276</v>
+        <v>128738867</v>
       </c>
       <c r="B77" t="n">
         <v>86949</v>
@@ -8360,10 +8339,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>717269</v>
+        <v>717115</v>
       </c>
       <c r="R77" t="n">
-        <v>6374317</v>
+        <v>6374297</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8393,9 +8372,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8410,44 +8399,44 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128742255</v>
+        <v>128738848</v>
       </c>
       <c r="B78" t="n">
-        <v>86972</v>
+        <v>57686</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3767</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8457,10 +8446,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>717059</v>
+        <v>717165</v>
       </c>
       <c r="R78" t="n">
-        <v>6374329</v>
+        <v>6374351</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8490,9 +8479,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8507,22 +8506,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128738848</v>
+        <v>128738892</v>
       </c>
       <c r="B79" t="n">
-        <v>57686</v>
+        <v>86927</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8530,21 +8529,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6003295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8554,10 +8553,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>717165</v>
+        <v>717037</v>
       </c>
       <c r="R79" t="n">
-        <v>6374351</v>
+        <v>6374150</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8589,7 +8588,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8599,7 +8598,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8608,6 +8607,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8626,45 +8626,48 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128740512</v>
+        <v>128738882</v>
       </c>
       <c r="B80" t="n">
-        <v>86753</v>
+        <v>87054</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3712</v>
+        <v>3563</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Stor granspindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius bovinus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Fr. sl.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>717079</v>
+        <v>717013</v>
       </c>
       <c r="R80" t="n">
-        <v>6374436</v>
+        <v>6374226</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8694,29 +8697,40 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -8830,32 +8844,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128738894</v>
+        <v>128740512</v>
       </c>
       <c r="B82" t="n">
-        <v>86927</v>
+        <v>86753</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8865,10 +8879,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>716975</v>
+        <v>717079</v>
       </c>
       <c r="R82" t="n">
-        <v>6374071</v>
+        <v>6374436</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8898,88 +8912,74 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128738882</v>
+        <v>128738894</v>
       </c>
       <c r="B83" t="n">
-        <v>87054</v>
+        <v>86927</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3563</v>
+        <v>6003295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stor granspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius bovinus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Fr. sl.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>717013</v>
+        <v>716975</v>
       </c>
       <c r="R83" t="n">
-        <v>6374226</v>
+        <v>6374071</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9011,7 +9011,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9049,32 +9049,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128738852</v>
+        <v>128738836</v>
       </c>
       <c r="B84" t="n">
-        <v>86927</v>
+        <v>86972</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9084,10 +9084,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>717045</v>
+        <v>717056</v>
       </c>
       <c r="R84" t="n">
-        <v>6374462</v>
+        <v>6374262</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9119,7 +9119,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9138,7 +9138,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9265,32 +9264,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128738836</v>
+        <v>128738852</v>
       </c>
       <c r="B86" t="n">
-        <v>86972</v>
+        <v>86927</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9300,10 +9299,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>717056</v>
+        <v>717045</v>
       </c>
       <c r="R86" t="n">
-        <v>6374262</v>
+        <v>6374462</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9335,7 +9334,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9345,7 +9344,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9354,6 +9353,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9372,32 +9372,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128740508</v>
+        <v>128742287</v>
       </c>
       <c r="B87" t="n">
-        <v>86949</v>
+        <v>86927</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9407,10 +9407,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>717063</v>
+        <v>717013</v>
       </c>
       <c r="R87" t="n">
-        <v>6374397</v>
+        <v>6374166</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9451,25 +9451,26 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128742287</v>
+        <v>128742270</v>
       </c>
       <c r="B88" t="n">
         <v>86927</v>
@@ -9504,10 +9505,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>717013</v>
+        <v>717071</v>
       </c>
       <c r="R88" t="n">
-        <v>6374166</v>
+        <v>6374305</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9567,7 +9568,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128742270</v>
+        <v>128742290</v>
       </c>
       <c r="B89" t="n">
         <v>86927</v>
@@ -9602,10 +9603,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>717071</v>
+        <v>716979</v>
       </c>
       <c r="R89" t="n">
-        <v>6374305</v>
+        <v>6374069</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9665,10 +9666,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128742251</v>
+        <v>128740508</v>
       </c>
       <c r="B90" t="n">
-        <v>86972</v>
+        <v>86949</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9676,21 +9677,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9700,10 +9701,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>717106</v>
+        <v>717063</v>
       </c>
       <c r="R90" t="n">
-        <v>6374415</v>
+        <v>6374397</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9750,44 +9751,44 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128742290</v>
+        <v>128742251</v>
       </c>
       <c r="B91" t="n">
-        <v>86927</v>
+        <v>86972</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9797,10 +9798,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>716979</v>
+        <v>717106</v>
       </c>
       <c r="R91" t="n">
-        <v>6374069</v>
+        <v>6374415</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9841,7 +9842,6 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -10172,32 +10172,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128740516</v>
+        <v>128738847</v>
       </c>
       <c r="B95" t="n">
-        <v>92098</v>
+        <v>86843</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6031</v>
+        <v>248956</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10207,10 +10207,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>717218</v>
+        <v>716980</v>
       </c>
       <c r="R95" t="n">
-        <v>6374124</v>
+        <v>6374264</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10240,9 +10240,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10257,44 +10267,44 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128738847</v>
+        <v>128740516</v>
       </c>
       <c r="B96" t="n">
-        <v>86843</v>
+        <v>92098</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>248956</v>
+        <v>6031</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10304,10 +10314,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>716980</v>
+        <v>717218</v>
       </c>
       <c r="R96" t="n">
-        <v>6374264</v>
+        <v>6374124</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10337,19 +10347,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>12:22</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10364,12 +10364,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -10678,10 +10678,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128740510</v>
+        <v>128740503</v>
       </c>
       <c r="B100" t="n">
-        <v>86893</v>
+        <v>86927</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10689,21 +10689,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6037417</v>
+        <v>6003295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10713,10 +10713,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>717105</v>
+        <v>717212</v>
       </c>
       <c r="R100" t="n">
-        <v>6374479</v>
+        <v>6374189</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10757,6 +10757,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10775,10 +10776,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128740503</v>
+        <v>128740510</v>
       </c>
       <c r="B101" t="n">
-        <v>86927</v>
+        <v>86893</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10786,21 +10787,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6003295</v>
+        <v>6037417</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10810,10 +10811,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>717212</v>
+        <v>717105</v>
       </c>
       <c r="R101" t="n">
-        <v>6374189</v>
+        <v>6374479</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10854,7 +10855,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42607-2025 artfynd.xlsx
+++ b/artfynd/A 42607-2025 artfynd.xlsx
@@ -2203,32 +2203,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128738898</v>
+        <v>128738885</v>
       </c>
       <c r="B17" t="n">
-        <v>86890</v>
+        <v>86775</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3674</v>
+        <v>424</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>716960</v>
+        <v>717029</v>
       </c>
       <c r="R17" t="n">
-        <v>6374150</v>
+        <v>6374326</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2310,32 +2310,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128738832</v>
+        <v>128742286</v>
       </c>
       <c r="B18" t="n">
-        <v>86972</v>
+        <v>86927</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>717000</v>
+        <v>716970</v>
       </c>
       <c r="R18" t="n">
-        <v>6374409</v>
+        <v>6374097</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2378,71 +2378,62 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128738885</v>
+        <v>128740498</v>
       </c>
       <c r="B19" t="n">
-        <v>86775</v>
+        <v>86927</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2452,10 +2443,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>717029</v>
+        <v>717099</v>
       </c>
       <c r="R19" t="n">
-        <v>6374326</v>
+        <v>6374395</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2485,71 +2476,62 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128738859</v>
+        <v>128738857</v>
       </c>
       <c r="B20" t="n">
-        <v>98625</v>
+        <v>86927</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219874</v>
+        <v>6003295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2559,10 +2541,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>716963</v>
+        <v>717049</v>
       </c>
       <c r="R20" t="n">
-        <v>6374082</v>
+        <v>6374317</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2594,7 +2576,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2604,7 +2586,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2613,6 +2595,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2631,7 +2614,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128742286</v>
+        <v>128738856</v>
       </c>
       <c r="B21" t="n">
         <v>86927</v>
@@ -2666,10 +2649,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>716970</v>
+        <v>716986</v>
       </c>
       <c r="R21" t="n">
-        <v>6374097</v>
+        <v>6374339</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2699,9 +2682,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2717,44 +2710,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128740498</v>
+        <v>128738898</v>
       </c>
       <c r="B22" t="n">
-        <v>86927</v>
+        <v>86890</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2764,10 +2757,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>717099</v>
+        <v>716960</v>
       </c>
       <c r="R22" t="n">
-        <v>6374395</v>
+        <v>6374150</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2797,62 +2790,71 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128738857</v>
+        <v>128738832</v>
       </c>
       <c r="B23" t="n">
-        <v>86927</v>
+        <v>86972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,10 +2864,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>717049</v>
+        <v>717000</v>
       </c>
       <c r="R23" t="n">
-        <v>6374317</v>
+        <v>6374409</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2897,7 +2899,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2907,7 +2909,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2916,7 +2918,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2935,32 +2936,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128738856</v>
+        <v>128738859</v>
       </c>
       <c r="B24" t="n">
-        <v>86927</v>
+        <v>98625</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6003295</v>
+        <v>219874</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2970,10 +2971,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>716986</v>
+        <v>716963</v>
       </c>
       <c r="R24" t="n">
-        <v>6374339</v>
+        <v>6374082</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3005,7 +3006,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3015,7 +3016,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3024,7 +3025,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3431,32 +3431,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128740489</v>
+        <v>128742283</v>
       </c>
       <c r="B29" t="n">
-        <v>90975</v>
+        <v>86927</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5741</v>
+        <v>6003295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>717220</v>
+        <v>717040</v>
       </c>
       <c r="R29" t="n">
-        <v>6374302</v>
+        <v>6374195</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3510,50 +3510,51 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128738846</v>
+        <v>128742281</v>
       </c>
       <c r="B30" t="n">
-        <v>90975</v>
+        <v>86927</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5741</v>
+        <v>6003295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3563,10 +3564,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>717037</v>
+        <v>717039</v>
       </c>
       <c r="R30" t="n">
-        <v>6374226</v>
+        <v>6374227</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3596,39 +3597,30 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3742,32 +3734,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128742283</v>
+        <v>128740489</v>
       </c>
       <c r="B32" t="n">
-        <v>86927</v>
+        <v>90975</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6003295</v>
+        <v>5741</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3777,10 +3769,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>717040</v>
+        <v>717220</v>
       </c>
       <c r="R32" t="n">
-        <v>6374195</v>
+        <v>6374302</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3821,51 +3813,50 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128742281</v>
+        <v>128738846</v>
       </c>
       <c r="B33" t="n">
-        <v>86927</v>
+        <v>90975</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6003295</v>
+        <v>5741</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3875,10 +3866,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>717039</v>
+        <v>717037</v>
       </c>
       <c r="R33" t="n">
-        <v>6374227</v>
+        <v>6374226</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3908,62 +3899,71 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128742293</v>
+        <v>128740500</v>
       </c>
       <c r="B34" t="n">
-        <v>86890</v>
+        <v>86927</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3973,10 +3973,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>717094</v>
+        <v>717281</v>
       </c>
       <c r="R34" t="n">
-        <v>6374468</v>
+        <v>6374283</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4017,50 +4017,51 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128742254</v>
+        <v>128740499</v>
       </c>
       <c r="B35" t="n">
-        <v>86972</v>
+        <v>86927</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4070,10 +4071,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>717285</v>
+        <v>717145</v>
       </c>
       <c r="R35" t="n">
-        <v>6374272</v>
+        <v>6374308</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4114,50 +4115,51 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128742272</v>
+        <v>128740502</v>
       </c>
       <c r="B36" t="n">
-        <v>91001</v>
+        <v>86927</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4167,10 +4169,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>717018</v>
+        <v>717282</v>
       </c>
       <c r="R36" t="n">
-        <v>6374179</v>
+        <v>6374266</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4211,50 +4213,51 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128740500</v>
+        <v>128742293</v>
       </c>
       <c r="B37" t="n">
-        <v>86927</v>
+        <v>86890</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4264,10 +4267,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>717281</v>
+        <v>717094</v>
       </c>
       <c r="R37" t="n">
-        <v>6374283</v>
+        <v>6374468</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4308,51 +4311,50 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128740499</v>
+        <v>128742254</v>
       </c>
       <c r="B38" t="n">
-        <v>86927</v>
+        <v>86972</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4362,10 +4364,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>717145</v>
+        <v>717285</v>
       </c>
       <c r="R38" t="n">
-        <v>6374308</v>
+        <v>6374272</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4406,51 +4408,50 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128740502</v>
+        <v>128742272</v>
       </c>
       <c r="B39" t="n">
-        <v>86927</v>
+        <v>91001</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6003295</v>
+        <v>5747</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4460,10 +4461,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>717282</v>
+        <v>717018</v>
       </c>
       <c r="R39" t="n">
-        <v>6374266</v>
+        <v>6374179</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4504,19 +4505,18 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -6285,7 +6285,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128738896</v>
+        <v>128742289</v>
       </c>
       <c r="B57" t="n">
         <v>86927</v>
@@ -6320,10 +6320,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>717038</v>
+        <v>716965</v>
       </c>
       <c r="R57" t="n">
-        <v>6374195</v>
+        <v>6374079</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6353,19 +6353,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>10:50</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6381,19 +6371,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128742289</v>
+        <v>128742269</v>
       </c>
       <c r="B58" t="n">
         <v>86927</v>
@@ -6428,10 +6418,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>716965</v>
+        <v>717186</v>
       </c>
       <c r="R58" t="n">
-        <v>6374079</v>
+        <v>6374129</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6491,7 +6481,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128742269</v>
+        <v>128742279</v>
       </c>
       <c r="B59" t="n">
         <v>86927</v>
@@ -6526,10 +6516,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>717186</v>
+        <v>717013</v>
       </c>
       <c r="R59" t="n">
-        <v>6374129</v>
+        <v>6374176</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6589,7 +6579,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128742279</v>
+        <v>128742288</v>
       </c>
       <c r="B60" t="n">
         <v>86927</v>
@@ -6624,10 +6614,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>717013</v>
+        <v>716995</v>
       </c>
       <c r="R60" t="n">
-        <v>6374176</v>
+        <v>6374147</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6687,7 +6677,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128742288</v>
+        <v>128738896</v>
       </c>
       <c r="B61" t="n">
         <v>86927</v>
@@ -6722,10 +6712,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>716995</v>
+        <v>717038</v>
       </c>
       <c r="R61" t="n">
-        <v>6374147</v>
+        <v>6374195</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6755,9 +6745,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6773,44 +6773,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128742291</v>
+        <v>128738840</v>
       </c>
       <c r="B62" t="n">
-        <v>86927</v>
+        <v>86972</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6820,10 +6820,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>716977</v>
+        <v>717020</v>
       </c>
       <c r="R62" t="n">
-        <v>6374073</v>
+        <v>6374147</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6853,37 +6853,46 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128742284</v>
+        <v>128742291</v>
       </c>
       <c r="B63" t="n">
         <v>86927</v>
@@ -6918,10 +6927,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>717033</v>
+        <v>716977</v>
       </c>
       <c r="R63" t="n">
-        <v>6374186</v>
+        <v>6374073</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6981,32 +6990,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128738840</v>
+        <v>128742284</v>
       </c>
       <c r="B64" t="n">
-        <v>86972</v>
+        <v>86927</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7016,10 +7025,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>717020</v>
+        <v>717033</v>
       </c>
       <c r="R64" t="n">
-        <v>6374147</v>
+        <v>6374186</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7049,71 +7058,62 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128742282</v>
+        <v>128738841</v>
       </c>
       <c r="B65" t="n">
-        <v>86927</v>
+        <v>86972</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7123,10 +7123,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>717040</v>
+        <v>716992</v>
       </c>
       <c r="R65" t="n">
-        <v>6374212</v>
+        <v>6374116</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7156,62 +7156,71 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128738893</v>
+        <v>128738835</v>
       </c>
       <c r="B66" t="n">
-        <v>86927</v>
+        <v>86972</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7221,10 +7230,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>717000</v>
+        <v>716983</v>
       </c>
       <c r="R66" t="n">
-        <v>6374121</v>
+        <v>6374357</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7256,7 +7265,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7266,7 +7275,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7275,7 +7284,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7294,7 +7302,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128738841</v>
+        <v>128742252</v>
       </c>
       <c r="B67" t="n">
         <v>86972</v>
@@ -7329,10 +7337,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>716992</v>
+        <v>717146</v>
       </c>
       <c r="R67" t="n">
-        <v>6374116</v>
+        <v>6374313</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7362,19 +7370,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>09:50</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7389,44 +7387,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128738835</v>
+        <v>128740522</v>
       </c>
       <c r="B68" t="n">
-        <v>86972</v>
+        <v>86890</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7436,10 +7434,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>716983</v>
+        <v>717274</v>
       </c>
       <c r="R68" t="n">
-        <v>6374357</v>
+        <v>6374210</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7469,19 +7467,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>14:27</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7496,22 +7484,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128742252</v>
+        <v>128738886</v>
       </c>
       <c r="B69" t="n">
-        <v>86972</v>
+        <v>86775</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7519,21 +7507,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3767</v>
+        <v>424</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7543,10 +7531,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>717146</v>
+        <v>716990</v>
       </c>
       <c r="R69" t="n">
-        <v>6374313</v>
+        <v>6374260</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7576,9 +7564,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7593,22 +7591,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128740522</v>
+        <v>128742263</v>
       </c>
       <c r="B70" t="n">
-        <v>86890</v>
+        <v>90975</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7616,21 +7614,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3674</v>
+        <v>5741</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7640,10 +7638,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>717274</v>
+        <v>717281</v>
       </c>
       <c r="R70" t="n">
-        <v>6374210</v>
+        <v>6374199</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7690,44 +7688,44 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128742263</v>
+        <v>128742282</v>
       </c>
       <c r="B71" t="n">
-        <v>90975</v>
+        <v>86927</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5741</v>
+        <v>6003295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7737,10 +7735,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>717281</v>
+        <v>717040</v>
       </c>
       <c r="R71" t="n">
-        <v>6374199</v>
+        <v>6374212</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7781,6 +7779,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7799,32 +7798,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128738886</v>
+        <v>128738893</v>
       </c>
       <c r="B72" t="n">
-        <v>86775</v>
+        <v>86927</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7834,10 +7833,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>716990</v>
+        <v>717000</v>
       </c>
       <c r="R72" t="n">
-        <v>6374260</v>
+        <v>6374121</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7869,7 +7868,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -7879,7 +7878,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7888,6 +7887,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7906,32 +7906,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128740491</v>
+        <v>128742276</v>
       </c>
       <c r="B73" t="n">
-        <v>86729</v>
+        <v>86949</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3762</v>
+        <v>449</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>717281</v>
+        <v>717269</v>
       </c>
       <c r="R73" t="n">
-        <v>6374215</v>
+        <v>6374317</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7991,22 +7991,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128742255</v>
+        <v>128738884</v>
       </c>
       <c r="B74" t="n">
-        <v>86972</v>
+        <v>86775</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8014,21 +8014,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3767</v>
+        <v>424</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8038,10 +8038,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>717059</v>
+        <v>716969</v>
       </c>
       <c r="R74" t="n">
-        <v>6374329</v>
+        <v>6374310</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8071,9 +8071,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8088,19 +8098,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128742276</v>
+        <v>128738867</v>
       </c>
       <c r="B75" t="n">
         <v>86949</v>
@@ -8135,10 +8145,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>717269</v>
+        <v>717115</v>
       </c>
       <c r="R75" t="n">
-        <v>6374317</v>
+        <v>6374297</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8168,9 +8178,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8185,44 +8205,44 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128738884</v>
+        <v>128740491</v>
       </c>
       <c r="B76" t="n">
-        <v>86775</v>
+        <v>86729</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>424</v>
+        <v>3762</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8232,10 +8252,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>716969</v>
+        <v>717281</v>
       </c>
       <c r="R76" t="n">
-        <v>6374310</v>
+        <v>6374215</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8265,19 +8285,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>14:32</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8292,22 +8302,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128738867</v>
+        <v>128742255</v>
       </c>
       <c r="B77" t="n">
-        <v>86949</v>
+        <v>86972</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8315,21 +8325,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8339,10 +8349,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>717115</v>
+        <v>717059</v>
       </c>
       <c r="R77" t="n">
-        <v>6374297</v>
+        <v>6374329</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8372,19 +8382,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>13:35</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8399,12 +8399,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>

--- a/artfynd/A 42607-2025 artfynd.xlsx
+++ b/artfynd/A 42607-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128738845</v>
       </c>
       <c r="B2" t="n">
-        <v>86729</v>
+        <v>86756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128738831</v>
       </c>
       <c r="B3" t="n">
-        <v>86972</v>
+        <v>86999</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128742256</v>
       </c>
       <c r="B4" t="n">
-        <v>86972</v>
+        <v>86999</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128740514</v>
       </c>
       <c r="B5" t="n">
-        <v>86753</v>
+        <v>86780</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,39 +1076,39 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128738854</v>
+        <v>128740505</v>
       </c>
       <c r="B6" t="n">
-        <v>86927</v>
+        <v>98641</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6003295</v>
+        <v>219862</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>716967</v>
+        <v>717182</v>
       </c>
       <c r="R6" t="n">
-        <v>6374338</v>
+        <v>6374336</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1151,50 +1151,39 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128740487</v>
+        <v>128738854</v>
       </c>
       <c r="B7" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717292</v>
+        <v>716967</v>
       </c>
       <c r="R7" t="n">
-        <v>6374265</v>
+        <v>6374338</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1259,9 +1248,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,44 +1276,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128740505</v>
+        <v>128740487</v>
       </c>
       <c r="B8" t="n">
-        <v>98614</v>
+        <v>86954</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219862</v>
+        <v>6003295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1323,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717182</v>
+        <v>717292</v>
       </c>
       <c r="R8" t="n">
-        <v>6374336</v>
+        <v>6374265</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,6 +1367,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1379,39 +1379,39 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128738853</v>
+        <v>128738834</v>
       </c>
       <c r="B9" t="n">
-        <v>86927</v>
+        <v>86999</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717033</v>
+        <v>716985</v>
       </c>
       <c r="R9" t="n">
-        <v>6374425</v>
+        <v>6374341</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1475,7 +1475,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1494,32 +1493,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128738834</v>
+        <v>128742266</v>
       </c>
       <c r="B10" t="n">
-        <v>86972</v>
+        <v>86756</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1529,10 +1528,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716985</v>
+        <v>717201</v>
       </c>
       <c r="R10" t="n">
-        <v>6374341</v>
+        <v>6374151</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1562,19 +1561,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1589,44 +1578,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128742266</v>
+        <v>128738837</v>
       </c>
       <c r="B11" t="n">
-        <v>86729</v>
+        <v>86999</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1636,10 +1625,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>717201</v>
+        <v>717037</v>
       </c>
       <c r="R11" t="n">
-        <v>6374151</v>
+        <v>6374236</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,9 +1658,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1686,44 +1685,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128738837</v>
+        <v>128738853</v>
       </c>
       <c r="B12" t="n">
-        <v>86972</v>
+        <v>86954</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1733,10 +1732,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>717037</v>
+        <v>717033</v>
       </c>
       <c r="R12" t="n">
-        <v>6374236</v>
+        <v>6374425</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1768,7 +1767,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1778,7 +1777,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1787,6 +1786,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1808,7 +1808,7 @@
         <v>128740482</v>
       </c>
       <c r="B13" t="n">
-        <v>86972</v>
+        <v>86999</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1905,7 +1905,7 @@
         <v>128740504</v>
       </c>
       <c r="B14" t="n">
-        <v>98614</v>
+        <v>98641</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2002,7 +2002,7 @@
         <v>128742285</v>
       </c>
       <c r="B15" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>128742275</v>
       </c>
       <c r="B16" t="n">
-        <v>86878</v>
+        <v>86905</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,32 +2203,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128738898</v>
+        <v>128742286</v>
       </c>
       <c r="B17" t="n">
-        <v>86890</v>
+        <v>86954</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>716960</v>
+        <v>716970</v>
       </c>
       <c r="R17" t="n">
-        <v>6374150</v>
+        <v>6374097</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2271,71 +2271,62 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128738832</v>
+        <v>128740498</v>
       </c>
       <c r="B18" t="n">
-        <v>86972</v>
+        <v>86954</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2345,10 +2336,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>717000</v>
+        <v>717099</v>
       </c>
       <c r="R18" t="n">
-        <v>6374409</v>
+        <v>6374395</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2378,71 +2369,62 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128738859</v>
+        <v>128738857</v>
       </c>
       <c r="B19" t="n">
-        <v>98626</v>
+        <v>86954</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219874</v>
+        <v>6003295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2452,10 +2434,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716963</v>
+        <v>717049</v>
       </c>
       <c r="R19" t="n">
-        <v>6374082</v>
+        <v>6374317</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2487,7 +2469,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2497,7 +2479,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2506,6 +2488,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2524,10 +2507,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128742286</v>
+        <v>128738856</v>
       </c>
       <c r="B20" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2559,10 +2542,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>716970</v>
+        <v>716986</v>
       </c>
       <c r="R20" t="n">
-        <v>6374097</v>
+        <v>6374339</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2592,9 +2575,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2610,44 +2603,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128740498</v>
+        <v>128738898</v>
       </c>
       <c r="B21" t="n">
-        <v>86927</v>
+        <v>86917</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2657,10 +2650,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>717099</v>
+        <v>716960</v>
       </c>
       <c r="R21" t="n">
-        <v>6374395</v>
+        <v>6374150</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2690,62 +2683,71 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128738856</v>
+        <v>128738832</v>
       </c>
       <c r="B22" t="n">
-        <v>86927</v>
+        <v>86999</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2757,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>716986</v>
+        <v>717000</v>
       </c>
       <c r="R22" t="n">
-        <v>6374339</v>
+        <v>6374409</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2790,7 +2792,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2800,7 +2802,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2809,7 +2811,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2828,32 +2829,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128738857</v>
+        <v>128738859</v>
       </c>
       <c r="B23" t="n">
-        <v>86927</v>
+        <v>98653</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6003295</v>
+        <v>219874</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2863,10 +2864,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>717049</v>
+        <v>716963</v>
       </c>
       <c r="R23" t="n">
-        <v>6374317</v>
+        <v>6374082</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2898,7 +2899,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2908,7 +2909,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2917,7 +2918,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2939,7 +2939,7 @@
         <v>128742257</v>
       </c>
       <c r="B24" t="n">
-        <v>86972</v>
+        <v>86999</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>128740485</v>
       </c>
       <c r="B25" t="n">
-        <v>86972</v>
+        <v>86999</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3133,7 +3133,7 @@
         <v>128742258</v>
       </c>
       <c r="B26" t="n">
-        <v>86972</v>
+        <v>86999</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3227,32 +3227,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128742273</v>
+        <v>128742283</v>
       </c>
       <c r="B27" t="n">
-        <v>86903</v>
+        <v>86954</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1988</v>
+        <v>6003295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>717014</v>
+        <v>717040</v>
       </c>
       <c r="R27" t="n">
-        <v>6374164</v>
+        <v>6374195</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3306,6 +3306,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3324,32 +3325,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128740489</v>
+        <v>128742281</v>
       </c>
       <c r="B28" t="n">
-        <v>90976</v>
+        <v>86954</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5741</v>
+        <v>6003295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3359,10 +3360,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>717220</v>
+        <v>717039</v>
       </c>
       <c r="R28" t="n">
-        <v>6374302</v>
+        <v>6374227</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3403,50 +3404,51 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128742283</v>
+        <v>128742273</v>
       </c>
       <c r="B29" t="n">
-        <v>86927</v>
+        <v>86930</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6003295</v>
+        <v>1988</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3456,10 +3458,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>717040</v>
+        <v>717014</v>
       </c>
       <c r="R29" t="n">
-        <v>6374195</v>
+        <v>6374164</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3500,7 +3502,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3519,32 +3520,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128742281</v>
+        <v>128740489</v>
       </c>
       <c r="B30" t="n">
-        <v>86927</v>
+        <v>91003</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6003295</v>
+        <v>5741</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3554,10 +3555,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>717039</v>
+        <v>717220</v>
       </c>
       <c r="R30" t="n">
-        <v>6374227</v>
+        <v>6374302</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3598,19 +3599,18 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3620,7 +3620,7 @@
         <v>128742272</v>
       </c>
       <c r="B31" t="n">
-        <v>91002</v>
+        <v>91029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>128742293</v>
       </c>
       <c r="B32" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>128742254</v>
       </c>
       <c r="B33" t="n">
-        <v>86972</v>
+        <v>86999</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>128740500</v>
       </c>
       <c r="B34" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3999,17 +3999,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128740502</v>
+        <v>128740499</v>
       </c>
       <c r="B35" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4041,10 +4041,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>717282</v>
+        <v>717145</v>
       </c>
       <c r="R35" t="n">
-        <v>6374266</v>
+        <v>6374308</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4097,17 +4097,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128740499</v>
+        <v>128740502</v>
       </c>
       <c r="B36" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4139,10 +4139,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>717145</v>
+        <v>717282</v>
       </c>
       <c r="R36" t="n">
-        <v>6374308</v>
+        <v>6374266</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4205,7 +4205,7 @@
         <v>128740521</v>
       </c>
       <c r="B37" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>128738900</v>
       </c>
       <c r="B38" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4406,10 +4406,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128738858</v>
+        <v>128742267</v>
       </c>
       <c r="B39" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>717003</v>
+        <v>717105</v>
       </c>
       <c r="R39" t="n">
-        <v>6374177</v>
+        <v>6374393</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4474,19 +4474,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:02</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4502,22 +4492,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128742267</v>
+        <v>128738858</v>
       </c>
       <c r="B40" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4549,10 +4539,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>717105</v>
+        <v>717003</v>
       </c>
       <c r="R40" t="n">
-        <v>6374393</v>
+        <v>6374177</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4582,9 +4572,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4600,22 +4600,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128742259</v>
+        <v>128740509</v>
       </c>
       <c r="B41" t="n">
-        <v>86972</v>
+        <v>86976</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4623,21 +4623,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4647,10 +4647,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>716980</v>
+        <v>717258</v>
       </c>
       <c r="R41" t="n">
-        <v>6374067</v>
+        <v>6374286</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4697,22 +4697,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128740509</v>
+        <v>128738887</v>
       </c>
       <c r="B42" t="n">
-        <v>86949</v>
+        <v>86802</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4720,21 +4720,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>449</v>
+        <v>424</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4744,10 +4744,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>717258</v>
+        <v>716984</v>
       </c>
       <c r="R42" t="n">
-        <v>6374286</v>
+        <v>6374264</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4777,9 +4777,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4794,22 +4804,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128738887</v>
+        <v>128742259</v>
       </c>
       <c r="B43" t="n">
-        <v>86775</v>
+        <v>86999</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4817,21 +4827,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>424</v>
+        <v>3767</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4841,10 +4851,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>716984</v>
+        <v>716980</v>
       </c>
       <c r="R43" t="n">
-        <v>6374264</v>
+        <v>6374067</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4874,19 +4884,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>12:19</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4901,22 +4901,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128742268</v>
+        <v>128738895</v>
       </c>
       <c r="B44" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4948,10 +4948,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>717267</v>
+        <v>716974</v>
       </c>
       <c r="R44" t="n">
-        <v>6374322</v>
+        <v>6374284</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4981,9 +4981,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4999,22 +5009,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128738895</v>
+        <v>128742268</v>
       </c>
       <c r="B45" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5046,10 +5056,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>716974</v>
+        <v>717267</v>
       </c>
       <c r="R45" t="n">
-        <v>6374284</v>
+        <v>6374322</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5079,19 +5089,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5107,12 +5107,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5122,7 +5122,7 @@
         <v>128742280</v>
       </c>
       <c r="B46" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         <v>128738880</v>
       </c>
       <c r="B47" t="n">
-        <v>86753</v>
+        <v>86780</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>128738838</v>
       </c>
       <c r="B48" t="n">
-        <v>86972</v>
+        <v>86999</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>128742289</v>
       </c>
       <c r="B49" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5529,10 +5529,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128742279</v>
+        <v>128742269</v>
       </c>
       <c r="B50" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5564,10 +5564,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>717013</v>
+        <v>717186</v>
       </c>
       <c r="R50" t="n">
-        <v>6374176</v>
+        <v>6374129</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5627,10 +5627,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128742269</v>
+        <v>128742279</v>
       </c>
       <c r="B51" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>717186</v>
+        <v>717013</v>
       </c>
       <c r="R51" t="n">
-        <v>6374129</v>
+        <v>6374176</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5728,7 +5728,7 @@
         <v>128742288</v>
       </c>
       <c r="B52" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>128738896</v>
       </c>
       <c r="B53" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5931,10 +5931,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128742284</v>
+        <v>128742291</v>
       </c>
       <c r="B54" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5966,10 +5966,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>717033</v>
+        <v>716977</v>
       </c>
       <c r="R54" t="n">
-        <v>6374186</v>
+        <v>6374073</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6029,10 +6029,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128742291</v>
+        <v>128742284</v>
       </c>
       <c r="B55" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6064,10 +6064,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>716977</v>
+        <v>717033</v>
       </c>
       <c r="R55" t="n">
-        <v>6374073</v>
+        <v>6374186</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6130,7 +6130,7 @@
         <v>128742282</v>
       </c>
       <c r="B56" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6225,32 +6225,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128738841</v>
+        <v>128742263</v>
       </c>
       <c r="B57" t="n">
-        <v>86972</v>
+        <v>91003</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3767</v>
+        <v>5741</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6260,10 +6260,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>716992</v>
+        <v>717281</v>
       </c>
       <c r="R57" t="n">
-        <v>6374116</v>
+        <v>6374199</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6293,19 +6293,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>09:50</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6320,22 +6310,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128738835</v>
+        <v>128738841</v>
       </c>
       <c r="B58" t="n">
-        <v>86972</v>
+        <v>86999</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6367,10 +6357,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>716983</v>
+        <v>716992</v>
       </c>
       <c r="R58" t="n">
-        <v>6374357</v>
+        <v>6374116</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6402,7 +6392,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6412,7 +6402,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6439,10 +6429,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128742252</v>
+        <v>128738835</v>
       </c>
       <c r="B59" t="n">
-        <v>86972</v>
+        <v>86999</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6474,10 +6464,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>717146</v>
+        <v>716983</v>
       </c>
       <c r="R59" t="n">
-        <v>6374313</v>
+        <v>6374357</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6507,9 +6497,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6524,44 +6524,44 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128740522</v>
+        <v>128742252</v>
       </c>
       <c r="B60" t="n">
-        <v>86890</v>
+        <v>86999</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6571,10 +6571,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>717274</v>
+        <v>717146</v>
       </c>
       <c r="R60" t="n">
-        <v>6374210</v>
+        <v>6374313</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6621,22 +6621,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128742263</v>
+        <v>128740522</v>
       </c>
       <c r="B61" t="n">
-        <v>90976</v>
+        <v>86917</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6644,21 +6644,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5741</v>
+        <v>3674</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6668,10 +6668,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>717281</v>
+        <v>717274</v>
       </c>
       <c r="R61" t="n">
-        <v>6374199</v>
+        <v>6374210</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6718,12 +6718,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6733,7 +6733,7 @@
         <v>128742276</v>
       </c>
       <c r="B62" t="n">
-        <v>86949</v>
+        <v>86976</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>128738884</v>
       </c>
       <c r="B63" t="n">
-        <v>86775</v>
+        <v>86802</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>128740491</v>
       </c>
       <c r="B64" t="n">
-        <v>86729</v>
+        <v>86756</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7034,7 +7034,7 @@
         <v>128742255</v>
       </c>
       <c r="B65" t="n">
-        <v>86972</v>
+        <v>86999</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>128738848</v>
       </c>
       <c r="B66" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         <v>128738851</v>
       </c>
       <c r="B67" t="n">
-        <v>86729</v>
+        <v>86756</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>128740512</v>
       </c>
       <c r="B68" t="n">
-        <v>86753</v>
+        <v>86780</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7432,39 +7432,39 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128738855</v>
+        <v>128738836</v>
       </c>
       <c r="B69" t="n">
-        <v>86927</v>
+        <v>86999</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7474,10 +7474,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>716966</v>
+        <v>717056</v>
       </c>
       <c r="R69" t="n">
-        <v>6374312</v>
+        <v>6374262</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7509,7 +7509,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7528,7 +7528,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7547,10 +7546,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128738852</v>
+        <v>128738855</v>
       </c>
       <c r="B70" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7582,10 +7581,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>717045</v>
+        <v>716966</v>
       </c>
       <c r="R70" t="n">
-        <v>6374462</v>
+        <v>6374312</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7617,7 +7616,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7627,7 +7626,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7655,32 +7654,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128738836</v>
+        <v>128738852</v>
       </c>
       <c r="B71" t="n">
-        <v>86972</v>
+        <v>86954</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7690,10 +7689,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>717056</v>
+        <v>717045</v>
       </c>
       <c r="R71" t="n">
-        <v>6374262</v>
+        <v>6374462</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7725,7 +7724,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7735,7 +7734,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7744,6 +7743,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7765,7 +7765,7 @@
         <v>128740508</v>
       </c>
       <c r="B72" t="n">
-        <v>86949</v>
+        <v>86976</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -7862,7 +7862,7 @@
         <v>128742251</v>
       </c>
       <c r="B73" t="n">
-        <v>86972</v>
+        <v>86999</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>128738833</v>
       </c>
       <c r="B74" t="n">
-        <v>86972</v>
+        <v>86999</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         <v>128740519</v>
       </c>
       <c r="B75" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>128742287</v>
       </c>
       <c r="B76" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8258,10 +8258,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128742290</v>
+        <v>128742270</v>
       </c>
       <c r="B77" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8293,10 +8293,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>716979</v>
+        <v>717071</v>
       </c>
       <c r="R77" t="n">
-        <v>6374069</v>
+        <v>6374305</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8356,10 +8356,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128742270</v>
+        <v>128742290</v>
       </c>
       <c r="B78" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8391,10 +8391,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>717071</v>
+        <v>716979</v>
       </c>
       <c r="R78" t="n">
-        <v>6374305</v>
+        <v>6374069</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8457,7 +8457,7 @@
         <v>128740516</v>
       </c>
       <c r="B79" t="n">
-        <v>92099</v>
+        <v>92126</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>128738891</v>
       </c>
       <c r="B80" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>128738890</v>
       </c>
       <c r="B81" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8767,32 +8767,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128740484</v>
+        <v>128740503</v>
       </c>
       <c r="B82" t="n">
-        <v>86972</v>
+        <v>86954</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8802,10 +8802,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>717279</v>
+        <v>717212</v>
       </c>
       <c r="R82" t="n">
-        <v>6374209</v>
+        <v>6374189</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8846,6 +8846,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8857,39 +8858,39 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128740518</v>
+        <v>128740510</v>
       </c>
       <c r="B83" t="n">
-        <v>86890</v>
+        <v>86920</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3674</v>
+        <v>6037417</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8899,10 +8900,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>717062</v>
+        <v>717105</v>
       </c>
       <c r="R83" t="n">
-        <v>6374393</v>
+        <v>6374479</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8954,39 +8955,39 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128740510</v>
+        <v>128740484</v>
       </c>
       <c r="B84" t="n">
-        <v>86893</v>
+        <v>86999</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6037417</v>
+        <v>3767</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8996,10 +8997,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>717105</v>
+        <v>717279</v>
       </c>
       <c r="R84" t="n">
-        <v>6374479</v>
+        <v>6374209</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9051,39 +9052,39 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128740503</v>
+        <v>128740518</v>
       </c>
       <c r="B85" t="n">
-        <v>86927</v>
+        <v>86917</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9093,10 +9094,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>717212</v>
+        <v>717062</v>
       </c>
       <c r="R85" t="n">
-        <v>6374189</v>
+        <v>6374393</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9137,7 +9138,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9159,7 +9159,7 @@
         <v>128738899</v>
       </c>
       <c r="B86" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>128806499</v>
       </c>
       <c r="B87" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9360,10 +9360,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128815957</v>
+        <v>128806483</v>
       </c>
       <c r="B88" t="n">
-        <v>86944</v>
+        <v>90969</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9371,21 +9371,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>248934</v>
+        <v>720</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knölfotad bananspindling</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cortinarius stjernegaardii</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Brandrud &amp; Frøslev</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9398,10 +9398,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>717020</v>
+        <v>717267</v>
       </c>
       <c r="R88" t="n">
-        <v>6374147</v>
+        <v>6374381</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9428,27 +9428,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>10:37</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Bilddokumentation av Ullas fynd. Uppsvullen bulb och orange basalmycel. Ek fanss på fyndplatsen som domineras av kalktallskog.</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9464,22 +9449,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128806483</v>
+        <v>128815957</v>
       </c>
       <c r="B89" t="n">
-        <v>90942</v>
+        <v>86971</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9487,21 +9472,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>720</v>
+        <v>248934</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Knölfotad bananspindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Cortinarius stjernegaardii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>Brandrud &amp; Frøslev</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9514,10 +9499,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>717267</v>
+        <v>717020</v>
       </c>
       <c r="R89" t="n">
-        <v>6374381</v>
+        <v>6374147</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9544,12 +9529,27 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Bilddokumentation av Ullas fynd. Uppsvullen bulb och orange basalmycel. Ek fanss på fyndplatsen som domineras av kalktallskog.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9565,12 +9565,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -9580,7 +9580,7 @@
         <v>128738885</v>
       </c>
       <c r="B90" t="n">
-        <v>86775</v>
+        <v>86802</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9687,7 +9687,7 @@
         <v>128805996</v>
       </c>
       <c r="B91" t="n">
-        <v>86972</v>
+        <v>86999</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>128806494</v>
       </c>
       <c r="B92" t="n">
-        <v>86949</v>
+        <v>86976</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>128806493</v>
       </c>
       <c r="B93" t="n">
-        <v>86949</v>
+        <v>86976</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>128806044</v>
       </c>
       <c r="B94" t="n">
-        <v>86949</v>
+        <v>86976</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         <v>128806038</v>
       </c>
       <c r="B95" t="n">
-        <v>98614</v>
+        <v>98641</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10169,10 +10169,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128815850</v>
+        <v>128738846</v>
       </c>
       <c r="B96" t="n">
-        <v>89445</v>
+        <v>91003</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10180,21 +10180,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>236437</v>
+        <v>5741</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Brun klibbskivling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Limacella glioderma</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Maire</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10204,10 +10204,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>716975</v>
+        <v>717037</v>
       </c>
       <c r="R96" t="n">
-        <v>6374071</v>
+        <v>6374226</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10239,7 +10239,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10249,7 +10249,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10279,7 +10279,7 @@
         <v>128738839</v>
       </c>
       <c r="B97" t="n">
-        <v>86972</v>
+        <v>86999</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10383,10 +10383,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128738846</v>
+        <v>128815850</v>
       </c>
       <c r="B98" t="n">
-        <v>90976</v>
+        <v>89472</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10394,21 +10394,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5741</v>
+        <v>236437</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Brun klibbskivling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Limacella glioderma</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Fr.) Maire</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10418,10 +10418,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>717037</v>
+        <v>716975</v>
       </c>
       <c r="R98" t="n">
-        <v>6374226</v>
+        <v>6374071</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10453,7 +10453,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10463,7 +10463,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10493,7 +10493,7 @@
         <v>128806004</v>
       </c>
       <c r="B99" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>128806484</v>
       </c>
       <c r="B100" t="n">
-        <v>90942</v>
+        <v>90969</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10688,32 +10688,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128738897</v>
+        <v>128806005</v>
       </c>
       <c r="B101" t="n">
-        <v>86927</v>
+        <v>91003</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6003295</v>
+        <v>5741</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10723,10 +10723,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>717015</v>
+        <v>717142</v>
       </c>
       <c r="R101" t="n">
-        <v>6374144</v>
+        <v>6374197</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10753,22 +10753,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>10:05</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>10:05</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10777,51 +10767,50 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128806005</v>
+        <v>128738866</v>
       </c>
       <c r="B102" t="n">
-        <v>90976</v>
+        <v>90235</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5741</v>
+        <v>970</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10831,10 +10820,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>717142</v>
+        <v>717039</v>
       </c>
       <c r="R102" t="n">
-        <v>6374197</v>
+        <v>6374321</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10861,12 +10850,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10875,28 +10874,29 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128806009</v>
+        <v>128738897</v>
       </c>
       <c r="B103" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10928,10 +10928,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>717132</v>
+        <v>717015</v>
       </c>
       <c r="R103" t="n">
-        <v>6374140</v>
+        <v>6374144</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10958,12 +10958,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10979,22 +10989,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128738866</v>
+        <v>128806009</v>
       </c>
       <c r="B104" t="n">
-        <v>90208</v>
+        <v>86954</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11002,21 +11012,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>970</v>
+        <v>6003295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11026,10 +11036,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>717039</v>
+        <v>717132</v>
       </c>
       <c r="R104" t="n">
-        <v>6374321</v>
+        <v>6374140</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11056,22 +11066,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>13:50</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>13:50</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11087,22 +11087,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128805993</v>
+        <v>128738875</v>
       </c>
       <c r="B105" t="n">
-        <v>86972</v>
+        <v>87011</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11110,23 +11110,19 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>3767</v>
+        <v>433</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Brandrud</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
@@ -11134,10 +11130,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>717148</v>
+        <v>716968</v>
       </c>
       <c r="R105" t="n">
-        <v>6374174</v>
+        <v>6374251</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11164,12 +11160,22 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11184,22 +11190,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128738875</v>
+        <v>128738842</v>
       </c>
       <c r="B106" t="n">
-        <v>86984</v>
+        <v>86999</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11207,19 +11213,23 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>433</v>
+        <v>3767</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr"/>
+          <t>Cortinarius violaceomaculatus</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -11227,10 +11237,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>716968</v>
+        <v>716981</v>
       </c>
       <c r="R106" t="n">
-        <v>6374251</v>
+        <v>6374088</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11262,7 +11272,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11272,7 +11282,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11299,10 +11309,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128738842</v>
+        <v>128805993</v>
       </c>
       <c r="B107" t="n">
-        <v>86972</v>
+        <v>86999</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11334,10 +11344,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>716981</v>
+        <v>717148</v>
       </c>
       <c r="R107" t="n">
-        <v>6374088</v>
+        <v>6374174</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11364,22 +11374,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>09:31</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>09:31</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11394,44 +11394,44 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128738843</v>
+        <v>128806056</v>
       </c>
       <c r="B108" t="n">
-        <v>86972</v>
+        <v>106944</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>3767</v>
+        <v>221849</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11441,10 +11441,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>716967</v>
+        <v>717370</v>
       </c>
       <c r="R108" t="n">
-        <v>6374084</v>
+        <v>6374168</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11471,22 +11471,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>09:26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>09:26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11501,44 +11491,44 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128806010</v>
+        <v>128738843</v>
       </c>
       <c r="B109" t="n">
-        <v>86927</v>
+        <v>86999</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11548,10 +11538,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>717186</v>
+        <v>716967</v>
       </c>
       <c r="R109" t="n">
-        <v>6374253</v>
+        <v>6374084</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11578,12 +11568,22 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11592,29 +11592,28 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128806023</v>
+        <v>128806010</v>
       </c>
       <c r="B110" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11646,10 +11645,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>717360</v>
+        <v>717186</v>
       </c>
       <c r="R110" t="n">
-        <v>6374214</v>
+        <v>6374253</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11709,10 +11708,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128806056</v>
+        <v>128806023</v>
       </c>
       <c r="B111" t="n">
-        <v>106916</v>
+        <v>86954</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11720,21 +11719,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>221849</v>
+        <v>6003295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11744,10 +11743,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>717370</v>
+        <v>717360</v>
       </c>
       <c r="R111" t="n">
-        <v>6374168</v>
+        <v>6374214</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11788,6 +11787,7 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -11799,7 +11799,7 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -11809,7 +11809,7 @@
         <v>128738840</v>
       </c>
       <c r="B112" t="n">
-        <v>86972</v>
+        <v>86999</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>128806497</v>
       </c>
       <c r="B113" t="n">
-        <v>86753</v>
+        <v>86780</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         <v>128806022</v>
       </c>
       <c r="B114" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12108,32 +12108,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128806050</v>
+        <v>128738886</v>
       </c>
       <c r="B115" t="n">
-        <v>86893</v>
+        <v>86802</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6037417</v>
+        <v>424</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12143,10 +12143,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>717311</v>
+        <v>716990</v>
       </c>
       <c r="R115" t="n">
-        <v>6374287</v>
+        <v>6374260</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12173,12 +12173,22 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12187,19 +12197,18 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
@@ -12209,7 +12218,7 @@
         <v>128806495</v>
       </c>
       <c r="B116" t="n">
-        <v>86815</v>
+        <v>86842</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12306,7 +12315,7 @@
         <v>128806049</v>
       </c>
       <c r="B117" t="n">
-        <v>86984</v>
+        <v>87011</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12396,32 +12405,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128806064</v>
+        <v>128806050</v>
       </c>
       <c r="B118" t="n">
-        <v>86890</v>
+        <v>86920</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3674</v>
+        <v>6037417</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12431,10 +12440,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>717299</v>
+        <v>717311</v>
       </c>
       <c r="R118" t="n">
-        <v>6374300</v>
+        <v>6374287</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12475,6 +12484,7 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -12493,32 +12503,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128806043</v>
+        <v>128738893</v>
       </c>
       <c r="B119" t="n">
-        <v>75115</v>
+        <v>86954</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6426</v>
+        <v>6003295</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12528,10 +12538,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>717359</v>
+        <v>717000</v>
       </c>
       <c r="R119" t="n">
-        <v>6374214</v>
+        <v>6374121</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12558,12 +12568,22 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12572,50 +12592,51 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128738886</v>
+        <v>128806064</v>
       </c>
       <c r="B120" t="n">
-        <v>86775</v>
+        <v>86917</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>424</v>
+        <v>3674</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12625,10 +12646,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>716990</v>
+        <v>717299</v>
       </c>
       <c r="R120" t="n">
-        <v>6374260</v>
+        <v>6374300</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12655,22 +12676,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12685,44 +12696,44 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128738893</v>
+        <v>128806043</v>
       </c>
       <c r="B121" t="n">
-        <v>86927</v>
+        <v>75142</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6003295</v>
+        <v>6426</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12732,10 +12743,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>717000</v>
+        <v>717359</v>
       </c>
       <c r="R121" t="n">
-        <v>6374121</v>
+        <v>6374214</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12762,22 +12773,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>10:04</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>10:04</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12786,51 +12787,50 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128738892</v>
+        <v>128738867</v>
       </c>
       <c r="B122" t="n">
-        <v>86927</v>
+        <v>86976</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12840,10 +12840,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>717037</v>
+        <v>717115</v>
       </c>
       <c r="R122" t="n">
-        <v>6374150</v>
+        <v>6374297</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12875,7 +12875,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -12885,7 +12885,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12894,7 +12894,6 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -12913,32 +12912,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128738867</v>
+        <v>128738892</v>
       </c>
       <c r="B123" t="n">
-        <v>86949</v>
+        <v>86954</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12948,10 +12947,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>717115</v>
+        <v>717037</v>
       </c>
       <c r="R123" t="n">
-        <v>6374297</v>
+        <v>6374150</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12983,7 +12982,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -12993,7 +12992,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13002,6 +13001,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13023,7 +13023,7 @@
         <v>128806052</v>
       </c>
       <c r="B124" t="n">
-        <v>86753</v>
+        <v>86780</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13117,32 +13117,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128806011</v>
+        <v>128806045</v>
       </c>
       <c r="B125" t="n">
-        <v>86927</v>
+        <v>86976</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13152,10 +13152,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>717367</v>
+        <v>717324</v>
       </c>
       <c r="R125" t="n">
-        <v>6374231</v>
+        <v>6374179</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13196,7 +13196,6 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -13208,39 +13207,39 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128806045</v>
+        <v>128806051</v>
       </c>
       <c r="B126" t="n">
-        <v>86949</v>
+        <v>86780</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>449</v>
+        <v>3712</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13250,10 +13249,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>717324</v>
+        <v>717327</v>
       </c>
       <c r="R126" t="n">
-        <v>6374179</v>
+        <v>6374171</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13312,32 +13311,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128806051</v>
+        <v>128806011</v>
       </c>
       <c r="B127" t="n">
-        <v>86753</v>
+        <v>86954</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13347,10 +13346,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>717327</v>
+        <v>717367</v>
       </c>
       <c r="R127" t="n">
-        <v>6374171</v>
+        <v>6374231</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13391,6 +13390,7 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13402,7 +13402,7 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
@@ -13412,7 +13412,7 @@
         <v>128738882</v>
       </c>
       <c r="B128" t="n">
-        <v>87054</v>
+        <v>87081</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13523,7 +13523,7 @@
         <v>128738894</v>
       </c>
       <c r="B129" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13628,32 +13628,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128806491</v>
+        <v>128806485</v>
       </c>
       <c r="B130" t="n">
-        <v>86927</v>
+        <v>86780</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13663,10 +13663,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>717324</v>
+        <v>717201</v>
       </c>
       <c r="R130" t="n">
-        <v>6374171</v>
+        <v>6374297</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13726,32 +13726,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128806492</v>
+        <v>128806491</v>
       </c>
       <c r="B131" t="n">
-        <v>91002</v>
+        <v>86954</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13761,10 +13761,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>717146</v>
+        <v>717324</v>
       </c>
       <c r="R131" t="n">
-        <v>6374178</v>
+        <v>6374171</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13805,6 +13805,7 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -13823,32 +13824,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128806485</v>
+        <v>128806492</v>
       </c>
       <c r="B132" t="n">
-        <v>86753</v>
+        <v>91029</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>3712</v>
+        <v>5747</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13858,10 +13859,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>717201</v>
+        <v>717146</v>
       </c>
       <c r="R132" t="n">
-        <v>6374297</v>
+        <v>6374178</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13902,7 +13903,6 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -13924,7 +13924,7 @@
         <v>128806057</v>
       </c>
       <c r="B133" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14021,7 +14021,7 @@
         <v>128806058</v>
       </c>
       <c r="B134" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14118,7 +14118,7 @@
         <v>128806487</v>
       </c>
       <c r="B135" t="n">
-        <v>86972</v>
+        <v>86999</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>128806490</v>
       </c>
       <c r="B136" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         <v>128738847</v>
       </c>
       <c r="B137" t="n">
-        <v>86843</v>
+        <v>86870</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         <v>128806013</v>
       </c>
       <c r="B138" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14518,7 +14518,7 @@
         <v>128806065</v>
       </c>
       <c r="B139" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>128806486</v>
       </c>
       <c r="B140" t="n">
-        <v>86972</v>
+        <v>86999</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14709,32 +14709,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128738883</v>
+        <v>128806496</v>
       </c>
       <c r="B141" t="n">
-        <v>86791</v>
+        <v>96215</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3561</v>
+        <v>2180</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Blåbandad spindling</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cortinarius borgsjoeensis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14744,10 +14744,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>716993</v>
+        <v>717337</v>
       </c>
       <c r="R141" t="n">
-        <v>6374384</v>
+        <v>6374082</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14774,22 +14774,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14798,51 +14788,50 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128806024</v>
+        <v>128805991</v>
       </c>
       <c r="B142" t="n">
-        <v>86927</v>
+        <v>86999</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14852,10 +14841,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>717366</v>
+        <v>717147</v>
       </c>
       <c r="R142" t="n">
-        <v>6374150</v>
+        <v>6374164</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14896,7 +14885,6 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -14908,39 +14896,39 @@
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128805991</v>
+        <v>128806024</v>
       </c>
       <c r="B143" t="n">
-        <v>86972</v>
+        <v>86954</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14950,10 +14938,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>717147</v>
+        <v>717366</v>
       </c>
       <c r="R143" t="n">
-        <v>6374164</v>
+        <v>6374150</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14994,6 +14982,7 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -15005,39 +14994,39 @@
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128806496</v>
+        <v>128738883</v>
       </c>
       <c r="B144" t="n">
-        <v>96188</v>
+        <v>86818</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>2180</v>
+        <v>3561</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blåbandad spindling</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cortinarius borgsjoeensis</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15047,10 +15036,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>717337</v>
+        <v>716993</v>
       </c>
       <c r="R144" t="n">
-        <v>6374082</v>
+        <v>6374384</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15077,12 +15066,22 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15091,18 +15090,19 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>

--- a/artfynd/A 42607-2025 artfynd.xlsx
+++ b/artfynd/A 42607-2025 artfynd.xlsx
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1379,39 +1379,39 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128738834</v>
+        <v>128738853</v>
       </c>
       <c r="B9" t="n">
-        <v>86999</v>
+        <v>86954</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716985</v>
+        <v>717033</v>
       </c>
       <c r="R9" t="n">
-        <v>6374341</v>
+        <v>6374425</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1475,6 +1475,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1493,32 +1494,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128742266</v>
+        <v>128738834</v>
       </c>
       <c r="B10" t="n">
-        <v>86756</v>
+        <v>86999</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1528,10 +1529,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717201</v>
+        <v>716985</v>
       </c>
       <c r="R10" t="n">
-        <v>6374151</v>
+        <v>6374341</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,9 +1562,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,44 +1589,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128738837</v>
+        <v>128742266</v>
       </c>
       <c r="B11" t="n">
-        <v>86999</v>
+        <v>86756</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1625,10 +1636,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>717037</v>
+        <v>717201</v>
       </c>
       <c r="R11" t="n">
-        <v>6374236</v>
+        <v>6374151</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1658,19 +1669,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,44 +1686,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128738853</v>
+        <v>128738837</v>
       </c>
       <c r="B12" t="n">
-        <v>86954</v>
+        <v>86999</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1732,10 +1733,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>717033</v>
+        <v>717037</v>
       </c>
       <c r="R12" t="n">
-        <v>6374425</v>
+        <v>6374236</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1767,7 +1768,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1777,7 +1778,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1786,7 +1787,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1895,39 +1895,39 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128740504</v>
+        <v>128742285</v>
       </c>
       <c r="B14" t="n">
-        <v>98641</v>
+        <v>86954</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219862</v>
+        <v>6003295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1937,10 +1937,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>717091</v>
+        <v>716995</v>
       </c>
       <c r="R14" t="n">
-        <v>6374400</v>
+        <v>6374141</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1981,63 +1981,67 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128742285</v>
+        <v>128742275</v>
       </c>
       <c r="B15" t="n">
-        <v>86954</v>
+        <v>86905</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6003295</v>
+        <v>6003296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Stor odörspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius mussivus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.) Melot</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>716995</v>
+        <v>716983</v>
       </c>
       <c r="R15" t="n">
-        <v>6374141</v>
+        <v>6374138</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2070,6 +2074,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Kollekt taget för sekvensering av Martin Axegård.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2097,48 +2106,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128742275</v>
+        <v>128740504</v>
       </c>
       <c r="B16" t="n">
-        <v>86905</v>
+        <v>98641</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6003296</v>
+        <v>219862</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>716983</v>
+        <v>717091</v>
       </c>
       <c r="R16" t="n">
-        <v>6374138</v>
+        <v>6374400</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2173,62 +2179,56 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Kollekt taget för sekvensering av Martin Axegård.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128742286</v>
+        <v>128738898</v>
       </c>
       <c r="B17" t="n">
-        <v>86954</v>
+        <v>86917</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>716970</v>
+        <v>716960</v>
       </c>
       <c r="R17" t="n">
-        <v>6374097</v>
+        <v>6374150</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2271,62 +2271,71 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128740498</v>
+        <v>128738832</v>
       </c>
       <c r="B18" t="n">
-        <v>86954</v>
+        <v>86999</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2336,10 +2345,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>717099</v>
+        <v>717000</v>
       </c>
       <c r="R18" t="n">
-        <v>6374395</v>
+        <v>6374409</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2369,62 +2378,71 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128738857</v>
+        <v>128738859</v>
       </c>
       <c r="B19" t="n">
-        <v>86954</v>
+        <v>98653</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6003295</v>
+        <v>219874</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2434,10 +2452,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>717049</v>
+        <v>716963</v>
       </c>
       <c r="R19" t="n">
-        <v>6374317</v>
+        <v>6374082</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2469,7 +2487,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2479,7 +2497,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2488,7 +2506,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2507,7 +2524,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128738856</v>
+        <v>128742286</v>
       </c>
       <c r="B20" t="n">
         <v>86954</v>
@@ -2542,10 +2559,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>716986</v>
+        <v>716970</v>
       </c>
       <c r="R20" t="n">
-        <v>6374339</v>
+        <v>6374097</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2575,19 +2592,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2603,44 +2610,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128738898</v>
+        <v>128740498</v>
       </c>
       <c r="B21" t="n">
-        <v>86917</v>
+        <v>86954</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2650,10 +2657,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>716960</v>
+        <v>717099</v>
       </c>
       <c r="R21" t="n">
-        <v>6374150</v>
+        <v>6374395</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2683,71 +2690,62 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128738832</v>
+        <v>128738857</v>
       </c>
       <c r="B22" t="n">
-        <v>86999</v>
+        <v>86954</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2757,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>717000</v>
+        <v>717049</v>
       </c>
       <c r="R22" t="n">
-        <v>6374409</v>
+        <v>6374317</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2792,7 +2790,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2802,7 +2800,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2811,6 +2809,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2829,32 +2828,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128738859</v>
+        <v>128738856</v>
       </c>
       <c r="B23" t="n">
-        <v>98653</v>
+        <v>86954</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219874</v>
+        <v>6003295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2864,10 +2863,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>716963</v>
+        <v>716986</v>
       </c>
       <c r="R23" t="n">
-        <v>6374082</v>
+        <v>6374339</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2899,7 +2898,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2909,7 +2908,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2918,6 +2917,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3227,32 +3227,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128742283</v>
+        <v>128742273</v>
       </c>
       <c r="B27" t="n">
-        <v>86954</v>
+        <v>86930</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6003295</v>
+        <v>1988</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>717040</v>
+        <v>717014</v>
       </c>
       <c r="R27" t="n">
-        <v>6374195</v>
+        <v>6374164</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3306,7 +3306,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3325,32 +3324,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128742281</v>
+        <v>128740489</v>
       </c>
       <c r="B28" t="n">
-        <v>86954</v>
+        <v>91003</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6003295</v>
+        <v>5741</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3360,10 +3359,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>717039</v>
+        <v>717220</v>
       </c>
       <c r="R28" t="n">
-        <v>6374227</v>
+        <v>6374302</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3404,51 +3403,50 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128742273</v>
+        <v>128742283</v>
       </c>
       <c r="B29" t="n">
-        <v>86930</v>
+        <v>86954</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1988</v>
+        <v>6003295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3458,10 +3456,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>717014</v>
+        <v>717040</v>
       </c>
       <c r="R29" t="n">
-        <v>6374164</v>
+        <v>6374195</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3502,6 +3500,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3520,32 +3519,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128740489</v>
+        <v>128742281</v>
       </c>
       <c r="B30" t="n">
-        <v>91003</v>
+        <v>86954</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5741</v>
+        <v>6003295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3555,10 +3554,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>717220</v>
+        <v>717039</v>
       </c>
       <c r="R30" t="n">
-        <v>6374302</v>
+        <v>6374227</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3599,50 +3598,51 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128742272</v>
+        <v>128742293</v>
       </c>
       <c r="B31" t="n">
-        <v>91029</v>
+        <v>86917</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5747</v>
+        <v>3674</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3652,10 +3652,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>717018</v>
+        <v>717094</v>
       </c>
       <c r="R31" t="n">
-        <v>6374179</v>
+        <v>6374468</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3714,32 +3714,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128742293</v>
+        <v>128742254</v>
       </c>
       <c r="B32" t="n">
-        <v>86917</v>
+        <v>86999</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3749,10 +3749,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>717094</v>
+        <v>717285</v>
       </c>
       <c r="R32" t="n">
-        <v>6374468</v>
+        <v>6374272</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3811,32 +3811,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128742254</v>
+        <v>128740500</v>
       </c>
       <c r="B33" t="n">
-        <v>86999</v>
+        <v>86954</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>717285</v>
+        <v>717281</v>
       </c>
       <c r="R33" t="n">
-        <v>6374272</v>
+        <v>6374283</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3890,25 +3890,26 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128740500</v>
+        <v>128740499</v>
       </c>
       <c r="B34" t="n">
         <v>86954</v>
@@ -3943,10 +3944,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>717281</v>
+        <v>717145</v>
       </c>
       <c r="R34" t="n">
-        <v>6374283</v>
+        <v>6374308</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3999,14 +4000,14 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
+          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128740499</v>
+        <v>128740502</v>
       </c>
       <c r="B35" t="n">
         <v>86954</v>
@@ -4041,10 +4042,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>717145</v>
+        <v>717282</v>
       </c>
       <c r="R35" t="n">
-        <v>6374308</v>
+        <v>6374266</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4097,39 +4098,39 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128740502</v>
+        <v>128742272</v>
       </c>
       <c r="B36" t="n">
-        <v>86954</v>
+        <v>91029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6003295</v>
+        <v>5747</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4139,10 +4140,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>717282</v>
+        <v>717018</v>
       </c>
       <c r="R36" t="n">
-        <v>6374266</v>
+        <v>6374179</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4183,19 +4184,18 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4612,32 +4612,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128740509</v>
+        <v>128738895</v>
       </c>
       <c r="B41" t="n">
-        <v>86976</v>
+        <v>86954</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4647,10 +4647,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>717258</v>
+        <v>716974</v>
       </c>
       <c r="R41" t="n">
-        <v>6374286</v>
+        <v>6374284</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4680,61 +4680,72 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128738887</v>
+        <v>128742268</v>
       </c>
       <c r="B42" t="n">
-        <v>86802</v>
+        <v>86954</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4744,10 +4755,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>716984</v>
+        <v>717267</v>
       </c>
       <c r="R42" t="n">
-        <v>6374264</v>
+        <v>6374322</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4777,71 +4788,62 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128742259</v>
+        <v>128742280</v>
       </c>
       <c r="B43" t="n">
-        <v>86999</v>
+        <v>86954</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4851,10 +4853,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>716980</v>
+        <v>717058</v>
       </c>
       <c r="R43" t="n">
-        <v>6374067</v>
+        <v>6374174</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4895,6 +4897,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4913,32 +4916,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128738895</v>
+        <v>128742259</v>
       </c>
       <c r="B44" t="n">
-        <v>86954</v>
+        <v>86999</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4948,10 +4951,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>716974</v>
+        <v>716980</v>
       </c>
       <c r="R44" t="n">
-        <v>6374284</v>
+        <v>6374067</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4981,72 +4984,61 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128742268</v>
+        <v>128740509</v>
       </c>
       <c r="B45" t="n">
-        <v>86954</v>
+        <v>86976</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5056,10 +5048,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>717267</v>
+        <v>717258</v>
       </c>
       <c r="R45" t="n">
-        <v>6374322</v>
+        <v>6374286</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5100,51 +5092,50 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128742280</v>
+        <v>128738887</v>
       </c>
       <c r="B46" t="n">
-        <v>86954</v>
+        <v>86802</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5154,10 +5145,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>717058</v>
+        <v>716984</v>
       </c>
       <c r="R46" t="n">
-        <v>6374174</v>
+        <v>6374264</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5187,30 +5178,39 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -6127,32 +6127,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128742282</v>
+        <v>128738841</v>
       </c>
       <c r="B56" t="n">
-        <v>86954</v>
+        <v>86999</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6162,10 +6162,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>717040</v>
+        <v>716992</v>
       </c>
       <c r="R56" t="n">
-        <v>6374212</v>
+        <v>6374116</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6195,62 +6195,71 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128742263</v>
+        <v>128738835</v>
       </c>
       <c r="B57" t="n">
-        <v>91003</v>
+        <v>86999</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5741</v>
+        <v>3767</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6260,10 +6269,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>717281</v>
+        <v>716983</v>
       </c>
       <c r="R57" t="n">
-        <v>6374199</v>
+        <v>6374357</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6293,9 +6302,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6310,19 +6329,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128738841</v>
+        <v>128742252</v>
       </c>
       <c r="B58" t="n">
         <v>86999</v>
@@ -6357,10 +6376,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>716992</v>
+        <v>717146</v>
       </c>
       <c r="R58" t="n">
-        <v>6374116</v>
+        <v>6374313</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6390,19 +6409,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>09:50</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6417,44 +6426,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128738835</v>
+        <v>128740522</v>
       </c>
       <c r="B59" t="n">
-        <v>86999</v>
+        <v>86917</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6464,10 +6473,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>716983</v>
+        <v>717274</v>
       </c>
       <c r="R59" t="n">
-        <v>6374357</v>
+        <v>6374210</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6497,19 +6506,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>14:27</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6524,44 +6523,44 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128742252</v>
+        <v>128742263</v>
       </c>
       <c r="B60" t="n">
-        <v>86999</v>
+        <v>91003</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3767</v>
+        <v>5741</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6571,10 +6570,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>717146</v>
+        <v>717281</v>
       </c>
       <c r="R60" t="n">
-        <v>6374313</v>
+        <v>6374199</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6633,32 +6632,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128740522</v>
+        <v>128742282</v>
       </c>
       <c r="B61" t="n">
-        <v>86917</v>
+        <v>86954</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6668,10 +6667,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>717274</v>
+        <v>717040</v>
       </c>
       <c r="R61" t="n">
-        <v>6374210</v>
+        <v>6374212</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6712,50 +6711,51 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128742276</v>
+        <v>128740491</v>
       </c>
       <c r="B62" t="n">
-        <v>86976</v>
+        <v>86756</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6765,10 +6765,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>717269</v>
+        <v>717281</v>
       </c>
       <c r="R62" t="n">
-        <v>6374317</v>
+        <v>6374215</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6815,22 +6815,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128738884</v>
+        <v>128742255</v>
       </c>
       <c r="B63" t="n">
-        <v>86802</v>
+        <v>86999</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6838,21 +6838,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>424</v>
+        <v>3767</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6862,10 +6862,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>716969</v>
+        <v>717059</v>
       </c>
       <c r="R63" t="n">
-        <v>6374310</v>
+        <v>6374329</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6895,19 +6895,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>14:32</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6922,44 +6912,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128740491</v>
+        <v>128738848</v>
       </c>
       <c r="B64" t="n">
-        <v>86756</v>
+        <v>57713</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3762</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6969,10 +6959,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>717281</v>
+        <v>717165</v>
       </c>
       <c r="R64" t="n">
-        <v>6374215</v>
+        <v>6374351</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7002,9 +6992,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7019,22 +7019,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128742255</v>
+        <v>128742276</v>
       </c>
       <c r="B65" t="n">
-        <v>86999</v>
+        <v>86976</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7042,21 +7042,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7066,10 +7066,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>717059</v>
+        <v>717269</v>
       </c>
       <c r="R65" t="n">
-        <v>6374329</v>
+        <v>6374317</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7128,32 +7128,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128738848</v>
+        <v>128738884</v>
       </c>
       <c r="B66" t="n">
-        <v>57713</v>
+        <v>86802</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>424</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7163,10 +7163,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>717165</v>
+        <v>716969</v>
       </c>
       <c r="R66" t="n">
-        <v>6374351</v>
+        <v>6374310</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7432,39 +7432,39 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128738836</v>
+        <v>128738855</v>
       </c>
       <c r="B69" t="n">
-        <v>86999</v>
+        <v>86954</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7474,10 +7474,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>717056</v>
+        <v>716966</v>
       </c>
       <c r="R69" t="n">
-        <v>6374262</v>
+        <v>6374312</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7509,7 +7509,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7528,6 +7528,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7546,7 +7547,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128738855</v>
+        <v>128738852</v>
       </c>
       <c r="B70" t="n">
         <v>86954</v>
@@ -7581,10 +7582,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>716966</v>
+        <v>717045</v>
       </c>
       <c r="R70" t="n">
-        <v>6374312</v>
+        <v>6374462</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7616,7 +7617,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7626,7 +7627,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7654,32 +7655,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128738852</v>
+        <v>128738836</v>
       </c>
       <c r="B71" t="n">
-        <v>86954</v>
+        <v>86999</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7689,10 +7690,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>717045</v>
+        <v>717056</v>
       </c>
       <c r="R71" t="n">
-        <v>6374462</v>
+        <v>6374262</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7724,7 +7725,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7734,7 +7735,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7743,7 +7744,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7762,10 +7762,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128740508</v>
+        <v>128742251</v>
       </c>
       <c r="B72" t="n">
-        <v>86976</v>
+        <v>86999</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7773,21 +7773,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7797,10 +7797,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>717063</v>
+        <v>717106</v>
       </c>
       <c r="R72" t="n">
-        <v>6374397</v>
+        <v>6374415</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7847,19 +7847,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128742251</v>
+        <v>128738833</v>
       </c>
       <c r="B73" t="n">
         <v>86999</v>
@@ -7894,10 +7894,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>717106</v>
+        <v>716976</v>
       </c>
       <c r="R73" t="n">
-        <v>6374415</v>
+        <v>6374331</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7927,9 +7927,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7944,44 +7954,44 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128738833</v>
+        <v>128740519</v>
       </c>
       <c r="B74" t="n">
-        <v>86999</v>
+        <v>86917</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7991,10 +8001,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>716976</v>
+        <v>717067</v>
       </c>
       <c r="R74" t="n">
-        <v>6374331</v>
+        <v>6374399</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8024,19 +8034,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8051,44 +8051,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128740519</v>
+        <v>128740508</v>
       </c>
       <c r="B75" t="n">
-        <v>86917</v>
+        <v>86976</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8098,10 +8098,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>717067</v>
+        <v>717063</v>
       </c>
       <c r="R75" t="n">
-        <v>6374399</v>
+        <v>6374397</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8858,7 +8858,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -8955,7 +8955,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9360,10 +9360,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128806483</v>
+        <v>128815957</v>
       </c>
       <c r="B88" t="n">
-        <v>90969</v>
+        <v>86971</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9371,21 +9371,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>720</v>
+        <v>248934</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Knölfotad bananspindling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Cortinarius stjernegaardii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>Brandrud &amp; Frøslev</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9398,10 +9398,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>717267</v>
+        <v>717020</v>
       </c>
       <c r="R88" t="n">
-        <v>6374381</v>
+        <v>6374147</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9428,12 +9428,27 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Bilddokumentation av Ullas fynd. Uppsvullen bulb och orange basalmycel. Ek fanss på fyndplatsen som domineras av kalktallskog.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9449,22 +9464,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128815957</v>
+        <v>128806483</v>
       </c>
       <c r="B89" t="n">
-        <v>86971</v>
+        <v>90969</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9472,21 +9487,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>248934</v>
+        <v>720</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knölfotad bananspindling</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius stjernegaardii</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Brandrud &amp; Frøslev</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9499,10 +9514,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>717020</v>
+        <v>717267</v>
       </c>
       <c r="R89" t="n">
-        <v>6374147</v>
+        <v>6374381</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9529,27 +9544,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>10:37</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Bilddokumentation av Ullas fynd. Uppsvullen bulb och orange basalmycel. Ek fanss på fyndplatsen som domineras av kalktallskog.</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9565,12 +9565,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -9684,10 +9684,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128805996</v>
+        <v>128806494</v>
       </c>
       <c r="B91" t="n">
-        <v>86999</v>
+        <v>86976</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9695,21 +9695,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9719,10 +9719,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>717308</v>
+        <v>717333</v>
       </c>
       <c r="R91" t="n">
-        <v>6374239</v>
+        <v>6374180</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9769,19 +9769,19 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128806494</v>
+        <v>128806493</v>
       </c>
       <c r="B92" t="n">
         <v>86976</v>
@@ -9816,10 +9816,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>717333</v>
+        <v>717133</v>
       </c>
       <c r="R92" t="n">
-        <v>6374180</v>
+        <v>6374199</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9878,10 +9878,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128806493</v>
+        <v>128805996</v>
       </c>
       <c r="B93" t="n">
-        <v>86976</v>
+        <v>86999</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9889,21 +9889,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9913,10 +9913,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>717133</v>
+        <v>717308</v>
       </c>
       <c r="R93" t="n">
-        <v>6374199</v>
+        <v>6374239</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9963,12 +9963,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -10072,10 +10072,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128806038</v>
+        <v>128738846</v>
       </c>
       <c r="B95" t="n">
-        <v>98641</v>
+        <v>91003</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10083,21 +10083,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>219862</v>
+        <v>5741</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10107,10 +10107,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>717113</v>
+        <v>717037</v>
       </c>
       <c r="R95" t="n">
-        <v>6374105</v>
+        <v>6374226</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10137,12 +10137,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10157,22 +10167,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128738846</v>
+        <v>128815850</v>
       </c>
       <c r="B96" t="n">
-        <v>91003</v>
+        <v>89472</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10180,21 +10190,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5741</v>
+        <v>236437</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Brun klibbskivling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Limacella glioderma</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Fr.) Maire</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10204,10 +10214,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>717037</v>
+        <v>716975</v>
       </c>
       <c r="R96" t="n">
-        <v>6374226</v>
+        <v>6374071</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10239,7 +10249,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10249,7 +10259,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10383,10 +10393,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128815850</v>
+        <v>128806038</v>
       </c>
       <c r="B98" t="n">
-        <v>89472</v>
+        <v>98641</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10394,21 +10404,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>236437</v>
+        <v>219862</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Brun klibbskivling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Limacella glioderma</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Maire</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10418,10 +10428,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>716975</v>
+        <v>717113</v>
       </c>
       <c r="R98" t="n">
-        <v>6374071</v>
+        <v>6374105</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10448,22 +10458,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>09:13</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>09:13</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10478,57 +10478,60 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128806004</v>
+        <v>128806484</v>
       </c>
       <c r="B99" t="n">
-        <v>91494</v>
+        <v>90969</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>720</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>717360</v>
+        <v>717273</v>
       </c>
       <c r="R99" t="n">
-        <v>6374175</v>
+        <v>6374379</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10569,66 +10572,64 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128806484</v>
+        <v>128806004</v>
       </c>
       <c r="B100" t="n">
-        <v>90969</v>
+        <v>91494</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>720</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>717273</v>
+        <v>717360</v>
       </c>
       <c r="R100" t="n">
-        <v>6374379</v>
+        <v>6374175</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10669,19 +10670,18 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -10785,10 +10785,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128738866</v>
+        <v>128806009</v>
       </c>
       <c r="B102" t="n">
-        <v>90235</v>
+        <v>86954</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10796,21 +10796,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>970</v>
+        <v>6003295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10820,10 +10820,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>717039</v>
+        <v>717132</v>
       </c>
       <c r="R102" t="n">
-        <v>6374321</v>
+        <v>6374140</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10850,22 +10850,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>13:50</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>13:50</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10881,22 +10871,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128738897</v>
+        <v>128738866</v>
       </c>
       <c r="B103" t="n">
-        <v>86954</v>
+        <v>90235</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10904,21 +10894,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6003295</v>
+        <v>970</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10928,10 +10918,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>717015</v>
+        <v>717039</v>
       </c>
       <c r="R103" t="n">
-        <v>6374144</v>
+        <v>6374321</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10963,7 +10953,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -10973,7 +10963,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11001,7 +10991,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128806009</v>
+        <v>128738897</v>
       </c>
       <c r="B104" t="n">
         <v>86954</v>
@@ -11036,10 +11026,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>717132</v>
+        <v>717015</v>
       </c>
       <c r="R104" t="n">
-        <v>6374140</v>
+        <v>6374144</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11066,12 +11056,22 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11087,22 +11087,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128738875</v>
+        <v>128738842</v>
       </c>
       <c r="B105" t="n">
-        <v>87011</v>
+        <v>86999</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11110,19 +11110,23 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>433</v>
+        <v>3767</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr"/>
+          <t>Cortinarius violaceomaculatus</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
@@ -11130,10 +11134,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>716968</v>
+        <v>716981</v>
       </c>
       <c r="R105" t="n">
-        <v>6374251</v>
+        <v>6374088</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11165,7 +11169,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11175,7 +11179,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11202,10 +11206,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128738842</v>
+        <v>128738875</v>
       </c>
       <c r="B106" t="n">
-        <v>86999</v>
+        <v>87011</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11213,23 +11217,19 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>3767</v>
+        <v>433</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Brandrud</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -11237,10 +11237,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>716981</v>
+        <v>716968</v>
       </c>
       <c r="R106" t="n">
-        <v>6374088</v>
+        <v>6374251</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11272,7 +11272,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11282,7 +11282,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11406,32 +11406,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128806056</v>
+        <v>128738843</v>
       </c>
       <c r="B108" t="n">
-        <v>106944</v>
+        <v>86999</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221849</v>
+        <v>3767</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11441,10 +11441,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>717370</v>
+        <v>716967</v>
       </c>
       <c r="R108" t="n">
-        <v>6374168</v>
+        <v>6374084</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11471,12 +11471,22 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11491,44 +11501,44 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128738843</v>
+        <v>128806056</v>
       </c>
       <c r="B109" t="n">
-        <v>86999</v>
+        <v>106944</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>3767</v>
+        <v>221849</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11538,10 +11548,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>716967</v>
+        <v>717370</v>
       </c>
       <c r="R109" t="n">
-        <v>6374084</v>
+        <v>6374168</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11568,22 +11578,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>09:26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>09:26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11598,12 +11598,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -11913,32 +11913,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128806497</v>
+        <v>128806022</v>
       </c>
       <c r="B113" t="n">
-        <v>86780</v>
+        <v>86954</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11948,10 +11948,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>717273</v>
+        <v>717284</v>
       </c>
       <c r="R113" t="n">
-        <v>6374182</v>
+        <v>6374309</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11992,50 +11992,51 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128806022</v>
+        <v>128806497</v>
       </c>
       <c r="B114" t="n">
-        <v>86954</v>
+        <v>86780</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12045,10 +12046,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>717284</v>
+        <v>717273</v>
       </c>
       <c r="R114" t="n">
-        <v>6374309</v>
+        <v>6374182</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12089,19 +12090,18 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -12405,32 +12405,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128806050</v>
+        <v>128806064</v>
       </c>
       <c r="B118" t="n">
-        <v>86920</v>
+        <v>86917</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6037417</v>
+        <v>3674</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12440,10 +12440,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>717311</v>
+        <v>717299</v>
       </c>
       <c r="R118" t="n">
-        <v>6374287</v>
+        <v>6374300</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12484,7 +12484,6 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -12503,32 +12502,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128738893</v>
+        <v>128806043</v>
       </c>
       <c r="B119" t="n">
-        <v>86954</v>
+        <v>75142</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6003295</v>
+        <v>6426</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12538,10 +12537,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>717000</v>
+        <v>717359</v>
       </c>
       <c r="R119" t="n">
-        <v>6374121</v>
+        <v>6374214</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12568,22 +12567,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>10:04</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>10:04</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12592,51 +12581,50 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128806064</v>
+        <v>128806050</v>
       </c>
       <c r="B120" t="n">
-        <v>86917</v>
+        <v>86920</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>3674</v>
+        <v>6037417</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12646,10 +12634,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>717299</v>
+        <v>717311</v>
       </c>
       <c r="R120" t="n">
-        <v>6374300</v>
+        <v>6374287</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12690,6 +12678,7 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12708,32 +12697,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128806043</v>
+        <v>128738893</v>
       </c>
       <c r="B121" t="n">
-        <v>75142</v>
+        <v>86954</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6426</v>
+        <v>6003295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12743,10 +12732,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>717359</v>
+        <v>717000</v>
       </c>
       <c r="R121" t="n">
-        <v>6374214</v>
+        <v>6374121</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12773,12 +12762,22 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12787,50 +12786,51 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128738867</v>
+        <v>128806052</v>
       </c>
       <c r="B122" t="n">
-        <v>86976</v>
+        <v>86780</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>449</v>
+        <v>3712</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12840,10 +12840,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>717115</v>
+        <v>717284</v>
       </c>
       <c r="R122" t="n">
-        <v>6374297</v>
+        <v>6374097</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12870,22 +12870,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>13:35</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>13:35</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12900,12 +12890,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
@@ -13020,32 +13010,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128806052</v>
+        <v>128806045</v>
       </c>
       <c r="B124" t="n">
-        <v>86780</v>
+        <v>86976</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>3712</v>
+        <v>449</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13055,10 +13045,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>717284</v>
+        <v>717324</v>
       </c>
       <c r="R124" t="n">
-        <v>6374097</v>
+        <v>6374179</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13117,32 +13107,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128806045</v>
+        <v>128806051</v>
       </c>
       <c r="B125" t="n">
-        <v>86976</v>
+        <v>86780</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>449</v>
+        <v>3712</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13152,10 +13142,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>717324</v>
+        <v>717327</v>
       </c>
       <c r="R125" t="n">
-        <v>6374179</v>
+        <v>6374171</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13214,45 +13204,48 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128806051</v>
+        <v>128738882</v>
       </c>
       <c r="B126" t="n">
-        <v>86780</v>
+        <v>87081</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>3712</v>
+        <v>3563</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Stor granspindling</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius bovinus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Fr. sl.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>717327</v>
+        <v>717013</v>
       </c>
       <c r="R126" t="n">
-        <v>6374171</v>
+        <v>6374226</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13279,12 +13272,22 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13293,18 +13296,19 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
@@ -13409,48 +13413,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128738882</v>
+        <v>128738894</v>
       </c>
       <c r="B128" t="n">
-        <v>87081</v>
+        <v>86954</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>3563</v>
+        <v>6003295</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stor granspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cortinarius bovinus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Fr. sl.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>717013</v>
+        <v>716975</v>
       </c>
       <c r="R128" t="n">
-        <v>6374226</v>
+        <v>6374071</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13482,7 +13483,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -13492,7 +13493,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13520,32 +13521,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128738894</v>
+        <v>128806485</v>
       </c>
       <c r="B129" t="n">
-        <v>86954</v>
+        <v>86780</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13555,10 +13556,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>716975</v>
+        <v>717201</v>
       </c>
       <c r="R129" t="n">
-        <v>6374071</v>
+        <v>6374297</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13585,22 +13586,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>09:15</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>09:15</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13616,44 +13607,44 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128806485</v>
+        <v>128806492</v>
       </c>
       <c r="B130" t="n">
-        <v>86780</v>
+        <v>91029</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>3712</v>
+        <v>5747</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13663,10 +13654,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>717201</v>
+        <v>717146</v>
       </c>
       <c r="R130" t="n">
-        <v>6374297</v>
+        <v>6374178</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13707,7 +13698,6 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13824,32 +13814,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128806492</v>
+        <v>128806057</v>
       </c>
       <c r="B132" t="n">
-        <v>91029</v>
+        <v>86917</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5747</v>
+        <v>3674</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13859,10 +13849,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>717146</v>
+        <v>717121</v>
       </c>
       <c r="R132" t="n">
-        <v>6374178</v>
+        <v>6374153</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13909,19 +13899,19 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128806057</v>
+        <v>128806058</v>
       </c>
       <c r="B133" t="n">
         <v>86917</v>
@@ -13956,10 +13946,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>717121</v>
+        <v>717196</v>
       </c>
       <c r="R133" t="n">
-        <v>6374153</v>
+        <v>6374281</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14018,32 +14008,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128806058</v>
+        <v>128806487</v>
       </c>
       <c r="B134" t="n">
-        <v>86917</v>
+        <v>86999</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14053,10 +14043,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>717196</v>
+        <v>717275</v>
       </c>
       <c r="R134" t="n">
-        <v>6374281</v>
+        <v>6374183</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14103,22 +14093,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128806487</v>
+        <v>128738847</v>
       </c>
       <c r="B135" t="n">
-        <v>86999</v>
+        <v>86870</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14126,21 +14116,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3767</v>
+        <v>248956</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14150,10 +14140,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>717275</v>
+        <v>716980</v>
       </c>
       <c r="R135" t="n">
-        <v>6374183</v>
+        <v>6374264</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14180,12 +14170,22 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14200,12 +14200,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -14310,32 +14310,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128738847</v>
+        <v>128806013</v>
       </c>
       <c r="B137" t="n">
-        <v>86870</v>
+        <v>86954</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14345,10 +14345,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>716980</v>
+        <v>717315</v>
       </c>
       <c r="R137" t="n">
-        <v>6374264</v>
+        <v>6374306</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14375,22 +14375,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14399,50 +14389,51 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128806013</v>
+        <v>128806065</v>
       </c>
       <c r="B138" t="n">
-        <v>86954</v>
+        <v>86917</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14452,10 +14443,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>717315</v>
+        <v>717316</v>
       </c>
       <c r="R138" t="n">
-        <v>6374306</v>
+        <v>6374280</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14496,7 +14487,6 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -14508,39 +14498,39 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128806065</v>
+        <v>128806486</v>
       </c>
       <c r="B139" t="n">
-        <v>86917</v>
+        <v>86999</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14550,10 +14540,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>717316</v>
+        <v>717170</v>
       </c>
       <c r="R139" t="n">
-        <v>6374280</v>
+        <v>6374288</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14600,22 +14590,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128806486</v>
+        <v>128738883</v>
       </c>
       <c r="B140" t="n">
-        <v>86999</v>
+        <v>86818</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14623,16 +14613,16 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>3767</v>
+        <v>3561</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blåbandad spindling</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius borgsjoeensis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -14647,10 +14637,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>717170</v>
+        <v>716993</v>
       </c>
       <c r="R140" t="n">
-        <v>6374288</v>
+        <v>6374384</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14677,12 +14667,22 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14691,18 +14691,19 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
@@ -15001,10 +15002,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128738883</v>
+        <v>128738867</v>
       </c>
       <c r="B144" t="n">
-        <v>86818</v>
+        <v>86976</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15012,34 +15013,37 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>3561</v>
+        <v>449</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Blåbandad spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Cortinarius borgsjoeensis</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>716993</v>
+        <v>717115</v>
       </c>
       <c r="R144" t="n">
-        <v>6374384</v>
+        <v>6374297</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15071,7 +15075,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15081,7 +15085,12 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Växer i gammal myrstack. Anna: luktar lite åt rättickahållet. Luktar svagt av rödbeta, lite som kantspindling men inte lika stickande söt .. utan mer som rödbeta. Majs är en bättre doftreferens.</t>
         </is>
       </c>
       <c r="AD144" t="b">

--- a/artfynd/A 42607-2025 artfynd.xlsx
+++ b/artfynd/A 42607-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128738845</v>
+        <v>128740505</v>
       </c>
       <c r="B2" t="n">
-        <v>86756</v>
+        <v>98647</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3762</v>
+        <v>219862</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716961</v>
+        <v>717182</v>
       </c>
       <c r="R2" t="n">
-        <v>6374255</v>
+        <v>6374336</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,19 +743,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,44 +760,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128738831</v>
+        <v>128738845</v>
       </c>
       <c r="B3" t="n">
-        <v>86999</v>
+        <v>86760</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717030</v>
+        <v>716961</v>
       </c>
       <c r="R3" t="n">
-        <v>6374429</v>
+        <v>6374255</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +842,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +852,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128742256</v>
+        <v>128738831</v>
       </c>
       <c r="B4" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717053</v>
+        <v>717030</v>
       </c>
       <c r="R4" t="n">
-        <v>6374253</v>
+        <v>6374429</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,9 +947,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,44 +974,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128740514</v>
+        <v>128742256</v>
       </c>
       <c r="B5" t="n">
-        <v>86780</v>
+        <v>87003</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3712</v>
+        <v>3767</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717295</v>
+        <v>717053</v>
       </c>
       <c r="R5" t="n">
-        <v>6374249</v>
+        <v>6374253</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128740505</v>
+        <v>128740514</v>
       </c>
       <c r="B6" t="n">
-        <v>98641</v>
+        <v>86784</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219862</v>
+        <v>3712</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717182</v>
+        <v>717295</v>
       </c>
       <c r="R6" t="n">
-        <v>6374336</v>
+        <v>6374249</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
         <v>128738854</v>
       </c>
       <c r="B7" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>128740487</v>
       </c>
       <c r="B8" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,32 +1386,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128738853</v>
+        <v>128738834</v>
       </c>
       <c r="B9" t="n">
-        <v>86954</v>
+        <v>87003</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717033</v>
+        <v>716985</v>
       </c>
       <c r="R9" t="n">
-        <v>6374425</v>
+        <v>6374341</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1475,7 +1475,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1494,32 +1493,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128738834</v>
+        <v>128742266</v>
       </c>
       <c r="B10" t="n">
-        <v>86999</v>
+        <v>86760</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1529,10 +1528,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716985</v>
+        <v>717201</v>
       </c>
       <c r="R10" t="n">
-        <v>6374341</v>
+        <v>6374151</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1562,19 +1561,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1589,44 +1578,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128742266</v>
+        <v>128738837</v>
       </c>
       <c r="B11" t="n">
-        <v>86756</v>
+        <v>87003</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1636,10 +1625,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>717201</v>
+        <v>717037</v>
       </c>
       <c r="R11" t="n">
-        <v>6374151</v>
+        <v>6374236</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,9 +1658,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1686,44 +1685,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128738837</v>
+        <v>128738853</v>
       </c>
       <c r="B12" t="n">
-        <v>86999</v>
+        <v>86958</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1733,10 +1732,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>717037</v>
+        <v>717033</v>
       </c>
       <c r="R12" t="n">
-        <v>6374236</v>
+        <v>6374425</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1768,7 +1767,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1778,7 +1777,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1787,6 +1786,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1808,7 +1808,7 @@
         <v>128740482</v>
       </c>
       <c r="B13" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,32 +1902,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128742285</v>
+        <v>128740504</v>
       </c>
       <c r="B14" t="n">
-        <v>86954</v>
+        <v>98647</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6003295</v>
+        <v>219862</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1937,10 +1937,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716995</v>
+        <v>717091</v>
       </c>
       <c r="R14" t="n">
-        <v>6374141</v>
+        <v>6374400</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1981,67 +1981,63 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128742275</v>
+        <v>128742285</v>
       </c>
       <c r="B15" t="n">
-        <v>86905</v>
+        <v>86958</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6003296</v>
+        <v>6003295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>716983</v>
+        <v>716995</v>
       </c>
       <c r="R15" t="n">
-        <v>6374138</v>
+        <v>6374141</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2074,11 +2070,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Kollekt taget för sekvensering av Martin Axegård.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2106,45 +2097,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128740504</v>
+        <v>128742275</v>
       </c>
       <c r="B16" t="n">
-        <v>98641</v>
+        <v>86909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219862</v>
+        <v>6003296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Stor odörspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius mussivus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Melot</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>717091</v>
+        <v>716983</v>
       </c>
       <c r="R16" t="n">
-        <v>6374400</v>
+        <v>6374138</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2179,56 +2173,62 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Kollekt taget för sekvensering av Martin Axegård.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128738898</v>
+        <v>128738832</v>
       </c>
       <c r="B17" t="n">
-        <v>86917</v>
+        <v>87003</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>716960</v>
+        <v>717000</v>
       </c>
       <c r="R17" t="n">
-        <v>6374150</v>
+        <v>6374409</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2310,32 +2310,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128738832</v>
+        <v>128738898</v>
       </c>
       <c r="B18" t="n">
-        <v>86999</v>
+        <v>86921</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>717000</v>
+        <v>716960</v>
       </c>
       <c r="R18" t="n">
-        <v>6374409</v>
+        <v>6374150</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2420,7 +2420,7 @@
         <v>128738859</v>
       </c>
       <c r="B19" t="n">
-        <v>98653</v>
+        <v>98659</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>128742286</v>
       </c>
       <c r="B20" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>128740498</v>
       </c>
       <c r="B21" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2723,7 +2723,7 @@
         <v>128738857</v>
       </c>
       <c r="B22" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>128738856</v>
       </c>
       <c r="B23" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>128742257</v>
       </c>
       <c r="B24" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>128740485</v>
       </c>
       <c r="B25" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>128742258</v>
       </c>
       <c r="B26" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>128742273</v>
       </c>
       <c r="B27" t="n">
-        <v>86930</v>
+        <v>86934</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>128740489</v>
       </c>
       <c r="B28" t="n">
-        <v>91003</v>
+        <v>91008</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>128742283</v>
       </c>
       <c r="B29" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>128742281</v>
       </c>
       <c r="B30" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3617,32 +3617,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128742293</v>
+        <v>128742254</v>
       </c>
       <c r="B31" t="n">
-        <v>86917</v>
+        <v>87003</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3652,10 +3652,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>717094</v>
+        <v>717285</v>
       </c>
       <c r="R31" t="n">
-        <v>6374468</v>
+        <v>6374272</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3714,10 +3714,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128742254</v>
+        <v>128742272</v>
       </c>
       <c r="B32" t="n">
-        <v>86999</v>
+        <v>91034</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3725,21 +3725,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3767</v>
+        <v>5747</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3749,10 +3749,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>717285</v>
+        <v>717018</v>
       </c>
       <c r="R32" t="n">
-        <v>6374272</v>
+        <v>6374179</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3811,32 +3811,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128740500</v>
+        <v>128742293</v>
       </c>
       <c r="B33" t="n">
-        <v>86954</v>
+        <v>86921</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>717281</v>
+        <v>717094</v>
       </c>
       <c r="R33" t="n">
-        <v>6374283</v>
+        <v>6374468</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3890,29 +3890,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128740499</v>
+        <v>128740500</v>
       </c>
       <c r="B34" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3944,10 +3943,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>717145</v>
+        <v>717281</v>
       </c>
       <c r="R34" t="n">
-        <v>6374308</v>
+        <v>6374283</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4000,17 +3999,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128740502</v>
+        <v>128740499</v>
       </c>
       <c r="B35" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4042,10 +4041,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>717282</v>
+        <v>717145</v>
       </c>
       <c r="R35" t="n">
-        <v>6374266</v>
+        <v>6374308</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4105,32 +4104,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128742272</v>
+        <v>128740502</v>
       </c>
       <c r="B36" t="n">
-        <v>91029</v>
+        <v>86958</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4140,10 +4139,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>717018</v>
+        <v>717282</v>
       </c>
       <c r="R36" t="n">
-        <v>6374179</v>
+        <v>6374266</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4184,50 +4183,51 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128740521</v>
+        <v>128738858</v>
       </c>
       <c r="B37" t="n">
-        <v>86917</v>
+        <v>86958</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4237,10 +4237,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>717216</v>
+        <v>717003</v>
       </c>
       <c r="R37" t="n">
-        <v>6374357</v>
+        <v>6374177</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4270,39 +4270,50 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128738900</v>
+        <v>128740521</v>
       </c>
       <c r="B38" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4334,10 +4345,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>716960</v>
+        <v>717216</v>
       </c>
       <c r="R38" t="n">
-        <v>6374079</v>
+        <v>6374357</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4367,19 +4378,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>09:09</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>09:09</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4394,44 +4395,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128742267</v>
+        <v>128738900</v>
       </c>
       <c r="B39" t="n">
-        <v>86954</v>
+        <v>86921</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4441,10 +4442,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>717105</v>
+        <v>716960</v>
       </c>
       <c r="R39" t="n">
-        <v>6374393</v>
+        <v>6374079</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4474,40 +4475,49 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128738858</v>
+        <v>128742267</v>
       </c>
       <c r="B40" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4539,10 +4549,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>717003</v>
+        <v>717105</v>
       </c>
       <c r="R40" t="n">
-        <v>6374177</v>
+        <v>6374393</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4572,19 +4582,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:02</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4600,44 +4600,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128738895</v>
+        <v>128742259</v>
       </c>
       <c r="B41" t="n">
-        <v>86954</v>
+        <v>87003</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4647,10 +4647,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>716974</v>
+        <v>716980</v>
       </c>
       <c r="R41" t="n">
-        <v>6374284</v>
+        <v>6374067</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4680,72 +4680,61 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128742268</v>
+        <v>128740509</v>
       </c>
       <c r="B42" t="n">
-        <v>86954</v>
+        <v>86980</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4755,10 +4744,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>717267</v>
+        <v>717258</v>
       </c>
       <c r="R42" t="n">
-        <v>6374322</v>
+        <v>6374286</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4799,51 +4788,50 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128742280</v>
+        <v>128738887</v>
       </c>
       <c r="B43" t="n">
-        <v>86954</v>
+        <v>86806</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4853,10 +4841,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>717058</v>
+        <v>716984</v>
       </c>
       <c r="R43" t="n">
-        <v>6374174</v>
+        <v>6374264</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4886,62 +4874,71 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128742259</v>
+        <v>128738895</v>
       </c>
       <c r="B44" t="n">
-        <v>86999</v>
+        <v>86958</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4951,10 +4948,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>716980</v>
+        <v>716974</v>
       </c>
       <c r="R44" t="n">
-        <v>6374067</v>
+        <v>6374284</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4984,61 +4981,72 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128740509</v>
+        <v>128742268</v>
       </c>
       <c r="B45" t="n">
-        <v>86976</v>
+        <v>86958</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5048,10 +5056,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>717258</v>
+        <v>717267</v>
       </c>
       <c r="R45" t="n">
-        <v>6374286</v>
+        <v>6374322</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5092,50 +5100,51 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128738887</v>
+        <v>128742280</v>
       </c>
       <c r="B46" t="n">
-        <v>86802</v>
+        <v>86958</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5145,10 +5154,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>716984</v>
+        <v>717058</v>
       </c>
       <c r="R46" t="n">
-        <v>6374264</v>
+        <v>6374174</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5178,39 +5187,30 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5220,7 +5220,7 @@
         <v>128738880</v>
       </c>
       <c r="B47" t="n">
-        <v>86780</v>
+        <v>86784</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>128738838</v>
       </c>
       <c r="B48" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>128742289</v>
       </c>
       <c r="B49" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         <v>128742269</v>
       </c>
       <c r="B50" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>128742279</v>
       </c>
       <c r="B51" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>128742288</v>
       </c>
       <c r="B52" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>128738896</v>
       </c>
       <c r="B53" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>128742291</v>
       </c>
       <c r="B54" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>128742284</v>
       </c>
       <c r="B55" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>128738841</v>
       </c>
       <c r="B56" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>128738835</v>
       </c>
       <c r="B57" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>128742252</v>
       </c>
       <c r="B58" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6438,10 +6438,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128740522</v>
+        <v>128742263</v>
       </c>
       <c r="B59" t="n">
-        <v>86917</v>
+        <v>91008</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6449,21 +6449,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3674</v>
+        <v>5741</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6473,10 +6473,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>717274</v>
+        <v>717281</v>
       </c>
       <c r="R59" t="n">
-        <v>6374210</v>
+        <v>6374199</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6523,22 +6523,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128742263</v>
+        <v>128740522</v>
       </c>
       <c r="B60" t="n">
-        <v>91003</v>
+        <v>86921</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6546,21 +6546,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5741</v>
+        <v>3674</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6570,10 +6570,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>717281</v>
+        <v>717274</v>
       </c>
       <c r="R60" t="n">
-        <v>6374199</v>
+        <v>6374210</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6620,12 +6620,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6635,7 +6635,7 @@
         <v>128742282</v>
       </c>
       <c r="B61" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>128740491</v>
       </c>
       <c r="B62" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>128742255</v>
       </c>
       <c r="B63" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>128742276</v>
       </c>
       <c r="B65" t="n">
-        <v>86976</v>
+        <v>86980</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>128738884</v>
       </c>
       <c r="B66" t="n">
-        <v>86802</v>
+        <v>86806</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         <v>128738851</v>
       </c>
       <c r="B67" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>128740512</v>
       </c>
       <c r="B68" t="n">
-        <v>86780</v>
+        <v>86784</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7439,32 +7439,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128738855</v>
+        <v>128738836</v>
       </c>
       <c r="B69" t="n">
-        <v>86954</v>
+        <v>87003</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7474,10 +7474,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>716966</v>
+        <v>717056</v>
       </c>
       <c r="R69" t="n">
-        <v>6374312</v>
+        <v>6374262</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7509,7 +7509,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7528,7 +7528,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7547,10 +7546,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128738852</v>
+        <v>128738855</v>
       </c>
       <c r="B70" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7582,10 +7581,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>717045</v>
+        <v>716966</v>
       </c>
       <c r="R70" t="n">
-        <v>6374462</v>
+        <v>6374312</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7617,7 +7616,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7627,7 +7626,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7655,32 +7654,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128738836</v>
+        <v>128738852</v>
       </c>
       <c r="B71" t="n">
-        <v>86999</v>
+        <v>86958</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7690,10 +7689,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>717056</v>
+        <v>717045</v>
       </c>
       <c r="R71" t="n">
-        <v>6374262</v>
+        <v>6374462</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7725,7 +7724,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7735,7 +7734,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7744,6 +7743,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7762,32 +7762,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128742251</v>
+        <v>128742287</v>
       </c>
       <c r="B72" t="n">
-        <v>86999</v>
+        <v>86958</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7797,10 +7797,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>717106</v>
+        <v>717013</v>
       </c>
       <c r="R72" t="n">
-        <v>6374415</v>
+        <v>6374166</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7841,6 +7841,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7859,32 +7860,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128738833</v>
+        <v>128742270</v>
       </c>
       <c r="B73" t="n">
-        <v>86999</v>
+        <v>86958</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7894,10 +7895,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>716976</v>
+        <v>717071</v>
       </c>
       <c r="R73" t="n">
-        <v>6374331</v>
+        <v>6374305</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7927,71 +7928,62 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128740519</v>
+        <v>128742290</v>
       </c>
       <c r="B74" t="n">
-        <v>86917</v>
+        <v>86958</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8001,10 +7993,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>717067</v>
+        <v>716979</v>
       </c>
       <c r="R74" t="n">
-        <v>6374399</v>
+        <v>6374069</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8045,28 +8037,29 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128740508</v>
+        <v>128742251</v>
       </c>
       <c r="B75" t="n">
-        <v>86976</v>
+        <v>87003</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8074,21 +8067,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8098,10 +8091,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>717063</v>
+        <v>717106</v>
       </c>
       <c r="R75" t="n">
-        <v>6374397</v>
+        <v>6374415</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8148,44 +8141,44 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128742287</v>
+        <v>128738833</v>
       </c>
       <c r="B76" t="n">
-        <v>86954</v>
+        <v>87003</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8195,10 +8188,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>717013</v>
+        <v>716976</v>
       </c>
       <c r="R76" t="n">
-        <v>6374166</v>
+        <v>6374331</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8228,62 +8221,71 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128742270</v>
+        <v>128740508</v>
       </c>
       <c r="B77" t="n">
-        <v>86954</v>
+        <v>86980</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8293,10 +8295,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>717071</v>
+        <v>717063</v>
       </c>
       <c r="R77" t="n">
-        <v>6374305</v>
+        <v>6374397</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8337,51 +8339,50 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128742290</v>
+        <v>128740519</v>
       </c>
       <c r="B78" t="n">
-        <v>86954</v>
+        <v>86921</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8391,10 +8392,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>716979</v>
+        <v>717067</v>
       </c>
       <c r="R78" t="n">
-        <v>6374069</v>
+        <v>6374399</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8435,19 +8436,18 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8457,7 +8457,7 @@
         <v>128740516</v>
       </c>
       <c r="B79" t="n">
-        <v>92126</v>
+        <v>92131</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>128738891</v>
       </c>
       <c r="B80" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>128738890</v>
       </c>
       <c r="B81" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8767,32 +8767,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128740503</v>
+        <v>128740484</v>
       </c>
       <c r="B82" t="n">
-        <v>86954</v>
+        <v>87003</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8802,10 +8802,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>717212</v>
+        <v>717279</v>
       </c>
       <c r="R82" t="n">
-        <v>6374189</v>
+        <v>6374209</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8846,7 +8846,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8865,32 +8864,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128740510</v>
+        <v>128740518</v>
       </c>
       <c r="B83" t="n">
-        <v>86920</v>
+        <v>86921</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6037417</v>
+        <v>3674</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8900,10 +8899,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>717105</v>
+        <v>717062</v>
       </c>
       <c r="R83" t="n">
-        <v>6374479</v>
+        <v>6374393</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8955,39 +8954,39 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128740484</v>
+        <v>128740503</v>
       </c>
       <c r="B84" t="n">
-        <v>86999</v>
+        <v>86958</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8997,10 +8996,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>717279</v>
+        <v>717212</v>
       </c>
       <c r="R84" t="n">
-        <v>6374209</v>
+        <v>6374189</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9041,6 +9040,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9059,32 +9059,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128740518</v>
+        <v>128740510</v>
       </c>
       <c r="B85" t="n">
-        <v>86917</v>
+        <v>86924</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3674</v>
+        <v>6037417</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9094,10 +9094,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>717062</v>
+        <v>717105</v>
       </c>
       <c r="R85" t="n">
-        <v>6374393</v>
+        <v>6374479</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9159,7 +9159,7 @@
         <v>128738899</v>
       </c>
       <c r="B86" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>128806499</v>
       </c>
       <c r="B87" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9360,10 +9360,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128815957</v>
+        <v>128806483</v>
       </c>
       <c r="B88" t="n">
-        <v>86971</v>
+        <v>90974</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9371,21 +9371,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>248934</v>
+        <v>720</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knölfotad bananspindling</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cortinarius stjernegaardii</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Brandrud &amp; Frøslev</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9398,10 +9398,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>717020</v>
+        <v>717267</v>
       </c>
       <c r="R88" t="n">
-        <v>6374147</v>
+        <v>6374381</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9428,27 +9428,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>10:37</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Bilddokumentation av Ullas fynd. Uppsvullen bulb och orange basalmycel. Ek fanss på fyndplatsen som domineras av kalktallskog.</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9464,22 +9449,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128806483</v>
+        <v>128815957</v>
       </c>
       <c r="B89" t="n">
-        <v>90969</v>
+        <v>86975</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9487,21 +9472,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>720</v>
+        <v>248934</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Knölfotad bananspindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Cortinarius stjernegaardii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>Brandrud &amp; Frøslev</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9514,10 +9499,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>717267</v>
+        <v>717020</v>
       </c>
       <c r="R89" t="n">
-        <v>6374381</v>
+        <v>6374147</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9544,12 +9529,27 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Bilddokumentation av Ullas fynd. Uppsvullen bulb och orange basalmycel. Ek fanss på fyndplatsen som domineras av kalktallskog.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9565,12 +9565,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -9580,7 +9580,7 @@
         <v>128738885</v>
       </c>
       <c r="B90" t="n">
-        <v>86802</v>
+        <v>86806</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9684,10 +9684,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128806494</v>
+        <v>128805996</v>
       </c>
       <c r="B91" t="n">
-        <v>86976</v>
+        <v>87003</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9695,21 +9695,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9719,10 +9719,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>717333</v>
+        <v>717308</v>
       </c>
       <c r="R91" t="n">
-        <v>6374180</v>
+        <v>6374239</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9769,22 +9769,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128806493</v>
+        <v>128806494</v>
       </c>
       <c r="B92" t="n">
-        <v>86976</v>
+        <v>86980</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9816,10 +9816,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>717133</v>
+        <v>717333</v>
       </c>
       <c r="R92" t="n">
-        <v>6374199</v>
+        <v>6374180</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9878,10 +9878,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128805996</v>
+        <v>128806493</v>
       </c>
       <c r="B93" t="n">
-        <v>86999</v>
+        <v>86980</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9889,21 +9889,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9913,10 +9913,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>717308</v>
+        <v>717133</v>
       </c>
       <c r="R93" t="n">
-        <v>6374239</v>
+        <v>6374199</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9963,22 +9963,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128806044</v>
+        <v>128738839</v>
       </c>
       <c r="B94" t="n">
-        <v>86976</v>
+        <v>87003</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9986,21 +9986,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10010,10 +10010,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>717148</v>
+        <v>717039</v>
       </c>
       <c r="R94" t="n">
-        <v>6374175</v>
+        <v>6374168</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10040,12 +10040,22 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10060,44 +10070,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128738846</v>
+        <v>128806044</v>
       </c>
       <c r="B95" t="n">
-        <v>91003</v>
+        <v>86980</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5741</v>
+        <v>449</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10107,10 +10117,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>717037</v>
+        <v>717148</v>
       </c>
       <c r="R95" t="n">
-        <v>6374226</v>
+        <v>6374175</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10137,22 +10147,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10167,22 +10167,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128815850</v>
+        <v>128738846</v>
       </c>
       <c r="B96" t="n">
-        <v>89472</v>
+        <v>91008</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10190,21 +10190,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>236437</v>
+        <v>5741</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Brun klibbskivling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Limacella glioderma</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Maire</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10214,10 +10214,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>716975</v>
+        <v>717037</v>
       </c>
       <c r="R96" t="n">
-        <v>6374071</v>
+        <v>6374226</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10249,7 +10249,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10286,32 +10286,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128738839</v>
+        <v>128806038</v>
       </c>
       <c r="B97" t="n">
-        <v>86999</v>
+        <v>98647</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3767</v>
+        <v>219862</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10321,10 +10321,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>717039</v>
+        <v>717113</v>
       </c>
       <c r="R97" t="n">
-        <v>6374168</v>
+        <v>6374105</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10351,22 +10351,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>10:24</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>10:24</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10381,22 +10371,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128806038</v>
+        <v>128815850</v>
       </c>
       <c r="B98" t="n">
-        <v>98641</v>
+        <v>89477</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10404,21 +10394,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>219862</v>
+        <v>236437</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Brun klibbskivling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Limacella glioderma</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Maire</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10428,10 +10418,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>717113</v>
+        <v>716975</v>
       </c>
       <c r="R98" t="n">
-        <v>6374105</v>
+        <v>6374071</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10458,12 +10448,22 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10478,12 +10478,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -10493,7 +10493,7 @@
         <v>128806484</v>
       </c>
       <c r="B99" t="n">
-        <v>90969</v>
+        <v>90974</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>128806004</v>
       </c>
       <c r="B100" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10688,32 +10688,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128806005</v>
+        <v>128738866</v>
       </c>
       <c r="B101" t="n">
-        <v>91003</v>
+        <v>90240</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5741</v>
+        <v>970</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10723,10 +10723,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>717142</v>
+        <v>717039</v>
       </c>
       <c r="R101" t="n">
-        <v>6374197</v>
+        <v>6374321</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10753,12 +10753,22 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10767,28 +10777,29 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128806009</v>
+        <v>128738897</v>
       </c>
       <c r="B102" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10820,10 +10831,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>717132</v>
+        <v>717015</v>
       </c>
       <c r="R102" t="n">
-        <v>6374140</v>
+        <v>6374144</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10850,12 +10861,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10871,44 +10892,44 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128738866</v>
+        <v>128806005</v>
       </c>
       <c r="B103" t="n">
-        <v>90235</v>
+        <v>91008</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>970</v>
+        <v>5741</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10918,10 +10939,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>717039</v>
+        <v>717142</v>
       </c>
       <c r="R103" t="n">
-        <v>6374321</v>
+        <v>6374197</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10948,22 +10969,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>13:50</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>13:50</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10972,29 +10983,28 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128738897</v>
+        <v>128806009</v>
       </c>
       <c r="B104" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11026,10 +11036,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>717015</v>
+        <v>717132</v>
       </c>
       <c r="R104" t="n">
-        <v>6374144</v>
+        <v>6374140</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11056,22 +11066,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>10:05</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>10:05</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11087,12 +11087,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -11102,7 +11102,7 @@
         <v>128738842</v>
       </c>
       <c r="B105" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
         <v>128738875</v>
       </c>
       <c r="B106" t="n">
-        <v>87011</v>
+        <v>87015</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         <v>128805993</v>
       </c>
       <c r="B107" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
         <v>128738843</v>
       </c>
       <c r="B108" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11516,7 +11516,7 @@
         <v>128806056</v>
       </c>
       <c r="B109" t="n">
-        <v>106944</v>
+        <v>106950</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>128806010</v>
       </c>
       <c r="B110" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         <v>128806023</v>
       </c>
       <c r="B111" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11809,7 +11809,7 @@
         <v>128738840</v>
       </c>
       <c r="B112" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11913,32 +11913,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128806022</v>
+        <v>128806497</v>
       </c>
       <c r="B113" t="n">
-        <v>86954</v>
+        <v>86784</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11948,10 +11948,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>717284</v>
+        <v>717273</v>
       </c>
       <c r="R113" t="n">
-        <v>6374309</v>
+        <v>6374182</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11992,51 +11992,50 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128806497</v>
+        <v>128806022</v>
       </c>
       <c r="B114" t="n">
-        <v>86780</v>
+        <v>86958</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12046,10 +12045,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>717273</v>
+        <v>717284</v>
       </c>
       <c r="R114" t="n">
-        <v>6374182</v>
+        <v>6374309</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12090,18 +12089,19 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -12111,7 +12111,7 @@
         <v>128738886</v>
       </c>
       <c r="B115" t="n">
-        <v>86802</v>
+        <v>86806</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12215,32 +12215,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128806495</v>
+        <v>128806064</v>
       </c>
       <c r="B116" t="n">
-        <v>86842</v>
+        <v>86921</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>442</v>
+        <v>3674</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12250,10 +12250,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>717357</v>
+        <v>717299</v>
       </c>
       <c r="R116" t="n">
-        <v>6374169</v>
+        <v>6374300</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12300,42 +12300,46 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128806049</v>
+        <v>128738893</v>
       </c>
       <c r="B117" t="n">
-        <v>87011</v>
+        <v>86958</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -12343,10 +12347,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>717128</v>
+        <v>717000</v>
       </c>
       <c r="R117" t="n">
-        <v>6374123</v>
+        <v>6374121</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12373,12 +12377,22 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12387,50 +12401,51 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128806064</v>
+        <v>128806495</v>
       </c>
       <c r="B118" t="n">
-        <v>86917</v>
+        <v>86846</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3674</v>
+        <v>442</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12440,10 +12455,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>717299</v>
+        <v>717357</v>
       </c>
       <c r="R118" t="n">
-        <v>6374300</v>
+        <v>6374169</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12490,46 +12505,42 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128806043</v>
+        <v>128806049</v>
       </c>
       <c r="B119" t="n">
-        <v>75142</v>
+        <v>87015</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6426</v>
+        <v>433</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
@@ -12537,10 +12548,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>717359</v>
+        <v>717128</v>
       </c>
       <c r="R119" t="n">
-        <v>6374214</v>
+        <v>6374123</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12599,32 +12610,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128806050</v>
+        <v>128806043</v>
       </c>
       <c r="B120" t="n">
-        <v>86920</v>
+        <v>75143</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6037417</v>
+        <v>6426</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12634,10 +12645,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>717311</v>
+        <v>717359</v>
       </c>
       <c r="R120" t="n">
-        <v>6374287</v>
+        <v>6374214</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12678,7 +12689,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12697,10 +12707,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128738893</v>
+        <v>128806050</v>
       </c>
       <c r="B121" t="n">
-        <v>86954</v>
+        <v>86924</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12708,21 +12718,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6003295</v>
+        <v>6037417</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12732,10 +12742,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>717000</v>
+        <v>717311</v>
       </c>
       <c r="R121" t="n">
-        <v>6374121</v>
+        <v>6374287</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12762,22 +12772,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>10:04</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>10:04</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12793,44 +12793,44 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128806052</v>
+        <v>128738892</v>
       </c>
       <c r="B122" t="n">
-        <v>86780</v>
+        <v>86958</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12840,10 +12840,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>717284</v>
+        <v>717037</v>
       </c>
       <c r="R122" t="n">
-        <v>6374097</v>
+        <v>6374150</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12870,12 +12870,22 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12884,50 +12894,51 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128738892</v>
+        <v>128806052</v>
       </c>
       <c r="B123" t="n">
-        <v>86954</v>
+        <v>86784</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12937,10 +12948,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>717037</v>
+        <v>717284</v>
       </c>
       <c r="R123" t="n">
-        <v>6374150</v>
+        <v>6374097</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12967,22 +12978,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>10:16</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>10:16</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -12991,29 +12992,28 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128806045</v>
+        <v>128738882</v>
       </c>
       <c r="B124" t="n">
-        <v>86976</v>
+        <v>87085</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13021,34 +13021,37 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>449</v>
+        <v>3563</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Stor granspindling</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius bovinus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Fr. sl.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>717324</v>
+        <v>717013</v>
       </c>
       <c r="R124" t="n">
-        <v>6374179</v>
+        <v>6374226</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13075,12 +13078,22 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13089,50 +13102,51 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128806051</v>
+        <v>128738894</v>
       </c>
       <c r="B125" t="n">
-        <v>86780</v>
+        <v>86958</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13142,10 +13156,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>717327</v>
+        <v>716975</v>
       </c>
       <c r="R125" t="n">
-        <v>6374171</v>
+        <v>6374071</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13172,12 +13186,22 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13186,28 +13210,29 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128738882</v>
+        <v>128806045</v>
       </c>
       <c r="B126" t="n">
-        <v>87081</v>
+        <v>86980</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13215,37 +13240,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>3563</v>
+        <v>449</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Stor granspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cortinarius bovinus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Fr. sl.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>717013</v>
+        <v>717324</v>
       </c>
       <c r="R126" t="n">
-        <v>6374226</v>
+        <v>6374179</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13272,22 +13294,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>13:07</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>13:07</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13296,51 +13308,50 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128806011</v>
+        <v>128806051</v>
       </c>
       <c r="B127" t="n">
-        <v>86954</v>
+        <v>86784</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13350,10 +13361,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>717367</v>
+        <v>717327</v>
       </c>
       <c r="R127" t="n">
-        <v>6374231</v>
+        <v>6374171</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13394,7 +13405,6 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13406,17 +13416,17 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128738894</v>
+        <v>128806011</v>
       </c>
       <c r="B128" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13448,10 +13458,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>716975</v>
+        <v>717367</v>
       </c>
       <c r="R128" t="n">
-        <v>6374071</v>
+        <v>6374231</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13478,22 +13488,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>09:15</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>09:15</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13509,12 +13509,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -13524,7 +13524,7 @@
         <v>128806485</v>
       </c>
       <c r="B129" t="n">
-        <v>86780</v>
+        <v>86784</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13619,32 +13619,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128806492</v>
+        <v>128806491</v>
       </c>
       <c r="B130" t="n">
-        <v>91029</v>
+        <v>86958</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13654,10 +13654,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>717146</v>
+        <v>717324</v>
       </c>
       <c r="R130" t="n">
-        <v>6374178</v>
+        <v>6374171</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13698,6 +13698,7 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13716,32 +13717,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128806491</v>
+        <v>128806492</v>
       </c>
       <c r="B131" t="n">
-        <v>86954</v>
+        <v>91034</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6003295</v>
+        <v>5747</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13751,10 +13752,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>717324</v>
+        <v>717146</v>
       </c>
       <c r="R131" t="n">
-        <v>6374171</v>
+        <v>6374178</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13795,7 +13796,6 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -13817,7 +13817,7 @@
         <v>128806057</v>
       </c>
       <c r="B132" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13911,32 +13911,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128806058</v>
+        <v>128738847</v>
       </c>
       <c r="B133" t="n">
-        <v>86917</v>
+        <v>86874</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>3674</v>
+        <v>248956</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13946,10 +13946,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>717196</v>
+        <v>716980</v>
       </c>
       <c r="R133" t="n">
-        <v>6374281</v>
+        <v>6374264</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13976,12 +13976,22 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -13996,44 +14006,44 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128806487</v>
+        <v>128806058</v>
       </c>
       <c r="B134" t="n">
-        <v>86999</v>
+        <v>86921</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14043,10 +14053,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>717275</v>
+        <v>717196</v>
       </c>
       <c r="R134" t="n">
-        <v>6374183</v>
+        <v>6374281</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14093,22 +14103,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128738847</v>
+        <v>128806487</v>
       </c>
       <c r="B135" t="n">
-        <v>86870</v>
+        <v>87003</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14116,21 +14126,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>248956</v>
+        <v>3767</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14140,10 +14150,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>716980</v>
+        <v>717275</v>
       </c>
       <c r="R135" t="n">
-        <v>6374264</v>
+        <v>6374183</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14170,22 +14180,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14200,12 +14200,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -14215,7 +14215,7 @@
         <v>128806490</v>
       </c>
       <c r="B136" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         <v>128806013</v>
       </c>
       <c r="B137" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14411,7 +14411,7 @@
         <v>128806065</v>
       </c>
       <c r="B138" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14508,7 +14508,7 @@
         <v>128806486</v>
       </c>
       <c r="B139" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14602,32 +14602,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128738883</v>
+        <v>128806024</v>
       </c>
       <c r="B140" t="n">
-        <v>86818</v>
+        <v>86958</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>3561</v>
+        <v>6003295</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Blåbandad spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cortinarius borgsjoeensis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14637,10 +14637,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>716993</v>
+        <v>717366</v>
       </c>
       <c r="R140" t="n">
-        <v>6374384</v>
+        <v>6374150</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14667,22 +14667,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14698,44 +14688,44 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128806496</v>
+        <v>128738883</v>
       </c>
       <c r="B141" t="n">
-        <v>96215</v>
+        <v>86822</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2180</v>
+        <v>3561</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blåbandad spindling</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cortinarius borgsjoeensis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14745,10 +14735,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>717337</v>
+        <v>716993</v>
       </c>
       <c r="R141" t="n">
-        <v>6374082</v>
+        <v>6374384</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14775,12 +14765,22 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14789,50 +14789,51 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128805991</v>
+        <v>128806496</v>
       </c>
       <c r="B142" t="n">
-        <v>86999</v>
+        <v>96221</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>3767</v>
+        <v>2180</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14842,10 +14843,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>717147</v>
+        <v>717337</v>
       </c>
       <c r="R142" t="n">
-        <v>6374164</v>
+        <v>6374082</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14892,44 +14893,44 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128806024</v>
+        <v>128805991</v>
       </c>
       <c r="B143" t="n">
-        <v>86954</v>
+        <v>87003</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14939,10 +14940,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>717366</v>
+        <v>717147</v>
       </c>
       <c r="R143" t="n">
-        <v>6374150</v>
+        <v>6374164</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14983,7 +14984,6 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -14995,7 +14995,7 @@
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
@@ -15005,7 +15005,7 @@
         <v>128738867</v>
       </c>
       <c r="B144" t="n">
-        <v>86976</v>
+        <v>86980</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 42607-2025 artfynd.xlsx
+++ b/artfynd/A 42607-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128740505</v>
+        <v>128738854</v>
       </c>
       <c r="B2" t="n">
-        <v>98647</v>
+        <v>86959</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219862</v>
+        <v>6003295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717182</v>
+        <v>716967</v>
       </c>
       <c r="R2" t="n">
-        <v>6374336</v>
+        <v>6374338</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,61 +743,72 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128738845</v>
+        <v>128740487</v>
       </c>
       <c r="B3" t="n">
-        <v>86760</v>
+        <v>86959</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716961</v>
+        <v>717292</v>
       </c>
       <c r="R3" t="n">
-        <v>6374255</v>
+        <v>6374265</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -840,49 +851,40 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128738831</v>
+        <v>128742256</v>
       </c>
       <c r="B4" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717030</v>
+        <v>717053</v>
       </c>
       <c r="R4" t="n">
-        <v>6374429</v>
+        <v>6374253</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -947,19 +949,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,22 +966,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128742256</v>
+        <v>128738831</v>
       </c>
       <c r="B5" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717053</v>
+        <v>717030</v>
       </c>
       <c r="R5" t="n">
-        <v>6374253</v>
+        <v>6374429</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,9 +1046,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,22 +1073,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128740514</v>
+        <v>128738845</v>
       </c>
       <c r="B6" t="n">
-        <v>86784</v>
+        <v>86760</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,21 +1096,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3712</v>
+        <v>3762</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1120,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717295</v>
+        <v>716961</v>
       </c>
       <c r="R6" t="n">
-        <v>6374249</v>
+        <v>6374255</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1151,9 +1153,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1168,44 +1180,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128738854</v>
+        <v>128740514</v>
       </c>
       <c r="B7" t="n">
-        <v>86958</v>
+        <v>86784</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1227,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716967</v>
+        <v>717295</v>
       </c>
       <c r="R7" t="n">
-        <v>6374338</v>
+        <v>6374249</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1248,72 +1260,61 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128740487</v>
+        <v>128740505</v>
       </c>
       <c r="B8" t="n">
-        <v>86958</v>
+        <v>98654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6003295</v>
+        <v>219862</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1323,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717292</v>
+        <v>717182</v>
       </c>
       <c r="R8" t="n">
-        <v>6374265</v>
+        <v>6374336</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,7 +1368,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>128738834</v>
       </c>
       <c r="B9" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>128738837</v>
       </c>
       <c r="B11" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>128738853</v>
       </c>
       <c r="B12" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,32 +1805,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128740482</v>
+        <v>128742285</v>
       </c>
       <c r="B13" t="n">
-        <v>87003</v>
+        <v>86959</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>717057</v>
+        <v>716995</v>
       </c>
       <c r="R13" t="n">
-        <v>6374457</v>
+        <v>6374141</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1884,63 +1884,67 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128740504</v>
+        <v>128742275</v>
       </c>
       <c r="B14" t="n">
-        <v>98647</v>
+        <v>86910</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219862</v>
+        <v>6003296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Stor odörspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius mussivus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Melot</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>717091</v>
+        <v>716983</v>
       </c>
       <c r="R14" t="n">
-        <v>6374400</v>
+        <v>6374138</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1975,56 +1979,62 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Kollekt taget för sekvensering av Martin Axegård.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128742285</v>
+        <v>128740504</v>
       </c>
       <c r="B15" t="n">
-        <v>86958</v>
+        <v>98654</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6003295</v>
+        <v>219862</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2034,10 +2044,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>716995</v>
+        <v>717091</v>
       </c>
       <c r="R15" t="n">
-        <v>6374141</v>
+        <v>6374400</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2078,29 +2088,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128742275</v>
+        <v>128740482</v>
       </c>
       <c r="B16" t="n">
-        <v>86909</v>
+        <v>87004</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2108,37 +2117,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6003296</v>
+        <v>3767</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>716983</v>
+        <v>717057</v>
       </c>
       <c r="R16" t="n">
-        <v>6374138</v>
+        <v>6374457</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2173,62 +2179,56 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Kollekt taget för sekvensering av Martin Axegård.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128738832</v>
+        <v>128738898</v>
       </c>
       <c r="B17" t="n">
-        <v>87003</v>
+        <v>86922</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>717000</v>
+        <v>716960</v>
       </c>
       <c r="R17" t="n">
-        <v>6374409</v>
+        <v>6374150</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2310,32 +2310,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128738898</v>
+        <v>128738832</v>
       </c>
       <c r="B18" t="n">
-        <v>86921</v>
+        <v>87004</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716960</v>
+        <v>717000</v>
       </c>
       <c r="R18" t="n">
-        <v>6374150</v>
+        <v>6374409</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2420,7 +2420,7 @@
         <v>128738859</v>
       </c>
       <c r="B19" t="n">
-        <v>98659</v>
+        <v>98666</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>128742286</v>
       </c>
       <c r="B20" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>128740498</v>
       </c>
       <c r="B21" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128738857</v>
+        <v>128738856</v>
       </c>
       <c r="B22" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>717049</v>
+        <v>716986</v>
       </c>
       <c r="R22" t="n">
-        <v>6374317</v>
+        <v>6374339</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2828,10 +2828,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128738856</v>
+        <v>128738857</v>
       </c>
       <c r="B23" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>716986</v>
+        <v>717049</v>
       </c>
       <c r="R23" t="n">
-        <v>6374339</v>
+        <v>6374317</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2936,10 +2936,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128742257</v>
+        <v>128740485</v>
       </c>
       <c r="B24" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>716992</v>
+        <v>717286</v>
       </c>
       <c r="R24" t="n">
-        <v>6374120</v>
+        <v>6374251</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,22 +3021,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128740485</v>
+        <v>128742258</v>
       </c>
       <c r="B25" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>717286</v>
+        <v>716976</v>
       </c>
       <c r="R25" t="n">
-        <v>6374251</v>
+        <v>6374072</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3118,22 +3118,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128742258</v>
+        <v>128742257</v>
       </c>
       <c r="B26" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>716976</v>
+        <v>716992</v>
       </c>
       <c r="R26" t="n">
-        <v>6374072</v>
+        <v>6374120</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,7 +3230,7 @@
         <v>128742273</v>
       </c>
       <c r="B27" t="n">
-        <v>86934</v>
+        <v>86935</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>128740489</v>
       </c>
       <c r="B28" t="n">
-        <v>91008</v>
+        <v>91013</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>128742283</v>
       </c>
       <c r="B29" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>128742281</v>
       </c>
       <c r="B30" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3617,32 +3617,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128742254</v>
+        <v>128742293</v>
       </c>
       <c r="B31" t="n">
-        <v>87003</v>
+        <v>86922</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3652,10 +3652,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>717285</v>
+        <v>717094</v>
       </c>
       <c r="R31" t="n">
-        <v>6374272</v>
+        <v>6374468</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3714,10 +3714,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128742272</v>
+        <v>128742254</v>
       </c>
       <c r="B32" t="n">
-        <v>91034</v>
+        <v>87004</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3725,21 +3725,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5747</v>
+        <v>3767</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3749,10 +3749,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>717018</v>
+        <v>717285</v>
       </c>
       <c r="R32" t="n">
-        <v>6374179</v>
+        <v>6374272</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3811,32 +3811,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128742293</v>
+        <v>128740500</v>
       </c>
       <c r="B33" t="n">
-        <v>86921</v>
+        <v>86959</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>717094</v>
+        <v>717281</v>
       </c>
       <c r="R33" t="n">
-        <v>6374468</v>
+        <v>6374283</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3890,28 +3890,29 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128740500</v>
+        <v>128740502</v>
       </c>
       <c r="B34" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3943,10 +3944,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>717281</v>
+        <v>717282</v>
       </c>
       <c r="R34" t="n">
-        <v>6374283</v>
+        <v>6374266</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4009,7 +4010,7 @@
         <v>128740499</v>
       </c>
       <c r="B35" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4104,32 +4105,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128740502</v>
+        <v>128742272</v>
       </c>
       <c r="B36" t="n">
-        <v>86958</v>
+        <v>91039</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6003295</v>
+        <v>5747</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4139,10 +4140,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>717282</v>
+        <v>717018</v>
       </c>
       <c r="R36" t="n">
-        <v>6374266</v>
+        <v>6374179</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4183,51 +4184,50 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128738858</v>
+        <v>128740521</v>
       </c>
       <c r="B37" t="n">
-        <v>86958</v>
+        <v>86922</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4237,10 +4237,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>717003</v>
+        <v>717216</v>
       </c>
       <c r="R37" t="n">
-        <v>6374177</v>
+        <v>6374357</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4270,50 +4270,39 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128740521</v>
+        <v>128738900</v>
       </c>
       <c r="B38" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4345,10 +4334,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>717216</v>
+        <v>716960</v>
       </c>
       <c r="R38" t="n">
-        <v>6374357</v>
+        <v>6374079</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4378,9 +4367,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4395,44 +4394,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128738900</v>
+        <v>128738858</v>
       </c>
       <c r="B39" t="n">
-        <v>86921</v>
+        <v>86959</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4442,10 +4441,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>716960</v>
+        <v>717003</v>
       </c>
       <c r="R39" t="n">
-        <v>6374079</v>
+        <v>6374177</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4477,7 +4476,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4487,7 +4486,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4496,6 +4495,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4517,7 +4517,7 @@
         <v>128742267</v>
       </c>
       <c r="B40" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4612,10 +4612,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128742259</v>
+        <v>128740509</v>
       </c>
       <c r="B41" t="n">
-        <v>87003</v>
+        <v>86981</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4623,21 +4623,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4647,10 +4647,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>716980</v>
+        <v>717258</v>
       </c>
       <c r="R41" t="n">
-        <v>6374067</v>
+        <v>6374286</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4697,22 +4697,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128740509</v>
+        <v>128738887</v>
       </c>
       <c r="B42" t="n">
-        <v>86980</v>
+        <v>86806</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4720,21 +4720,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>449</v>
+        <v>424</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4744,10 +4744,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>717258</v>
+        <v>716984</v>
       </c>
       <c r="R42" t="n">
-        <v>6374286</v>
+        <v>6374264</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4777,9 +4777,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4794,22 +4804,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128738887</v>
+        <v>128742259</v>
       </c>
       <c r="B43" t="n">
-        <v>86806</v>
+        <v>87004</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4817,21 +4827,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>424</v>
+        <v>3767</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4841,10 +4851,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>716984</v>
+        <v>716980</v>
       </c>
       <c r="R43" t="n">
-        <v>6374264</v>
+        <v>6374067</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4874,19 +4884,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>12:19</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4901,22 +4901,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128738895</v>
+        <v>128742268</v>
       </c>
       <c r="B44" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4948,10 +4948,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>716974</v>
+        <v>717267</v>
       </c>
       <c r="R44" t="n">
-        <v>6374284</v>
+        <v>6374322</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4981,19 +4981,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5009,22 +4999,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128742268</v>
+        <v>128738895</v>
       </c>
       <c r="B45" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5056,10 +5046,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>717267</v>
+        <v>716974</v>
       </c>
       <c r="R45" t="n">
-        <v>6374322</v>
+        <v>6374284</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5089,9 +5079,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5107,12 +5107,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5122,7 +5122,7 @@
         <v>128742280</v>
       </c>
       <c r="B46" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5217,32 +5217,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128738880</v>
+        <v>128738838</v>
       </c>
       <c r="B47" t="n">
-        <v>86784</v>
+        <v>87004</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3712</v>
+        <v>3767</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5252,10 +5252,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>716983</v>
+        <v>717020</v>
       </c>
       <c r="R47" t="n">
-        <v>6374266</v>
+        <v>6374199</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5324,32 +5324,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128738838</v>
+        <v>128738880</v>
       </c>
       <c r="B48" t="n">
-        <v>87003</v>
+        <v>86784</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3767</v>
+        <v>3712</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5359,10 +5359,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>717020</v>
+        <v>716983</v>
       </c>
       <c r="R48" t="n">
-        <v>6374199</v>
+        <v>6374266</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5434,7 +5434,7 @@
         <v>128742289</v>
       </c>
       <c r="B49" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5529,10 +5529,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128742269</v>
+        <v>128742279</v>
       </c>
       <c r="B50" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5564,10 +5564,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>717186</v>
+        <v>717013</v>
       </c>
       <c r="R50" t="n">
-        <v>6374129</v>
+        <v>6374176</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5627,10 +5627,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128742279</v>
+        <v>128742269</v>
       </c>
       <c r="B51" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>717013</v>
+        <v>717186</v>
       </c>
       <c r="R51" t="n">
-        <v>6374176</v>
+        <v>6374129</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5728,7 +5728,7 @@
         <v>128742288</v>
       </c>
       <c r="B52" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>128738896</v>
       </c>
       <c r="B53" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5931,10 +5931,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128742291</v>
+        <v>128742284</v>
       </c>
       <c r="B54" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5966,10 +5966,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>716977</v>
+        <v>717033</v>
       </c>
       <c r="R54" t="n">
-        <v>6374073</v>
+        <v>6374186</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6029,10 +6029,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128742284</v>
+        <v>128742291</v>
       </c>
       <c r="B55" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6064,10 +6064,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>717033</v>
+        <v>716977</v>
       </c>
       <c r="R55" t="n">
-        <v>6374186</v>
+        <v>6374073</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6130,7 +6130,7 @@
         <v>128738841</v>
       </c>
       <c r="B56" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>128738835</v>
       </c>
       <c r="B57" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>128742252</v>
       </c>
       <c r="B58" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>128742263</v>
       </c>
       <c r="B59" t="n">
-        <v>91008</v>
+        <v>91013</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>128740522</v>
       </c>
       <c r="B60" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         <v>128742282</v>
       </c>
       <c r="B61" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6730,32 +6730,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128740491</v>
+        <v>128742276</v>
       </c>
       <c r="B62" t="n">
-        <v>86760</v>
+        <v>86981</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3762</v>
+        <v>449</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6765,10 +6765,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>717281</v>
+        <v>717269</v>
       </c>
       <c r="R62" t="n">
-        <v>6374215</v>
+        <v>6374317</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6815,22 +6815,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128742255</v>
+        <v>128738884</v>
       </c>
       <c r="B63" t="n">
-        <v>87003</v>
+        <v>86806</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6838,21 +6838,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3767</v>
+        <v>424</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6862,10 +6862,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>717059</v>
+        <v>716969</v>
       </c>
       <c r="R63" t="n">
-        <v>6374329</v>
+        <v>6374310</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6895,9 +6895,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6912,44 +6922,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128738848</v>
+        <v>128740491</v>
       </c>
       <c r="B64" t="n">
-        <v>57713</v>
+        <v>86760</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>3762</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6959,10 +6969,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>717165</v>
+        <v>717281</v>
       </c>
       <c r="R64" t="n">
-        <v>6374351</v>
+        <v>6374215</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6992,19 +7002,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>10:25</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7019,22 +7019,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128742276</v>
+        <v>128742255</v>
       </c>
       <c r="B65" t="n">
-        <v>86980</v>
+        <v>87004</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7042,21 +7042,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7066,10 +7066,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>717269</v>
+        <v>717059</v>
       </c>
       <c r="R65" t="n">
-        <v>6374317</v>
+        <v>6374329</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7128,32 +7128,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128738884</v>
+        <v>128738848</v>
       </c>
       <c r="B66" t="n">
-        <v>86806</v>
+        <v>57713</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>424</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7163,10 +7163,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>716969</v>
+        <v>717165</v>
       </c>
       <c r="R66" t="n">
-        <v>6374310</v>
+        <v>6374351</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7235,10 +7235,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128738851</v>
+        <v>128740512</v>
       </c>
       <c r="B67" t="n">
-        <v>86760</v>
+        <v>86784</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7246,21 +7246,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7270,10 +7270,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>717040</v>
+        <v>717079</v>
       </c>
       <c r="R67" t="n">
-        <v>6374229</v>
+        <v>6374436</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7303,19 +7303,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7330,22 +7320,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128740512</v>
+        <v>128738851</v>
       </c>
       <c r="B68" t="n">
-        <v>86784</v>
+        <v>86760</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7353,21 +7343,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3712</v>
+        <v>3762</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7377,10 +7367,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>717079</v>
+        <v>717040</v>
       </c>
       <c r="R68" t="n">
-        <v>6374436</v>
+        <v>6374229</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7410,9 +7400,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7427,12 +7427,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7442,7 +7442,7 @@
         <v>128738836</v>
       </c>
       <c r="B69" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         <v>128738855</v>
       </c>
       <c r="B70" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>128738852</v>
       </c>
       <c r="B71" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7762,32 +7762,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128742287</v>
+        <v>128740508</v>
       </c>
       <c r="B72" t="n">
-        <v>86958</v>
+        <v>86981</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7797,10 +7797,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>717013</v>
+        <v>717063</v>
       </c>
       <c r="R72" t="n">
-        <v>6374166</v>
+        <v>6374397</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7841,51 +7841,50 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128742270</v>
+        <v>128740519</v>
       </c>
       <c r="B73" t="n">
-        <v>86958</v>
+        <v>86922</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7895,10 +7894,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>717071</v>
+        <v>717067</v>
       </c>
       <c r="R73" t="n">
-        <v>6374305</v>
+        <v>6374399</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7939,29 +7938,28 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128742290</v>
+        <v>128742287</v>
       </c>
       <c r="B74" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7993,10 +7991,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>716979</v>
+        <v>717013</v>
       </c>
       <c r="R74" t="n">
-        <v>6374069</v>
+        <v>6374166</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8056,32 +8054,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128742251</v>
+        <v>128742290</v>
       </c>
       <c r="B75" t="n">
-        <v>87003</v>
+        <v>86959</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8091,10 +8089,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>717106</v>
+        <v>716979</v>
       </c>
       <c r="R75" t="n">
-        <v>6374415</v>
+        <v>6374069</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8135,6 +8133,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8153,32 +8152,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128738833</v>
+        <v>128742270</v>
       </c>
       <c r="B76" t="n">
-        <v>87003</v>
+        <v>86959</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8188,10 +8187,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>716976</v>
+        <v>717071</v>
       </c>
       <c r="R76" t="n">
-        <v>6374331</v>
+        <v>6374305</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8221,49 +8220,40 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128740508</v>
+        <v>128742251</v>
       </c>
       <c r="B77" t="n">
-        <v>86980</v>
+        <v>87004</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8271,21 +8261,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8295,10 +8285,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>717063</v>
+        <v>717106</v>
       </c>
       <c r="R77" t="n">
-        <v>6374397</v>
+        <v>6374415</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8345,44 +8335,44 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128740519</v>
+        <v>128738833</v>
       </c>
       <c r="B78" t="n">
-        <v>86921</v>
+        <v>87004</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8392,10 +8382,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>717067</v>
+        <v>716976</v>
       </c>
       <c r="R78" t="n">
-        <v>6374399</v>
+        <v>6374331</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8425,9 +8415,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8442,12 +8442,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8457,7 +8457,7 @@
         <v>128740516</v>
       </c>
       <c r="B79" t="n">
-        <v>92131</v>
+        <v>92136</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>128738891</v>
       </c>
       <c r="B80" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>128738890</v>
       </c>
       <c r="B81" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8767,32 +8767,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128740484</v>
+        <v>128740510</v>
       </c>
       <c r="B82" t="n">
-        <v>87003</v>
+        <v>86925</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3767</v>
+        <v>6037417</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8802,10 +8802,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>717279</v>
+        <v>717105</v>
       </c>
       <c r="R82" t="n">
-        <v>6374209</v>
+        <v>6374479</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8864,32 +8864,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128740518</v>
+        <v>128740503</v>
       </c>
       <c r="B83" t="n">
-        <v>86921</v>
+        <v>86959</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8899,10 +8899,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>717062</v>
+        <v>717212</v>
       </c>
       <c r="R83" t="n">
-        <v>6374393</v>
+        <v>6374189</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8943,6 +8943,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -8954,39 +8955,39 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128740503</v>
+        <v>128740518</v>
       </c>
       <c r="B84" t="n">
-        <v>86958</v>
+        <v>86922</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8996,10 +8997,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>717212</v>
+        <v>717062</v>
       </c>
       <c r="R84" t="n">
-        <v>6374189</v>
+        <v>6374393</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9040,7 +9041,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9052,39 +9052,39 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128740510</v>
+        <v>128740484</v>
       </c>
       <c r="B85" t="n">
-        <v>86924</v>
+        <v>87004</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6037417</v>
+        <v>3767</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9094,10 +9094,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>717105</v>
+        <v>717279</v>
       </c>
       <c r="R85" t="n">
-        <v>6374479</v>
+        <v>6374209</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9159,7 +9159,7 @@
         <v>128738899</v>
       </c>
       <c r="B86" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>128806499</v>
       </c>
       <c r="B87" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9360,10 +9360,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128806483</v>
+        <v>128815957</v>
       </c>
       <c r="B88" t="n">
-        <v>90974</v>
+        <v>86976</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9371,21 +9371,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>720</v>
+        <v>248934</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Knölfotad bananspindling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Cortinarius stjernegaardii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>Brandrud &amp; Frøslev</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9398,10 +9398,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>717267</v>
+        <v>717020</v>
       </c>
       <c r="R88" t="n">
-        <v>6374381</v>
+        <v>6374147</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9428,12 +9428,27 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Bilddokumentation av Ullas fynd. Uppsvullen bulb och orange basalmycel. Ek fanss på fyndplatsen som domineras av kalktallskog.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9449,22 +9464,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128815957</v>
+        <v>128806483</v>
       </c>
       <c r="B89" t="n">
-        <v>86975</v>
+        <v>90979</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9472,21 +9487,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>248934</v>
+        <v>720</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knölfotad bananspindling</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius stjernegaardii</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Brandrud &amp; Frøslev</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9499,10 +9514,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>717020</v>
+        <v>717267</v>
       </c>
       <c r="R89" t="n">
-        <v>6374147</v>
+        <v>6374381</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9529,27 +9544,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>10:37</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Bilddokumentation av Ullas fynd. Uppsvullen bulb och orange basalmycel. Ek fanss på fyndplatsen som domineras av kalktallskog.</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9565,12 +9565,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -9684,10 +9684,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128805996</v>
+        <v>128806494</v>
       </c>
       <c r="B91" t="n">
-        <v>87003</v>
+        <v>86981</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9695,21 +9695,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9719,10 +9719,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>717308</v>
+        <v>717333</v>
       </c>
       <c r="R91" t="n">
-        <v>6374239</v>
+        <v>6374180</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9769,22 +9769,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128806494</v>
+        <v>128806493</v>
       </c>
       <c r="B92" t="n">
-        <v>86980</v>
+        <v>86981</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9816,10 +9816,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>717333</v>
+        <v>717133</v>
       </c>
       <c r="R92" t="n">
-        <v>6374180</v>
+        <v>6374199</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9878,10 +9878,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128806493</v>
+        <v>128805996</v>
       </c>
       <c r="B93" t="n">
-        <v>86980</v>
+        <v>87004</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9889,21 +9889,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9913,10 +9913,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>717133</v>
+        <v>717308</v>
       </c>
       <c r="R93" t="n">
-        <v>6374199</v>
+        <v>6374239</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9963,12 +9963,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -9978,7 +9978,7 @@
         <v>128738839</v>
       </c>
       <c r="B94" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10082,32 +10082,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128806044</v>
+        <v>128738846</v>
       </c>
       <c r="B95" t="n">
-        <v>86980</v>
+        <v>91013</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>449</v>
+        <v>5741</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10117,10 +10117,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>717148</v>
+        <v>717037</v>
       </c>
       <c r="R95" t="n">
-        <v>6374175</v>
+        <v>6374226</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10147,12 +10147,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10167,44 +10177,44 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128738846</v>
+        <v>128806044</v>
       </c>
       <c r="B96" t="n">
-        <v>91008</v>
+        <v>86981</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5741</v>
+        <v>449</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10214,10 +10224,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>717037</v>
+        <v>717148</v>
       </c>
       <c r="R96" t="n">
-        <v>6374226</v>
+        <v>6374175</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10244,22 +10254,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10274,12 +10274,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -10289,7 +10289,7 @@
         <v>128806038</v>
       </c>
       <c r="B97" t="n">
-        <v>98647</v>
+        <v>98654</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>128815850</v>
       </c>
       <c r="B98" t="n">
-        <v>89477</v>
+        <v>89482</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10490,48 +10490,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128806484</v>
+        <v>128806004</v>
       </c>
       <c r="B99" t="n">
-        <v>90974</v>
+        <v>91504</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>720</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>717273</v>
+        <v>717360</v>
       </c>
       <c r="R99" t="n">
-        <v>6374379</v>
+        <v>6374175</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10572,64 +10569,66 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128806004</v>
+        <v>128806484</v>
       </c>
       <c r="B100" t="n">
-        <v>91499</v>
+        <v>90979</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>720</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>717360</v>
+        <v>717273</v>
       </c>
       <c r="R100" t="n">
-        <v>6374175</v>
+        <v>6374379</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10670,28 +10669,29 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128738866</v>
+        <v>128806009</v>
       </c>
       <c r="B101" t="n">
-        <v>90240</v>
+        <v>86959</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10699,21 +10699,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>970</v>
+        <v>6003295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10723,10 +10723,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>717039</v>
+        <v>717132</v>
       </c>
       <c r="R101" t="n">
-        <v>6374321</v>
+        <v>6374140</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10753,22 +10753,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>13:50</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>13:50</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10784,44 +10774,44 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128738897</v>
+        <v>128806005</v>
       </c>
       <c r="B102" t="n">
-        <v>86958</v>
+        <v>91013</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6003295</v>
+        <v>5741</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10831,10 +10821,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>717015</v>
+        <v>717142</v>
       </c>
       <c r="R102" t="n">
-        <v>6374144</v>
+        <v>6374197</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10861,22 +10851,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>10:05</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>10:05</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10885,51 +10865,50 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128806005</v>
+        <v>128738866</v>
       </c>
       <c r="B103" t="n">
-        <v>91008</v>
+        <v>90245</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5741</v>
+        <v>970</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10939,10 +10918,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>717142</v>
+        <v>717039</v>
       </c>
       <c r="R103" t="n">
-        <v>6374197</v>
+        <v>6374321</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10969,12 +10948,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10983,28 +10972,29 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128806009</v>
+        <v>128738897</v>
       </c>
       <c r="B104" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11036,10 +11026,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>717132</v>
+        <v>717015</v>
       </c>
       <c r="R104" t="n">
-        <v>6374140</v>
+        <v>6374144</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11066,12 +11056,22 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11087,22 +11087,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128738842</v>
+        <v>128805993</v>
       </c>
       <c r="B105" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11134,10 +11134,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>716981</v>
+        <v>717148</v>
       </c>
       <c r="R105" t="n">
-        <v>6374088</v>
+        <v>6374174</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11164,22 +11164,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>09:31</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>09:31</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11194,12 +11184,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -11209,7 +11199,7 @@
         <v>128738875</v>
       </c>
       <c r="B106" t="n">
-        <v>87015</v>
+        <v>87016</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11309,10 +11299,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128805993</v>
+        <v>128738842</v>
       </c>
       <c r="B107" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11344,10 +11334,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>717148</v>
+        <v>716981</v>
       </c>
       <c r="R107" t="n">
-        <v>6374174</v>
+        <v>6374088</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11374,12 +11364,22 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11394,44 +11394,44 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128738843</v>
+        <v>128806056</v>
       </c>
       <c r="B108" t="n">
-        <v>87003</v>
+        <v>106957</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>3767</v>
+        <v>221849</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11441,10 +11441,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>716967</v>
+        <v>717370</v>
       </c>
       <c r="R108" t="n">
-        <v>6374084</v>
+        <v>6374168</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11471,22 +11471,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>09:26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>09:26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11501,44 +11491,44 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128806056</v>
+        <v>128738843</v>
       </c>
       <c r="B109" t="n">
-        <v>106950</v>
+        <v>87004</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221849</v>
+        <v>3767</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11548,10 +11538,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>717370</v>
+        <v>716967</v>
       </c>
       <c r="R109" t="n">
-        <v>6374168</v>
+        <v>6374084</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11578,12 +11568,22 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11598,12 +11598,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -11613,7 +11613,7 @@
         <v>128806010</v>
       </c>
       <c r="B110" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         <v>128806023</v>
       </c>
       <c r="B111" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11806,32 +11806,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128738840</v>
+        <v>128806497</v>
       </c>
       <c r="B112" t="n">
-        <v>87003</v>
+        <v>86784</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>3767</v>
+        <v>3712</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11841,10 +11841,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>717020</v>
+        <v>717273</v>
       </c>
       <c r="R112" t="n">
-        <v>6374147</v>
+        <v>6374182</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11871,22 +11871,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>10:06</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>10:06</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11901,44 +11891,44 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128806497</v>
+        <v>128738840</v>
       </c>
       <c r="B113" t="n">
-        <v>86784</v>
+        <v>87004</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>3712</v>
+        <v>3767</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11948,10 +11938,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>717273</v>
+        <v>717020</v>
       </c>
       <c r="R113" t="n">
-        <v>6374182</v>
+        <v>6374147</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11978,12 +11968,22 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11998,12 +11998,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
@@ -12013,7 +12013,7 @@
         <v>128806022</v>
       </c>
       <c r="B114" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12108,32 +12108,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128738886</v>
+        <v>128806064</v>
       </c>
       <c r="B115" t="n">
-        <v>86806</v>
+        <v>86922</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>424</v>
+        <v>3674</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12143,10 +12143,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>716990</v>
+        <v>717299</v>
       </c>
       <c r="R115" t="n">
-        <v>6374260</v>
+        <v>6374300</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12173,22 +12173,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12203,44 +12193,44 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128806064</v>
+        <v>128806495</v>
       </c>
       <c r="B116" t="n">
-        <v>86921</v>
+        <v>86846</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3674</v>
+        <v>442</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12250,10 +12240,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>717299</v>
+        <v>717357</v>
       </c>
       <c r="R116" t="n">
-        <v>6374300</v>
+        <v>6374169</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12300,46 +12290,42 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128738893</v>
+        <v>128806049</v>
       </c>
       <c r="B117" t="n">
-        <v>86958</v>
+        <v>87016</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -12347,10 +12333,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>717000</v>
+        <v>717128</v>
       </c>
       <c r="R117" t="n">
-        <v>6374121</v>
+        <v>6374123</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12377,22 +12363,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>10:04</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>10:04</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12401,51 +12377,50 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128806495</v>
+        <v>128806043</v>
       </c>
       <c r="B118" t="n">
-        <v>86846</v>
+        <v>75143</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>442</v>
+        <v>6426</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12455,10 +12430,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>717357</v>
+        <v>717359</v>
       </c>
       <c r="R118" t="n">
-        <v>6374169</v>
+        <v>6374214</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12505,22 +12480,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128806049</v>
+        <v>128738886</v>
       </c>
       <c r="B119" t="n">
-        <v>87015</v>
+        <v>86806</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12528,19 +12503,23 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
@@ -12548,10 +12527,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>717128</v>
+        <v>716990</v>
       </c>
       <c r="R119" t="n">
-        <v>6374123</v>
+        <v>6374260</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12578,12 +12557,22 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12598,44 +12587,44 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128806043</v>
+        <v>128806050</v>
       </c>
       <c r="B120" t="n">
-        <v>75143</v>
+        <v>86925</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6426</v>
+        <v>6037417</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12645,10 +12634,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>717359</v>
+        <v>717311</v>
       </c>
       <c r="R120" t="n">
-        <v>6374214</v>
+        <v>6374287</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12689,6 +12678,7 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12707,10 +12697,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128806050</v>
+        <v>128738893</v>
       </c>
       <c r="B121" t="n">
-        <v>86924</v>
+        <v>86959</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12718,21 +12708,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6037417</v>
+        <v>6003295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12742,10 +12732,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>717311</v>
+        <v>717000</v>
       </c>
       <c r="R121" t="n">
-        <v>6374287</v>
+        <v>6374121</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12772,12 +12762,22 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12793,12 +12793,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -12808,7 +12808,7 @@
         <v>128738892</v>
       </c>
       <c r="B122" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13010,48 +13010,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128738882</v>
+        <v>128806051</v>
       </c>
       <c r="B124" t="n">
-        <v>87085</v>
+        <v>86784</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>3563</v>
+        <v>3712</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Stor granspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cortinarius bovinus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Fr. sl.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>717013</v>
+        <v>717327</v>
       </c>
       <c r="R124" t="n">
-        <v>6374226</v>
+        <v>6374171</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13078,22 +13075,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>13:07</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>13:07</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13102,19 +13089,18 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -13124,7 +13110,7 @@
         <v>128738894</v>
       </c>
       <c r="B125" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13232,7 +13218,7 @@
         <v>128806045</v>
       </c>
       <c r="B126" t="n">
-        <v>86980</v>
+        <v>86981</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13326,45 +13312,48 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128806051</v>
+        <v>128738882</v>
       </c>
       <c r="B127" t="n">
-        <v>86784</v>
+        <v>87086</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>3712</v>
+        <v>3563</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Stor granspindling</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius bovinus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Fr. sl.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>717327</v>
+        <v>717013</v>
       </c>
       <c r="R127" t="n">
-        <v>6374171</v>
+        <v>6374226</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13391,12 +13380,22 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13405,18 +13404,19 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
@@ -13426,7 +13426,7 @@
         <v>128806011</v>
       </c>
       <c r="B128" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13619,32 +13619,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128806491</v>
+        <v>128806492</v>
       </c>
       <c r="B130" t="n">
-        <v>86958</v>
+        <v>91039</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6003295</v>
+        <v>5747</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13654,10 +13654,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>717324</v>
+        <v>717146</v>
       </c>
       <c r="R130" t="n">
-        <v>6374171</v>
+        <v>6374178</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13698,7 +13698,6 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13717,32 +13716,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128806492</v>
+        <v>128806491</v>
       </c>
       <c r="B131" t="n">
-        <v>91034</v>
+        <v>86959</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13752,10 +13751,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>717146</v>
+        <v>717324</v>
       </c>
       <c r="R131" t="n">
-        <v>6374178</v>
+        <v>6374171</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13796,6 +13795,7 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -13817,7 +13817,7 @@
         <v>128806057</v>
       </c>
       <c r="B132" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13911,32 +13911,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128738847</v>
+        <v>128806490</v>
       </c>
       <c r="B133" t="n">
-        <v>86874</v>
+        <v>86959</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13946,10 +13946,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>716980</v>
+        <v>717333</v>
       </c>
       <c r="R133" t="n">
-        <v>6374264</v>
+        <v>6374202</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13976,22 +13976,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14000,50 +13990,51 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128806058</v>
+        <v>128738847</v>
       </c>
       <c r="B134" t="n">
-        <v>86921</v>
+        <v>86875</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>3674</v>
+        <v>248956</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14053,10 +14044,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>717196</v>
+        <v>716980</v>
       </c>
       <c r="R134" t="n">
-        <v>6374281</v>
+        <v>6374264</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14083,12 +14074,22 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14103,44 +14104,44 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128806487</v>
+        <v>128806058</v>
       </c>
       <c r="B135" t="n">
-        <v>87003</v>
+        <v>86922</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14150,10 +14151,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>717275</v>
+        <v>717196</v>
       </c>
       <c r="R135" t="n">
-        <v>6374183</v>
+        <v>6374281</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14200,44 +14201,44 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128806490</v>
+        <v>128806487</v>
       </c>
       <c r="B136" t="n">
-        <v>86958</v>
+        <v>87004</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14247,10 +14248,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>717333</v>
+        <v>717275</v>
       </c>
       <c r="R136" t="n">
-        <v>6374202</v>
+        <v>6374183</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14291,7 +14292,6 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14313,7 +14313,7 @@
         <v>128806013</v>
       </c>
       <c r="B137" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14411,7 +14411,7 @@
         <v>128806065</v>
       </c>
       <c r="B138" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14508,7 +14508,7 @@
         <v>128806486</v>
       </c>
       <c r="B139" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14602,32 +14602,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128806024</v>
+        <v>128806496</v>
       </c>
       <c r="B140" t="n">
-        <v>86958</v>
+        <v>96228</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6003295</v>
+        <v>2180</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14637,10 +14637,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>717366</v>
+        <v>717337</v>
       </c>
       <c r="R140" t="n">
-        <v>6374150</v>
+        <v>6374082</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14681,29 +14681,28 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128738883</v>
+        <v>128805991</v>
       </c>
       <c r="B141" t="n">
-        <v>86822</v>
+        <v>87004</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14711,16 +14710,16 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3561</v>
+        <v>3767</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Blåbandad spindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cortinarius borgsjoeensis</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -14735,10 +14734,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>716993</v>
+        <v>717147</v>
       </c>
       <c r="R141" t="n">
-        <v>6374384</v>
+        <v>6374164</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14765,22 +14764,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14789,51 +14778,50 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128806496</v>
+        <v>128738883</v>
       </c>
       <c r="B142" t="n">
-        <v>96221</v>
+        <v>86822</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2180</v>
+        <v>3561</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blåbandad spindling</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cortinarius borgsjoeensis</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14843,10 +14831,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>717337</v>
+        <v>716993</v>
       </c>
       <c r="R142" t="n">
-        <v>6374082</v>
+        <v>6374384</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14873,12 +14861,22 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -14887,50 +14885,51 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128805991</v>
+        <v>128806024</v>
       </c>
       <c r="B143" t="n">
-        <v>87003</v>
+        <v>86959</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14940,10 +14939,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>717147</v>
+        <v>717366</v>
       </c>
       <c r="R143" t="n">
-        <v>6374164</v>
+        <v>6374150</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14984,6 +14983,7 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -14995,7 +14995,7 @@
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
@@ -15005,7 +15005,7 @@
         <v>128738867</v>
       </c>
       <c r="B144" t="n">
-        <v>86980</v>
+        <v>86981</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 42607-2025 artfynd.xlsx
+++ b/artfynd/A 42607-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128738854</v>
+        <v>128738845</v>
       </c>
       <c r="B2" t="n">
-        <v>86959</v>
+        <v>86760</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716967</v>
+        <v>716961</v>
       </c>
       <c r="R2" t="n">
-        <v>6374338</v>
+        <v>6374255</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,7 +764,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -783,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128740487</v>
+        <v>128738831</v>
       </c>
       <c r="B3" t="n">
-        <v>86959</v>
+        <v>87004</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -818,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717292</v>
+        <v>717030</v>
       </c>
       <c r="R3" t="n">
-        <v>6374265</v>
+        <v>6374429</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,30 +850,39 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -978,32 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128738831</v>
+        <v>128740514</v>
       </c>
       <c r="B5" t="n">
-        <v>87004</v>
+        <v>86784</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3767</v>
+        <v>3712</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717030</v>
+        <v>717295</v>
       </c>
       <c r="R5" t="n">
-        <v>6374429</v>
+        <v>6374249</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1046,19 +1054,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128738845</v>
+        <v>128740505</v>
       </c>
       <c r="B6" t="n">
-        <v>86760</v>
+        <v>98654</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1096,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3762</v>
+        <v>219862</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1120,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>716961</v>
+        <v>717182</v>
       </c>
       <c r="R6" t="n">
-        <v>6374255</v>
+        <v>6374336</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,19 +1151,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,44 +1168,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128740514</v>
+        <v>128738854</v>
       </c>
       <c r="B7" t="n">
-        <v>86784</v>
+        <v>86959</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1227,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717295</v>
+        <v>716967</v>
       </c>
       <c r="R7" t="n">
-        <v>6374249</v>
+        <v>6374338</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,61 +1248,72 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128740505</v>
+        <v>128740487</v>
       </c>
       <c r="B8" t="n">
-        <v>98654</v>
+        <v>86959</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219862</v>
+        <v>6003295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1323,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717182</v>
+        <v>717292</v>
       </c>
       <c r="R8" t="n">
-        <v>6374336</v>
+        <v>6374265</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,6 +1367,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1805,45 +1805,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128742285</v>
+        <v>128742275</v>
       </c>
       <c r="B13" t="n">
-        <v>86959</v>
+        <v>86910</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6003295</v>
+        <v>6003296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Stor odörspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius mussivus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.) Melot</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716995</v>
+        <v>716983</v>
       </c>
       <c r="R13" t="n">
-        <v>6374141</v>
+        <v>6374138</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,6 +1879,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Kollekt taget för sekvensering av Martin Axegård.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1903,10 +1911,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128742275</v>
+        <v>128740482</v>
       </c>
       <c r="B14" t="n">
-        <v>86910</v>
+        <v>87004</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1914,37 +1922,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6003296</v>
+        <v>3767</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716983</v>
+        <v>717057</v>
       </c>
       <c r="R14" t="n">
-        <v>6374138</v>
+        <v>6374457</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1979,62 +1984,56 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Kollekt taget för sekvensering av Martin Axegård.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128740504</v>
+        <v>128742285</v>
       </c>
       <c r="B15" t="n">
-        <v>98654</v>
+        <v>86959</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219862</v>
+        <v>6003295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2044,10 +2043,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>717091</v>
+        <v>716995</v>
       </c>
       <c r="R15" t="n">
-        <v>6374400</v>
+        <v>6374141</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2088,50 +2087,51 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128740482</v>
+        <v>128740504</v>
       </c>
       <c r="B16" t="n">
-        <v>87004</v>
+        <v>98654</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3767</v>
+        <v>219862</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2141,10 +2141,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>717057</v>
+        <v>717091</v>
       </c>
       <c r="R16" t="n">
-        <v>6374457</v>
+        <v>6374400</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128740485</v>
+        <v>128742257</v>
       </c>
       <c r="B24" t="n">
         <v>87004</v>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>717286</v>
+        <v>716992</v>
       </c>
       <c r="R24" t="n">
-        <v>6374251</v>
+        <v>6374120</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,19 +3021,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128742258</v>
+        <v>128740485</v>
       </c>
       <c r="B25" t="n">
         <v>87004</v>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>716976</v>
+        <v>717286</v>
       </c>
       <c r="R25" t="n">
-        <v>6374072</v>
+        <v>6374251</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3118,19 +3118,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128742257</v>
+        <v>128742258</v>
       </c>
       <c r="B26" t="n">
         <v>87004</v>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>716992</v>
+        <v>716976</v>
       </c>
       <c r="R26" t="n">
-        <v>6374120</v>
+        <v>6374072</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3227,32 +3227,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128742273</v>
+        <v>128742283</v>
       </c>
       <c r="B27" t="n">
-        <v>86935</v>
+        <v>86959</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1988</v>
+        <v>6003295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>717014</v>
+        <v>717040</v>
       </c>
       <c r="R27" t="n">
-        <v>6374164</v>
+        <v>6374195</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3306,6 +3306,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3324,32 +3325,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128740489</v>
+        <v>128742281</v>
       </c>
       <c r="B28" t="n">
-        <v>91013</v>
+        <v>86959</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5741</v>
+        <v>6003295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3359,10 +3360,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>717220</v>
+        <v>717039</v>
       </c>
       <c r="R28" t="n">
-        <v>6374302</v>
+        <v>6374227</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3403,50 +3404,51 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128742283</v>
+        <v>128742273</v>
       </c>
       <c r="B29" t="n">
-        <v>86959</v>
+        <v>86935</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6003295</v>
+        <v>1988</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3456,10 +3458,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>717040</v>
+        <v>717014</v>
       </c>
       <c r="R29" t="n">
-        <v>6374195</v>
+        <v>6374164</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3500,7 +3502,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3519,32 +3520,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128742281</v>
+        <v>128740489</v>
       </c>
       <c r="B30" t="n">
-        <v>86959</v>
+        <v>91013</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6003295</v>
+        <v>5741</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3554,10 +3555,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>717039</v>
+        <v>717220</v>
       </c>
       <c r="R30" t="n">
-        <v>6374227</v>
+        <v>6374302</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3598,51 +3599,50 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128742293</v>
+        <v>128742254</v>
       </c>
       <c r="B31" t="n">
-        <v>86922</v>
+        <v>87004</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3652,10 +3652,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>717094</v>
+        <v>717285</v>
       </c>
       <c r="R31" t="n">
-        <v>6374468</v>
+        <v>6374272</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3714,10 +3714,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128742254</v>
+        <v>128742272</v>
       </c>
       <c r="B32" t="n">
-        <v>87004</v>
+        <v>91039</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3725,21 +3725,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3767</v>
+        <v>5747</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3749,10 +3749,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>717285</v>
+        <v>717018</v>
       </c>
       <c r="R32" t="n">
-        <v>6374272</v>
+        <v>6374179</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3811,32 +3811,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128740500</v>
+        <v>128742293</v>
       </c>
       <c r="B33" t="n">
-        <v>86959</v>
+        <v>86922</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>717281</v>
+        <v>717094</v>
       </c>
       <c r="R33" t="n">
-        <v>6374283</v>
+        <v>6374468</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3890,26 +3890,25 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128740502</v>
+        <v>128740500</v>
       </c>
       <c r="B34" t="n">
         <v>86959</v>
@@ -3944,10 +3943,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>717282</v>
+        <v>717281</v>
       </c>
       <c r="R34" t="n">
-        <v>6374266</v>
+        <v>6374283</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4007,7 +4006,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128740499</v>
+        <v>128740502</v>
       </c>
       <c r="B35" t="n">
         <v>86959</v>
@@ -4042,10 +4041,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>717145</v>
+        <v>717282</v>
       </c>
       <c r="R35" t="n">
-        <v>6374308</v>
+        <v>6374266</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4105,32 +4104,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128742272</v>
+        <v>128740499</v>
       </c>
       <c r="B36" t="n">
-        <v>91039</v>
+        <v>86959</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4140,10 +4139,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>717018</v>
+        <v>717145</v>
       </c>
       <c r="R36" t="n">
-        <v>6374179</v>
+        <v>6374308</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4184,25 +4183,26 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128740521</v>
+        <v>128738900</v>
       </c>
       <c r="B37" t="n">
         <v>86922</v>
@@ -4237,10 +4237,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>717216</v>
+        <v>716960</v>
       </c>
       <c r="R37" t="n">
-        <v>6374357</v>
+        <v>6374079</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4270,9 +4270,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4287,19 +4297,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128738900</v>
+        <v>128740521</v>
       </c>
       <c r="B38" t="n">
         <v>86922</v>
@@ -4334,10 +4344,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>716960</v>
+        <v>717216</v>
       </c>
       <c r="R38" t="n">
-        <v>6374079</v>
+        <v>6374357</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4367,19 +4377,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>09:09</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>09:09</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4394,12 +4394,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -6127,32 +6127,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128738841</v>
+        <v>128742263</v>
       </c>
       <c r="B56" t="n">
-        <v>87004</v>
+        <v>91013</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3767</v>
+        <v>5741</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6162,10 +6162,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>716992</v>
+        <v>717281</v>
       </c>
       <c r="R56" t="n">
-        <v>6374116</v>
+        <v>6374199</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6195,19 +6195,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>09:50</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6222,44 +6212,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128738835</v>
+        <v>128740522</v>
       </c>
       <c r="B57" t="n">
-        <v>87004</v>
+        <v>86922</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6269,10 +6259,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>716983</v>
+        <v>717274</v>
       </c>
       <c r="R57" t="n">
-        <v>6374357</v>
+        <v>6374210</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6302,19 +6292,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>14:27</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6329,44 +6309,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128742252</v>
+        <v>128742282</v>
       </c>
       <c r="B58" t="n">
-        <v>87004</v>
+        <v>86959</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6376,10 +6356,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>717146</v>
+        <v>717040</v>
       </c>
       <c r="R58" t="n">
-        <v>6374313</v>
+        <v>6374212</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6420,6 +6400,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6438,32 +6419,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128742263</v>
+        <v>128738841</v>
       </c>
       <c r="B59" t="n">
-        <v>91013</v>
+        <v>87004</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5741</v>
+        <v>3767</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6473,10 +6454,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>717281</v>
+        <v>716992</v>
       </c>
       <c r="R59" t="n">
-        <v>6374199</v>
+        <v>6374116</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6506,9 +6487,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6523,44 +6514,44 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128740522</v>
+        <v>128738835</v>
       </c>
       <c r="B60" t="n">
-        <v>86922</v>
+        <v>87004</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6570,10 +6561,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>717274</v>
+        <v>716983</v>
       </c>
       <c r="R60" t="n">
-        <v>6374210</v>
+        <v>6374357</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6603,9 +6594,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6620,44 +6621,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128742282</v>
+        <v>128742252</v>
       </c>
       <c r="B61" t="n">
-        <v>86959</v>
+        <v>87004</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6667,10 +6668,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>717040</v>
+        <v>717146</v>
       </c>
       <c r="R61" t="n">
-        <v>6374212</v>
+        <v>6374313</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6711,7 +6712,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7235,10 +7235,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128740512</v>
+        <v>128738851</v>
       </c>
       <c r="B67" t="n">
-        <v>86784</v>
+        <v>86760</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7246,21 +7246,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3712</v>
+        <v>3762</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7270,10 +7270,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>717079</v>
+        <v>717040</v>
       </c>
       <c r="R67" t="n">
-        <v>6374436</v>
+        <v>6374229</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7303,9 +7303,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7320,22 +7330,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128738851</v>
+        <v>128740512</v>
       </c>
       <c r="B68" t="n">
-        <v>86760</v>
+        <v>86784</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7343,21 +7353,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7367,10 +7377,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>717040</v>
+        <v>717079</v>
       </c>
       <c r="R68" t="n">
-        <v>6374229</v>
+        <v>6374436</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7400,19 +7410,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7427,12 +7427,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7762,32 +7762,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128740508</v>
+        <v>128742287</v>
       </c>
       <c r="B72" t="n">
-        <v>86981</v>
+        <v>86959</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7797,10 +7797,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>717063</v>
+        <v>717013</v>
       </c>
       <c r="R72" t="n">
-        <v>6374397</v>
+        <v>6374166</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7841,50 +7841,51 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128740519</v>
+        <v>128740508</v>
       </c>
       <c r="B73" t="n">
-        <v>86922</v>
+        <v>86981</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7894,10 +7895,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>717067</v>
+        <v>717063</v>
       </c>
       <c r="R73" t="n">
-        <v>6374399</v>
+        <v>6374397</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7949,39 +7950,39 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128742287</v>
+        <v>128742251</v>
       </c>
       <c r="B74" t="n">
-        <v>86959</v>
+        <v>87004</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7991,10 +7992,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>717013</v>
+        <v>717106</v>
       </c>
       <c r="R74" t="n">
-        <v>6374166</v>
+        <v>6374415</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8035,7 +8036,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8054,32 +8054,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128742290</v>
+        <v>128738833</v>
       </c>
       <c r="B75" t="n">
-        <v>86959</v>
+        <v>87004</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8089,10 +8089,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>716979</v>
+        <v>716976</v>
       </c>
       <c r="R75" t="n">
-        <v>6374069</v>
+        <v>6374331</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8122,62 +8122,71 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128742270</v>
+        <v>128740519</v>
       </c>
       <c r="B76" t="n">
-        <v>86959</v>
+        <v>86922</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8187,10 +8196,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>717071</v>
+        <v>717067</v>
       </c>
       <c r="R76" t="n">
-        <v>6374305</v>
+        <v>6374399</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8231,51 +8240,50 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128742251</v>
+        <v>128742290</v>
       </c>
       <c r="B77" t="n">
-        <v>87004</v>
+        <v>86959</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8285,10 +8293,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>717106</v>
+        <v>716979</v>
       </c>
       <c r="R77" t="n">
-        <v>6374415</v>
+        <v>6374069</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8329,6 +8337,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8347,32 +8356,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128738833</v>
+        <v>128742270</v>
       </c>
       <c r="B78" t="n">
-        <v>87004</v>
+        <v>86959</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8382,10 +8391,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>716976</v>
+        <v>717071</v>
       </c>
       <c r="R78" t="n">
-        <v>6374331</v>
+        <v>6374305</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8415,39 +8424,30 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8767,32 +8767,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128740510</v>
+        <v>128740484</v>
       </c>
       <c r="B82" t="n">
-        <v>86925</v>
+        <v>87004</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6037417</v>
+        <v>3767</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8802,10 +8802,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>717105</v>
+        <v>717279</v>
       </c>
       <c r="R82" t="n">
-        <v>6374479</v>
+        <v>6374209</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8864,32 +8864,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128740503</v>
+        <v>128740518</v>
       </c>
       <c r="B83" t="n">
-        <v>86959</v>
+        <v>86922</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8899,10 +8899,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>717212</v>
+        <v>717062</v>
       </c>
       <c r="R83" t="n">
-        <v>6374189</v>
+        <v>6374393</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8943,7 +8943,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -8955,39 +8954,39 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128740518</v>
+        <v>128740510</v>
       </c>
       <c r="B84" t="n">
-        <v>86922</v>
+        <v>86925</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3674</v>
+        <v>6037417</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8997,10 +8996,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>717062</v>
+        <v>717105</v>
       </c>
       <c r="R84" t="n">
-        <v>6374393</v>
+        <v>6374479</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9052,39 +9051,39 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128740484</v>
+        <v>128740503</v>
       </c>
       <c r="B85" t="n">
-        <v>87004</v>
+        <v>86959</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9094,10 +9093,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>717279</v>
+        <v>717212</v>
       </c>
       <c r="R85" t="n">
-        <v>6374209</v>
+        <v>6374189</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9138,6 +9137,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9360,10 +9360,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128815957</v>
+        <v>128806483</v>
       </c>
       <c r="B88" t="n">
-        <v>86976</v>
+        <v>90979</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9371,21 +9371,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>248934</v>
+        <v>720</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knölfotad bananspindling</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cortinarius stjernegaardii</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Brandrud &amp; Frøslev</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9398,10 +9398,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>717020</v>
+        <v>717267</v>
       </c>
       <c r="R88" t="n">
-        <v>6374147</v>
+        <v>6374381</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9428,27 +9428,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>10:37</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Bilddokumentation av Ullas fynd. Uppsvullen bulb och orange basalmycel. Ek fanss på fyndplatsen som domineras av kalktallskog.</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9464,22 +9449,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128806483</v>
+        <v>128815957</v>
       </c>
       <c r="B89" t="n">
-        <v>90979</v>
+        <v>86976</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9487,21 +9472,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>720</v>
+        <v>248934</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Knölfotad bananspindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Cortinarius stjernegaardii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>Brandrud &amp; Frøslev</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9514,10 +9499,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>717267</v>
+        <v>717020</v>
       </c>
       <c r="R89" t="n">
-        <v>6374381</v>
+        <v>6374147</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9544,12 +9529,27 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Bilddokumentation av Ullas fynd. Uppsvullen bulb och orange basalmycel. Ek fanss på fyndplatsen som domineras av kalktallskog.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9565,12 +9565,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -9684,10 +9684,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128806494</v>
+        <v>128805996</v>
       </c>
       <c r="B91" t="n">
-        <v>86981</v>
+        <v>87004</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9695,21 +9695,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9719,10 +9719,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>717333</v>
+        <v>717308</v>
       </c>
       <c r="R91" t="n">
-        <v>6374180</v>
+        <v>6374239</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9769,12 +9769,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -9878,10 +9878,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128805996</v>
+        <v>128806494</v>
       </c>
       <c r="B93" t="n">
-        <v>87004</v>
+        <v>86981</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9889,21 +9889,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9913,10 +9913,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>717308</v>
+        <v>717333</v>
       </c>
       <c r="R93" t="n">
-        <v>6374239</v>
+        <v>6374180</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9963,12 +9963,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -10082,10 +10082,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128738846</v>
+        <v>128806038</v>
       </c>
       <c r="B95" t="n">
-        <v>91013</v>
+        <v>98654</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10093,21 +10093,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5741</v>
+        <v>219862</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10117,10 +10117,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>717037</v>
+        <v>717113</v>
       </c>
       <c r="R95" t="n">
-        <v>6374226</v>
+        <v>6374105</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10147,22 +10147,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10177,12 +10167,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -10286,10 +10276,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128806038</v>
+        <v>128738846</v>
       </c>
       <c r="B97" t="n">
-        <v>98654</v>
+        <v>91013</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10297,21 +10287,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>219862</v>
+        <v>5741</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10321,10 +10311,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>717113</v>
+        <v>717037</v>
       </c>
       <c r="R97" t="n">
-        <v>6374105</v>
+        <v>6374226</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10351,12 +10341,22 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10371,12 +10371,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -10490,45 +10490,48 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128806004</v>
+        <v>128806484</v>
       </c>
       <c r="B99" t="n">
-        <v>91504</v>
+        <v>90979</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>720</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>717360</v>
+        <v>717273</v>
       </c>
       <c r="R99" t="n">
-        <v>6374175</v>
+        <v>6374379</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10569,66 +10572,64 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128806484</v>
+        <v>128806004</v>
       </c>
       <c r="B100" t="n">
-        <v>90979</v>
+        <v>91504</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>720</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>717273</v>
+        <v>717360</v>
       </c>
       <c r="R100" t="n">
-        <v>6374379</v>
+        <v>6374175</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10669,19 +10670,18 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11406,32 +11406,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128806056</v>
+        <v>128738843</v>
       </c>
       <c r="B108" t="n">
-        <v>106957</v>
+        <v>87004</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221849</v>
+        <v>3767</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11441,10 +11441,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>717370</v>
+        <v>716967</v>
       </c>
       <c r="R108" t="n">
-        <v>6374168</v>
+        <v>6374084</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11471,12 +11471,22 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11491,44 +11501,44 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128738843</v>
+        <v>128806056</v>
       </c>
       <c r="B109" t="n">
-        <v>87004</v>
+        <v>106957</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>3767</v>
+        <v>221849</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11538,10 +11548,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>716967</v>
+        <v>717370</v>
       </c>
       <c r="R109" t="n">
-        <v>6374084</v>
+        <v>6374168</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11568,22 +11578,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>09:26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>09:26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11598,12 +11598,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -11806,32 +11806,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128806497</v>
+        <v>128806022</v>
       </c>
       <c r="B112" t="n">
-        <v>86784</v>
+        <v>86959</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11841,10 +11841,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>717273</v>
+        <v>717284</v>
       </c>
       <c r="R112" t="n">
-        <v>6374182</v>
+        <v>6374309</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11885,50 +11885,51 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128738840</v>
+        <v>128806497</v>
       </c>
       <c r="B113" t="n">
-        <v>87004</v>
+        <v>86784</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>3767</v>
+        <v>3712</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11938,10 +11939,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>717020</v>
+        <v>717273</v>
       </c>
       <c r="R113" t="n">
-        <v>6374147</v>
+        <v>6374182</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11968,22 +11969,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>10:06</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>10:06</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11998,44 +11989,44 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128806022</v>
+        <v>128738840</v>
       </c>
       <c r="B114" t="n">
-        <v>86959</v>
+        <v>87004</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12045,10 +12036,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>717284</v>
+        <v>717020</v>
       </c>
       <c r="R114" t="n">
-        <v>6374309</v>
+        <v>6374147</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12075,12 +12066,22 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12089,29 +12090,28 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128806064</v>
+        <v>128806043</v>
       </c>
       <c r="B115" t="n">
-        <v>86922</v>
+        <v>75143</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12119,21 +12119,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12143,10 +12143,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>717299</v>
+        <v>717359</v>
       </c>
       <c r="R115" t="n">
-        <v>6374300</v>
+        <v>6374214</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12205,10 +12205,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128806495</v>
+        <v>128738886</v>
       </c>
       <c r="B116" t="n">
-        <v>86846</v>
+        <v>86806</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12216,21 +12216,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>442</v>
+        <v>424</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12240,10 +12240,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>717357</v>
+        <v>716990</v>
       </c>
       <c r="R116" t="n">
-        <v>6374169</v>
+        <v>6374260</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12270,12 +12270,22 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12290,42 +12300,46 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128806049</v>
+        <v>128738893</v>
       </c>
       <c r="B117" t="n">
-        <v>87016</v>
+        <v>86959</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -12333,10 +12347,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>717128</v>
+        <v>717000</v>
       </c>
       <c r="R117" t="n">
-        <v>6374123</v>
+        <v>6374121</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12363,12 +12377,22 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12377,28 +12401,29 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128806043</v>
+        <v>128806064</v>
       </c>
       <c r="B118" t="n">
-        <v>75143</v>
+        <v>86922</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12406,21 +12431,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12430,10 +12455,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>717359</v>
+        <v>717299</v>
       </c>
       <c r="R118" t="n">
-        <v>6374214</v>
+        <v>6374300</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12492,10 +12517,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128738886</v>
+        <v>128806495</v>
       </c>
       <c r="B119" t="n">
-        <v>86806</v>
+        <v>86846</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12503,21 +12528,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>424</v>
+        <v>442</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12527,10 +12552,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>716990</v>
+        <v>717357</v>
       </c>
       <c r="R119" t="n">
-        <v>6374260</v>
+        <v>6374169</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12557,22 +12582,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12587,46 +12602,42 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128806050</v>
+        <v>128806049</v>
       </c>
       <c r="B120" t="n">
-        <v>86925</v>
+        <v>87016</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6037417</v>
+        <v>433</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>A.Ortega &amp; al.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -12634,10 +12645,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>717311</v>
+        <v>717128</v>
       </c>
       <c r="R120" t="n">
-        <v>6374287</v>
+        <v>6374123</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12678,7 +12689,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12697,10 +12707,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128738893</v>
+        <v>128806050</v>
       </c>
       <c r="B121" t="n">
-        <v>86959</v>
+        <v>86925</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12708,21 +12718,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6003295</v>
+        <v>6037417</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12732,10 +12742,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>717000</v>
+        <v>717311</v>
       </c>
       <c r="R121" t="n">
-        <v>6374121</v>
+        <v>6374287</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12762,22 +12772,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>10:04</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>10:04</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12793,44 +12793,44 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128738892</v>
+        <v>128806052</v>
       </c>
       <c r="B122" t="n">
-        <v>86959</v>
+        <v>86784</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12840,10 +12840,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>717037</v>
+        <v>717284</v>
       </c>
       <c r="R122" t="n">
-        <v>6374150</v>
+        <v>6374097</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12870,22 +12870,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>10:16</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>10:16</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12894,51 +12884,50 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128806052</v>
+        <v>128738892</v>
       </c>
       <c r="B123" t="n">
-        <v>86784</v>
+        <v>86959</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12948,10 +12937,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>717284</v>
+        <v>717037</v>
       </c>
       <c r="R123" t="n">
-        <v>6374097</v>
+        <v>6374150</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12978,12 +12967,22 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -12992,18 +12991,19 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
@@ -13107,32 +13107,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128738894</v>
+        <v>128806045</v>
       </c>
       <c r="B125" t="n">
-        <v>86959</v>
+        <v>86981</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13142,10 +13142,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>716975</v>
+        <v>717324</v>
       </c>
       <c r="R125" t="n">
-        <v>6374071</v>
+        <v>6374179</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13172,22 +13172,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>09:15</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>09:15</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13196,51 +13186,50 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128806045</v>
+        <v>128806011</v>
       </c>
       <c r="B126" t="n">
-        <v>86981</v>
+        <v>86959</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13250,10 +13239,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>717324</v>
+        <v>717367</v>
       </c>
       <c r="R126" t="n">
-        <v>6374179</v>
+        <v>6374231</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13294,6 +13283,7 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13305,55 +13295,52 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128738882</v>
+        <v>128738894</v>
       </c>
       <c r="B127" t="n">
-        <v>87086</v>
+        <v>86959</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>3563</v>
+        <v>6003295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Stor granspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cortinarius bovinus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Fr. sl.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>717013</v>
+        <v>716975</v>
       </c>
       <c r="R127" t="n">
-        <v>6374226</v>
+        <v>6374071</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13385,7 +13372,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -13395,7 +13382,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13423,45 +13410,48 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128806011</v>
+        <v>128738882</v>
       </c>
       <c r="B128" t="n">
-        <v>86959</v>
+        <v>87086</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6003295</v>
+        <v>3563</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Stor granspindling</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius bovinus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr. sl.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>717367</v>
+        <v>717013</v>
       </c>
       <c r="R128" t="n">
-        <v>6374231</v>
+        <v>6374226</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13488,12 +13478,22 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13509,12 +13509,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -14009,32 +14009,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128738847</v>
+        <v>128806058</v>
       </c>
       <c r="B134" t="n">
-        <v>86875</v>
+        <v>86922</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>248956</v>
+        <v>3674</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14044,10 +14044,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>716980</v>
+        <v>717196</v>
       </c>
       <c r="R134" t="n">
-        <v>6374264</v>
+        <v>6374281</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14074,22 +14074,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14104,44 +14094,44 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128806058</v>
+        <v>128806487</v>
       </c>
       <c r="B135" t="n">
-        <v>86922</v>
+        <v>87004</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14151,10 +14141,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>717196</v>
+        <v>717275</v>
       </c>
       <c r="R135" t="n">
-        <v>6374281</v>
+        <v>6374183</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14201,22 +14191,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128806487</v>
+        <v>128738847</v>
       </c>
       <c r="B136" t="n">
-        <v>87004</v>
+        <v>86875</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14224,21 +14214,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>3767</v>
+        <v>248956</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14248,10 +14238,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>717275</v>
+        <v>716980</v>
       </c>
       <c r="R136" t="n">
-        <v>6374183</v>
+        <v>6374264</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14278,12 +14268,22 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14298,12 +14298,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
@@ -14602,32 +14602,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128806496</v>
+        <v>128805991</v>
       </c>
       <c r="B140" t="n">
-        <v>96228</v>
+        <v>87004</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2180</v>
+        <v>3767</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14637,10 +14637,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>717337</v>
+        <v>717147</v>
       </c>
       <c r="R140" t="n">
-        <v>6374082</v>
+        <v>6374164</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14687,44 +14687,44 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128805991</v>
+        <v>128806496</v>
       </c>
       <c r="B141" t="n">
-        <v>87004</v>
+        <v>96228</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3767</v>
+        <v>2180</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14734,10 +14734,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>717147</v>
+        <v>717337</v>
       </c>
       <c r="R141" t="n">
-        <v>6374164</v>
+        <v>6374082</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14784,12 +14784,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>

--- a/artfynd/A 42607-2025 artfynd.xlsx
+++ b/artfynd/A 42607-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128738845</v>
+        <v>128740505</v>
       </c>
       <c r="B2" t="n">
-        <v>86760</v>
+        <v>98654</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3762</v>
+        <v>219862</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716961</v>
+        <v>717182</v>
       </c>
       <c r="R2" t="n">
-        <v>6374255</v>
+        <v>6374336</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,19 +743,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,44 +760,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128738831</v>
+        <v>128738854</v>
       </c>
       <c r="B3" t="n">
-        <v>87004</v>
+        <v>86959</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717030</v>
+        <v>716967</v>
       </c>
       <c r="R3" t="n">
-        <v>6374429</v>
+        <v>6374338</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +842,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +852,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,6 +861,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,32 +880,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128742256</v>
+        <v>128740487</v>
       </c>
       <c r="B4" t="n">
-        <v>87004</v>
+        <v>86959</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717053</v>
+        <v>717292</v>
       </c>
       <c r="R4" t="n">
-        <v>6374253</v>
+        <v>6374265</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,50 +959,51 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128740514</v>
+        <v>128738831</v>
       </c>
       <c r="B5" t="n">
-        <v>86784</v>
+        <v>87004</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3712</v>
+        <v>3767</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717295</v>
+        <v>717030</v>
       </c>
       <c r="R5" t="n">
-        <v>6374249</v>
+        <v>6374429</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,9 +1046,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,44 +1073,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128740505</v>
+        <v>128742256</v>
       </c>
       <c r="B6" t="n">
-        <v>98654</v>
+        <v>87004</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219862</v>
+        <v>3767</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1120,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717182</v>
+        <v>717053</v>
       </c>
       <c r="R6" t="n">
-        <v>6374336</v>
+        <v>6374253</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,44 +1170,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128738854</v>
+        <v>128738845</v>
       </c>
       <c r="B7" t="n">
-        <v>86959</v>
+        <v>86760</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1217,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716967</v>
+        <v>716961</v>
       </c>
       <c r="R7" t="n">
-        <v>6374338</v>
+        <v>6374255</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1250,7 +1252,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1260,7 +1262,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1269,7 +1271,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1288,32 +1289,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128740487</v>
+        <v>128740514</v>
       </c>
       <c r="B8" t="n">
-        <v>86959</v>
+        <v>86784</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1323,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717292</v>
+        <v>717295</v>
       </c>
       <c r="R8" t="n">
-        <v>6374265</v>
+        <v>6374249</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,7 +1368,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1386,32 +1386,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128738834</v>
+        <v>128738853</v>
       </c>
       <c r="B9" t="n">
-        <v>87004</v>
+        <v>86959</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716985</v>
+        <v>717033</v>
       </c>
       <c r="R9" t="n">
-        <v>6374341</v>
+        <v>6374425</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1475,6 +1475,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1493,32 +1494,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128742266</v>
+        <v>128738834</v>
       </c>
       <c r="B10" t="n">
-        <v>86760</v>
+        <v>87004</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1528,10 +1529,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717201</v>
+        <v>716985</v>
       </c>
       <c r="R10" t="n">
-        <v>6374151</v>
+        <v>6374341</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,9 +1562,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,12 +1589,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1697,32 +1708,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128738853</v>
+        <v>128742266</v>
       </c>
       <c r="B12" t="n">
-        <v>86959</v>
+        <v>86760</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1732,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>717033</v>
+        <v>717201</v>
       </c>
       <c r="R12" t="n">
-        <v>6374425</v>
+        <v>6374151</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1765,50 +1776,39 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128742275</v>
+        <v>128740482</v>
       </c>
       <c r="B13" t="n">
-        <v>86910</v>
+        <v>87004</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1816,37 +1816,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6003296</v>
+        <v>3767</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716983</v>
+        <v>717057</v>
       </c>
       <c r="R13" t="n">
-        <v>6374138</v>
+        <v>6374457</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1881,62 +1878,56 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Kollekt taget för sekvensering av Martin Axegård.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128740482</v>
+        <v>128740504</v>
       </c>
       <c r="B14" t="n">
-        <v>87004</v>
+        <v>98654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3767</v>
+        <v>219862</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1946,10 +1937,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>717057</v>
+        <v>717091</v>
       </c>
       <c r="R14" t="n">
-        <v>6374457</v>
+        <v>6374400</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2106,10 +2097,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128740504</v>
+        <v>128738898</v>
       </c>
       <c r="B16" t="n">
-        <v>98654</v>
+        <v>86922</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2117,21 +2108,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219862</v>
+        <v>3674</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2141,10 +2132,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>717091</v>
+        <v>716960</v>
       </c>
       <c r="R16" t="n">
-        <v>6374400</v>
+        <v>6374150</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2174,9 +2165,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2191,44 +2192,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128738898</v>
+        <v>128738832</v>
       </c>
       <c r="B17" t="n">
-        <v>86922</v>
+        <v>87004</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2238,10 +2239,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>716960</v>
+        <v>717000</v>
       </c>
       <c r="R17" t="n">
-        <v>6374150</v>
+        <v>6374409</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2273,7 +2274,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2283,7 +2284,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2310,32 +2311,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128738832</v>
+        <v>128738859</v>
       </c>
       <c r="B18" t="n">
-        <v>87004</v>
+        <v>98666</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3767</v>
+        <v>219874</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2345,10 +2346,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>717000</v>
+        <v>716963</v>
       </c>
       <c r="R18" t="n">
-        <v>6374409</v>
+        <v>6374082</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2380,7 +2381,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2390,7 +2391,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2417,32 +2418,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128738859</v>
+        <v>128742286</v>
       </c>
       <c r="B19" t="n">
-        <v>98666</v>
+        <v>86959</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219874</v>
+        <v>6003295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2452,10 +2453,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716963</v>
+        <v>716970</v>
       </c>
       <c r="R19" t="n">
-        <v>6374082</v>
+        <v>6374097</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2485,46 +2486,37 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128742286</v>
+        <v>128740498</v>
       </c>
       <c r="B20" t="n">
         <v>86959</v>
@@ -2559,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>716970</v>
+        <v>717099</v>
       </c>
       <c r="R20" t="n">
-        <v>6374097</v>
+        <v>6374395</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2610,19 +2602,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128740498</v>
+        <v>128738857</v>
       </c>
       <c r="B21" t="n">
         <v>86959</v>
@@ -2657,10 +2649,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>717099</v>
+        <v>717049</v>
       </c>
       <c r="R21" t="n">
-        <v>6374395</v>
+        <v>6374317</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2690,9 +2682,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2708,12 +2710,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2828,32 +2830,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128738857</v>
+        <v>128742257</v>
       </c>
       <c r="B23" t="n">
-        <v>86959</v>
+        <v>87004</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2863,10 +2865,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>717049</v>
+        <v>716992</v>
       </c>
       <c r="R23" t="n">
-        <v>6374317</v>
+        <v>6374120</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2896,47 +2898,36 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128742257</v>
+        <v>128740485</v>
       </c>
       <c r="B24" t="n">
         <v>87004</v>
@@ -2971,10 +2962,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>716992</v>
+        <v>717286</v>
       </c>
       <c r="R24" t="n">
-        <v>6374120</v>
+        <v>6374251</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,19 +3012,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128740485</v>
+        <v>128742258</v>
       </c>
       <c r="B25" t="n">
         <v>87004</v>
@@ -3068,10 +3059,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>717286</v>
+        <v>716976</v>
       </c>
       <c r="R25" t="n">
-        <v>6374251</v>
+        <v>6374072</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3118,44 +3109,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128742258</v>
+        <v>128742283</v>
       </c>
       <c r="B26" t="n">
-        <v>87004</v>
+        <v>86959</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3165,10 +3156,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>716976</v>
+        <v>717040</v>
       </c>
       <c r="R26" t="n">
-        <v>6374072</v>
+        <v>6374195</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3209,6 +3200,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3227,7 +3219,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128742283</v>
+        <v>128742281</v>
       </c>
       <c r="B27" t="n">
         <v>86959</v>
@@ -3262,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>717040</v>
+        <v>717039</v>
       </c>
       <c r="R27" t="n">
-        <v>6374195</v>
+        <v>6374227</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3325,32 +3317,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128742281</v>
+        <v>128740489</v>
       </c>
       <c r="B28" t="n">
-        <v>86959</v>
+        <v>91013</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6003295</v>
+        <v>5741</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3360,10 +3352,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>717039</v>
+        <v>717220</v>
       </c>
       <c r="R28" t="n">
-        <v>6374227</v>
+        <v>6374302</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3404,19 +3396,18 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3520,32 +3511,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128740489</v>
+        <v>128742254</v>
       </c>
       <c r="B30" t="n">
-        <v>91013</v>
+        <v>87004</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5741</v>
+        <v>3767</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3555,10 +3546,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>717220</v>
+        <v>717285</v>
       </c>
       <c r="R30" t="n">
-        <v>6374302</v>
+        <v>6374272</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3605,22 +3596,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128742254</v>
+        <v>128742272</v>
       </c>
       <c r="B31" t="n">
-        <v>87004</v>
+        <v>91039</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3628,21 +3619,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3767</v>
+        <v>5747</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3652,10 +3643,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>717285</v>
+        <v>717018</v>
       </c>
       <c r="R31" t="n">
-        <v>6374272</v>
+        <v>6374179</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3714,32 +3705,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128742272</v>
+        <v>128742293</v>
       </c>
       <c r="B32" t="n">
-        <v>91039</v>
+        <v>86922</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5747</v>
+        <v>3674</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3749,10 +3740,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>717018</v>
+        <v>717094</v>
       </c>
       <c r="R32" t="n">
-        <v>6374179</v>
+        <v>6374468</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3811,32 +3802,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128742293</v>
+        <v>128740500</v>
       </c>
       <c r="B33" t="n">
-        <v>86922</v>
+        <v>86959</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3846,10 +3837,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>717094</v>
+        <v>717281</v>
       </c>
       <c r="R33" t="n">
-        <v>6374468</v>
+        <v>6374283</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3890,25 +3881,26 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128740500</v>
+        <v>128740499</v>
       </c>
       <c r="B34" t="n">
         <v>86959</v>
@@ -3943,10 +3935,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>717281</v>
+        <v>717145</v>
       </c>
       <c r="R34" t="n">
-        <v>6374283</v>
+        <v>6374308</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4104,32 +4096,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128740499</v>
+        <v>128740521</v>
       </c>
       <c r="B36" t="n">
-        <v>86959</v>
+        <v>86922</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4139,10 +4131,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>717145</v>
+        <v>717216</v>
       </c>
       <c r="R36" t="n">
-        <v>6374308</v>
+        <v>6374357</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4183,7 +4175,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4195,7 +4186,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4309,32 +4300,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128740521</v>
+        <v>128742267</v>
       </c>
       <c r="B38" t="n">
-        <v>86922</v>
+        <v>86959</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4344,10 +4335,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>717216</v>
+        <v>717105</v>
       </c>
       <c r="R38" t="n">
-        <v>6374357</v>
+        <v>6374393</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4388,18 +4379,19 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4514,32 +4506,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128742267</v>
+        <v>128738887</v>
       </c>
       <c r="B40" t="n">
-        <v>86959</v>
+        <v>86806</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4549,10 +4541,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>717105</v>
+        <v>716984</v>
       </c>
       <c r="R40" t="n">
-        <v>6374393</v>
+        <v>6374264</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4582,30 +4574,39 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4709,10 +4710,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128738887</v>
+        <v>128742259</v>
       </c>
       <c r="B42" t="n">
-        <v>86806</v>
+        <v>87004</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4720,21 +4721,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>424</v>
+        <v>3767</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4744,10 +4745,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>716984</v>
+        <v>716980</v>
       </c>
       <c r="R42" t="n">
-        <v>6374264</v>
+        <v>6374067</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4777,19 +4778,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>12:19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4804,44 +4795,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128742259</v>
+        <v>128738895</v>
       </c>
       <c r="B43" t="n">
-        <v>87004</v>
+        <v>86959</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4851,10 +4842,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>716980</v>
+        <v>716974</v>
       </c>
       <c r="R43" t="n">
-        <v>6374067</v>
+        <v>6374284</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4884,29 +4875,40 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5011,7 +5013,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128738895</v>
+        <v>128742280</v>
       </c>
       <c r="B45" t="n">
         <v>86959</v>
@@ -5046,10 +5048,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>716974</v>
+        <v>717058</v>
       </c>
       <c r="R45" t="n">
-        <v>6374284</v>
+        <v>6374174</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5079,19 +5081,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5107,19 +5099,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128742280</v>
+        <v>128742289</v>
       </c>
       <c r="B46" t="n">
         <v>86959</v>
@@ -5154,10 +5146,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>717058</v>
+        <v>716965</v>
       </c>
       <c r="R46" t="n">
-        <v>6374174</v>
+        <v>6374079</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5217,32 +5209,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128738838</v>
+        <v>128742269</v>
       </c>
       <c r="B47" t="n">
-        <v>87004</v>
+        <v>86959</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5252,10 +5244,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>717020</v>
+        <v>717186</v>
       </c>
       <c r="R47" t="n">
-        <v>6374199</v>
+        <v>6374129</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5285,71 +5277,62 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128738880</v>
+        <v>128742279</v>
       </c>
       <c r="B48" t="n">
-        <v>86784</v>
+        <v>86959</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5359,10 +5342,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>716983</v>
+        <v>717013</v>
       </c>
       <c r="R48" t="n">
-        <v>6374266</v>
+        <v>6374176</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5392,46 +5375,37 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128742289</v>
+        <v>128742288</v>
       </c>
       <c r="B49" t="n">
         <v>86959</v>
@@ -5466,10 +5440,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>716965</v>
+        <v>716995</v>
       </c>
       <c r="R49" t="n">
-        <v>6374079</v>
+        <v>6374147</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5529,7 +5503,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128742279</v>
+        <v>128738896</v>
       </c>
       <c r="B50" t="n">
         <v>86959</v>
@@ -5564,10 +5538,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>717013</v>
+        <v>717038</v>
       </c>
       <c r="R50" t="n">
-        <v>6374176</v>
+        <v>6374195</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5597,9 +5571,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5615,44 +5599,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128742269</v>
+        <v>128738880</v>
       </c>
       <c r="B51" t="n">
-        <v>86959</v>
+        <v>86784</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5662,10 +5646,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>717186</v>
+        <v>716983</v>
       </c>
       <c r="R51" t="n">
-        <v>6374129</v>
+        <v>6374266</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5695,62 +5679,71 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128742288</v>
+        <v>128738838</v>
       </c>
       <c r="B52" t="n">
-        <v>86959</v>
+        <v>87004</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5760,10 +5753,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>716995</v>
+        <v>717020</v>
       </c>
       <c r="R52" t="n">
-        <v>6374147</v>
+        <v>6374199</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5793,37 +5786,46 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128738896</v>
+        <v>128742291</v>
       </c>
       <c r="B53" t="n">
         <v>86959</v>
@@ -5858,10 +5860,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>717038</v>
+        <v>716977</v>
       </c>
       <c r="R53" t="n">
-        <v>6374195</v>
+        <v>6374073</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5891,19 +5893,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>10:50</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5919,12 +5911,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6029,32 +6021,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128742291</v>
+        <v>128738841</v>
       </c>
       <c r="B55" t="n">
-        <v>86959</v>
+        <v>87004</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6064,10 +6056,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>716977</v>
+        <v>716992</v>
       </c>
       <c r="R55" t="n">
-        <v>6374073</v>
+        <v>6374116</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6097,62 +6089,71 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128742263</v>
+        <v>128738835</v>
       </c>
       <c r="B56" t="n">
-        <v>91013</v>
+        <v>87004</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5741</v>
+        <v>3767</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6162,10 +6163,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>717281</v>
+        <v>716983</v>
       </c>
       <c r="R56" t="n">
-        <v>6374199</v>
+        <v>6374357</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6195,9 +6196,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6212,12 +6223,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6321,32 +6332,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128742282</v>
+        <v>128742252</v>
       </c>
       <c r="B58" t="n">
-        <v>86959</v>
+        <v>87004</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6356,10 +6367,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>717040</v>
+        <v>717146</v>
       </c>
       <c r="R58" t="n">
-        <v>6374212</v>
+        <v>6374313</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6400,7 +6411,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6419,32 +6429,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128738841</v>
+        <v>128742263</v>
       </c>
       <c r="B59" t="n">
-        <v>87004</v>
+        <v>91013</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3767</v>
+        <v>5741</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6454,10 +6464,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>716992</v>
+        <v>717281</v>
       </c>
       <c r="R59" t="n">
-        <v>6374116</v>
+        <v>6374199</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6487,19 +6497,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>09:50</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6514,44 +6514,44 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128738835</v>
+        <v>128742282</v>
       </c>
       <c r="B60" t="n">
-        <v>87004</v>
+        <v>86959</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6561,10 +6561,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>716983</v>
+        <v>717040</v>
       </c>
       <c r="R60" t="n">
-        <v>6374357</v>
+        <v>6374212</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6594,49 +6594,40 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128742252</v>
+        <v>128738884</v>
       </c>
       <c r="B61" t="n">
-        <v>87004</v>
+        <v>86806</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6644,21 +6635,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3767</v>
+        <v>424</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6668,10 +6659,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>717146</v>
+        <v>716969</v>
       </c>
       <c r="R61" t="n">
-        <v>6374313</v>
+        <v>6374310</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6701,9 +6692,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6718,12 +6719,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6827,32 +6828,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128738884</v>
+        <v>128740491</v>
       </c>
       <c r="B63" t="n">
-        <v>86806</v>
+        <v>86760</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>424</v>
+        <v>3762</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6862,10 +6863,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>716969</v>
+        <v>717281</v>
       </c>
       <c r="R63" t="n">
-        <v>6374310</v>
+        <v>6374215</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6895,19 +6896,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>14:32</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6922,44 +6913,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128740491</v>
+        <v>128742255</v>
       </c>
       <c r="B64" t="n">
-        <v>86760</v>
+        <v>87004</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6969,10 +6960,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>717281</v>
+        <v>717059</v>
       </c>
       <c r="R64" t="n">
-        <v>6374215</v>
+        <v>6374329</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7019,44 +7010,44 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128742255</v>
+        <v>128738848</v>
       </c>
       <c r="B65" t="n">
-        <v>87004</v>
+        <v>57713</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3767</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7066,10 +7057,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>717059</v>
+        <v>717165</v>
       </c>
       <c r="R65" t="n">
-        <v>6374329</v>
+        <v>6374351</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7099,9 +7090,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7116,44 +7117,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128738848</v>
+        <v>128738851</v>
       </c>
       <c r="B66" t="n">
-        <v>57713</v>
+        <v>86760</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>3762</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7163,10 +7164,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>717165</v>
+        <v>717040</v>
       </c>
       <c r="R66" t="n">
-        <v>6374351</v>
+        <v>6374229</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7198,7 +7199,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7208,7 +7209,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7235,10 +7236,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128738851</v>
+        <v>128740512</v>
       </c>
       <c r="B67" t="n">
-        <v>86760</v>
+        <v>86784</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7246,21 +7247,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7270,10 +7271,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>717040</v>
+        <v>717079</v>
       </c>
       <c r="R67" t="n">
-        <v>6374229</v>
+        <v>6374436</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7303,19 +7304,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7330,44 +7321,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128740512</v>
+        <v>128738836</v>
       </c>
       <c r="B68" t="n">
-        <v>86784</v>
+        <v>87004</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3712</v>
+        <v>3767</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7377,10 +7368,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>717079</v>
+        <v>717056</v>
       </c>
       <c r="R68" t="n">
-        <v>6374436</v>
+        <v>6374262</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7410,9 +7401,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7427,44 +7428,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128738836</v>
+        <v>128738855</v>
       </c>
       <c r="B69" t="n">
-        <v>87004</v>
+        <v>86959</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7474,10 +7475,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>717056</v>
+        <v>716966</v>
       </c>
       <c r="R69" t="n">
-        <v>6374262</v>
+        <v>6374312</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7509,7 +7510,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7519,7 +7520,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7528,6 +7529,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7546,7 +7548,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128738855</v>
+        <v>128738852</v>
       </c>
       <c r="B70" t="n">
         <v>86959</v>
@@ -7581,10 +7583,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>716966</v>
+        <v>717045</v>
       </c>
       <c r="R70" t="n">
-        <v>6374312</v>
+        <v>6374462</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7616,7 +7618,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7626,7 +7628,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7654,7 +7656,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128738852</v>
+        <v>128742287</v>
       </c>
       <c r="B71" t="n">
         <v>86959</v>
@@ -7689,10 +7691,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>717045</v>
+        <v>717013</v>
       </c>
       <c r="R71" t="n">
-        <v>6374462</v>
+        <v>6374166</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7722,19 +7724,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>15:02</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7750,19 +7742,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128742287</v>
+        <v>128742270</v>
       </c>
       <c r="B72" t="n">
         <v>86959</v>
@@ -7797,10 +7789,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>717013</v>
+        <v>717071</v>
       </c>
       <c r="R72" t="n">
-        <v>6374166</v>
+        <v>6374305</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7860,32 +7852,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128740508</v>
+        <v>128742290</v>
       </c>
       <c r="B73" t="n">
-        <v>86981</v>
+        <v>86959</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7895,10 +7887,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>717063</v>
+        <v>716979</v>
       </c>
       <c r="R73" t="n">
-        <v>6374397</v>
+        <v>6374069</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7939,18 +7931,19 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8054,32 +8047,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128738833</v>
+        <v>128740519</v>
       </c>
       <c r="B75" t="n">
-        <v>87004</v>
+        <v>86922</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8089,10 +8082,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>716976</v>
+        <v>717067</v>
       </c>
       <c r="R75" t="n">
-        <v>6374331</v>
+        <v>6374399</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8122,19 +8115,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8149,44 +8132,44 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128740519</v>
+        <v>128738833</v>
       </c>
       <c r="B76" t="n">
-        <v>86922</v>
+        <v>87004</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8196,10 +8179,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>717067</v>
+        <v>716976</v>
       </c>
       <c r="R76" t="n">
-        <v>6374399</v>
+        <v>6374331</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8229,9 +8212,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8246,44 +8239,44 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128742290</v>
+        <v>128740508</v>
       </c>
       <c r="B77" t="n">
-        <v>86959</v>
+        <v>86981</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8293,10 +8286,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>716979</v>
+        <v>717063</v>
       </c>
       <c r="R77" t="n">
-        <v>6374069</v>
+        <v>6374397</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8337,51 +8330,50 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128742270</v>
+        <v>128740516</v>
       </c>
       <c r="B78" t="n">
-        <v>86959</v>
+        <v>92136</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6003295</v>
+        <v>6031</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8391,10 +8383,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>717071</v>
+        <v>717218</v>
       </c>
       <c r="R78" t="n">
-        <v>6374305</v>
+        <v>6374124</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8435,51 +8427,50 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128740516</v>
+        <v>128738891</v>
       </c>
       <c r="B79" t="n">
-        <v>92136</v>
+        <v>86959</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6031</v>
+        <v>6003295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8489,10 +8480,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>717218</v>
+        <v>717025</v>
       </c>
       <c r="R79" t="n">
-        <v>6374124</v>
+        <v>6374225</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8522,36 +8513,47 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128738891</v>
+        <v>128738890</v>
       </c>
       <c r="B80" t="n">
         <v>86959</v>
@@ -8586,10 +8588,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>717025</v>
+        <v>717014</v>
       </c>
       <c r="R80" t="n">
-        <v>6374225</v>
+        <v>6374343</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8621,7 +8623,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8631,7 +8633,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8659,32 +8661,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128738890</v>
+        <v>128740518</v>
       </c>
       <c r="B81" t="n">
-        <v>86959</v>
+        <v>86922</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8694,10 +8696,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>717014</v>
+        <v>717062</v>
       </c>
       <c r="R81" t="n">
-        <v>6374343</v>
+        <v>6374393</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8727,40 +8729,29 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -8864,32 +8855,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128740518</v>
+        <v>128740503</v>
       </c>
       <c r="B83" t="n">
-        <v>86922</v>
+        <v>86959</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8899,10 +8890,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>717062</v>
+        <v>717212</v>
       </c>
       <c r="R83" t="n">
-        <v>6374393</v>
+        <v>6374189</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8943,6 +8934,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -8954,7 +8946,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -9058,32 +9050,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128740503</v>
+        <v>128738899</v>
       </c>
       <c r="B85" t="n">
-        <v>86959</v>
+        <v>86922</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9093,10 +9085,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>717212</v>
+        <v>717099</v>
       </c>
       <c r="R85" t="n">
-        <v>6374189</v>
+        <v>6374317</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9126,37 +9118,46 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128738899</v>
+        <v>128806499</v>
       </c>
       <c r="B86" t="n">
         <v>86922</v>
@@ -9191,10 +9192,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>717099</v>
+        <v>717372</v>
       </c>
       <c r="R86" t="n">
-        <v>6374317</v>
+        <v>6374153</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9221,22 +9222,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>13:38</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>13:38</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9251,57 +9242,60 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128806499</v>
+        <v>128806483</v>
       </c>
       <c r="B87" t="n">
-        <v>86922</v>
+        <v>90979</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>3674</v>
+        <v>720</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>717372</v>
+        <v>717267</v>
       </c>
       <c r="R87" t="n">
-        <v>6374153</v>
+        <v>6374381</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9342,6 +9336,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9360,10 +9355,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128806483</v>
+        <v>128815957</v>
       </c>
       <c r="B88" t="n">
-        <v>90979</v>
+        <v>86976</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9371,21 +9366,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>720</v>
+        <v>248934</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Knölfotad bananspindling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Cortinarius stjernegaardii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>Brandrud &amp; Frøslev</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9398,10 +9393,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>717267</v>
+        <v>717020</v>
       </c>
       <c r="R88" t="n">
-        <v>6374381</v>
+        <v>6374147</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9428,12 +9423,27 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Bilddokumentation av Ullas fynd. Uppsvullen bulb och orange basalmycel. Ek fanss på fyndplatsen som domineras av kalktallskog.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9449,22 +9459,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128815957</v>
+        <v>128738885</v>
       </c>
       <c r="B89" t="n">
-        <v>86976</v>
+        <v>86806</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9472,37 +9482,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>248934</v>
+        <v>424</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knölfotad bananspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius stjernegaardii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Brandrud &amp; Frøslev</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>717020</v>
+        <v>717029</v>
       </c>
       <c r="R89" t="n">
-        <v>6374147</v>
+        <v>6374326</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9534,7 +9541,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -9544,12 +9551,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:37</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Bilddokumentation av Ullas fynd. Uppsvullen bulb och orange basalmycel. Ek fanss på fyndplatsen som domineras av kalktallskog.</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9558,7 +9560,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9577,10 +9578,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128738885</v>
+        <v>128806494</v>
       </c>
       <c r="B90" t="n">
-        <v>86806</v>
+        <v>86981</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9588,21 +9589,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>424</v>
+        <v>449</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9612,10 +9613,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>717029</v>
+        <v>717333</v>
       </c>
       <c r="R90" t="n">
-        <v>6374326</v>
+        <v>6374180</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9642,22 +9643,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>13:52</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>13:52</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9672,22 +9663,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128805996</v>
+        <v>128806493</v>
       </c>
       <c r="B91" t="n">
-        <v>87004</v>
+        <v>86981</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9695,21 +9686,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9719,10 +9710,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>717308</v>
+        <v>717133</v>
       </c>
       <c r="R91" t="n">
-        <v>6374239</v>
+        <v>6374199</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9769,22 +9760,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128806493</v>
+        <v>128805996</v>
       </c>
       <c r="B92" t="n">
-        <v>86981</v>
+        <v>87004</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9792,21 +9783,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9816,10 +9807,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>717133</v>
+        <v>717308</v>
       </c>
       <c r="R92" t="n">
-        <v>6374199</v>
+        <v>6374239</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9866,22 +9857,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128806494</v>
+        <v>128738839</v>
       </c>
       <c r="B93" t="n">
-        <v>86981</v>
+        <v>87004</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9889,21 +9880,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9913,10 +9904,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>717333</v>
+        <v>717039</v>
       </c>
       <c r="R93" t="n">
-        <v>6374180</v>
+        <v>6374168</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9943,12 +9934,22 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9963,44 +9964,44 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128738839</v>
+        <v>128738846</v>
       </c>
       <c r="B94" t="n">
-        <v>87004</v>
+        <v>91013</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3767</v>
+        <v>5741</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10010,10 +10011,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>717039</v>
+        <v>717037</v>
       </c>
       <c r="R94" t="n">
-        <v>6374168</v>
+        <v>6374226</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10045,7 +10046,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10055,7 +10056,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10082,10 +10083,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128806038</v>
+        <v>128815850</v>
       </c>
       <c r="B95" t="n">
-        <v>98654</v>
+        <v>89482</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10093,21 +10094,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>219862</v>
+        <v>236437</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Brun klibbskivling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Limacella glioderma</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Maire</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10117,10 +10118,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>717113</v>
+        <v>716975</v>
       </c>
       <c r="R95" t="n">
-        <v>6374105</v>
+        <v>6374071</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10147,12 +10148,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10167,12 +10178,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -10276,10 +10287,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128738846</v>
+        <v>128806038</v>
       </c>
       <c r="B97" t="n">
-        <v>91013</v>
+        <v>98654</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10287,21 +10298,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5741</v>
+        <v>219862</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10311,10 +10322,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>717037</v>
+        <v>717113</v>
       </c>
       <c r="R97" t="n">
-        <v>6374226</v>
+        <v>6374105</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10341,22 +10352,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10371,44 +10372,44 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128815850</v>
+        <v>128806004</v>
       </c>
       <c r="B98" t="n">
-        <v>89482</v>
+        <v>91504</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>236437</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Brun klibbskivling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Limacella glioderma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Maire</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10418,10 +10419,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>716975</v>
+        <v>717360</v>
       </c>
       <c r="R98" t="n">
-        <v>6374071</v>
+        <v>6374175</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10448,22 +10449,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>09:13</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>09:13</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10478,12 +10469,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -10591,10 +10582,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128806004</v>
+        <v>128806009</v>
       </c>
       <c r="B100" t="n">
-        <v>91504</v>
+        <v>86959</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10602,21 +10593,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>6003295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10626,10 +10617,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>717360</v>
+        <v>717132</v>
       </c>
       <c r="R100" t="n">
-        <v>6374175</v>
+        <v>6374140</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10670,6 +10661,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10681,17 +10673,17 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128806009</v>
+        <v>128738866</v>
       </c>
       <c r="B101" t="n">
-        <v>86959</v>
+        <v>90245</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10699,21 +10691,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6003295</v>
+        <v>970</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10723,10 +10715,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>717132</v>
+        <v>717039</v>
       </c>
       <c r="R101" t="n">
-        <v>6374140</v>
+        <v>6374321</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10753,12 +10745,22 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10774,12 +10776,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -10883,10 +10885,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128738866</v>
+        <v>128738897</v>
       </c>
       <c r="B103" t="n">
-        <v>90245</v>
+        <v>86959</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10894,21 +10896,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>970</v>
+        <v>6003295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10918,10 +10920,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>717039</v>
+        <v>717015</v>
       </c>
       <c r="R103" t="n">
-        <v>6374321</v>
+        <v>6374144</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10953,7 +10955,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -10963,7 +10965,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10991,34 +10993,30 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128738897</v>
+        <v>128738875</v>
       </c>
       <c r="B104" t="n">
-        <v>86959</v>
+        <v>87016</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -11026,10 +11024,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>717015</v>
+        <v>716968</v>
       </c>
       <c r="R104" t="n">
-        <v>6374144</v>
+        <v>6374251</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11061,7 +11059,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11071,7 +11069,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11080,7 +11078,6 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11099,7 +11096,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128805993</v>
+        <v>128738842</v>
       </c>
       <c r="B105" t="n">
         <v>87004</v>
@@ -11134,10 +11131,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>717148</v>
+        <v>716981</v>
       </c>
       <c r="R105" t="n">
-        <v>6374174</v>
+        <v>6374088</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11164,12 +11161,22 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11184,22 +11191,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128738875</v>
+        <v>128805993</v>
       </c>
       <c r="B106" t="n">
-        <v>87016</v>
+        <v>87004</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11207,19 +11214,23 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>433</v>
+        <v>3767</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr"/>
+          <t>Cortinarius violaceomaculatus</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -11227,10 +11238,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>716968</v>
+        <v>717148</v>
       </c>
       <c r="R106" t="n">
-        <v>6374251</v>
+        <v>6374174</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11257,22 +11268,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>12:41</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>12:41</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11287,44 +11288,44 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128738842</v>
+        <v>128806023</v>
       </c>
       <c r="B107" t="n">
-        <v>87004</v>
+        <v>86959</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11334,10 +11335,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>716981</v>
+        <v>717360</v>
       </c>
       <c r="R107" t="n">
-        <v>6374088</v>
+        <v>6374214</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11364,22 +11365,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>09:31</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>09:31</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11388,18 +11379,19 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -11708,32 +11700,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128806023</v>
+        <v>128806497</v>
       </c>
       <c r="B111" t="n">
-        <v>86959</v>
+        <v>86784</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11743,10 +11735,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>717360</v>
+        <v>717273</v>
       </c>
       <c r="R111" t="n">
-        <v>6374214</v>
+        <v>6374182</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11787,51 +11779,50 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128806022</v>
+        <v>128738840</v>
       </c>
       <c r="B112" t="n">
-        <v>86959</v>
+        <v>87004</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11841,10 +11832,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>717284</v>
+        <v>717020</v>
       </c>
       <c r="R112" t="n">
-        <v>6374309</v>
+        <v>6374147</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11871,12 +11862,22 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11885,51 +11886,50 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128806497</v>
+        <v>128806022</v>
       </c>
       <c r="B113" t="n">
-        <v>86784</v>
+        <v>86959</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11939,10 +11939,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>717273</v>
+        <v>717284</v>
       </c>
       <c r="R113" t="n">
-        <v>6374182</v>
+        <v>6374309</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11983,28 +11983,29 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128738840</v>
+        <v>128738886</v>
       </c>
       <c r="B114" t="n">
-        <v>87004</v>
+        <v>86806</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12012,21 +12013,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3767</v>
+        <v>424</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12036,10 +12037,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>717020</v>
+        <v>716990</v>
       </c>
       <c r="R114" t="n">
-        <v>6374147</v>
+        <v>6374260</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12071,7 +12072,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12081,7 +12082,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12108,32 +12109,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128806043</v>
+        <v>128806495</v>
       </c>
       <c r="B115" t="n">
-        <v>75143</v>
+        <v>86846</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6426</v>
+        <v>442</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12143,10 +12144,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>717359</v>
+        <v>717357</v>
       </c>
       <c r="R115" t="n">
-        <v>6374214</v>
+        <v>6374169</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12193,22 +12194,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128738886</v>
+        <v>128806049</v>
       </c>
       <c r="B116" t="n">
-        <v>86806</v>
+        <v>87016</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12216,23 +12217,19 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -12240,10 +12237,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>716990</v>
+        <v>717128</v>
       </c>
       <c r="R116" t="n">
-        <v>6374260</v>
+        <v>6374123</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12270,22 +12267,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12300,44 +12287,44 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128738893</v>
+        <v>128806064</v>
       </c>
       <c r="B117" t="n">
-        <v>86959</v>
+        <v>86922</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12347,10 +12334,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>717000</v>
+        <v>717299</v>
       </c>
       <c r="R117" t="n">
-        <v>6374121</v>
+        <v>6374300</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12377,22 +12364,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>10:04</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>10:04</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12401,51 +12378,50 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128806064</v>
+        <v>128738893</v>
       </c>
       <c r="B118" t="n">
-        <v>86922</v>
+        <v>86959</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12455,10 +12431,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>717299</v>
+        <v>717000</v>
       </c>
       <c r="R118" t="n">
-        <v>6374300</v>
+        <v>6374121</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12485,12 +12461,22 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12499,50 +12485,51 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128806495</v>
+        <v>128806043</v>
       </c>
       <c r="B119" t="n">
-        <v>86846</v>
+        <v>75143</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>442</v>
+        <v>6426</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12552,10 +12539,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>717357</v>
+        <v>717359</v>
       </c>
       <c r="R119" t="n">
-        <v>6374169</v>
+        <v>6374214</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12602,42 +12589,46 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128806049</v>
+        <v>128806050</v>
       </c>
       <c r="B120" t="n">
-        <v>87016</v>
+        <v>86925</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>433</v>
+        <v>6037417</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr"/>
+          <t>Cortinarius olivaceodionysae</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>A.Ortega &amp; al.</t>
+        </is>
+      </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -12645,10 +12636,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>717128</v>
+        <v>717311</v>
       </c>
       <c r="R120" t="n">
-        <v>6374123</v>
+        <v>6374287</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12689,6 +12680,7 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12707,32 +12699,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128806050</v>
+        <v>128806052</v>
       </c>
       <c r="B121" t="n">
-        <v>86925</v>
+        <v>86784</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6037417</v>
+        <v>3712</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12742,10 +12734,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>717311</v>
+        <v>717284</v>
       </c>
       <c r="R121" t="n">
-        <v>6374287</v>
+        <v>6374097</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12786,7 +12778,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12805,32 +12796,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128806052</v>
+        <v>128738892</v>
       </c>
       <c r="B122" t="n">
-        <v>86784</v>
+        <v>86959</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12840,10 +12831,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>717284</v>
+        <v>717037</v>
       </c>
       <c r="R122" t="n">
-        <v>6374097</v>
+        <v>6374150</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12870,12 +12861,22 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12884,63 +12885,67 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128738892</v>
+        <v>128738882</v>
       </c>
       <c r="B123" t="n">
-        <v>86959</v>
+        <v>87086</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6003295</v>
+        <v>3563</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Stor granspindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius bovinus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr. sl.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>717037</v>
+        <v>717013</v>
       </c>
       <c r="R123" t="n">
-        <v>6374150</v>
+        <v>6374226</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12972,7 +12977,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -12982,7 +12987,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13107,32 +13112,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128806045</v>
+        <v>128738894</v>
       </c>
       <c r="B125" t="n">
-        <v>86981</v>
+        <v>86959</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13142,10 +13147,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>717324</v>
+        <v>716975</v>
       </c>
       <c r="R125" t="n">
-        <v>6374179</v>
+        <v>6374071</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13172,12 +13177,22 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13186,50 +13201,51 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128806011</v>
+        <v>128806045</v>
       </c>
       <c r="B126" t="n">
-        <v>86959</v>
+        <v>86981</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13239,10 +13255,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>717367</v>
+        <v>717324</v>
       </c>
       <c r="R126" t="n">
-        <v>6374231</v>
+        <v>6374179</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13283,7 +13299,6 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13295,14 +13310,14 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128738894</v>
+        <v>128806011</v>
       </c>
       <c r="B127" t="n">
         <v>86959</v>
@@ -13337,10 +13352,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>716975</v>
+        <v>717367</v>
       </c>
       <c r="R127" t="n">
-        <v>6374071</v>
+        <v>6374231</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13367,22 +13382,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>09:15</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>09:15</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13398,60 +13403,57 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128738882</v>
+        <v>128806485</v>
       </c>
       <c r="B128" t="n">
-        <v>87086</v>
+        <v>86784</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>3563</v>
+        <v>3712</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stor granspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cortinarius bovinus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Fr. sl.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>717013</v>
+        <v>717201</v>
       </c>
       <c r="R128" t="n">
-        <v>6374226</v>
+        <v>6374297</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13478,22 +13480,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>13:07</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>13:07</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13509,44 +13501,44 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128806485</v>
+        <v>128806492</v>
       </c>
       <c r="B129" t="n">
-        <v>86784</v>
+        <v>91039</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>3712</v>
+        <v>5747</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13556,10 +13548,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>717201</v>
+        <v>717146</v>
       </c>
       <c r="R129" t="n">
-        <v>6374297</v>
+        <v>6374178</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13600,7 +13592,6 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13619,32 +13610,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128806492</v>
+        <v>128806491</v>
       </c>
       <c r="B130" t="n">
-        <v>91039</v>
+        <v>86959</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13654,10 +13645,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>717146</v>
+        <v>717324</v>
       </c>
       <c r="R130" t="n">
-        <v>6374178</v>
+        <v>6374171</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13698,6 +13689,7 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13716,32 +13708,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128806491</v>
+        <v>128806057</v>
       </c>
       <c r="B131" t="n">
-        <v>86959</v>
+        <v>86922</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13751,10 +13743,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>717324</v>
+        <v>717121</v>
       </c>
       <c r="R131" t="n">
-        <v>6374171</v>
+        <v>6374153</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13795,51 +13787,50 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128806057</v>
+        <v>128806487</v>
       </c>
       <c r="B132" t="n">
-        <v>86922</v>
+        <v>87004</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13849,10 +13840,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>717121</v>
+        <v>717275</v>
       </c>
       <c r="R132" t="n">
-        <v>6374153</v>
+        <v>6374183</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13899,44 +13890,44 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128806490</v>
+        <v>128738847</v>
       </c>
       <c r="B133" t="n">
-        <v>86959</v>
+        <v>86875</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13946,10 +13937,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>717333</v>
+        <v>716980</v>
       </c>
       <c r="R133" t="n">
-        <v>6374202</v>
+        <v>6374264</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13976,12 +13967,22 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -13990,19 +13991,18 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -14106,32 +14106,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128806487</v>
+        <v>128806490</v>
       </c>
       <c r="B135" t="n">
-        <v>87004</v>
+        <v>86959</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14141,10 +14141,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>717275</v>
+        <v>717333</v>
       </c>
       <c r="R135" t="n">
-        <v>6374183</v>
+        <v>6374202</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14185,6 +14185,7 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -14203,32 +14204,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128738847</v>
+        <v>128806013</v>
       </c>
       <c r="B136" t="n">
-        <v>86875</v>
+        <v>86959</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14238,10 +14239,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>716980</v>
+        <v>717315</v>
       </c>
       <c r="R136" t="n">
-        <v>6374264</v>
+        <v>6374306</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14268,22 +14269,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14292,50 +14283,51 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128806013</v>
+        <v>128806065</v>
       </c>
       <c r="B137" t="n">
-        <v>86959</v>
+        <v>86922</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14345,10 +14337,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>717315</v>
+        <v>717316</v>
       </c>
       <c r="R137" t="n">
-        <v>6374306</v>
+        <v>6374280</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14389,7 +14381,6 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -14401,39 +14392,39 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128806065</v>
+        <v>128806486</v>
       </c>
       <c r="B138" t="n">
-        <v>86922</v>
+        <v>87004</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14443,10 +14434,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>717316</v>
+        <v>717170</v>
       </c>
       <c r="R138" t="n">
-        <v>6374280</v>
+        <v>6374288</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14493,44 +14484,44 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128806486</v>
+        <v>128806496</v>
       </c>
       <c r="B139" t="n">
-        <v>87004</v>
+        <v>96228</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>3767</v>
+        <v>2180</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14540,10 +14531,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>717170</v>
+        <v>717337</v>
       </c>
       <c r="R139" t="n">
-        <v>6374288</v>
+        <v>6374082</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14699,32 +14690,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128806496</v>
+        <v>128806024</v>
       </c>
       <c r="B141" t="n">
-        <v>96228</v>
+        <v>86959</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2180</v>
+        <v>6003295</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14734,10 +14725,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>717337</v>
+        <v>717366</v>
       </c>
       <c r="R141" t="n">
-        <v>6374082</v>
+        <v>6374150</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14778,18 +14769,19 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
@@ -14904,45 +14896,48 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128806024</v>
+        <v>128738867</v>
       </c>
       <c r="B143" t="n">
-        <v>86959</v>
+        <v>86981</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>717366</v>
+        <v>717115</v>
       </c>
       <c r="R143" t="n">
-        <v>6374150</v>
+        <v>6374297</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14969,12 +14964,27 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Växer i gammal myrstack. Anna: luktar lite åt rättickahållet. Luktar svagt av rödbeta, lite som kantspindling men inte lika stickande söt .. utan mer som rödbeta. Majs är en bättre doftreferens.</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -14990,22 +15000,22 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128738867</v>
+        <v>128742275</v>
       </c>
       <c r="B144" t="n">
-        <v>86981</v>
+        <v>86910</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15013,21 +15023,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>449</v>
+        <v>6003296</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Stor odörspindling</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius mussivus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.) Melot</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15040,10 +15050,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>717115</v>
+        <v>716983</v>
       </c>
       <c r="R144" t="n">
-        <v>6374297</v>
+        <v>6374138</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15073,24 +15083,14 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Växer i gammal myrstack. Anna: luktar lite åt rättickahållet. Luktar svagt av rödbeta, lite som kantspindling men inte lika stickande söt .. utan mer som rödbeta. Majs är en bättre doftreferens.</t>
+          <t>Kollekt taget för sekvensering av Martin Axegård.</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15106,12 +15106,12 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>

--- a/artfynd/A 42607-2025 artfynd.xlsx
+++ b/artfynd/A 42607-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128740505</v>
+        <v>128738845</v>
       </c>
       <c r="B2" t="n">
-        <v>98654</v>
+        <v>86764</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219862</v>
+        <v>3762</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717182</v>
+        <v>716961</v>
       </c>
       <c r="R2" t="n">
-        <v>6374336</v>
+        <v>6374255</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,9 +743,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,44 +770,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128738854</v>
+        <v>128740514</v>
       </c>
       <c r="B3" t="n">
-        <v>86959</v>
+        <v>86788</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716967</v>
+        <v>717295</v>
       </c>
       <c r="R3" t="n">
-        <v>6374338</v>
+        <v>6374249</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -840,72 +850,61 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128740487</v>
+        <v>128738831</v>
       </c>
       <c r="B4" t="n">
-        <v>86959</v>
+        <v>87008</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -915,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717292</v>
+        <v>717030</v>
       </c>
       <c r="R4" t="n">
-        <v>6374265</v>
+        <v>6374429</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,40 +947,49 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128738831</v>
+        <v>128742256</v>
       </c>
       <c r="B5" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717030</v>
+        <v>717053</v>
       </c>
       <c r="R5" t="n">
-        <v>6374429</v>
+        <v>6374253</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1046,19 +1054,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,44 +1071,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128742256</v>
+        <v>128740505</v>
       </c>
       <c r="B6" t="n">
-        <v>87004</v>
+        <v>98658</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3767</v>
+        <v>219862</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1120,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717053</v>
+        <v>717182</v>
       </c>
       <c r="R6" t="n">
-        <v>6374253</v>
+        <v>6374336</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,44 +1168,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128738845</v>
+        <v>128738854</v>
       </c>
       <c r="B7" t="n">
-        <v>86760</v>
+        <v>86963</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1217,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716961</v>
+        <v>716967</v>
       </c>
       <c r="R7" t="n">
-        <v>6374255</v>
+        <v>6374338</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1252,7 +1250,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1262,7 +1260,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1271,6 +1269,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1289,32 +1288,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128740514</v>
+        <v>128740487</v>
       </c>
       <c r="B8" t="n">
-        <v>86784</v>
+        <v>86963</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1323,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717295</v>
+        <v>717292</v>
       </c>
       <c r="R8" t="n">
-        <v>6374249</v>
+        <v>6374265</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,6 +1367,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1386,32 +1386,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128738853</v>
+        <v>128738834</v>
       </c>
       <c r="B9" t="n">
-        <v>86959</v>
+        <v>87008</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717033</v>
+        <v>716985</v>
       </c>
       <c r="R9" t="n">
-        <v>6374425</v>
+        <v>6374341</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1475,7 +1475,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1494,32 +1493,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128738834</v>
+        <v>128742266</v>
       </c>
       <c r="B10" t="n">
-        <v>87004</v>
+        <v>86764</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1529,10 +1528,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716985</v>
+        <v>717201</v>
       </c>
       <c r="R10" t="n">
-        <v>6374341</v>
+        <v>6374151</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1562,19 +1561,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1589,12 +1578,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1604,7 +1593,7 @@
         <v>128738837</v>
       </c>
       <c r="B11" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,32 +1697,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128742266</v>
+        <v>128738853</v>
       </c>
       <c r="B12" t="n">
-        <v>86760</v>
+        <v>86963</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1743,10 +1732,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>717201</v>
+        <v>717033</v>
       </c>
       <c r="R12" t="n">
-        <v>6374151</v>
+        <v>6374425</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,29 +1765,40 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1808,7 +1808,7 @@
         <v>128740482</v>
       </c>
       <c r="B13" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,32 +1902,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128740504</v>
+        <v>128742285</v>
       </c>
       <c r="B14" t="n">
-        <v>98654</v>
+        <v>86963</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219862</v>
+        <v>6003295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1937,10 +1937,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>717091</v>
+        <v>716995</v>
       </c>
       <c r="R14" t="n">
-        <v>6374400</v>
+        <v>6374141</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1981,50 +1981,51 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128742285</v>
+        <v>128740504</v>
       </c>
       <c r="B15" t="n">
-        <v>86959</v>
+        <v>98658</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6003295</v>
+        <v>219862</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2034,10 +2035,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>716995</v>
+        <v>717091</v>
       </c>
       <c r="R15" t="n">
-        <v>6374141</v>
+        <v>6374400</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2078,19 +2079,18 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2100,7 +2100,7 @@
         <v>128738898</v>
       </c>
       <c r="B16" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>128738832</v>
       </c>
       <c r="B17" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>128738859</v>
       </c>
       <c r="B18" t="n">
-        <v>98666</v>
+        <v>98670</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>128742286</v>
       </c>
       <c r="B19" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>128740498</v>
       </c>
       <c r="B20" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2614,10 +2614,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128738857</v>
+        <v>128738856</v>
       </c>
       <c r="B21" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2649,10 +2649,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>717049</v>
+        <v>716986</v>
       </c>
       <c r="R21" t="n">
-        <v>6374317</v>
+        <v>6374339</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2722,10 +2722,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128738856</v>
+        <v>128738857</v>
       </c>
       <c r="B22" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>716986</v>
+        <v>717049</v>
       </c>
       <c r="R22" t="n">
-        <v>6374339</v>
+        <v>6374317</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2833,7 +2833,7 @@
         <v>128742257</v>
       </c>
       <c r="B23" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>128740485</v>
       </c>
       <c r="B24" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>128742258</v>
       </c>
       <c r="B25" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3121,32 +3121,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128742283</v>
+        <v>128742273</v>
       </c>
       <c r="B26" t="n">
-        <v>86959</v>
+        <v>86939</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6003295</v>
+        <v>1988</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>717040</v>
+        <v>717014</v>
       </c>
       <c r="R26" t="n">
-        <v>6374195</v>
+        <v>6374164</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3200,7 +3200,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3219,10 +3218,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128742281</v>
+        <v>128742283</v>
       </c>
       <c r="B27" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3254,10 +3253,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>717039</v>
+        <v>717040</v>
       </c>
       <c r="R27" t="n">
-        <v>6374227</v>
+        <v>6374195</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3317,32 +3316,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128740489</v>
+        <v>128742281</v>
       </c>
       <c r="B28" t="n">
-        <v>91013</v>
+        <v>86963</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5741</v>
+        <v>6003295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3352,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>717220</v>
+        <v>717039</v>
       </c>
       <c r="R28" t="n">
-        <v>6374302</v>
+        <v>6374227</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3396,28 +3395,29 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128742273</v>
+        <v>128740489</v>
       </c>
       <c r="B29" t="n">
-        <v>86935</v>
+        <v>91017</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3425,21 +3425,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1988</v>
+        <v>5741</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3449,10 +3449,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>717014</v>
+        <v>717220</v>
       </c>
       <c r="R29" t="n">
-        <v>6374164</v>
+        <v>6374302</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3499,22 +3499,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128742254</v>
+        <v>128742272</v>
       </c>
       <c r="B30" t="n">
-        <v>87004</v>
+        <v>91043</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3522,21 +3522,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3767</v>
+        <v>5747</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3546,10 +3546,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>717285</v>
+        <v>717018</v>
       </c>
       <c r="R30" t="n">
-        <v>6374272</v>
+        <v>6374179</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3608,32 +3608,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128742272</v>
+        <v>128742293</v>
       </c>
       <c r="B31" t="n">
-        <v>91039</v>
+        <v>86926</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5747</v>
+        <v>3674</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>717018</v>
+        <v>717094</v>
       </c>
       <c r="R31" t="n">
-        <v>6374179</v>
+        <v>6374468</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3705,32 +3705,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128742293</v>
+        <v>128742254</v>
       </c>
       <c r="B32" t="n">
-        <v>86922</v>
+        <v>87008</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>717094</v>
+        <v>717285</v>
       </c>
       <c r="R32" t="n">
-        <v>6374468</v>
+        <v>6374272</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3805,7 +3805,7 @@
         <v>128740500</v>
       </c>
       <c r="B33" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3900,10 +3900,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128740499</v>
+        <v>128740502</v>
       </c>
       <c r="B34" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3935,10 +3935,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>717145</v>
+        <v>717282</v>
       </c>
       <c r="R34" t="n">
-        <v>6374308</v>
+        <v>6374266</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3998,10 +3998,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128740502</v>
+        <v>128740499</v>
       </c>
       <c r="B35" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>717282</v>
+        <v>717145</v>
       </c>
       <c r="R35" t="n">
-        <v>6374266</v>
+        <v>6374308</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4099,7 +4099,7 @@
         <v>128740521</v>
       </c>
       <c r="B36" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>128738900</v>
       </c>
       <c r="B37" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4300,10 +4300,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128742267</v>
+        <v>128738858</v>
       </c>
       <c r="B38" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4335,10 +4335,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>717105</v>
+        <v>717003</v>
       </c>
       <c r="R38" t="n">
-        <v>6374393</v>
+        <v>6374177</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4368,9 +4368,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4386,22 +4396,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128738858</v>
+        <v>128742267</v>
       </c>
       <c r="B39" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4433,10 +4443,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>717003</v>
+        <v>717105</v>
       </c>
       <c r="R39" t="n">
-        <v>6374177</v>
+        <v>6374393</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4466,19 +4476,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:02</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4494,22 +4494,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128738887</v>
+        <v>128740509</v>
       </c>
       <c r="B40" t="n">
-        <v>86806</v>
+        <v>86985</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4517,21 +4517,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>424</v>
+        <v>449</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4541,10 +4541,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>716984</v>
+        <v>717258</v>
       </c>
       <c r="R40" t="n">
-        <v>6374264</v>
+        <v>6374286</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4574,19 +4574,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>12:19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4601,22 +4591,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128740509</v>
+        <v>128738887</v>
       </c>
       <c r="B41" t="n">
-        <v>86981</v>
+        <v>86810</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4624,21 +4614,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>449</v>
+        <v>424</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4648,10 +4638,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>717258</v>
+        <v>716984</v>
       </c>
       <c r="R41" t="n">
-        <v>6374286</v>
+        <v>6374264</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4681,9 +4671,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4698,12 +4698,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4713,7 +4713,7 @@
         <v>128742259</v>
       </c>
       <c r="B42" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4807,10 +4807,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128738895</v>
+        <v>128742268</v>
       </c>
       <c r="B43" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>716974</v>
+        <v>717267</v>
       </c>
       <c r="R43" t="n">
-        <v>6374284</v>
+        <v>6374322</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4875,19 +4875,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4903,22 +4893,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128742268</v>
+        <v>128738895</v>
       </c>
       <c r="B44" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4950,10 +4940,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>717267</v>
+        <v>716974</v>
       </c>
       <c r="R44" t="n">
-        <v>6374322</v>
+        <v>6374284</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4983,9 +4973,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5001,12 +5001,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5016,7 +5016,7 @@
         <v>128742280</v>
       </c>
       <c r="B45" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5111,32 +5111,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128742289</v>
+        <v>128738880</v>
       </c>
       <c r="B46" t="n">
-        <v>86959</v>
+        <v>86788</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>716965</v>
+        <v>716983</v>
       </c>
       <c r="R46" t="n">
-        <v>6374079</v>
+        <v>6374266</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5179,62 +5179,71 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128742269</v>
+        <v>128738838</v>
       </c>
       <c r="B47" t="n">
-        <v>86959</v>
+        <v>87008</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5244,10 +5253,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>717186</v>
+        <v>717020</v>
       </c>
       <c r="R47" t="n">
-        <v>6374129</v>
+        <v>6374199</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5277,40 +5286,49 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128742279</v>
+        <v>128742289</v>
       </c>
       <c r="B48" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5342,10 +5360,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>717013</v>
+        <v>716965</v>
       </c>
       <c r="R48" t="n">
-        <v>6374176</v>
+        <v>6374079</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5405,10 +5423,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128742288</v>
+        <v>128742279</v>
       </c>
       <c r="B49" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5440,10 +5458,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>716995</v>
+        <v>717013</v>
       </c>
       <c r="R49" t="n">
-        <v>6374147</v>
+        <v>6374176</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5503,10 +5521,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128738896</v>
+        <v>128742269</v>
       </c>
       <c r="B50" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5538,10 +5556,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>717038</v>
+        <v>717186</v>
       </c>
       <c r="R50" t="n">
-        <v>6374195</v>
+        <v>6374129</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5571,19 +5589,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>10:50</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5599,44 +5607,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128738880</v>
+        <v>128742288</v>
       </c>
       <c r="B51" t="n">
-        <v>86784</v>
+        <v>86963</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5646,10 +5654,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>716983</v>
+        <v>716995</v>
       </c>
       <c r="R51" t="n">
-        <v>6374266</v>
+        <v>6374147</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5679,71 +5687,62 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128738838</v>
+        <v>128738896</v>
       </c>
       <c r="B52" t="n">
-        <v>87004</v>
+        <v>86963</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5753,10 +5752,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>717020</v>
+        <v>717038</v>
       </c>
       <c r="R52" t="n">
-        <v>6374199</v>
+        <v>6374195</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5788,7 +5787,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5798,7 +5797,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5807,6 +5806,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5825,10 +5825,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128742291</v>
+        <v>128742284</v>
       </c>
       <c r="B53" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5860,10 +5860,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>716977</v>
+        <v>717033</v>
       </c>
       <c r="R53" t="n">
-        <v>6374073</v>
+        <v>6374186</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5923,10 +5923,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128742284</v>
+        <v>128742291</v>
       </c>
       <c r="B54" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5958,10 +5958,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>717033</v>
+        <v>716977</v>
       </c>
       <c r="R54" t="n">
-        <v>6374186</v>
+        <v>6374073</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6021,32 +6021,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128738841</v>
+        <v>128742263</v>
       </c>
       <c r="B55" t="n">
-        <v>87004</v>
+        <v>91017</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3767</v>
+        <v>5741</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6056,10 +6056,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>716992</v>
+        <v>717281</v>
       </c>
       <c r="R55" t="n">
-        <v>6374116</v>
+        <v>6374199</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6089,19 +6089,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>09:50</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6116,22 +6106,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128738835</v>
+        <v>128738841</v>
       </c>
       <c r="B56" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6163,10 +6153,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>716983</v>
+        <v>716992</v>
       </c>
       <c r="R56" t="n">
-        <v>6374357</v>
+        <v>6374116</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6198,7 +6188,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6208,7 +6198,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6235,32 +6225,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128740522</v>
+        <v>128738835</v>
       </c>
       <c r="B57" t="n">
-        <v>86922</v>
+        <v>87008</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6270,10 +6260,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>717274</v>
+        <v>716983</v>
       </c>
       <c r="R57" t="n">
-        <v>6374210</v>
+        <v>6374357</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6303,9 +6293,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6320,12 +6320,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6335,7 +6335,7 @@
         <v>128742252</v>
       </c>
       <c r="B58" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6429,10 +6429,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128742263</v>
+        <v>128740522</v>
       </c>
       <c r="B59" t="n">
-        <v>91013</v>
+        <v>86926</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6440,21 +6440,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5741</v>
+        <v>3674</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6464,10 +6464,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>717281</v>
+        <v>717274</v>
       </c>
       <c r="R59" t="n">
-        <v>6374199</v>
+        <v>6374210</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6514,12 +6514,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6529,7 +6529,7 @@
         <v>128742282</v>
       </c>
       <c r="B60" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6624,10 +6624,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128738884</v>
+        <v>128742276</v>
       </c>
       <c r="B61" t="n">
-        <v>86806</v>
+        <v>86985</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6635,21 +6635,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>424</v>
+        <v>449</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6659,10 +6659,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>716969</v>
+        <v>717269</v>
       </c>
       <c r="R61" t="n">
-        <v>6374310</v>
+        <v>6374317</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6692,19 +6692,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>14:32</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6719,22 +6709,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128742276</v>
+        <v>128738884</v>
       </c>
       <c r="B62" t="n">
-        <v>86981</v>
+        <v>86810</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6742,21 +6732,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>449</v>
+        <v>424</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6766,10 +6756,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>717269</v>
+        <v>716969</v>
       </c>
       <c r="R62" t="n">
-        <v>6374317</v>
+        <v>6374310</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6799,9 +6789,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6816,12 +6816,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -6831,7 +6831,7 @@
         <v>128740491</v>
       </c>
       <c r="B63" t="n">
-        <v>86760</v>
+        <v>86764</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>128742255</v>
       </c>
       <c r="B64" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7025,7 +7025,7 @@
         <v>128738848</v>
       </c>
       <c r="B65" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>128738851</v>
       </c>
       <c r="B66" t="n">
-        <v>86760</v>
+        <v>86764</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>128740512</v>
       </c>
       <c r="B67" t="n">
-        <v>86784</v>
+        <v>86788</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>128738836</v>
       </c>
       <c r="B68" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>128738855</v>
       </c>
       <c r="B69" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>128738852</v>
       </c>
       <c r="B70" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7656,32 +7656,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128742287</v>
+        <v>128740508</v>
       </c>
       <c r="B71" t="n">
-        <v>86959</v>
+        <v>86985</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7691,10 +7691,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>717013</v>
+        <v>717063</v>
       </c>
       <c r="R71" t="n">
-        <v>6374166</v>
+        <v>6374397</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7735,51 +7735,50 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128742270</v>
+        <v>128742251</v>
       </c>
       <c r="B72" t="n">
-        <v>86959</v>
+        <v>87008</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7789,10 +7788,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>717071</v>
+        <v>717106</v>
       </c>
       <c r="R72" t="n">
-        <v>6374305</v>
+        <v>6374415</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7833,7 +7832,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7852,32 +7850,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128742290</v>
+        <v>128738833</v>
       </c>
       <c r="B73" t="n">
-        <v>86959</v>
+        <v>87008</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7887,10 +7885,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>716979</v>
+        <v>716976</v>
       </c>
       <c r="R73" t="n">
-        <v>6374069</v>
+        <v>6374331</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7920,62 +7918,71 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128742251</v>
+        <v>128740519</v>
       </c>
       <c r="B74" t="n">
-        <v>87004</v>
+        <v>86926</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7985,10 +7992,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>717106</v>
+        <v>717067</v>
       </c>
       <c r="R74" t="n">
-        <v>6374415</v>
+        <v>6374399</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8035,44 +8042,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128740519</v>
+        <v>128742287</v>
       </c>
       <c r="B75" t="n">
-        <v>86922</v>
+        <v>86963</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8082,10 +8089,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>717067</v>
+        <v>717013</v>
       </c>
       <c r="R75" t="n">
-        <v>6374399</v>
+        <v>6374166</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8126,50 +8133,51 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128738833</v>
+        <v>128742290</v>
       </c>
       <c r="B76" t="n">
-        <v>87004</v>
+        <v>86963</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8179,10 +8187,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>716976</v>
+        <v>716979</v>
       </c>
       <c r="R76" t="n">
-        <v>6374331</v>
+        <v>6374069</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8212,71 +8220,62 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128740508</v>
+        <v>128742270</v>
       </c>
       <c r="B77" t="n">
-        <v>86981</v>
+        <v>86963</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8286,10 +8285,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>717063</v>
+        <v>717071</v>
       </c>
       <c r="R77" t="n">
-        <v>6374397</v>
+        <v>6374305</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8330,18 +8329,19 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8351,7 +8351,7 @@
         <v>128740516</v>
       </c>
       <c r="B78" t="n">
-        <v>92136</v>
+        <v>92140</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>128738891</v>
       </c>
       <c r="B79" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>128738890</v>
       </c>
       <c r="B80" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8661,32 +8661,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128740518</v>
+        <v>128740484</v>
       </c>
       <c r="B81" t="n">
-        <v>86922</v>
+        <v>87008</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8696,10 +8696,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>717062</v>
+        <v>717279</v>
       </c>
       <c r="R81" t="n">
-        <v>6374393</v>
+        <v>6374209</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8751,39 +8751,39 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128740484</v>
+        <v>128740518</v>
       </c>
       <c r="B82" t="n">
-        <v>87004</v>
+        <v>86926</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8793,10 +8793,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>717279</v>
+        <v>717062</v>
       </c>
       <c r="R82" t="n">
-        <v>6374209</v>
+        <v>6374393</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8848,17 +8848,17 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128740503</v>
+        <v>128740510</v>
       </c>
       <c r="B83" t="n">
-        <v>86959</v>
+        <v>86929</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8866,21 +8866,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6003295</v>
+        <v>6037417</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8890,10 +8890,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>717212</v>
+        <v>717105</v>
       </c>
       <c r="R83" t="n">
-        <v>6374189</v>
+        <v>6374479</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8934,7 +8934,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -8953,10 +8952,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128740510</v>
+        <v>128740503</v>
       </c>
       <c r="B84" t="n">
-        <v>86925</v>
+        <v>86963</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8964,21 +8963,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6037417</v>
+        <v>6003295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8988,10 +8987,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>717105</v>
+        <v>717212</v>
       </c>
       <c r="R84" t="n">
-        <v>6374479</v>
+        <v>6374189</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9032,6 +9031,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9053,7 +9053,7 @@
         <v>128738899</v>
       </c>
       <c r="B85" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>128806499</v>
       </c>
       <c r="B86" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>128806483</v>
       </c>
       <c r="B87" t="n">
-        <v>90979</v>
+        <v>90983</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
         <v>128815957</v>
       </c>
       <c r="B88" t="n">
-        <v>86976</v>
+        <v>86980</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>128738885</v>
       </c>
       <c r="B89" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
         <v>128806494</v>
       </c>
       <c r="B90" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>128806493</v>
       </c>
       <c r="B91" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         <v>128805996</v>
       </c>
       <c r="B92" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9869,10 +9869,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128738839</v>
+        <v>128806044</v>
       </c>
       <c r="B93" t="n">
-        <v>87004</v>
+        <v>86985</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9880,21 +9880,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9904,10 +9904,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>717039</v>
+        <v>717148</v>
       </c>
       <c r="R93" t="n">
-        <v>6374168</v>
+        <v>6374175</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9934,22 +9934,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>10:24</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>10:24</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9964,22 +9954,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128738846</v>
+        <v>128806038</v>
       </c>
       <c r="B94" t="n">
-        <v>91013</v>
+        <v>98658</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9987,21 +9977,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5741</v>
+        <v>219862</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10011,10 +10001,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>717037</v>
+        <v>717113</v>
       </c>
       <c r="R94" t="n">
-        <v>6374226</v>
+        <v>6374105</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10041,22 +10031,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10071,12 +10051,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -10086,7 +10066,7 @@
         <v>128815850</v>
       </c>
       <c r="B95" t="n">
-        <v>89482</v>
+        <v>89486</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10190,32 +10170,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128806044</v>
+        <v>128738846</v>
       </c>
       <c r="B96" t="n">
-        <v>86981</v>
+        <v>91017</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>449</v>
+        <v>5741</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10225,10 +10205,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>717148</v>
+        <v>717037</v>
       </c>
       <c r="R96" t="n">
-        <v>6374175</v>
+        <v>6374226</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10255,12 +10235,22 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10275,44 +10265,44 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128806038</v>
+        <v>128738839</v>
       </c>
       <c r="B97" t="n">
-        <v>98654</v>
+        <v>87008</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>219862</v>
+        <v>3767</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10322,10 +10312,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>717113</v>
+        <v>717039</v>
       </c>
       <c r="R97" t="n">
-        <v>6374105</v>
+        <v>6374168</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10352,12 +10342,22 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10372,12 +10372,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -10387,7 +10387,7 @@
         <v>128806004</v>
       </c>
       <c r="B98" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>128806484</v>
       </c>
       <c r="B99" t="n">
-        <v>90979</v>
+        <v>90983</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10582,32 +10582,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128806009</v>
+        <v>128806005</v>
       </c>
       <c r="B100" t="n">
-        <v>86959</v>
+        <v>91017</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6003295</v>
+        <v>5741</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10617,10 +10617,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>717132</v>
+        <v>717142</v>
       </c>
       <c r="R100" t="n">
-        <v>6374140</v>
+        <v>6374197</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10661,7 +10661,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10673,17 +10672,17 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128738866</v>
+        <v>128806009</v>
       </c>
       <c r="B101" t="n">
-        <v>90245</v>
+        <v>86963</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10691,21 +10690,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>970</v>
+        <v>6003295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10715,10 +10714,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>717039</v>
+        <v>717132</v>
       </c>
       <c r="R101" t="n">
-        <v>6374321</v>
+        <v>6374140</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10745,22 +10744,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>13:50</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>13:50</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10776,44 +10765,44 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128806005</v>
+        <v>128738866</v>
       </c>
       <c r="B102" t="n">
-        <v>91013</v>
+        <v>90249</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5741</v>
+        <v>970</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10823,10 +10812,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>717142</v>
+        <v>717039</v>
       </c>
       <c r="R102" t="n">
-        <v>6374197</v>
+        <v>6374321</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10853,12 +10842,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10867,18 +10866,19 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -10888,7 +10888,7 @@
         <v>128738897</v>
       </c>
       <c r="B103" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>128738875</v>
       </c>
       <c r="B104" t="n">
-        <v>87016</v>
+        <v>87020</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11096,10 +11096,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128738842</v>
+        <v>128805993</v>
       </c>
       <c r="B105" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11131,10 +11131,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>716981</v>
+        <v>717148</v>
       </c>
       <c r="R105" t="n">
-        <v>6374088</v>
+        <v>6374174</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11161,22 +11161,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>09:31</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>09:31</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11191,22 +11181,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128805993</v>
+        <v>128738842</v>
       </c>
       <c r="B106" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11238,10 +11228,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>717148</v>
+        <v>716981</v>
       </c>
       <c r="R106" t="n">
-        <v>6374174</v>
+        <v>6374088</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11268,12 +11258,22 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11288,22 +11288,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128806023</v>
+        <v>128806056</v>
       </c>
       <c r="B107" t="n">
-        <v>86959</v>
+        <v>106961</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11311,21 +11311,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6003295</v>
+        <v>221849</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11335,10 +11335,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>717360</v>
+        <v>717370</v>
       </c>
       <c r="R107" t="n">
-        <v>6374214</v>
+        <v>6374168</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11379,7 +11379,6 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11391,39 +11390,39 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128738843</v>
+        <v>128806010</v>
       </c>
       <c r="B108" t="n">
-        <v>87004</v>
+        <v>86963</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11433,10 +11432,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>716967</v>
+        <v>717186</v>
       </c>
       <c r="R108" t="n">
-        <v>6374084</v>
+        <v>6374253</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11463,22 +11462,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>09:26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>09:26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11487,28 +11476,29 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128806056</v>
+        <v>128806023</v>
       </c>
       <c r="B109" t="n">
-        <v>106957</v>
+        <v>86963</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11516,21 +11506,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221849</v>
+        <v>6003295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11540,10 +11530,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>717370</v>
+        <v>717360</v>
       </c>
       <c r="R109" t="n">
-        <v>6374168</v>
+        <v>6374214</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11584,6 +11574,7 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -11595,39 +11586,39 @@
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128806010</v>
+        <v>128738843</v>
       </c>
       <c r="B110" t="n">
-        <v>86959</v>
+        <v>87008</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11637,10 +11628,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>717186</v>
+        <v>716967</v>
       </c>
       <c r="R110" t="n">
-        <v>6374253</v>
+        <v>6374084</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11667,12 +11658,22 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11681,51 +11682,50 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128806497</v>
+        <v>128806022</v>
       </c>
       <c r="B111" t="n">
-        <v>86784</v>
+        <v>86963</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11735,10 +11735,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>717273</v>
+        <v>717284</v>
       </c>
       <c r="R111" t="n">
-        <v>6374182</v>
+        <v>6374309</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11779,18 +11779,19 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -11800,7 +11801,7 @@
         <v>128738840</v>
       </c>
       <c r="B112" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11904,32 +11905,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128806022</v>
+        <v>128806497</v>
       </c>
       <c r="B113" t="n">
-        <v>86959</v>
+        <v>86788</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11939,10 +11940,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>717284</v>
+        <v>717273</v>
       </c>
       <c r="R113" t="n">
-        <v>6374309</v>
+        <v>6374182</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11983,19 +11984,18 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
@@ -12005,7 +12005,7 @@
         <v>128738886</v>
       </c>
       <c r="B114" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         <v>128806495</v>
       </c>
       <c r="B115" t="n">
-        <v>86846</v>
+        <v>86850</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         <v>128806049</v>
       </c>
       <c r="B116" t="n">
-        <v>87016</v>
+        <v>87020</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>128806064</v>
       </c>
       <c r="B117" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12396,32 +12396,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128738893</v>
+        <v>128806043</v>
       </c>
       <c r="B118" t="n">
-        <v>86959</v>
+        <v>75147</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6003295</v>
+        <v>6426</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12431,10 +12431,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>717000</v>
+        <v>717359</v>
       </c>
       <c r="R118" t="n">
-        <v>6374121</v>
+        <v>6374214</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12461,22 +12461,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>10:04</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>10:04</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12485,51 +12475,50 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128806043</v>
+        <v>128806050</v>
       </c>
       <c r="B119" t="n">
-        <v>75143</v>
+        <v>86929</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6426</v>
+        <v>6037417</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12539,10 +12528,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>717359</v>
+        <v>717311</v>
       </c>
       <c r="R119" t="n">
-        <v>6374214</v>
+        <v>6374287</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12583,6 +12572,7 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -12601,10 +12591,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128806050</v>
+        <v>128738893</v>
       </c>
       <c r="B120" t="n">
-        <v>86925</v>
+        <v>86963</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12612,21 +12602,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6037417</v>
+        <v>6003295</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12636,10 +12626,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>717311</v>
+        <v>717000</v>
       </c>
       <c r="R120" t="n">
-        <v>6374287</v>
+        <v>6374121</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12666,12 +12656,22 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12687,12 +12687,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -12702,7 +12702,7 @@
         <v>128806052</v>
       </c>
       <c r="B121" t="n">
-        <v>86784</v>
+        <v>86788</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12799,7 +12799,7 @@
         <v>128738892</v>
       </c>
       <c r="B122" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12907,7 +12907,7 @@
         <v>128738882</v>
       </c>
       <c r="B123" t="n">
-        <v>87086</v>
+        <v>87090</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13015,32 +13015,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128806051</v>
+        <v>128738894</v>
       </c>
       <c r="B124" t="n">
-        <v>86784</v>
+        <v>86963</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13050,10 +13050,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>717327</v>
+        <v>716975</v>
       </c>
       <c r="R124" t="n">
-        <v>6374171</v>
+        <v>6374071</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13080,12 +13080,22 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13094,50 +13104,51 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128738894</v>
+        <v>128806051</v>
       </c>
       <c r="B125" t="n">
-        <v>86959</v>
+        <v>86788</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13147,10 +13158,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>716975</v>
+        <v>717327</v>
       </c>
       <c r="R125" t="n">
-        <v>6374071</v>
+        <v>6374171</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13177,22 +13188,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>09:15</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>09:15</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13201,51 +13202,50 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128806045</v>
+        <v>128806011</v>
       </c>
       <c r="B126" t="n">
-        <v>86981</v>
+        <v>86963</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13255,10 +13255,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>717324</v>
+        <v>717367</v>
       </c>
       <c r="R126" t="n">
-        <v>6374179</v>
+        <v>6374231</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13299,6 +13299,7 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13310,39 +13311,39 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128806011</v>
+        <v>128806045</v>
       </c>
       <c r="B127" t="n">
-        <v>86959</v>
+        <v>86985</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13352,10 +13353,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>717367</v>
+        <v>717324</v>
       </c>
       <c r="R127" t="n">
-        <v>6374231</v>
+        <v>6374179</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13396,7 +13397,6 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13408,39 +13408,39 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128806485</v>
+        <v>128806492</v>
       </c>
       <c r="B128" t="n">
-        <v>86784</v>
+        <v>91043</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>3712</v>
+        <v>5747</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13450,10 +13450,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>717201</v>
+        <v>717146</v>
       </c>
       <c r="R128" t="n">
-        <v>6374297</v>
+        <v>6374178</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13494,7 +13494,6 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13513,32 +13512,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128806492</v>
+        <v>128806485</v>
       </c>
       <c r="B129" t="n">
-        <v>91039</v>
+        <v>86788</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5747</v>
+        <v>3712</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13548,10 +13547,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>717146</v>
+        <v>717201</v>
       </c>
       <c r="R129" t="n">
-        <v>6374178</v>
+        <v>6374297</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13592,6 +13591,7 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13613,7 +13613,7 @@
         <v>128806491</v>
       </c>
       <c r="B130" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>128806057</v>
       </c>
       <c r="B131" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13805,32 +13805,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128806487</v>
+        <v>128806058</v>
       </c>
       <c r="B132" t="n">
-        <v>87004</v>
+        <v>86926</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13840,10 +13840,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>717275</v>
+        <v>717196</v>
       </c>
       <c r="R132" t="n">
-        <v>6374183</v>
+        <v>6374281</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13890,22 +13890,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128738847</v>
+        <v>128806487</v>
       </c>
       <c r="B133" t="n">
-        <v>86875</v>
+        <v>87008</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13913,21 +13913,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>248956</v>
+        <v>3767</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13937,10 +13937,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>716980</v>
+        <v>717275</v>
       </c>
       <c r="R133" t="n">
-        <v>6374264</v>
+        <v>6374183</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13967,22 +13967,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -13997,44 +13987,44 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128806058</v>
+        <v>128738847</v>
       </c>
       <c r="B134" t="n">
-        <v>86922</v>
+        <v>86879</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>3674</v>
+        <v>248956</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14044,10 +14034,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>717196</v>
+        <v>716980</v>
       </c>
       <c r="R134" t="n">
-        <v>6374281</v>
+        <v>6374264</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14074,12 +14064,22 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14094,12 +14094,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
@@ -14109,7 +14109,7 @@
         <v>128806490</v>
       </c>
       <c r="B135" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         <v>128806013</v>
       </c>
       <c r="B136" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14305,7 +14305,7 @@
         <v>128806065</v>
       </c>
       <c r="B137" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14402,7 +14402,7 @@
         <v>128806486</v>
       </c>
       <c r="B138" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         <v>128806496</v>
       </c>
       <c r="B139" t="n">
-        <v>96228</v>
+        <v>96232</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14596,7 +14596,7 @@
         <v>128805991</v>
       </c>
       <c r="B140" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14690,32 +14690,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128806024</v>
+        <v>128738883</v>
       </c>
       <c r="B141" t="n">
-        <v>86959</v>
+        <v>86826</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6003295</v>
+        <v>3561</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blåbandad spindling</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius borgsjoeensis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14725,10 +14725,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>717366</v>
+        <v>716993</v>
       </c>
       <c r="R141" t="n">
-        <v>6374150</v>
+        <v>6374384</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14755,12 +14755,22 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14776,44 +14786,44 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128738883</v>
+        <v>128806024</v>
       </c>
       <c r="B142" t="n">
-        <v>86822</v>
+        <v>86963</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>3561</v>
+        <v>6003295</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Blåbandad spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cortinarius borgsjoeensis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14823,10 +14833,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>716993</v>
+        <v>717366</v>
       </c>
       <c r="R142" t="n">
-        <v>6374384</v>
+        <v>6374150</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14853,22 +14863,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -14884,12 +14884,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
@@ -14899,7 +14899,7 @@
         <v>128738867</v>
       </c>
       <c r="B143" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>128742275</v>
       </c>
       <c r="B144" t="n">
-        <v>86910</v>
+        <v>86914</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 42607-2025 artfynd.xlsx
+++ b/artfynd/A 42607-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128738845</v>
+        <v>128738854</v>
       </c>
       <c r="B2" t="n">
-        <v>86764</v>
+        <v>86963</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716961</v>
+        <v>716967</v>
       </c>
       <c r="R2" t="n">
-        <v>6374255</v>
+        <v>6374338</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,6 +764,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,32 +783,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128740514</v>
+        <v>128740487</v>
       </c>
       <c r="B3" t="n">
-        <v>86788</v>
+        <v>86963</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717295</v>
+        <v>717292</v>
       </c>
       <c r="R3" t="n">
-        <v>6374249</v>
+        <v>6374265</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,6 +862,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -872,39 +874,39 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128738831</v>
+        <v>128738845</v>
       </c>
       <c r="B4" t="n">
-        <v>87008</v>
+        <v>86764</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717030</v>
+        <v>716961</v>
       </c>
       <c r="R4" t="n">
-        <v>6374429</v>
+        <v>6374255</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,7 +951,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -959,7 +961,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,7 +988,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128742256</v>
+        <v>128738831</v>
       </c>
       <c r="B5" t="n">
         <v>87008</v>
@@ -1021,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717053</v>
+        <v>717030</v>
       </c>
       <c r="R5" t="n">
-        <v>6374253</v>
+        <v>6374429</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,9 +1056,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,44 +1083,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128740505</v>
+        <v>128742256</v>
       </c>
       <c r="B6" t="n">
-        <v>98658</v>
+        <v>87008</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219862</v>
+        <v>3767</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717182</v>
+        <v>717053</v>
       </c>
       <c r="R6" t="n">
-        <v>6374336</v>
+        <v>6374253</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,44 +1180,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128738854</v>
+        <v>128740514</v>
       </c>
       <c r="B7" t="n">
-        <v>86963</v>
+        <v>86788</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1227,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716967</v>
+        <v>717295</v>
       </c>
       <c r="R7" t="n">
-        <v>6374338</v>
+        <v>6374249</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1248,72 +1260,61 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128740487</v>
+        <v>128740505</v>
       </c>
       <c r="B8" t="n">
-        <v>86963</v>
+        <v>98658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6003295</v>
+        <v>219862</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1323,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717292</v>
+        <v>717182</v>
       </c>
       <c r="R8" t="n">
-        <v>6374265</v>
+        <v>6374336</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,7 +1368,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1805,32 +1805,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128740482</v>
+        <v>128742285</v>
       </c>
       <c r="B13" t="n">
-        <v>87008</v>
+        <v>86963</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>717057</v>
+        <v>716995</v>
       </c>
       <c r="R13" t="n">
-        <v>6374457</v>
+        <v>6374141</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1884,50 +1884,51 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128742285</v>
+        <v>128740504</v>
       </c>
       <c r="B14" t="n">
-        <v>86963</v>
+        <v>98658</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6003295</v>
+        <v>219862</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1937,10 +1938,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716995</v>
+        <v>717091</v>
       </c>
       <c r="R14" t="n">
-        <v>6374141</v>
+        <v>6374400</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1981,51 +1982,50 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128740504</v>
+        <v>128740482</v>
       </c>
       <c r="B15" t="n">
-        <v>98658</v>
+        <v>87008</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219862</v>
+        <v>3767</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2035,10 +2035,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>717091</v>
+        <v>717057</v>
       </c>
       <c r="R15" t="n">
-        <v>6374400</v>
+        <v>6374457</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2607,14 +2607,14 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128738856</v>
+        <v>128738857</v>
       </c>
       <c r="B21" t="n">
         <v>86963</v>
@@ -2649,10 +2649,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>716986</v>
+        <v>717049</v>
       </c>
       <c r="R21" t="n">
-        <v>6374339</v>
+        <v>6374317</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2722,7 +2722,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128738857</v>
+        <v>128738856</v>
       </c>
       <c r="B22" t="n">
         <v>86963</v>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>717049</v>
+        <v>716986</v>
       </c>
       <c r="R22" t="n">
-        <v>6374317</v>
+        <v>6374339</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3218,32 +3218,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128742283</v>
+        <v>128740489</v>
       </c>
       <c r="B27" t="n">
-        <v>86963</v>
+        <v>91017</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6003295</v>
+        <v>5741</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>717040</v>
+        <v>717220</v>
       </c>
       <c r="R27" t="n">
-        <v>6374195</v>
+        <v>6374302</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3297,26 +3297,25 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128742281</v>
+        <v>128742283</v>
       </c>
       <c r="B28" t="n">
         <v>86963</v>
@@ -3351,10 +3350,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>717039</v>
+        <v>717040</v>
       </c>
       <c r="R28" t="n">
-        <v>6374227</v>
+        <v>6374195</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3414,32 +3413,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128740489</v>
+        <v>128742281</v>
       </c>
       <c r="B29" t="n">
-        <v>91017</v>
+        <v>86963</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5741</v>
+        <v>6003295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3449,10 +3448,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>717220</v>
+        <v>717039</v>
       </c>
       <c r="R29" t="n">
-        <v>6374302</v>
+        <v>6374227</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3493,50 +3492,51 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128742272</v>
+        <v>128742293</v>
       </c>
       <c r="B30" t="n">
-        <v>91043</v>
+        <v>86926</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5747</v>
+        <v>3674</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3546,10 +3546,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>717018</v>
+        <v>717094</v>
       </c>
       <c r="R30" t="n">
-        <v>6374179</v>
+        <v>6374468</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3608,32 +3608,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128742293</v>
+        <v>128742254</v>
       </c>
       <c r="B31" t="n">
-        <v>86926</v>
+        <v>87008</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>717094</v>
+        <v>717285</v>
       </c>
       <c r="R31" t="n">
-        <v>6374468</v>
+        <v>6374272</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3705,32 +3705,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128742254</v>
+        <v>128740500</v>
       </c>
       <c r="B32" t="n">
-        <v>87008</v>
+        <v>86963</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>717285</v>
+        <v>717281</v>
       </c>
       <c r="R32" t="n">
-        <v>6374272</v>
+        <v>6374283</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3784,25 +3784,26 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128740500</v>
+        <v>128740499</v>
       </c>
       <c r="B33" t="n">
         <v>86963</v>
@@ -3837,10 +3838,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>717281</v>
+        <v>717145</v>
       </c>
       <c r="R33" t="n">
-        <v>6374283</v>
+        <v>6374308</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3893,7 +3894,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -3991,39 +3992,39 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128740499</v>
+        <v>128742272</v>
       </c>
       <c r="B35" t="n">
-        <v>86963</v>
+        <v>91043</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6003295</v>
+        <v>5747</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4033,10 +4034,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>717145</v>
+        <v>717018</v>
       </c>
       <c r="R35" t="n">
-        <v>6374308</v>
+        <v>6374179</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4077,51 +4078,50 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128740521</v>
+        <v>128742267</v>
       </c>
       <c r="B36" t="n">
-        <v>86926</v>
+        <v>86963</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4131,10 +4131,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>717216</v>
+        <v>717105</v>
       </c>
       <c r="R36" t="n">
-        <v>6374357</v>
+        <v>6374393</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4175,50 +4175,51 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128738900</v>
+        <v>128738858</v>
       </c>
       <c r="B37" t="n">
-        <v>86926</v>
+        <v>86963</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4228,10 +4229,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>716960</v>
+        <v>717003</v>
       </c>
       <c r="R37" t="n">
-        <v>6374079</v>
+        <v>6374177</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4263,7 +4264,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4273,7 +4274,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4282,6 +4283,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4300,32 +4302,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128738858</v>
+        <v>128740521</v>
       </c>
       <c r="B38" t="n">
-        <v>86963</v>
+        <v>86926</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4335,10 +4337,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>717003</v>
+        <v>717216</v>
       </c>
       <c r="R38" t="n">
-        <v>6374177</v>
+        <v>6374357</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4368,72 +4370,61 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128742267</v>
+        <v>128738900</v>
       </c>
       <c r="B39" t="n">
-        <v>86963</v>
+        <v>86926</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4443,10 +4434,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>717105</v>
+        <v>716960</v>
       </c>
       <c r="R39" t="n">
-        <v>6374393</v>
+        <v>6374079</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4476,30 +4467,39 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4807,7 +4807,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128742268</v>
+        <v>128738895</v>
       </c>
       <c r="B43" t="n">
         <v>86963</v>
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>717267</v>
+        <v>716974</v>
       </c>
       <c r="R43" t="n">
-        <v>6374322</v>
+        <v>6374284</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4875,9 +4875,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4893,19 +4903,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128738895</v>
+        <v>128742268</v>
       </c>
       <c r="B44" t="n">
         <v>86963</v>
@@ -4940,10 +4950,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>716974</v>
+        <v>717267</v>
       </c>
       <c r="R44" t="n">
-        <v>6374284</v>
+        <v>6374322</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4973,19 +4983,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5001,12 +5001,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5423,7 +5423,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128742279</v>
+        <v>128742269</v>
       </c>
       <c r="B49" t="n">
         <v>86963</v>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>717013</v>
+        <v>717186</v>
       </c>
       <c r="R49" t="n">
-        <v>6374176</v>
+        <v>6374129</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5521,7 +5521,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128742269</v>
+        <v>128742279</v>
       </c>
       <c r="B50" t="n">
         <v>86963</v>
@@ -5556,10 +5556,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>717186</v>
+        <v>717013</v>
       </c>
       <c r="R50" t="n">
-        <v>6374129</v>
+        <v>6374176</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5825,7 +5825,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128742284</v>
+        <v>128742291</v>
       </c>
       <c r="B53" t="n">
         <v>86963</v>
@@ -5860,10 +5860,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>717033</v>
+        <v>716977</v>
       </c>
       <c r="R53" t="n">
-        <v>6374186</v>
+        <v>6374073</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5923,7 +5923,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128742291</v>
+        <v>128742284</v>
       </c>
       <c r="B54" t="n">
         <v>86963</v>
@@ -5958,10 +5958,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>716977</v>
+        <v>717033</v>
       </c>
       <c r="R54" t="n">
-        <v>6374073</v>
+        <v>6374186</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7656,32 +7656,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128740508</v>
+        <v>128742287</v>
       </c>
       <c r="B71" t="n">
-        <v>86985</v>
+        <v>86963</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7691,10 +7691,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>717063</v>
+        <v>717013</v>
       </c>
       <c r="R71" t="n">
-        <v>6374397</v>
+        <v>6374166</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7735,50 +7735,51 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128742251</v>
+        <v>128742270</v>
       </c>
       <c r="B72" t="n">
-        <v>87008</v>
+        <v>86963</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7788,10 +7789,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>717106</v>
+        <v>717071</v>
       </c>
       <c r="R72" t="n">
-        <v>6374415</v>
+        <v>6374305</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7832,6 +7833,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7850,32 +7852,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128738833</v>
+        <v>128742290</v>
       </c>
       <c r="B73" t="n">
-        <v>87008</v>
+        <v>86963</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7885,10 +7887,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>716976</v>
+        <v>716979</v>
       </c>
       <c r="R73" t="n">
-        <v>6374331</v>
+        <v>6374069</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7918,71 +7920,62 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128740519</v>
+        <v>128740508</v>
       </c>
       <c r="B74" t="n">
-        <v>86926</v>
+        <v>86985</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7992,10 +7985,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>717067</v>
+        <v>717063</v>
       </c>
       <c r="R74" t="n">
-        <v>6374399</v>
+        <v>6374397</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8047,39 +8040,39 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128742287</v>
+        <v>128742251</v>
       </c>
       <c r="B75" t="n">
-        <v>86963</v>
+        <v>87008</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8089,10 +8082,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>717013</v>
+        <v>717106</v>
       </c>
       <c r="R75" t="n">
-        <v>6374166</v>
+        <v>6374415</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8133,7 +8126,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8152,32 +8144,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128742290</v>
+        <v>128738833</v>
       </c>
       <c r="B76" t="n">
-        <v>86963</v>
+        <v>87008</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8187,10 +8179,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>716979</v>
+        <v>716976</v>
       </c>
       <c r="R76" t="n">
-        <v>6374069</v>
+        <v>6374331</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8220,62 +8212,71 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128742270</v>
+        <v>128740519</v>
       </c>
       <c r="B77" t="n">
-        <v>86963</v>
+        <v>86926</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8285,10 +8286,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>717071</v>
+        <v>717067</v>
       </c>
       <c r="R77" t="n">
-        <v>6374305</v>
+        <v>6374399</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8329,19 +8330,18 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8751,7 +8751,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -8855,10 +8855,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128740510</v>
+        <v>128740503</v>
       </c>
       <c r="B83" t="n">
-        <v>86929</v>
+        <v>86963</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8866,21 +8866,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6037417</v>
+        <v>6003295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8890,10 +8890,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>717105</v>
+        <v>717212</v>
       </c>
       <c r="R83" t="n">
-        <v>6374479</v>
+        <v>6374189</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8934,6 +8934,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -8945,17 +8946,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128740503</v>
+        <v>128740510</v>
       </c>
       <c r="B84" t="n">
-        <v>86963</v>
+        <v>86929</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8963,21 +8964,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6003295</v>
+        <v>6037417</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8987,10 +8988,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>717212</v>
+        <v>717105</v>
       </c>
       <c r="R84" t="n">
-        <v>6374189</v>
+        <v>6374479</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9031,7 +9032,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9254,10 +9254,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128806483</v>
+        <v>128815957</v>
       </c>
       <c r="B87" t="n">
-        <v>90983</v>
+        <v>86980</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9265,21 +9265,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>720</v>
+        <v>248934</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Knölfotad bananspindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Cortinarius stjernegaardii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>Brandrud &amp; Frøslev</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9292,10 +9292,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>717267</v>
+        <v>717020</v>
       </c>
       <c r="R87" t="n">
-        <v>6374381</v>
+        <v>6374147</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9322,12 +9322,27 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Bilddokumentation av Ullas fynd. Uppsvullen bulb och orange basalmycel. Ek fanss på fyndplatsen som domineras av kalktallskog.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9343,22 +9358,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128815957</v>
+        <v>128806483</v>
       </c>
       <c r="B88" t="n">
-        <v>86980</v>
+        <v>90983</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9366,21 +9381,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>248934</v>
+        <v>720</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knölfotad bananspindling</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cortinarius stjernegaardii</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Brandrud &amp; Frøslev</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9393,10 +9408,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>717020</v>
+        <v>717267</v>
       </c>
       <c r="R88" t="n">
-        <v>6374147</v>
+        <v>6374381</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9423,27 +9438,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>10:37</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Bilddokumentation av Ullas fynd. Uppsvullen bulb och orange basalmycel. Ek fanss på fyndplatsen som domineras av kalktallskog.</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9459,12 +9459,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -9578,10 +9578,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128806494</v>
+        <v>128805996</v>
       </c>
       <c r="B90" t="n">
-        <v>86985</v>
+        <v>87008</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9589,21 +9589,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9613,10 +9613,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>717333</v>
+        <v>717308</v>
       </c>
       <c r="R90" t="n">
-        <v>6374180</v>
+        <v>6374239</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9663,19 +9663,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128806493</v>
+        <v>128806494</v>
       </c>
       <c r="B91" t="n">
         <v>86985</v>
@@ -9710,10 +9710,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>717133</v>
+        <v>717333</v>
       </c>
       <c r="R91" t="n">
-        <v>6374199</v>
+        <v>6374180</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9772,10 +9772,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128805996</v>
+        <v>128806493</v>
       </c>
       <c r="B92" t="n">
-        <v>87008</v>
+        <v>86985</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9783,21 +9783,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9807,10 +9807,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>717308</v>
+        <v>717133</v>
       </c>
       <c r="R92" t="n">
-        <v>6374239</v>
+        <v>6374199</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9857,22 +9857,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128806044</v>
+        <v>128738839</v>
       </c>
       <c r="B93" t="n">
-        <v>86985</v>
+        <v>87008</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9880,21 +9880,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9904,10 +9904,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>717148</v>
+        <v>717039</v>
       </c>
       <c r="R93" t="n">
-        <v>6374175</v>
+        <v>6374168</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9934,12 +9934,22 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9954,44 +9964,44 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128806038</v>
+        <v>128806044</v>
       </c>
       <c r="B94" t="n">
-        <v>98658</v>
+        <v>86985</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>219862</v>
+        <v>449</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10001,10 +10011,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>717113</v>
+        <v>717148</v>
       </c>
       <c r="R94" t="n">
-        <v>6374105</v>
+        <v>6374175</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10063,10 +10073,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128815850</v>
+        <v>128738846</v>
       </c>
       <c r="B95" t="n">
-        <v>89486</v>
+        <v>91017</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10074,21 +10084,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>236437</v>
+        <v>5741</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Brun klibbskivling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Limacella glioderma</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Maire</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10098,10 +10108,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>716975</v>
+        <v>717037</v>
       </c>
       <c r="R95" t="n">
-        <v>6374071</v>
+        <v>6374226</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10133,7 +10143,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10143,7 +10153,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10170,10 +10180,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128738846</v>
+        <v>128806038</v>
       </c>
       <c r="B96" t="n">
-        <v>91017</v>
+        <v>98658</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10181,21 +10191,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5741</v>
+        <v>219862</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10205,10 +10215,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>717037</v>
+        <v>717113</v>
       </c>
       <c r="R96" t="n">
-        <v>6374226</v>
+        <v>6374105</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10235,22 +10245,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10265,44 +10265,44 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128738839</v>
+        <v>128815850</v>
       </c>
       <c r="B97" t="n">
-        <v>87008</v>
+        <v>89486</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3767</v>
+        <v>236437</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Brun klibbskivling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Limacella glioderma</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.) Maire</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10312,10 +10312,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>717039</v>
+        <v>716975</v>
       </c>
       <c r="R97" t="n">
-        <v>6374168</v>
+        <v>6374071</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10347,7 +10347,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10357,7 +10357,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10384,45 +10384,48 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128806004</v>
+        <v>128806484</v>
       </c>
       <c r="B98" t="n">
-        <v>91508</v>
+        <v>90983</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>720</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>717360</v>
+        <v>717273</v>
       </c>
       <c r="R98" t="n">
-        <v>6374175</v>
+        <v>6374379</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10463,66 +10466,64 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128806484</v>
+        <v>128806004</v>
       </c>
       <c r="B99" t="n">
-        <v>90983</v>
+        <v>91508</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>720</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>717273</v>
+        <v>717360</v>
       </c>
       <c r="R99" t="n">
-        <v>6374379</v>
+        <v>6374175</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10563,51 +10564,50 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128806005</v>
+        <v>128738866</v>
       </c>
       <c r="B100" t="n">
-        <v>91017</v>
+        <v>90249</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5741</v>
+        <v>970</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10617,10 +10617,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>717142</v>
+        <v>717039</v>
       </c>
       <c r="R100" t="n">
-        <v>6374197</v>
+        <v>6374321</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10647,12 +10647,22 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10661,18 +10671,19 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -10777,32 +10788,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128738866</v>
+        <v>128806005</v>
       </c>
       <c r="B102" t="n">
-        <v>90249</v>
+        <v>91017</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>970</v>
+        <v>5741</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10812,10 +10823,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>717039</v>
+        <v>717142</v>
       </c>
       <c r="R102" t="n">
-        <v>6374321</v>
+        <v>6374197</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10842,22 +10853,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>13:50</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>13:50</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10866,19 +10867,18 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -11096,7 +11096,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128805993</v>
+        <v>128738842</v>
       </c>
       <c r="B105" t="n">
         <v>87008</v>
@@ -11131,10 +11131,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>717148</v>
+        <v>716981</v>
       </c>
       <c r="R105" t="n">
-        <v>6374174</v>
+        <v>6374088</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11161,12 +11161,22 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11181,19 +11191,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128738842</v>
+        <v>128805993</v>
       </c>
       <c r="B106" t="n">
         <v>87008</v>
@@ -11228,10 +11238,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>716981</v>
+        <v>717148</v>
       </c>
       <c r="R106" t="n">
-        <v>6374088</v>
+        <v>6374174</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11258,22 +11268,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>09:31</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>09:31</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11288,44 +11288,44 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128806056</v>
+        <v>128738843</v>
       </c>
       <c r="B107" t="n">
-        <v>106961</v>
+        <v>87008</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221849</v>
+        <v>3767</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11335,10 +11335,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>717370</v>
+        <v>716967</v>
       </c>
       <c r="R107" t="n">
-        <v>6374168</v>
+        <v>6374084</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11365,12 +11365,22 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11385,12 +11395,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -11593,32 +11603,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128738843</v>
+        <v>128806056</v>
       </c>
       <c r="B110" t="n">
-        <v>87008</v>
+        <v>106961</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>3767</v>
+        <v>221849</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11628,10 +11638,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>716967</v>
+        <v>717370</v>
       </c>
       <c r="R110" t="n">
-        <v>6374084</v>
+        <v>6374168</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11658,22 +11668,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>09:26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>09:26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11688,44 +11688,44 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128806022</v>
+        <v>128738840</v>
       </c>
       <c r="B111" t="n">
-        <v>86963</v>
+        <v>87008</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11735,10 +11735,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>717284</v>
+        <v>717020</v>
       </c>
       <c r="R111" t="n">
-        <v>6374309</v>
+        <v>6374147</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11765,12 +11765,22 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11779,51 +11789,50 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128738840</v>
+        <v>128806497</v>
       </c>
       <c r="B112" t="n">
-        <v>87008</v>
+        <v>86788</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>3767</v>
+        <v>3712</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11833,10 +11842,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>717020</v>
+        <v>717273</v>
       </c>
       <c r="R112" t="n">
-        <v>6374147</v>
+        <v>6374182</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11863,22 +11872,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>10:06</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>10:06</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11893,44 +11892,44 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128806497</v>
+        <v>128806022</v>
       </c>
       <c r="B113" t="n">
-        <v>86788</v>
+        <v>86963</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11940,10 +11939,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>717273</v>
+        <v>717284</v>
       </c>
       <c r="R113" t="n">
-        <v>6374182</v>
+        <v>6374309</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11984,18 +11983,19 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
@@ -13015,32 +13015,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128738894</v>
+        <v>128806045</v>
       </c>
       <c r="B124" t="n">
-        <v>86963</v>
+        <v>86985</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13050,10 +13050,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>716975</v>
+        <v>717324</v>
       </c>
       <c r="R124" t="n">
-        <v>6374071</v>
+        <v>6374179</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13080,22 +13080,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>09:15</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>09:15</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13104,19 +13094,18 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -13220,7 +13209,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128806011</v>
+        <v>128738894</v>
       </c>
       <c r="B126" t="n">
         <v>86963</v>
@@ -13255,10 +13244,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>717367</v>
+        <v>716975</v>
       </c>
       <c r="R126" t="n">
-        <v>6374231</v>
+        <v>6374071</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13285,12 +13274,22 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13306,44 +13305,44 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128806045</v>
+        <v>128806011</v>
       </c>
       <c r="B127" t="n">
-        <v>86985</v>
+        <v>86963</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13353,10 +13352,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>717324</v>
+        <v>717367</v>
       </c>
       <c r="R127" t="n">
-        <v>6374179</v>
+        <v>6374231</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13397,6 +13396,7 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13408,39 +13408,39 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128806492</v>
+        <v>128806491</v>
       </c>
       <c r="B128" t="n">
-        <v>91043</v>
+        <v>86963</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13450,10 +13450,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>717146</v>
+        <v>717324</v>
       </c>
       <c r="R128" t="n">
-        <v>6374178</v>
+        <v>6374171</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13494,6 +13494,7 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13512,32 +13513,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128806485</v>
+        <v>128806492</v>
       </c>
       <c r="B129" t="n">
-        <v>86788</v>
+        <v>91043</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>3712</v>
+        <v>5747</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13547,10 +13548,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>717201</v>
+        <v>717146</v>
       </c>
       <c r="R129" t="n">
-        <v>6374297</v>
+        <v>6374178</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13591,7 +13592,6 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13610,32 +13610,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128806491</v>
+        <v>128806485</v>
       </c>
       <c r="B130" t="n">
-        <v>86963</v>
+        <v>86788</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13645,10 +13645,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>717324</v>
+        <v>717201</v>
       </c>
       <c r="R130" t="n">
-        <v>6374171</v>
+        <v>6374297</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13902,32 +13902,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128806487</v>
+        <v>128806490</v>
       </c>
       <c r="B133" t="n">
-        <v>87008</v>
+        <v>86963</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13937,10 +13937,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>717275</v>
+        <v>717333</v>
       </c>
       <c r="R133" t="n">
-        <v>6374183</v>
+        <v>6374202</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13981,6 +13981,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14106,32 +14107,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128806490</v>
+        <v>128806487</v>
       </c>
       <c r="B135" t="n">
-        <v>86963</v>
+        <v>87008</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14141,10 +14142,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>717333</v>
+        <v>717275</v>
       </c>
       <c r="R135" t="n">
-        <v>6374202</v>
+        <v>6374183</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14185,7 +14186,6 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -14496,32 +14496,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128806496</v>
+        <v>128805991</v>
       </c>
       <c r="B139" t="n">
-        <v>96232</v>
+        <v>87008</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2180</v>
+        <v>3767</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14531,10 +14531,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>717337</v>
+        <v>717147</v>
       </c>
       <c r="R139" t="n">
-        <v>6374082</v>
+        <v>6374164</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14581,22 +14581,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128805991</v>
+        <v>128738883</v>
       </c>
       <c r="B140" t="n">
-        <v>87008</v>
+        <v>86826</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14604,16 +14604,16 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>3767</v>
+        <v>3561</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blåbandad spindling</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius borgsjoeensis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -14628,10 +14628,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>717147</v>
+        <v>716993</v>
       </c>
       <c r="R140" t="n">
-        <v>6374164</v>
+        <v>6374384</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14658,12 +14658,22 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14672,50 +14682,51 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128738883</v>
+        <v>128806496</v>
       </c>
       <c r="B141" t="n">
-        <v>86826</v>
+        <v>96232</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3561</v>
+        <v>2180</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Blåbandad spindling</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cortinarius borgsjoeensis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14725,10 +14736,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>716993</v>
+        <v>717337</v>
       </c>
       <c r="R141" t="n">
-        <v>6374384</v>
+        <v>6374082</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14755,22 +14766,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14779,19 +14780,18 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>

--- a/artfynd/A 42607-2025 artfynd.xlsx
+++ b/artfynd/A 42607-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128738854</v>
+        <v>128738845</v>
       </c>
       <c r="B2" t="n">
-        <v>86963</v>
+        <v>86764</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716967</v>
+        <v>716961</v>
       </c>
       <c r="R2" t="n">
-        <v>6374338</v>
+        <v>6374255</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,7 +764,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -783,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128740487</v>
+        <v>128738831</v>
       </c>
       <c r="B3" t="n">
-        <v>86963</v>
+        <v>87008</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -818,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717292</v>
+        <v>717030</v>
       </c>
       <c r="R3" t="n">
-        <v>6374265</v>
+        <v>6374429</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,62 +850,71 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128738845</v>
+        <v>128742256</v>
       </c>
       <c r="B4" t="n">
-        <v>86764</v>
+        <v>87008</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -916,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716961</v>
+        <v>717053</v>
       </c>
       <c r="R4" t="n">
-        <v>6374255</v>
+        <v>6374253</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,19 +957,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,44 +974,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128738831</v>
+        <v>128740514</v>
       </c>
       <c r="B5" t="n">
-        <v>87008</v>
+        <v>86788</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3767</v>
+        <v>3712</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1023,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717030</v>
+        <v>717295</v>
       </c>
       <c r="R5" t="n">
-        <v>6374429</v>
+        <v>6374249</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,19 +1054,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,44 +1071,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128742256</v>
+        <v>128740505</v>
       </c>
       <c r="B6" t="n">
-        <v>87008</v>
+        <v>98658</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3767</v>
+        <v>219862</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1130,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717053</v>
+        <v>717182</v>
       </c>
       <c r="R6" t="n">
-        <v>6374253</v>
+        <v>6374336</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,44 +1168,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128740514</v>
+        <v>128738854</v>
       </c>
       <c r="B7" t="n">
-        <v>86788</v>
+        <v>86963</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1227,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717295</v>
+        <v>716967</v>
       </c>
       <c r="R7" t="n">
-        <v>6374249</v>
+        <v>6374338</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,61 +1248,72 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128740505</v>
+        <v>128740487</v>
       </c>
       <c r="B8" t="n">
-        <v>98658</v>
+        <v>86963</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219862</v>
+        <v>6003295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1323,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717182</v>
+        <v>717292</v>
       </c>
       <c r="R8" t="n">
-        <v>6374336</v>
+        <v>6374265</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,6 +1367,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1805,32 +1805,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128742285</v>
+        <v>128740482</v>
       </c>
       <c r="B13" t="n">
-        <v>86963</v>
+        <v>87008</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716995</v>
+        <v>717057</v>
       </c>
       <c r="R13" t="n">
-        <v>6374141</v>
+        <v>6374457</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1884,19 +1884,18 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1993,39 +1992,39 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128740482</v>
+        <v>128742285</v>
       </c>
       <c r="B15" t="n">
-        <v>87008</v>
+        <v>86963</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2035,10 +2034,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>717057</v>
+        <v>716995</v>
       </c>
       <c r="R15" t="n">
-        <v>6374457</v>
+        <v>6374141</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2079,18 +2078,19 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3121,10 +3121,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128742273</v>
+        <v>128740489</v>
       </c>
       <c r="B26" t="n">
-        <v>86939</v>
+        <v>91017</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3132,21 +3132,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1988</v>
+        <v>5741</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>717014</v>
+        <v>717220</v>
       </c>
       <c r="R26" t="n">
-        <v>6374164</v>
+        <v>6374302</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3206,44 +3206,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128740489</v>
+        <v>128742283</v>
       </c>
       <c r="B27" t="n">
-        <v>91017</v>
+        <v>86963</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5741</v>
+        <v>6003295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>717220</v>
+        <v>717040</v>
       </c>
       <c r="R27" t="n">
-        <v>6374302</v>
+        <v>6374195</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3297,25 +3297,26 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128742283</v>
+        <v>128742281</v>
       </c>
       <c r="B28" t="n">
         <v>86963</v>
@@ -3350,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>717040</v>
+        <v>717039</v>
       </c>
       <c r="R28" t="n">
-        <v>6374195</v>
+        <v>6374227</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3413,32 +3414,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128742281</v>
+        <v>128742273</v>
       </c>
       <c r="B29" t="n">
-        <v>86963</v>
+        <v>86939</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6003295</v>
+        <v>1988</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3448,10 +3449,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>717039</v>
+        <v>717014</v>
       </c>
       <c r="R29" t="n">
-        <v>6374227</v>
+        <v>6374164</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3492,7 +3493,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3511,32 +3511,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128742293</v>
+        <v>128742272</v>
       </c>
       <c r="B30" t="n">
-        <v>86926</v>
+        <v>91043</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3674</v>
+        <v>5747</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3546,10 +3546,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>717094</v>
+        <v>717018</v>
       </c>
       <c r="R30" t="n">
-        <v>6374468</v>
+        <v>6374179</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3608,32 +3608,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128742254</v>
+        <v>128742293</v>
       </c>
       <c r="B31" t="n">
-        <v>87008</v>
+        <v>86926</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>717285</v>
+        <v>717094</v>
       </c>
       <c r="R31" t="n">
-        <v>6374272</v>
+        <v>6374468</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3705,32 +3705,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128740500</v>
+        <v>128742254</v>
       </c>
       <c r="B32" t="n">
-        <v>86963</v>
+        <v>87008</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>717281</v>
+        <v>717285</v>
       </c>
       <c r="R32" t="n">
-        <v>6374283</v>
+        <v>6374272</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3784,26 +3784,25 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128740499</v>
+        <v>128740500</v>
       </c>
       <c r="B33" t="n">
         <v>86963</v>
@@ -3838,10 +3837,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>717145</v>
+        <v>717281</v>
       </c>
       <c r="R33" t="n">
-        <v>6374308</v>
+        <v>6374283</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3894,14 +3893,14 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128740502</v>
+        <v>128740499</v>
       </c>
       <c r="B34" t="n">
         <v>86963</v>
@@ -3936,10 +3935,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>717282</v>
+        <v>717145</v>
       </c>
       <c r="R34" t="n">
-        <v>6374266</v>
+        <v>6374308</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3992,39 +3991,39 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128742272</v>
+        <v>128740502</v>
       </c>
       <c r="B35" t="n">
-        <v>91043</v>
+        <v>86963</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4034,10 +4033,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>717018</v>
+        <v>717282</v>
       </c>
       <c r="R35" t="n">
-        <v>6374179</v>
+        <v>6374266</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4078,50 +4077,51 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128742267</v>
+        <v>128740521</v>
       </c>
       <c r="B36" t="n">
-        <v>86963</v>
+        <v>86926</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4131,10 +4131,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>717105</v>
+        <v>717216</v>
       </c>
       <c r="R36" t="n">
-        <v>6374393</v>
+        <v>6374357</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4175,51 +4175,50 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128738858</v>
+        <v>128738900</v>
       </c>
       <c r="B37" t="n">
-        <v>86963</v>
+        <v>86926</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4229,10 +4228,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>717003</v>
+        <v>716960</v>
       </c>
       <c r="R37" t="n">
-        <v>6374177</v>
+        <v>6374079</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4264,7 +4263,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4274,7 +4273,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4283,7 +4282,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4302,32 +4300,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128740521</v>
+        <v>128742267</v>
       </c>
       <c r="B38" t="n">
-        <v>86926</v>
+        <v>86963</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4337,10 +4335,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>717216</v>
+        <v>717105</v>
       </c>
       <c r="R38" t="n">
-        <v>6374357</v>
+        <v>6374393</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4381,50 +4379,51 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128738900</v>
+        <v>128738858</v>
       </c>
       <c r="B39" t="n">
-        <v>86926</v>
+        <v>86963</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4434,10 +4433,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>716960</v>
+        <v>717003</v>
       </c>
       <c r="R39" t="n">
-        <v>6374079</v>
+        <v>6374177</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4469,7 +4468,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4479,7 +4478,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4488,6 +4487,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7656,32 +7656,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128742287</v>
+        <v>128740508</v>
       </c>
       <c r="B71" t="n">
-        <v>86963</v>
+        <v>86985</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7691,10 +7691,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>717013</v>
+        <v>717063</v>
       </c>
       <c r="R71" t="n">
-        <v>6374166</v>
+        <v>6374397</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7735,51 +7735,50 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128742270</v>
+        <v>128742251</v>
       </c>
       <c r="B72" t="n">
-        <v>86963</v>
+        <v>87008</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7789,10 +7788,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>717071</v>
+        <v>717106</v>
       </c>
       <c r="R72" t="n">
-        <v>6374305</v>
+        <v>6374415</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7833,7 +7832,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7852,32 +7850,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128742290</v>
+        <v>128738833</v>
       </c>
       <c r="B73" t="n">
-        <v>86963</v>
+        <v>87008</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7887,10 +7885,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>716979</v>
+        <v>716976</v>
       </c>
       <c r="R73" t="n">
-        <v>6374069</v>
+        <v>6374331</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7920,62 +7918,71 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128740508</v>
+        <v>128740519</v>
       </c>
       <c r="B74" t="n">
-        <v>86985</v>
+        <v>86926</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7985,10 +7992,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>717063</v>
+        <v>717067</v>
       </c>
       <c r="R74" t="n">
-        <v>6374397</v>
+        <v>6374399</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8040,39 +8047,39 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128742251</v>
+        <v>128742287</v>
       </c>
       <c r="B75" t="n">
-        <v>87008</v>
+        <v>86963</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8082,10 +8089,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>717106</v>
+        <v>717013</v>
       </c>
       <c r="R75" t="n">
-        <v>6374415</v>
+        <v>6374166</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8126,6 +8133,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8144,32 +8152,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128738833</v>
+        <v>128742270</v>
       </c>
       <c r="B76" t="n">
-        <v>87008</v>
+        <v>86963</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8179,10 +8187,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>716976</v>
+        <v>717071</v>
       </c>
       <c r="R76" t="n">
-        <v>6374331</v>
+        <v>6374305</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8212,71 +8220,62 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128740519</v>
+        <v>128742290</v>
       </c>
       <c r="B77" t="n">
-        <v>86926</v>
+        <v>86963</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8286,10 +8285,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>717067</v>
+        <v>716979</v>
       </c>
       <c r="R77" t="n">
-        <v>6374399</v>
+        <v>6374069</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8330,18 +8329,19 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8751,7 +8751,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -8946,7 +8946,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9254,10 +9254,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128815957</v>
+        <v>128806483</v>
       </c>
       <c r="B87" t="n">
-        <v>86980</v>
+        <v>90983</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9265,21 +9265,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>248934</v>
+        <v>720</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knölfotad bananspindling</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius stjernegaardii</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Brandrud &amp; Frøslev</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9292,10 +9292,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>717020</v>
+        <v>717267</v>
       </c>
       <c r="R87" t="n">
-        <v>6374147</v>
+        <v>6374381</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9322,27 +9322,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>10:37</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Bilddokumentation av Ullas fynd. Uppsvullen bulb och orange basalmycel. Ek fanss på fyndplatsen som domineras av kalktallskog.</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9358,22 +9343,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128806483</v>
+        <v>128815957</v>
       </c>
       <c r="B88" t="n">
-        <v>90983</v>
+        <v>86980</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9381,21 +9366,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>720</v>
+        <v>248934</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Knölfotad bananspindling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Cortinarius stjernegaardii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>Brandrud &amp; Frøslev</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9408,10 +9393,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>717267</v>
+        <v>717020</v>
       </c>
       <c r="R88" t="n">
-        <v>6374381</v>
+        <v>6374147</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9438,12 +9423,27 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Bilddokumentation av Ullas fynd. Uppsvullen bulb och orange basalmycel. Ek fanss på fyndplatsen som domineras av kalktallskog.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9459,12 +9459,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -9578,10 +9578,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128805996</v>
+        <v>128806494</v>
       </c>
       <c r="B90" t="n">
-        <v>87008</v>
+        <v>86985</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9589,21 +9589,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9613,10 +9613,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>717308</v>
+        <v>717333</v>
       </c>
       <c r="R90" t="n">
-        <v>6374239</v>
+        <v>6374180</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9663,19 +9663,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128806494</v>
+        <v>128806493</v>
       </c>
       <c r="B91" t="n">
         <v>86985</v>
@@ -9710,10 +9710,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>717333</v>
+        <v>717133</v>
       </c>
       <c r="R91" t="n">
-        <v>6374180</v>
+        <v>6374199</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9772,10 +9772,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128806493</v>
+        <v>128805996</v>
       </c>
       <c r="B92" t="n">
-        <v>86985</v>
+        <v>87008</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9783,21 +9783,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9807,10 +9807,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>717133</v>
+        <v>717308</v>
       </c>
       <c r="R92" t="n">
-        <v>6374199</v>
+        <v>6374239</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9857,44 +9857,44 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128738839</v>
+        <v>128738846</v>
       </c>
       <c r="B93" t="n">
-        <v>87008</v>
+        <v>91017</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3767</v>
+        <v>5741</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9904,10 +9904,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>717039</v>
+        <v>717037</v>
       </c>
       <c r="R93" t="n">
-        <v>6374168</v>
+        <v>6374226</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9976,10 +9976,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128806044</v>
+        <v>128738839</v>
       </c>
       <c r="B94" t="n">
-        <v>86985</v>
+        <v>87008</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9987,21 +9987,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10011,10 +10011,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>717148</v>
+        <v>717039</v>
       </c>
       <c r="R94" t="n">
-        <v>6374175</v>
+        <v>6374168</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10041,12 +10041,22 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10061,44 +10071,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128738846</v>
+        <v>128806044</v>
       </c>
       <c r="B95" t="n">
-        <v>91017</v>
+        <v>86985</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5741</v>
+        <v>449</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10108,10 +10118,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>717037</v>
+        <v>717148</v>
       </c>
       <c r="R95" t="n">
-        <v>6374226</v>
+        <v>6374175</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10138,22 +10148,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10168,12 +10168,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -10384,48 +10384,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128806484</v>
+        <v>128806004</v>
       </c>
       <c r="B98" t="n">
-        <v>90983</v>
+        <v>91508</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>720</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>717273</v>
+        <v>717360</v>
       </c>
       <c r="R98" t="n">
-        <v>6374379</v>
+        <v>6374175</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10466,64 +10463,66 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128806004</v>
+        <v>128806484</v>
       </c>
       <c r="B99" t="n">
-        <v>91508</v>
+        <v>90983</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>720</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>717360</v>
+        <v>717273</v>
       </c>
       <c r="R99" t="n">
-        <v>6374175</v>
+        <v>6374379</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10564,18 +10563,19 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -10690,7 +10690,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128806009</v>
+        <v>128738897</v>
       </c>
       <c r="B101" t="n">
         <v>86963</v>
@@ -10725,10 +10725,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>717132</v>
+        <v>717015</v>
       </c>
       <c r="R101" t="n">
-        <v>6374140</v>
+        <v>6374144</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10755,12 +10755,22 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10776,12 +10786,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -10885,7 +10895,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128738897</v>
+        <v>128806009</v>
       </c>
       <c r="B103" t="n">
         <v>86963</v>
@@ -10920,10 +10930,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>717015</v>
+        <v>717132</v>
       </c>
       <c r="R103" t="n">
-        <v>6374144</v>
+        <v>6374140</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10950,22 +10960,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>10:05</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>10:05</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10981,22 +10981,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128738875</v>
+        <v>128805993</v>
       </c>
       <c r="B104" t="n">
-        <v>87020</v>
+        <v>87008</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11004,19 +11004,23 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>433</v>
+        <v>3767</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr"/>
+          <t>Cortinarius violaceomaculatus</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -11024,10 +11028,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>716968</v>
+        <v>717148</v>
       </c>
       <c r="R104" t="n">
-        <v>6374251</v>
+        <v>6374174</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11054,22 +11058,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>12:41</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>12:41</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11084,22 +11078,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128738842</v>
+        <v>128738875</v>
       </c>
       <c r="B105" t="n">
-        <v>87008</v>
+        <v>87020</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11107,23 +11101,19 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>3767</v>
+        <v>433</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Brandrud</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
@@ -11131,10 +11121,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>716981</v>
+        <v>716968</v>
       </c>
       <c r="R105" t="n">
-        <v>6374088</v>
+        <v>6374251</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11166,7 +11156,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11176,7 +11166,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11203,7 +11193,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128805993</v>
+        <v>128738842</v>
       </c>
       <c r="B106" t="n">
         <v>87008</v>
@@ -11238,10 +11228,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>717148</v>
+        <v>716981</v>
       </c>
       <c r="R106" t="n">
-        <v>6374174</v>
+        <v>6374088</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11268,12 +11258,22 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11288,12 +11288,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -11407,10 +11407,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128806010</v>
+        <v>128806056</v>
       </c>
       <c r="B108" t="n">
-        <v>86963</v>
+        <v>106961</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11418,21 +11418,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6003295</v>
+        <v>221849</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11442,10 +11442,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>717186</v>
+        <v>717370</v>
       </c>
       <c r="R108" t="n">
-        <v>6374253</v>
+        <v>6374168</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11486,7 +11486,6 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11498,7 +11497,7 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -11603,10 +11602,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128806056</v>
+        <v>128806010</v>
       </c>
       <c r="B110" t="n">
-        <v>106961</v>
+        <v>86963</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11614,21 +11613,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>221849</v>
+        <v>6003295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11638,10 +11637,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>717370</v>
+        <v>717186</v>
       </c>
       <c r="R110" t="n">
-        <v>6374168</v>
+        <v>6374253</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11682,6 +11681,7 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
@@ -12002,32 +12002,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128738886</v>
+        <v>128738893</v>
       </c>
       <c r="B114" t="n">
-        <v>86810</v>
+        <v>86963</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12037,10 +12037,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>716990</v>
+        <v>717000</v>
       </c>
       <c r="R114" t="n">
-        <v>6374260</v>
+        <v>6374121</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12072,7 +12072,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12091,6 +12091,7 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12109,10 +12110,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128806495</v>
+        <v>128738886</v>
       </c>
       <c r="B115" t="n">
-        <v>86850</v>
+        <v>86810</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12120,21 +12121,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>442</v>
+        <v>424</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12144,10 +12145,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>717357</v>
+        <v>716990</v>
       </c>
       <c r="R115" t="n">
-        <v>6374169</v>
+        <v>6374260</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12174,12 +12175,22 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12194,42 +12205,46 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128806049</v>
+        <v>128806043</v>
       </c>
       <c r="B116" t="n">
-        <v>87020</v>
+        <v>75147</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>433</v>
+        <v>6426</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -12237,10 +12252,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>717128</v>
+        <v>717359</v>
       </c>
       <c r="R116" t="n">
-        <v>6374123</v>
+        <v>6374214</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12299,32 +12314,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128806064</v>
+        <v>128806050</v>
       </c>
       <c r="B117" t="n">
-        <v>86926</v>
+        <v>86929</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3674</v>
+        <v>6037417</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12334,10 +12349,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>717299</v>
+        <v>717311</v>
       </c>
       <c r="R117" t="n">
-        <v>6374300</v>
+        <v>6374287</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12378,6 +12393,7 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -12396,10 +12412,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128806043</v>
+        <v>128806064</v>
       </c>
       <c r="B118" t="n">
-        <v>75147</v>
+        <v>86926</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12407,21 +12423,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12431,10 +12447,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>717359</v>
+        <v>717299</v>
       </c>
       <c r="R118" t="n">
-        <v>6374214</v>
+        <v>6374300</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12493,32 +12509,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128806050</v>
+        <v>128806495</v>
       </c>
       <c r="B119" t="n">
-        <v>86929</v>
+        <v>86850</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6037417</v>
+        <v>442</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12528,10 +12544,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>717311</v>
+        <v>717357</v>
       </c>
       <c r="R119" t="n">
-        <v>6374287</v>
+        <v>6374169</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12572,53 +12588,48 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128738893</v>
+        <v>128806049</v>
       </c>
       <c r="B120" t="n">
-        <v>86963</v>
+        <v>87020</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -12626,10 +12637,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>717000</v>
+        <v>717128</v>
       </c>
       <c r="R120" t="n">
-        <v>6374121</v>
+        <v>6374123</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12656,22 +12667,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>10:04</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>10:04</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12680,51 +12681,50 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128806052</v>
+        <v>128738892</v>
       </c>
       <c r="B121" t="n">
-        <v>86788</v>
+        <v>86963</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12734,10 +12734,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>717284</v>
+        <v>717037</v>
       </c>
       <c r="R121" t="n">
-        <v>6374097</v>
+        <v>6374150</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12764,12 +12764,22 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12778,50 +12788,51 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128738892</v>
+        <v>128806052</v>
       </c>
       <c r="B122" t="n">
-        <v>86963</v>
+        <v>86788</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12831,10 +12842,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>717037</v>
+        <v>717284</v>
       </c>
       <c r="R122" t="n">
-        <v>6374150</v>
+        <v>6374097</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12861,22 +12872,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>10:16</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>10:16</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12885,67 +12886,63 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128738882</v>
+        <v>128738894</v>
       </c>
       <c r="B123" t="n">
-        <v>87090</v>
+        <v>86963</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>3563</v>
+        <v>6003295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Stor granspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius bovinus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Fr. sl.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>717013</v>
+        <v>716975</v>
       </c>
       <c r="R123" t="n">
-        <v>6374226</v>
+        <v>6374071</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12977,7 +12974,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -12987,7 +12984,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13015,32 +13012,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128806045</v>
+        <v>128806011</v>
       </c>
       <c r="B124" t="n">
-        <v>86985</v>
+        <v>86963</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13050,10 +13047,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>717324</v>
+        <v>717367</v>
       </c>
       <c r="R124" t="n">
-        <v>6374179</v>
+        <v>6374231</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13094,6 +13091,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13105,52 +13103,55 @@
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128806051</v>
+        <v>128738882</v>
       </c>
       <c r="B125" t="n">
-        <v>86788</v>
+        <v>87090</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>3712</v>
+        <v>3563</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Stor granspindling</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius bovinus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Fr. sl.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>717327</v>
+        <v>717013</v>
       </c>
       <c r="R125" t="n">
-        <v>6374171</v>
+        <v>6374226</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13177,12 +13178,22 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13191,50 +13202,51 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128738894</v>
+        <v>128806045</v>
       </c>
       <c r="B126" t="n">
-        <v>86963</v>
+        <v>86985</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13244,10 +13256,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>716975</v>
+        <v>717324</v>
       </c>
       <c r="R126" t="n">
-        <v>6374071</v>
+        <v>6374179</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13274,22 +13286,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>09:15</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>09:15</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13298,51 +13300,50 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128806011</v>
+        <v>128806051</v>
       </c>
       <c r="B127" t="n">
-        <v>86963</v>
+        <v>86788</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13352,10 +13353,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>717367</v>
+        <v>717327</v>
       </c>
       <c r="R127" t="n">
-        <v>6374231</v>
+        <v>6374171</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13396,7 +13397,6 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13408,39 +13408,39 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128806491</v>
+        <v>128806485</v>
       </c>
       <c r="B128" t="n">
-        <v>86963</v>
+        <v>86788</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13450,10 +13450,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>717324</v>
+        <v>717201</v>
       </c>
       <c r="R128" t="n">
-        <v>6374171</v>
+        <v>6374297</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13610,32 +13610,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128806485</v>
+        <v>128806491</v>
       </c>
       <c r="B130" t="n">
-        <v>86788</v>
+        <v>86963</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13645,10 +13645,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>717201</v>
+        <v>717324</v>
       </c>
       <c r="R130" t="n">
-        <v>6374297</v>
+        <v>6374171</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13902,32 +13902,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128806490</v>
+        <v>128806487</v>
       </c>
       <c r="B133" t="n">
-        <v>86963</v>
+        <v>87008</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13937,10 +13937,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>717333</v>
+        <v>717275</v>
       </c>
       <c r="R133" t="n">
-        <v>6374202</v>
+        <v>6374183</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13981,7 +13981,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14000,32 +13999,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128738847</v>
+        <v>128806490</v>
       </c>
       <c r="B134" t="n">
-        <v>86879</v>
+        <v>86963</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14035,10 +14034,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>716980</v>
+        <v>717333</v>
       </c>
       <c r="R134" t="n">
-        <v>6374264</v>
+        <v>6374202</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14065,22 +14064,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14089,28 +14078,29 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128806487</v>
+        <v>128738847</v>
       </c>
       <c r="B135" t="n">
-        <v>87008</v>
+        <v>86879</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14118,21 +14108,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3767</v>
+        <v>248956</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14142,10 +14132,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>717275</v>
+        <v>716980</v>
       </c>
       <c r="R135" t="n">
-        <v>6374183</v>
+        <v>6374264</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14172,12 +14162,22 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14192,12 +14192,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -14496,32 +14496,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128805991</v>
+        <v>128806024</v>
       </c>
       <c r="B139" t="n">
-        <v>87008</v>
+        <v>86963</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14531,10 +14531,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>717147</v>
+        <v>717366</v>
       </c>
       <c r="R139" t="n">
-        <v>6374164</v>
+        <v>6374150</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14575,6 +14575,7 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14586,17 +14587,17 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128738883</v>
+        <v>128805991</v>
       </c>
       <c r="B140" t="n">
-        <v>86826</v>
+        <v>87008</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14604,16 +14605,16 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>3561</v>
+        <v>3767</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Blåbandad spindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cortinarius borgsjoeensis</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -14628,10 +14629,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>716993</v>
+        <v>717147</v>
       </c>
       <c r="R140" t="n">
-        <v>6374384</v>
+        <v>6374164</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14658,22 +14659,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14682,19 +14673,18 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
@@ -14798,32 +14788,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128806024</v>
+        <v>128738883</v>
       </c>
       <c r="B142" t="n">
-        <v>86963</v>
+        <v>86826</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6003295</v>
+        <v>3561</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blåbandad spindling</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius borgsjoeensis</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14833,10 +14823,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>717366</v>
+        <v>716993</v>
       </c>
       <c r="R142" t="n">
-        <v>6374150</v>
+        <v>6374384</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14863,12 +14853,22 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -14884,12 +14884,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>

--- a/artfynd/A 42607-2025 artfynd.xlsx
+++ b/artfynd/A 42607-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128738845</v>
       </c>
       <c r="B2" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128738831</v>
       </c>
       <c r="B3" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128742256</v>
       </c>
       <c r="B4" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128740514</v>
       </c>
       <c r="B5" t="n">
-        <v>86788</v>
+        <v>86793</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,32 +1083,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128740505</v>
+        <v>128738854</v>
       </c>
       <c r="B6" t="n">
-        <v>98658</v>
+        <v>86968</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219862</v>
+        <v>6003295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717182</v>
+        <v>716967</v>
       </c>
       <c r="R6" t="n">
-        <v>6374336</v>
+        <v>6374338</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1151,39 +1151,50 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128738854</v>
+        <v>128740487</v>
       </c>
       <c r="B7" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,10 +1226,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716967</v>
+        <v>717292</v>
       </c>
       <c r="R7" t="n">
-        <v>6374338</v>
+        <v>6374265</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1248,19 +1259,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1276,44 +1277,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128740487</v>
+        <v>128740505</v>
       </c>
       <c r="B8" t="n">
-        <v>86963</v>
+        <v>98665</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6003295</v>
+        <v>219862</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1323,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717292</v>
+        <v>717182</v>
       </c>
       <c r="R8" t="n">
-        <v>6374265</v>
+        <v>6374336</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,7 +1368,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>128738834</v>
       </c>
       <c r="B9" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>128742266</v>
       </c>
       <c r="B10" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>128738837</v>
       </c>
       <c r="B11" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>128738853</v>
       </c>
       <c r="B12" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>128740482</v>
       </c>
       <c r="B13" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>128740504</v>
       </c>
       <c r="B14" t="n">
-        <v>98658</v>
+        <v>98665</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>128742285</v>
       </c>
       <c r="B15" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>128738898</v>
       </c>
       <c r="B16" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>128738832</v>
       </c>
       <c r="B17" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>128738859</v>
       </c>
       <c r="B18" t="n">
-        <v>98670</v>
+        <v>98677</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>128742286</v>
       </c>
       <c r="B19" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>128740498</v>
       </c>
       <c r="B20" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>128738857</v>
       </c>
       <c r="B21" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>128738856</v>
       </c>
       <c r="B22" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>128742257</v>
       </c>
       <c r="B23" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>128740485</v>
       </c>
       <c r="B24" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>128742258</v>
       </c>
       <c r="B25" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3121,10 +3121,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128740489</v>
+        <v>128742273</v>
       </c>
       <c r="B26" t="n">
-        <v>91017</v>
+        <v>86944</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3132,21 +3132,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5741</v>
+        <v>1988</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>717220</v>
+        <v>717014</v>
       </c>
       <c r="R26" t="n">
-        <v>6374302</v>
+        <v>6374164</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3206,44 +3206,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128742283</v>
+        <v>128740489</v>
       </c>
       <c r="B27" t="n">
-        <v>86963</v>
+        <v>91022</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6003295</v>
+        <v>5741</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>717040</v>
+        <v>717220</v>
       </c>
       <c r="R27" t="n">
-        <v>6374195</v>
+        <v>6374302</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3297,29 +3297,28 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128742281</v>
+        <v>128742283</v>
       </c>
       <c r="B28" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3351,10 +3350,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>717039</v>
+        <v>717040</v>
       </c>
       <c r="R28" t="n">
-        <v>6374227</v>
+        <v>6374195</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3414,32 +3413,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128742273</v>
+        <v>128742281</v>
       </c>
       <c r="B29" t="n">
-        <v>86939</v>
+        <v>86968</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1988</v>
+        <v>6003295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3449,10 +3448,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>717014</v>
+        <v>717039</v>
       </c>
       <c r="R29" t="n">
-        <v>6374164</v>
+        <v>6374227</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3493,6 +3492,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3511,32 +3511,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128742272</v>
+        <v>128742293</v>
       </c>
       <c r="B30" t="n">
-        <v>91043</v>
+        <v>86931</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5747</v>
+        <v>3674</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3546,10 +3546,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>717018</v>
+        <v>717094</v>
       </c>
       <c r="R30" t="n">
-        <v>6374179</v>
+        <v>6374468</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3608,32 +3608,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128742293</v>
+        <v>128742254</v>
       </c>
       <c r="B31" t="n">
-        <v>86926</v>
+        <v>87013</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>717094</v>
+        <v>717285</v>
       </c>
       <c r="R31" t="n">
-        <v>6374468</v>
+        <v>6374272</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3705,10 +3705,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128742254</v>
+        <v>128742272</v>
       </c>
       <c r="B32" t="n">
-        <v>87008</v>
+        <v>91048</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3716,21 +3716,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3767</v>
+        <v>5747</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>717285</v>
+        <v>717018</v>
       </c>
       <c r="R32" t="n">
-        <v>6374272</v>
+        <v>6374179</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3805,7 +3805,7 @@
         <v>128740500</v>
       </c>
       <c r="B33" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>128740499</v>
       </c>
       <c r="B34" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>128740502</v>
       </c>
       <c r="B35" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>128740521</v>
       </c>
       <c r="B36" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>128738900</v>
       </c>
       <c r="B37" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>128742267</v>
       </c>
       <c r="B38" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>128738858</v>
       </c>
       <c r="B39" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>128740509</v>
       </c>
       <c r="B40" t="n">
-        <v>86985</v>
+        <v>86990</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>128738887</v>
       </c>
       <c r="B41" t="n">
-        <v>86810</v>
+        <v>86815</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>128742259</v>
       </c>
       <c r="B42" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>128738895</v>
       </c>
       <c r="B43" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>128742268</v>
       </c>
       <c r="B44" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>128742280</v>
       </c>
       <c r="B45" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>128738880</v>
       </c>
       <c r="B46" t="n">
-        <v>86788</v>
+        <v>86793</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
         <v>128738838</v>
       </c>
       <c r="B47" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5328,7 +5328,7 @@
         <v>128742289</v>
       </c>
       <c r="B48" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>128742269</v>
       </c>
       <c r="B49" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>128742279</v>
       </c>
       <c r="B50" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5622,7 +5622,7 @@
         <v>128742288</v>
       </c>
       <c r="B51" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>128738896</v>
       </c>
       <c r="B52" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>128742291</v>
       </c>
       <c r="B53" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>128742284</v>
       </c>
       <c r="B54" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>128742263</v>
       </c>
       <c r="B55" t="n">
-        <v>91017</v>
+        <v>91022</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6118,32 +6118,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128738841</v>
+        <v>128742282</v>
       </c>
       <c r="B56" t="n">
-        <v>87008</v>
+        <v>86968</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6153,10 +6153,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>716992</v>
+        <v>717040</v>
       </c>
       <c r="R56" t="n">
-        <v>6374116</v>
+        <v>6374212</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6186,49 +6186,40 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128738835</v>
+        <v>128738841</v>
       </c>
       <c r="B57" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6260,10 +6251,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>716983</v>
+        <v>716992</v>
       </c>
       <c r="R57" t="n">
-        <v>6374357</v>
+        <v>6374116</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6295,7 +6286,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6305,7 +6296,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6332,10 +6323,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128742252</v>
+        <v>128738835</v>
       </c>
       <c r="B58" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6367,10 +6358,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>717146</v>
+        <v>716983</v>
       </c>
       <c r="R58" t="n">
-        <v>6374313</v>
+        <v>6374357</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6400,9 +6391,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6417,44 +6418,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128740522</v>
+        <v>128742252</v>
       </c>
       <c r="B59" t="n">
-        <v>86926</v>
+        <v>87013</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6464,10 +6465,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>717274</v>
+        <v>717146</v>
       </c>
       <c r="R59" t="n">
-        <v>6374210</v>
+        <v>6374313</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6514,44 +6515,44 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128742282</v>
+        <v>128740522</v>
       </c>
       <c r="B60" t="n">
-        <v>86963</v>
+        <v>86931</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6561,10 +6562,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>717040</v>
+        <v>717274</v>
       </c>
       <c r="R60" t="n">
-        <v>6374212</v>
+        <v>6374210</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6605,51 +6606,50 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128742276</v>
+        <v>128738848</v>
       </c>
       <c r="B61" t="n">
-        <v>86985</v>
+        <v>57720</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>449</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6659,10 +6659,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>717269</v>
+        <v>717165</v>
       </c>
       <c r="R61" t="n">
-        <v>6374317</v>
+        <v>6374351</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6692,9 +6692,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6709,22 +6719,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128738884</v>
+        <v>128742276</v>
       </c>
       <c r="B62" t="n">
-        <v>86810</v>
+        <v>86990</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6732,21 +6742,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>424</v>
+        <v>449</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6756,10 +6766,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>716969</v>
+        <v>717269</v>
       </c>
       <c r="R62" t="n">
-        <v>6374310</v>
+        <v>6374317</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6789,19 +6799,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>14:32</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6816,44 +6816,44 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128740491</v>
+        <v>128738884</v>
       </c>
       <c r="B63" t="n">
-        <v>86764</v>
+        <v>86815</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3762</v>
+        <v>424</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6863,10 +6863,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>717281</v>
+        <v>716969</v>
       </c>
       <c r="R63" t="n">
-        <v>6374215</v>
+        <v>6374310</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6896,9 +6896,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6913,44 +6923,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128742255</v>
+        <v>128740491</v>
       </c>
       <c r="B64" t="n">
-        <v>87008</v>
+        <v>86769</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6960,10 +6970,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>717059</v>
+        <v>717281</v>
       </c>
       <c r="R64" t="n">
-        <v>6374329</v>
+        <v>6374215</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7010,44 +7020,44 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128738848</v>
+        <v>128742255</v>
       </c>
       <c r="B65" t="n">
-        <v>57717</v>
+        <v>87013</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>3767</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7057,10 +7067,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>717165</v>
+        <v>717059</v>
       </c>
       <c r="R65" t="n">
-        <v>6374351</v>
+        <v>6374329</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7090,19 +7100,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>10:25</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7117,12 +7117,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7132,7 +7132,7 @@
         <v>128738851</v>
       </c>
       <c r="B66" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>128740512</v>
       </c>
       <c r="B67" t="n">
-        <v>86788</v>
+        <v>86793</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>128738836</v>
       </c>
       <c r="B68" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>128738855</v>
       </c>
       <c r="B69" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>128738852</v>
       </c>
       <c r="B70" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>128740508</v>
       </c>
       <c r="B71" t="n">
-        <v>86985</v>
+        <v>86990</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>128742251</v>
       </c>
       <c r="B72" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>128738833</v>
       </c>
       <c r="B73" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>128740519</v>
       </c>
       <c r="B74" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>128742287</v>
       </c>
       <c r="B75" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>128742270</v>
       </c>
       <c r="B76" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>128742290</v>
       </c>
       <c r="B77" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>128740516</v>
       </c>
       <c r="B78" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>128738891</v>
       </c>
       <c r="B79" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>128738890</v>
       </c>
       <c r="B80" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8661,32 +8661,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128740484</v>
+        <v>128740503</v>
       </c>
       <c r="B81" t="n">
-        <v>87008</v>
+        <v>86968</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8696,10 +8696,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>717279</v>
+        <v>717212</v>
       </c>
       <c r="R81" t="n">
-        <v>6374209</v>
+        <v>6374189</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8740,6 +8740,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8758,32 +8759,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128740518</v>
+        <v>128740510</v>
       </c>
       <c r="B82" t="n">
-        <v>86926</v>
+        <v>86934</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3674</v>
+        <v>6037417</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8793,10 +8794,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>717062</v>
+        <v>717105</v>
       </c>
       <c r="R82" t="n">
-        <v>6374393</v>
+        <v>6374479</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8848,39 +8849,39 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128740503</v>
+        <v>128740484</v>
       </c>
       <c r="B83" t="n">
-        <v>86963</v>
+        <v>87013</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8890,10 +8891,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>717212</v>
+        <v>717279</v>
       </c>
       <c r="R83" t="n">
-        <v>6374189</v>
+        <v>6374209</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8934,7 +8935,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -8953,32 +8953,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128740510</v>
+        <v>128740518</v>
       </c>
       <c r="B84" t="n">
-        <v>86929</v>
+        <v>86931</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6037417</v>
+        <v>3674</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8988,10 +8988,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>717105</v>
+        <v>717062</v>
       </c>
       <c r="R84" t="n">
-        <v>6374479</v>
+        <v>6374393</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9053,7 +9053,7 @@
         <v>128738899</v>
       </c>
       <c r="B85" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>128806499</v>
       </c>
       <c r="B86" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>128806483</v>
       </c>
       <c r="B87" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
         <v>128815957</v>
       </c>
       <c r="B88" t="n">
-        <v>86980</v>
+        <v>86985</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>128738885</v>
       </c>
       <c r="B89" t="n">
-        <v>86810</v>
+        <v>86815</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9578,10 +9578,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128806494</v>
+        <v>128805996</v>
       </c>
       <c r="B90" t="n">
-        <v>86985</v>
+        <v>87013</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9589,21 +9589,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9613,10 +9613,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>717333</v>
+        <v>717308</v>
       </c>
       <c r="R90" t="n">
-        <v>6374180</v>
+        <v>6374239</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9663,22 +9663,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128806493</v>
+        <v>128806494</v>
       </c>
       <c r="B91" t="n">
-        <v>86985</v>
+        <v>86990</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9710,10 +9710,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>717133</v>
+        <v>717333</v>
       </c>
       <c r="R91" t="n">
-        <v>6374199</v>
+        <v>6374180</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9772,10 +9772,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128805996</v>
+        <v>128806493</v>
       </c>
       <c r="B92" t="n">
-        <v>87008</v>
+        <v>86990</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9783,21 +9783,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9807,10 +9807,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>717308</v>
+        <v>717133</v>
       </c>
       <c r="R92" t="n">
-        <v>6374239</v>
+        <v>6374199</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9857,44 +9857,44 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128738846</v>
+        <v>128738839</v>
       </c>
       <c r="B93" t="n">
-        <v>91017</v>
+        <v>87013</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5741</v>
+        <v>3767</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9904,10 +9904,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>717037</v>
+        <v>717039</v>
       </c>
       <c r="R93" t="n">
-        <v>6374226</v>
+        <v>6374168</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9976,32 +9976,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128738839</v>
+        <v>128738846</v>
       </c>
       <c r="B94" t="n">
-        <v>87008</v>
+        <v>91022</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3767</v>
+        <v>5741</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10011,10 +10011,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>717039</v>
+        <v>717037</v>
       </c>
       <c r="R94" t="n">
-        <v>6374168</v>
+        <v>6374226</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10046,7 +10046,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10083,32 +10083,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128806044</v>
+        <v>128806038</v>
       </c>
       <c r="B95" t="n">
-        <v>86985</v>
+        <v>98665</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>449</v>
+        <v>219862</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10118,10 +10118,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>717148</v>
+        <v>717113</v>
       </c>
       <c r="R95" t="n">
-        <v>6374175</v>
+        <v>6374105</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10180,10 +10180,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128806038</v>
+        <v>128815850</v>
       </c>
       <c r="B96" t="n">
-        <v>98658</v>
+        <v>89491</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10191,21 +10191,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>219862</v>
+        <v>236437</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Brun klibbskivling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Limacella glioderma</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Maire</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10215,10 +10215,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>717113</v>
+        <v>716975</v>
       </c>
       <c r="R96" t="n">
-        <v>6374105</v>
+        <v>6374071</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10245,12 +10245,22 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10265,44 +10275,44 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128815850</v>
+        <v>128806044</v>
       </c>
       <c r="B97" t="n">
-        <v>89486</v>
+        <v>86990</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>236437</v>
+        <v>449</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Brun klibbskivling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Limacella glioderma</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Maire</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10312,10 +10322,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>716975</v>
+        <v>717148</v>
       </c>
       <c r="R97" t="n">
-        <v>6374071</v>
+        <v>6374175</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10342,22 +10352,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>09:13</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>09:13</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10372,12 +10372,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -10387,7 +10387,7 @@
         <v>128806004</v>
       </c>
       <c r="B98" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>128806484</v>
       </c>
       <c r="B99" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>128738866</v>
       </c>
       <c r="B100" t="n">
-        <v>90249</v>
+        <v>90254</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10690,32 +10690,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128738897</v>
+        <v>128806005</v>
       </c>
       <c r="B101" t="n">
-        <v>86963</v>
+        <v>91022</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6003295</v>
+        <v>5741</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10725,10 +10725,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>717015</v>
+        <v>717142</v>
       </c>
       <c r="R101" t="n">
-        <v>6374144</v>
+        <v>6374197</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10755,22 +10755,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>10:05</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>10:05</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10779,51 +10769,50 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128806005</v>
+        <v>128806009</v>
       </c>
       <c r="B102" t="n">
-        <v>91017</v>
+        <v>86968</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5741</v>
+        <v>6003295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10833,10 +10822,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>717142</v>
+        <v>717132</v>
       </c>
       <c r="R102" t="n">
-        <v>6374197</v>
+        <v>6374140</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10877,6 +10866,7 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -10888,17 +10878,17 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128806009</v>
+        <v>128738897</v>
       </c>
       <c r="B103" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10930,10 +10920,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>717132</v>
+        <v>717015</v>
       </c>
       <c r="R103" t="n">
-        <v>6374140</v>
+        <v>6374144</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10960,12 +10950,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10981,22 +10981,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128805993</v>
+        <v>128738842</v>
       </c>
       <c r="B104" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11028,10 +11028,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>717148</v>
+        <v>716981</v>
       </c>
       <c r="R104" t="n">
-        <v>6374174</v>
+        <v>6374088</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11058,12 +11058,22 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11078,22 +11088,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128738875</v>
+        <v>128805993</v>
       </c>
       <c r="B105" t="n">
-        <v>87020</v>
+        <v>87013</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11101,19 +11111,23 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>433</v>
+        <v>3767</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr"/>
+          <t>Cortinarius violaceomaculatus</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
@@ -11121,10 +11135,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>716968</v>
+        <v>717148</v>
       </c>
       <c r="R105" t="n">
-        <v>6374251</v>
+        <v>6374174</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11151,22 +11165,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>12:41</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>12:41</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11181,22 +11185,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128738842</v>
+        <v>128738875</v>
       </c>
       <c r="B106" t="n">
-        <v>87008</v>
+        <v>87025</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11204,23 +11208,19 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>3767</v>
+        <v>433</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Brandrud</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -11228,10 +11228,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>716981</v>
+        <v>716968</v>
       </c>
       <c r="R106" t="n">
-        <v>6374088</v>
+        <v>6374251</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11263,7 +11263,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11273,7 +11273,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11303,7 +11303,7 @@
         <v>128738843</v>
       </c>
       <c r="B107" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         <v>128806056</v>
       </c>
       <c r="B108" t="n">
-        <v>106961</v>
+        <v>106969</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11504,10 +11504,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128806023</v>
+        <v>128806010</v>
       </c>
       <c r="B109" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11539,10 +11539,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>717360</v>
+        <v>717186</v>
       </c>
       <c r="R109" t="n">
-        <v>6374214</v>
+        <v>6374253</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11602,10 +11602,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128806010</v>
+        <v>128806023</v>
       </c>
       <c r="B110" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11637,10 +11637,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>717186</v>
+        <v>717360</v>
       </c>
       <c r="R110" t="n">
-        <v>6374253</v>
+        <v>6374214</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11703,7 +11703,7 @@
         <v>128738840</v>
       </c>
       <c r="B111" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>128806497</v>
       </c>
       <c r="B112" t="n">
-        <v>86788</v>
+        <v>86793</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>128806022</v>
       </c>
       <c r="B113" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12002,32 +12002,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128738893</v>
+        <v>128806495</v>
       </c>
       <c r="B114" t="n">
-        <v>86963</v>
+        <v>86855</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6003295</v>
+        <v>442</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12037,10 +12037,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>717000</v>
+        <v>717357</v>
       </c>
       <c r="R114" t="n">
-        <v>6374121</v>
+        <v>6374169</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12067,22 +12067,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>10:04</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>10:04</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12091,29 +12081,28 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128738886</v>
+        <v>128806049</v>
       </c>
       <c r="B115" t="n">
-        <v>86810</v>
+        <v>87025</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12121,23 +12110,19 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -12145,10 +12130,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>716990</v>
+        <v>717128</v>
       </c>
       <c r="R115" t="n">
-        <v>6374260</v>
+        <v>6374123</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12175,22 +12160,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12205,12 +12180,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
@@ -12220,7 +12195,7 @@
         <v>128806043</v>
       </c>
       <c r="B116" t="n">
-        <v>75147</v>
+        <v>75150</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12317,7 +12292,7 @@
         <v>128806050</v>
       </c>
       <c r="B117" t="n">
-        <v>86929</v>
+        <v>86934</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12415,7 +12390,7 @@
         <v>128806064</v>
       </c>
       <c r="B118" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12509,32 +12484,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128806495</v>
+        <v>128738893</v>
       </c>
       <c r="B119" t="n">
-        <v>86850</v>
+        <v>86968</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>442</v>
+        <v>6003295</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12544,10 +12519,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>717357</v>
+        <v>717000</v>
       </c>
       <c r="R119" t="n">
-        <v>6374169</v>
+        <v>6374121</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12574,12 +12549,22 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12588,28 +12573,29 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128806049</v>
+        <v>128738886</v>
       </c>
       <c r="B120" t="n">
-        <v>87020</v>
+        <v>86815</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12617,19 +12603,23 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr"/>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -12637,10 +12627,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>717128</v>
+        <v>716990</v>
       </c>
       <c r="R120" t="n">
-        <v>6374123</v>
+        <v>6374260</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12667,12 +12657,22 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12687,44 +12687,44 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128738892</v>
+        <v>128806052</v>
       </c>
       <c r="B121" t="n">
-        <v>86963</v>
+        <v>86793</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12734,10 +12734,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>717037</v>
+        <v>717284</v>
       </c>
       <c r="R121" t="n">
-        <v>6374150</v>
+        <v>6374097</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12764,22 +12764,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>10:16</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>10:16</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12788,51 +12778,50 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128806052</v>
+        <v>128738892</v>
       </c>
       <c r="B122" t="n">
-        <v>86788</v>
+        <v>86968</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12842,10 +12831,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>717284</v>
+        <v>717037</v>
       </c>
       <c r="R122" t="n">
-        <v>6374097</v>
+        <v>6374150</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12872,12 +12861,22 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12886,18 +12885,19 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
@@ -12907,7 +12907,7 @@
         <v>128738894</v>
       </c>
       <c r="B123" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13012,45 +13012,48 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128806011</v>
+        <v>128738882</v>
       </c>
       <c r="B124" t="n">
-        <v>86963</v>
+        <v>87095</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6003295</v>
+        <v>3563</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Stor granspindling</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius bovinus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr. sl.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>717367</v>
+        <v>717013</v>
       </c>
       <c r="R124" t="n">
-        <v>6374231</v>
+        <v>6374226</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13077,12 +13080,22 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13098,22 +13111,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128738882</v>
+        <v>128806045</v>
       </c>
       <c r="B125" t="n">
-        <v>87090</v>
+        <v>86990</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13121,37 +13134,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>3563</v>
+        <v>449</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Stor granspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cortinarius bovinus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Fr. sl.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>717013</v>
+        <v>717324</v>
       </c>
       <c r="R125" t="n">
-        <v>6374226</v>
+        <v>6374179</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13178,22 +13188,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>13:07</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>13:07</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13202,51 +13202,50 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128806045</v>
+        <v>128806051</v>
       </c>
       <c r="B126" t="n">
-        <v>86985</v>
+        <v>86793</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>449</v>
+        <v>3712</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13256,10 +13255,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>717324</v>
+        <v>717327</v>
       </c>
       <c r="R126" t="n">
-        <v>6374179</v>
+        <v>6374171</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13318,32 +13317,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128806051</v>
+        <v>128806011</v>
       </c>
       <c r="B127" t="n">
-        <v>86788</v>
+        <v>86968</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13353,10 +13352,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>717327</v>
+        <v>717367</v>
       </c>
       <c r="R127" t="n">
-        <v>6374171</v>
+        <v>6374231</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13397,6 +13396,7 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13408,39 +13408,39 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128806485</v>
+        <v>128806492</v>
       </c>
       <c r="B128" t="n">
-        <v>86788</v>
+        <v>91048</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>3712</v>
+        <v>5747</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13450,10 +13450,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>717201</v>
+        <v>717146</v>
       </c>
       <c r="R128" t="n">
-        <v>6374297</v>
+        <v>6374178</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13494,7 +13494,6 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13513,32 +13512,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128806492</v>
+        <v>128806485</v>
       </c>
       <c r="B129" t="n">
-        <v>91043</v>
+        <v>86793</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5747</v>
+        <v>3712</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13548,10 +13547,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>717146</v>
+        <v>717201</v>
       </c>
       <c r="R129" t="n">
-        <v>6374178</v>
+        <v>6374297</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13592,6 +13591,7 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13613,7 +13613,7 @@
         <v>128806491</v>
       </c>
       <c r="B130" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>128806057</v>
       </c>
       <c r="B131" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>128806058</v>
       </c>
       <c r="B132" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13902,10 +13902,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128806487</v>
+        <v>128738847</v>
       </c>
       <c r="B133" t="n">
-        <v>87008</v>
+        <v>86884</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13913,21 +13913,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>3767</v>
+        <v>248956</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13937,10 +13937,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>717275</v>
+        <v>716980</v>
       </c>
       <c r="R133" t="n">
-        <v>6374183</v>
+        <v>6374264</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13967,12 +13967,22 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -13987,12 +13997,12 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -14002,7 +14012,7 @@
         <v>128806490</v>
       </c>
       <c r="B134" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14097,10 +14107,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128738847</v>
+        <v>128806487</v>
       </c>
       <c r="B135" t="n">
-        <v>86879</v>
+        <v>87013</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14108,21 +14118,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>248956</v>
+        <v>3767</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14132,10 +14142,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>716980</v>
+        <v>717275</v>
       </c>
       <c r="R135" t="n">
-        <v>6374264</v>
+        <v>6374183</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14162,22 +14172,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14192,12 +14192,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -14207,7 +14207,7 @@
         <v>128806013</v>
       </c>
       <c r="B136" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14305,7 +14305,7 @@
         <v>128806065</v>
       </c>
       <c r="B137" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14402,7 +14402,7 @@
         <v>128806486</v>
       </c>
       <c r="B138" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         <v>128806024</v>
       </c>
       <c r="B139" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>128805991</v>
       </c>
       <c r="B140" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14691,32 +14691,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128806496</v>
+        <v>128738883</v>
       </c>
       <c r="B141" t="n">
-        <v>96232</v>
+        <v>86831</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2180</v>
+        <v>3561</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blåbandad spindling</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cortinarius borgsjoeensis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14726,10 +14726,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>717337</v>
+        <v>716993</v>
       </c>
       <c r="R141" t="n">
-        <v>6374082</v>
+        <v>6374384</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14756,12 +14756,22 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14770,50 +14780,51 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128738883</v>
+        <v>128806496</v>
       </c>
       <c r="B142" t="n">
-        <v>86826</v>
+        <v>96239</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>3561</v>
+        <v>2180</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Blåbandad spindling</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cortinarius borgsjoeensis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14823,10 +14834,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>716993</v>
+        <v>717337</v>
       </c>
       <c r="R142" t="n">
-        <v>6374384</v>
+        <v>6374082</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14853,22 +14864,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -14877,19 +14878,18 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
@@ -14899,7 +14899,7 @@
         <v>128738867</v>
       </c>
       <c r="B143" t="n">
-        <v>86985</v>
+        <v>86990</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>128742275</v>
       </c>
       <c r="B144" t="n">
-        <v>86914</v>
+        <v>86919</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 42607-2025 artfynd.xlsx
+++ b/artfynd/A 42607-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128738845</v>
+        <v>128740505</v>
       </c>
       <c r="B2" t="n">
-        <v>86776</v>
+        <v>98673</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3762</v>
+        <v>219862</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716961</v>
+        <v>717182</v>
       </c>
       <c r="R2" t="n">
-        <v>6374255</v>
+        <v>6374336</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,19 +743,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,44 +760,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128738831</v>
+        <v>128738845</v>
       </c>
       <c r="B3" t="n">
-        <v>87020</v>
+        <v>86776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717030</v>
+        <v>716961</v>
       </c>
       <c r="R3" t="n">
-        <v>6374429</v>
+        <v>6374255</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +842,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +852,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128742256</v>
+        <v>128738831</v>
       </c>
       <c r="B4" t="n">
         <v>87020</v>
@@ -924,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717053</v>
+        <v>717030</v>
       </c>
       <c r="R4" t="n">
-        <v>6374253</v>
+        <v>6374429</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,9 +947,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,44 +974,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128740514</v>
+        <v>128742256</v>
       </c>
       <c r="B5" t="n">
-        <v>86800</v>
+        <v>87020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3712</v>
+        <v>3767</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717295</v>
+        <v>717053</v>
       </c>
       <c r="R5" t="n">
-        <v>6374249</v>
+        <v>6374253</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128740505</v>
+        <v>128740514</v>
       </c>
       <c r="B6" t="n">
-        <v>98673</v>
+        <v>86800</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219862</v>
+        <v>3712</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717182</v>
+        <v>717295</v>
       </c>
       <c r="R6" t="n">
-        <v>6374336</v>
+        <v>6374249</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1386,32 +1386,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128738834</v>
+        <v>128738853</v>
       </c>
       <c r="B9" t="n">
-        <v>87020</v>
+        <v>86975</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716985</v>
+        <v>717033</v>
       </c>
       <c r="R9" t="n">
-        <v>6374341</v>
+        <v>6374425</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1475,6 +1475,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1493,32 +1494,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128742266</v>
+        <v>128738834</v>
       </c>
       <c r="B10" t="n">
-        <v>86776</v>
+        <v>87020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1528,10 +1529,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717201</v>
+        <v>716985</v>
       </c>
       <c r="R10" t="n">
-        <v>6374151</v>
+        <v>6374341</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,9 +1562,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,44 +1589,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128738837</v>
+        <v>128742266</v>
       </c>
       <c r="B11" t="n">
-        <v>87020</v>
+        <v>86776</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1625,10 +1636,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>717037</v>
+        <v>717201</v>
       </c>
       <c r="R11" t="n">
-        <v>6374236</v>
+        <v>6374151</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1658,19 +1669,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,44 +1686,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128738853</v>
+        <v>128738837</v>
       </c>
       <c r="B12" t="n">
-        <v>86975</v>
+        <v>87020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1732,10 +1733,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>717033</v>
+        <v>717037</v>
       </c>
       <c r="R12" t="n">
-        <v>6374425</v>
+        <v>6374236</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1767,7 +1768,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1777,7 +1778,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1786,7 +1787,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -3705,32 +3705,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128740500</v>
+        <v>128742272</v>
       </c>
       <c r="B32" t="n">
-        <v>86975</v>
+        <v>91055</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6003295</v>
+        <v>5747</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>717281</v>
+        <v>717018</v>
       </c>
       <c r="R32" t="n">
-        <v>6374283</v>
+        <v>6374179</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3784,26 +3784,25 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128740499</v>
+        <v>128740500</v>
       </c>
       <c r="B33" t="n">
         <v>86975</v>
@@ -3838,10 +3837,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>717145</v>
+        <v>717281</v>
       </c>
       <c r="R33" t="n">
-        <v>6374308</v>
+        <v>6374283</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3901,7 +3900,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128740502</v>
+        <v>128740499</v>
       </c>
       <c r="B34" t="n">
         <v>86975</v>
@@ -3936,10 +3935,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>717282</v>
+        <v>717145</v>
       </c>
       <c r="R34" t="n">
-        <v>6374266</v>
+        <v>6374308</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3999,32 +3998,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128742272</v>
+        <v>128740502</v>
       </c>
       <c r="B35" t="n">
-        <v>91055</v>
+        <v>86975</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4034,10 +4033,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>717018</v>
+        <v>717282</v>
       </c>
       <c r="R35" t="n">
-        <v>6374179</v>
+        <v>6374266</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4078,18 +4077,19 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4506,32 +4506,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128742259</v>
+        <v>128738895</v>
       </c>
       <c r="B40" t="n">
-        <v>87020</v>
+        <v>86975</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4541,10 +4541,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>716980</v>
+        <v>716974</v>
       </c>
       <c r="R40" t="n">
-        <v>6374067</v>
+        <v>6374284</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4574,61 +4574,72 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128740509</v>
+        <v>128742268</v>
       </c>
       <c r="B41" t="n">
-        <v>86997</v>
+        <v>86975</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4638,10 +4649,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>717258</v>
+        <v>717267</v>
       </c>
       <c r="R41" t="n">
-        <v>6374286</v>
+        <v>6374322</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4682,50 +4693,51 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128738887</v>
+        <v>128742280</v>
       </c>
       <c r="B42" t="n">
-        <v>86822</v>
+        <v>86975</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4735,10 +4747,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>716984</v>
+        <v>717058</v>
       </c>
       <c r="R42" t="n">
-        <v>6374264</v>
+        <v>6374174</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4768,71 +4780,62 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128738895</v>
+        <v>128740509</v>
       </c>
       <c r="B43" t="n">
-        <v>86975</v>
+        <v>86997</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4842,10 +4845,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>716974</v>
+        <v>717258</v>
       </c>
       <c r="R43" t="n">
-        <v>6374284</v>
+        <v>6374286</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4875,72 +4878,61 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128742268</v>
+        <v>128738887</v>
       </c>
       <c r="B44" t="n">
-        <v>86975</v>
+        <v>86822</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4950,10 +4942,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>717267</v>
+        <v>716984</v>
       </c>
       <c r="R44" t="n">
-        <v>6374322</v>
+        <v>6374264</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4983,62 +4975,71 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128742280</v>
+        <v>128742259</v>
       </c>
       <c r="B45" t="n">
-        <v>86975</v>
+        <v>87020</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5048,10 +5049,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>717058</v>
+        <v>716980</v>
       </c>
       <c r="R45" t="n">
-        <v>6374174</v>
+        <v>6374067</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5092,7 +5093,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -8348,32 +8348,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128740516</v>
+        <v>128738891</v>
       </c>
       <c r="B78" t="n">
-        <v>92153</v>
+        <v>86975</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6031</v>
+        <v>6003295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8383,10 +8383,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>717218</v>
+        <v>717025</v>
       </c>
       <c r="R78" t="n">
-        <v>6374124</v>
+        <v>6374225</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8416,61 +8416,72 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128738891</v>
+        <v>128740516</v>
       </c>
       <c r="B79" t="n">
-        <v>86975</v>
+        <v>92153</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6003295</v>
+        <v>6031</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8480,10 +8491,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>717025</v>
+        <v>717218</v>
       </c>
       <c r="R79" t="n">
-        <v>6374225</v>
+        <v>6374124</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8513,40 +8524,29 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -11300,32 +11300,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128738843</v>
+        <v>128806056</v>
       </c>
       <c r="B107" t="n">
-        <v>87020</v>
+        <v>106977</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>3767</v>
+        <v>221849</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11335,10 +11335,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>716967</v>
+        <v>717370</v>
       </c>
       <c r="R107" t="n">
-        <v>6374084</v>
+        <v>6374168</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11365,22 +11365,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>09:26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>09:26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11395,12 +11385,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -11603,32 +11593,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128806056</v>
+        <v>128738843</v>
       </c>
       <c r="B110" t="n">
-        <v>106977</v>
+        <v>87020</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>221849</v>
+        <v>3767</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11638,10 +11628,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>717370</v>
+        <v>716967</v>
       </c>
       <c r="R110" t="n">
-        <v>6374168</v>
+        <v>6374084</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11668,12 +11658,22 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11688,12 +11688,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
@@ -12407,10 +12407,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128806043</v>
+        <v>128806064</v>
       </c>
       <c r="B118" t="n">
-        <v>75155</v>
+        <v>86938</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12418,21 +12418,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12442,10 +12442,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>717359</v>
+        <v>717299</v>
       </c>
       <c r="R118" t="n">
-        <v>6374214</v>
+        <v>6374300</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12504,10 +12504,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128806064</v>
+        <v>128806043</v>
       </c>
       <c r="B119" t="n">
-        <v>86938</v>
+        <v>75155</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12515,21 +12515,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12539,10 +12539,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>717299</v>
+        <v>717359</v>
       </c>
       <c r="R119" t="n">
-        <v>6374300</v>
+        <v>6374214</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12904,32 +12904,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128806045</v>
+        <v>128806051</v>
       </c>
       <c r="B123" t="n">
-        <v>86997</v>
+        <v>86800</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>449</v>
+        <v>3712</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12939,10 +12939,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>717324</v>
+        <v>717327</v>
       </c>
       <c r="R123" t="n">
-        <v>6374179</v>
+        <v>6374171</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13001,45 +13001,48 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128806051</v>
+        <v>128738882</v>
       </c>
       <c r="B124" t="n">
-        <v>86800</v>
+        <v>87102</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>3712</v>
+        <v>3563</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Stor granspindling</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius bovinus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Fr. sl.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>717327</v>
+        <v>717013</v>
       </c>
       <c r="R124" t="n">
-        <v>6374171</v>
+        <v>6374226</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13066,12 +13069,22 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13080,25 +13093,26 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128806011</v>
+        <v>128738894</v>
       </c>
       <c r="B125" t="n">
         <v>86975</v>
@@ -13133,10 +13147,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>717367</v>
+        <v>716975</v>
       </c>
       <c r="R125" t="n">
-        <v>6374231</v>
+        <v>6374071</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13163,12 +13177,22 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13184,60 +13208,57 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128738882</v>
+        <v>128806011</v>
       </c>
       <c r="B126" t="n">
-        <v>87102</v>
+        <v>86975</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>3563</v>
+        <v>6003295</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Stor granspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cortinarius bovinus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Fr. sl.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>717013</v>
+        <v>717367</v>
       </c>
       <c r="R126" t="n">
-        <v>6374226</v>
+        <v>6374231</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13264,22 +13285,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>13:07</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>13:07</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13295,44 +13306,44 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128738894</v>
+        <v>128806045</v>
       </c>
       <c r="B127" t="n">
-        <v>86975</v>
+        <v>86997</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13342,10 +13353,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>716975</v>
+        <v>717324</v>
       </c>
       <c r="R127" t="n">
-        <v>6374071</v>
+        <v>6374179</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13372,22 +13383,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>09:15</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>09:15</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13396,19 +13397,18 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
@@ -13513,32 +13513,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128806491</v>
+        <v>128806492</v>
       </c>
       <c r="B129" t="n">
-        <v>86975</v>
+        <v>91055</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6003295</v>
+        <v>5747</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13548,10 +13548,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>717324</v>
+        <v>717146</v>
       </c>
       <c r="R129" t="n">
-        <v>6374171</v>
+        <v>6374178</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13592,7 +13592,6 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13611,32 +13610,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128806492</v>
+        <v>128806491</v>
       </c>
       <c r="B130" t="n">
-        <v>91055</v>
+        <v>86975</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13646,10 +13645,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>717146</v>
+        <v>717324</v>
       </c>
       <c r="R130" t="n">
-        <v>6374178</v>
+        <v>6374171</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13690,6 +13689,7 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -14302,32 +14302,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128806065</v>
+        <v>128806486</v>
       </c>
       <c r="B137" t="n">
-        <v>86938</v>
+        <v>87020</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14337,10 +14337,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>717316</v>
+        <v>717170</v>
       </c>
       <c r="R137" t="n">
-        <v>6374280</v>
+        <v>6374288</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14387,44 +14387,44 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128806486</v>
+        <v>128806065</v>
       </c>
       <c r="B138" t="n">
-        <v>87020</v>
+        <v>86938</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14434,10 +14434,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>717170</v>
+        <v>717316</v>
       </c>
       <c r="R138" t="n">
-        <v>6374288</v>
+        <v>6374280</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14484,12 +14484,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>

--- a/artfynd/A 42607-2025 artfynd.xlsx
+++ b/artfynd/A 42607-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128740505</v>
+        <v>128738845</v>
       </c>
       <c r="B2" t="n">
-        <v>98673</v>
+        <v>86779</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219862</v>
+        <v>3762</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717182</v>
+        <v>716961</v>
       </c>
       <c r="R2" t="n">
-        <v>6374336</v>
+        <v>6374255</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,9 +743,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128738845</v>
+        <v>128740514</v>
       </c>
       <c r="B3" t="n">
-        <v>86776</v>
+        <v>86803</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716961</v>
+        <v>717295</v>
       </c>
       <c r="R3" t="n">
-        <v>6374255</v>
+        <v>6374249</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -840,19 +850,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,12 +867,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -882,7 +882,7 @@
         <v>128738831</v>
       </c>
       <c r="B4" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128742256</v>
       </c>
       <c r="B5" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128740514</v>
+        <v>128740505</v>
       </c>
       <c r="B6" t="n">
-        <v>86800</v>
+        <v>98678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3712</v>
+        <v>219862</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717295</v>
+        <v>717182</v>
       </c>
       <c r="R6" t="n">
-        <v>6374249</v>
+        <v>6374336</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128738854</v>
+        <v>128740487</v>
       </c>
       <c r="B7" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716967</v>
+        <v>717292</v>
       </c>
       <c r="R7" t="n">
-        <v>6374338</v>
+        <v>6374265</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1248,19 +1248,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1276,22 +1266,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128740487</v>
+        <v>128738854</v>
       </c>
       <c r="B8" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,10 +1313,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717292</v>
+        <v>716967</v>
       </c>
       <c r="R8" t="n">
-        <v>6374265</v>
+        <v>6374338</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1356,9 +1346,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,12 +1374,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1389,7 +1389,7 @@
         <v>128738853</v>
       </c>
       <c r="B9" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>128738834</v>
       </c>
       <c r="B10" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>128742266</v>
       </c>
       <c r="B11" t="n">
-        <v>86776</v>
+        <v>86779</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>128738837</v>
       </c>
       <c r="B12" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,32 +1805,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128740504</v>
+        <v>128742285</v>
       </c>
       <c r="B13" t="n">
-        <v>98673</v>
+        <v>86978</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219862</v>
+        <v>6003295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>717091</v>
+        <v>716995</v>
       </c>
       <c r="R13" t="n">
-        <v>6374400</v>
+        <v>6374141</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1884,50 +1884,51 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128742285</v>
+        <v>128740482</v>
       </c>
       <c r="B14" t="n">
-        <v>86975</v>
+        <v>87023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1937,10 +1938,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716995</v>
+        <v>717057</v>
       </c>
       <c r="R14" t="n">
-        <v>6374141</v>
+        <v>6374457</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1981,51 +1982,50 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128740482</v>
+        <v>128740504</v>
       </c>
       <c r="B15" t="n">
-        <v>87020</v>
+        <v>98678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3767</v>
+        <v>219862</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2035,10 +2035,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>717057</v>
+        <v>717091</v>
       </c>
       <c r="R15" t="n">
-        <v>6374457</v>
+        <v>6374400</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2097,32 +2097,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128738898</v>
+        <v>128742286</v>
       </c>
       <c r="B16" t="n">
-        <v>86938</v>
+        <v>86978</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>716960</v>
+        <v>716970</v>
       </c>
       <c r="R16" t="n">
-        <v>6374150</v>
+        <v>6374097</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2165,71 +2165,62 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128738832</v>
+        <v>128740498</v>
       </c>
       <c r="B17" t="n">
-        <v>87020</v>
+        <v>86978</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2239,10 +2230,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>717000</v>
+        <v>717099</v>
       </c>
       <c r="R17" t="n">
-        <v>6374409</v>
+        <v>6374395</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2272,71 +2263,62 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128738859</v>
+        <v>128738857</v>
       </c>
       <c r="B18" t="n">
-        <v>98685</v>
+        <v>86978</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219874</v>
+        <v>6003295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2346,10 +2328,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716963</v>
+        <v>717049</v>
       </c>
       <c r="R18" t="n">
-        <v>6374082</v>
+        <v>6374317</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2381,7 +2363,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2391,7 +2373,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2400,6 +2382,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2418,10 +2401,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128742286</v>
+        <v>128738856</v>
       </c>
       <c r="B19" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2453,10 +2436,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716970</v>
+        <v>716986</v>
       </c>
       <c r="R19" t="n">
-        <v>6374097</v>
+        <v>6374339</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2486,9 +2469,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2504,44 +2497,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128740498</v>
+        <v>128738898</v>
       </c>
       <c r="B20" t="n">
-        <v>86975</v>
+        <v>86941</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2544,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>717099</v>
+        <v>716960</v>
       </c>
       <c r="R20" t="n">
-        <v>6374395</v>
+        <v>6374150</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2584,62 +2577,71 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128738857</v>
+        <v>128738832</v>
       </c>
       <c r="B21" t="n">
-        <v>86975</v>
+        <v>87023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2649,10 +2651,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>717049</v>
+        <v>717000</v>
       </c>
       <c r="R21" t="n">
-        <v>6374317</v>
+        <v>6374409</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2684,7 +2686,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2694,7 +2696,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2703,7 +2705,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2722,32 +2723,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128738856</v>
+        <v>128738859</v>
       </c>
       <c r="B22" t="n">
-        <v>86975</v>
+        <v>98690</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6003295</v>
+        <v>219874</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2757,10 +2758,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>716986</v>
+        <v>716963</v>
       </c>
       <c r="R22" t="n">
-        <v>6374339</v>
+        <v>6374082</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2792,7 +2793,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2802,7 +2803,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2811,7 +2812,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2833,7 +2833,7 @@
         <v>128742257</v>
       </c>
       <c r="B23" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>128740485</v>
       </c>
       <c r="B24" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>128742258</v>
       </c>
       <c r="B25" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3121,32 +3121,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128742283</v>
+        <v>128742273</v>
       </c>
       <c r="B26" t="n">
-        <v>86975</v>
+        <v>86954</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6003295</v>
+        <v>1988</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>717040</v>
+        <v>717014</v>
       </c>
       <c r="R26" t="n">
-        <v>6374195</v>
+        <v>6374164</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3200,7 +3200,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3219,32 +3218,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128742281</v>
+        <v>128740489</v>
       </c>
       <c r="B27" t="n">
-        <v>86975</v>
+        <v>91032</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6003295</v>
+        <v>5741</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3254,10 +3253,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>717039</v>
+        <v>717220</v>
       </c>
       <c r="R27" t="n">
-        <v>6374227</v>
+        <v>6374302</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3298,51 +3297,50 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128742273</v>
+        <v>128742281</v>
       </c>
       <c r="B28" t="n">
-        <v>86951</v>
+        <v>86978</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1988</v>
+        <v>6003295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3352,10 +3350,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>717014</v>
+        <v>717039</v>
       </c>
       <c r="R28" t="n">
-        <v>6374164</v>
+        <v>6374227</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3396,6 +3394,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3414,32 +3413,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128740489</v>
+        <v>128742283</v>
       </c>
       <c r="B29" t="n">
-        <v>91029</v>
+        <v>86978</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5741</v>
+        <v>6003295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3449,10 +3448,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>717220</v>
+        <v>717040</v>
       </c>
       <c r="R29" t="n">
-        <v>6374302</v>
+        <v>6374195</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3493,50 +3492,51 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128742293</v>
+        <v>128740500</v>
       </c>
       <c r="B30" t="n">
-        <v>86938</v>
+        <v>86978</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3546,10 +3546,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>717094</v>
+        <v>717281</v>
       </c>
       <c r="R30" t="n">
-        <v>6374468</v>
+        <v>6374283</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3590,50 +3590,51 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128742254</v>
+        <v>128740499</v>
       </c>
       <c r="B31" t="n">
-        <v>87020</v>
+        <v>86978</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3643,10 +3644,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>717285</v>
+        <v>717145</v>
       </c>
       <c r="R31" t="n">
-        <v>6374272</v>
+        <v>6374308</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3687,50 +3688,51 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128742272</v>
+        <v>128740502</v>
       </c>
       <c r="B32" t="n">
-        <v>91055</v>
+        <v>86978</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3740,10 +3742,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>717018</v>
+        <v>717282</v>
       </c>
       <c r="R32" t="n">
-        <v>6374179</v>
+        <v>6374266</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3784,50 +3786,51 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128740500</v>
+        <v>128742254</v>
       </c>
       <c r="B33" t="n">
-        <v>86975</v>
+        <v>87023</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3837,10 +3840,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>717281</v>
+        <v>717285</v>
       </c>
       <c r="R33" t="n">
-        <v>6374283</v>
+        <v>6374272</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3881,51 +3884,50 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128740499</v>
+        <v>128742293</v>
       </c>
       <c r="B34" t="n">
-        <v>86975</v>
+        <v>86941</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3935,10 +3937,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>717145</v>
+        <v>717094</v>
       </c>
       <c r="R34" t="n">
-        <v>6374308</v>
+        <v>6374468</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3979,51 +3981,50 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128740502</v>
+        <v>128742272</v>
       </c>
       <c r="B35" t="n">
-        <v>86975</v>
+        <v>91058</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6003295</v>
+        <v>5747</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4033,10 +4034,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>717282</v>
+        <v>717018</v>
       </c>
       <c r="R35" t="n">
-        <v>6374266</v>
+        <v>6374179</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4077,19 +4078,18 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4099,7 +4099,7 @@
         <v>128740521</v>
       </c>
       <c r="B36" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>128738900</v>
       </c>
       <c r="B37" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>128742267</v>
       </c>
       <c r="B38" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>128738858</v>
       </c>
       <c r="B39" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4506,32 +4506,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128738895</v>
+        <v>128740509</v>
       </c>
       <c r="B40" t="n">
-        <v>86975</v>
+        <v>87000</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4541,10 +4541,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>716974</v>
+        <v>717258</v>
       </c>
       <c r="R40" t="n">
-        <v>6374284</v>
+        <v>6374286</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4574,72 +4574,61 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128742268</v>
+        <v>128738887</v>
       </c>
       <c r="B41" t="n">
-        <v>86975</v>
+        <v>86825</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4649,10 +4638,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>717267</v>
+        <v>716984</v>
       </c>
       <c r="R41" t="n">
-        <v>6374322</v>
+        <v>6374264</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4682,62 +4671,71 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128742280</v>
+        <v>128742259</v>
       </c>
       <c r="B42" t="n">
-        <v>86975</v>
+        <v>87023</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4747,10 +4745,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>717058</v>
+        <v>716980</v>
       </c>
       <c r="R42" t="n">
-        <v>6374174</v>
+        <v>6374067</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4791,7 +4789,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4810,32 +4807,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128740509</v>
+        <v>128738895</v>
       </c>
       <c r="B43" t="n">
-        <v>86997</v>
+        <v>86978</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4845,10 +4842,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>717258</v>
+        <v>716974</v>
       </c>
       <c r="R43" t="n">
-        <v>6374286</v>
+        <v>6374284</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4878,61 +4875,72 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128738887</v>
+        <v>128742268</v>
       </c>
       <c r="B44" t="n">
-        <v>86822</v>
+        <v>86978</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4942,10 +4950,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>716984</v>
+        <v>717267</v>
       </c>
       <c r="R44" t="n">
-        <v>6374264</v>
+        <v>6374322</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4975,71 +4983,62 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128742259</v>
+        <v>128742280</v>
       </c>
       <c r="B45" t="n">
-        <v>87020</v>
+        <v>86978</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5049,10 +5048,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>716980</v>
+        <v>717058</v>
       </c>
       <c r="R45" t="n">
-        <v>6374067</v>
+        <v>6374174</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5093,6 +5092,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5114,7 +5114,7 @@
         <v>128738880</v>
       </c>
       <c r="B46" t="n">
-        <v>86800</v>
+        <v>86803</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
         <v>128738838</v>
       </c>
       <c r="B47" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5325,10 +5325,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128742289</v>
+        <v>128742269</v>
       </c>
       <c r="B48" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5360,10 +5360,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>716965</v>
+        <v>717186</v>
       </c>
       <c r="R48" t="n">
-        <v>6374079</v>
+        <v>6374129</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5423,10 +5423,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128742269</v>
+        <v>128742288</v>
       </c>
       <c r="B49" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>717186</v>
+        <v>716995</v>
       </c>
       <c r="R49" t="n">
-        <v>6374129</v>
+        <v>6374147</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5521,10 +5521,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128742279</v>
+        <v>128742289</v>
       </c>
       <c r="B50" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5556,10 +5556,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>717013</v>
+        <v>716965</v>
       </c>
       <c r="R50" t="n">
-        <v>6374176</v>
+        <v>6374079</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5619,10 +5619,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128742288</v>
+        <v>128742279</v>
       </c>
       <c r="B51" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5654,10 +5654,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>716995</v>
+        <v>717013</v>
       </c>
       <c r="R51" t="n">
-        <v>6374147</v>
+        <v>6374176</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5720,7 +5720,7 @@
         <v>128738896</v>
       </c>
       <c r="B52" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>128742291</v>
       </c>
       <c r="B53" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>128742284</v>
       </c>
       <c r="B54" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6021,32 +6021,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128742263</v>
+        <v>128738841</v>
       </c>
       <c r="B55" t="n">
-        <v>91029</v>
+        <v>87023</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5741</v>
+        <v>3767</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6056,10 +6056,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>717281</v>
+        <v>716992</v>
       </c>
       <c r="R55" t="n">
-        <v>6374199</v>
+        <v>6374116</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6089,9 +6089,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6106,22 +6116,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128738841</v>
+        <v>128738835</v>
       </c>
       <c r="B56" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6153,10 +6163,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>716992</v>
+        <v>716983</v>
       </c>
       <c r="R56" t="n">
-        <v>6374116</v>
+        <v>6374357</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6188,7 +6198,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6198,7 +6208,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6225,10 +6235,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128738835</v>
+        <v>128742252</v>
       </c>
       <c r="B57" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6260,10 +6270,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>716983</v>
+        <v>717146</v>
       </c>
       <c r="R57" t="n">
-        <v>6374357</v>
+        <v>6374313</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6293,19 +6303,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>14:27</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6320,44 +6320,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128742252</v>
+        <v>128740522</v>
       </c>
       <c r="B58" t="n">
-        <v>87020</v>
+        <v>86941</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6367,10 +6367,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>717146</v>
+        <v>717274</v>
       </c>
       <c r="R58" t="n">
-        <v>6374313</v>
+        <v>6374210</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6417,22 +6417,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128740522</v>
+        <v>128742263</v>
       </c>
       <c r="B59" t="n">
-        <v>86938</v>
+        <v>91032</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6440,21 +6440,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3674</v>
+        <v>5741</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6464,10 +6464,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>717274</v>
+        <v>717281</v>
       </c>
       <c r="R59" t="n">
-        <v>6374210</v>
+        <v>6374199</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6514,12 +6514,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6529,7 +6529,7 @@
         <v>128742282</v>
       </c>
       <c r="B60" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>128742276</v>
       </c>
       <c r="B61" t="n">
-        <v>86997</v>
+        <v>87000</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>128738884</v>
       </c>
       <c r="B62" t="n">
-        <v>86822</v>
+        <v>86825</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6828,32 +6828,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128740491</v>
+        <v>128738848</v>
       </c>
       <c r="B63" t="n">
-        <v>86776</v>
+        <v>57720</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3762</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6863,10 +6863,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>717281</v>
+        <v>717165</v>
       </c>
       <c r="R63" t="n">
-        <v>6374215</v>
+        <v>6374351</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6896,9 +6896,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6913,44 +6923,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128742255</v>
+        <v>128740491</v>
       </c>
       <c r="B64" t="n">
-        <v>87020</v>
+        <v>86779</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6960,10 +6970,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>717059</v>
+        <v>717281</v>
       </c>
       <c r="R64" t="n">
-        <v>6374329</v>
+        <v>6374215</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7010,44 +7020,44 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128738848</v>
+        <v>128742255</v>
       </c>
       <c r="B65" t="n">
-        <v>57720</v>
+        <v>87023</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>3767</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7057,10 +7067,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>717165</v>
+        <v>717059</v>
       </c>
       <c r="R65" t="n">
-        <v>6374351</v>
+        <v>6374329</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7090,19 +7100,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>10:25</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7117,22 +7117,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128738851</v>
+        <v>128740512</v>
       </c>
       <c r="B66" t="n">
-        <v>86776</v>
+        <v>86803</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7140,21 +7140,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7164,10 +7164,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>717040</v>
+        <v>717079</v>
       </c>
       <c r="R66" t="n">
-        <v>6374229</v>
+        <v>6374436</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7197,19 +7197,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7224,22 +7214,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128740512</v>
+        <v>128738851</v>
       </c>
       <c r="B67" t="n">
-        <v>86800</v>
+        <v>86779</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7247,21 +7237,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3712</v>
+        <v>3762</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7271,10 +7261,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>717079</v>
+        <v>717040</v>
       </c>
       <c r="R67" t="n">
-        <v>6374436</v>
+        <v>6374229</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7304,9 +7294,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7321,12 +7321,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7336,7 +7336,7 @@
         <v>128738836</v>
       </c>
       <c r="B68" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>128738855</v>
       </c>
       <c r="B69" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>128738852</v>
       </c>
       <c r="B70" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>128740508</v>
       </c>
       <c r="B71" t="n">
-        <v>86997</v>
+        <v>87000</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7753,32 +7753,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128742251</v>
+        <v>128740519</v>
       </c>
       <c r="B72" t="n">
-        <v>87020</v>
+        <v>86941</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7788,10 +7788,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>717106</v>
+        <v>717067</v>
       </c>
       <c r="R72" t="n">
-        <v>6374415</v>
+        <v>6374399</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7838,22 +7838,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128738833</v>
+        <v>128742251</v>
       </c>
       <c r="B73" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7885,10 +7885,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>716976</v>
+        <v>717106</v>
       </c>
       <c r="R73" t="n">
-        <v>6374331</v>
+        <v>6374415</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7918,19 +7918,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7945,44 +7935,44 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128740519</v>
+        <v>128738833</v>
       </c>
       <c r="B74" t="n">
-        <v>86938</v>
+        <v>87023</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7992,10 +7982,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>717067</v>
+        <v>716976</v>
       </c>
       <c r="R74" t="n">
-        <v>6374399</v>
+        <v>6374331</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8025,9 +8015,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8042,12 +8042,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8057,7 +8057,7 @@
         <v>128742287</v>
       </c>
       <c r="B75" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>128742270</v>
       </c>
       <c r="B76" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>128742290</v>
       </c>
       <c r="B77" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8348,32 +8348,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128738891</v>
+        <v>128740516</v>
       </c>
       <c r="B78" t="n">
-        <v>86975</v>
+        <v>92158</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6003295</v>
+        <v>6031</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8383,10 +8383,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>717025</v>
+        <v>717218</v>
       </c>
       <c r="R78" t="n">
-        <v>6374225</v>
+        <v>6374124</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8416,72 +8416,61 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128740516</v>
+        <v>128738891</v>
       </c>
       <c r="B79" t="n">
-        <v>92153</v>
+        <v>86978</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6031</v>
+        <v>6003295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8491,10 +8480,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>717218</v>
+        <v>717025</v>
       </c>
       <c r="R79" t="n">
-        <v>6374124</v>
+        <v>6374225</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8524,29 +8513,40 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -8556,7 +8556,7 @@
         <v>128738890</v>
       </c>
       <c r="B80" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>128740484</v>
       </c>
       <c r="B81" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>128740518</v>
       </c>
       <c r="B82" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>128740503</v>
       </c>
       <c r="B83" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>128740510</v>
       </c>
       <c r="B84" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
         <v>128738899</v>
       </c>
       <c r="B85" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>128806499</v>
       </c>
       <c r="B86" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9254,10 +9254,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128815957</v>
+        <v>128806483</v>
       </c>
       <c r="B87" t="n">
-        <v>86992</v>
+        <v>90998</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9265,21 +9265,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>248934</v>
+        <v>720</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knölfotad bananspindling</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius stjernegaardii</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Brandrud &amp; Frøslev</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9292,10 +9292,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>717020</v>
+        <v>717267</v>
       </c>
       <c r="R87" t="n">
-        <v>6374147</v>
+        <v>6374381</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9322,27 +9322,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>10:37</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Bilddokumentation av Ullas fynd. Uppsvullen bulb och orange basalmycel. Ek fanss på fyndplatsen som domineras av kalktallskog.</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9358,22 +9343,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128806483</v>
+        <v>128815957</v>
       </c>
       <c r="B88" t="n">
-        <v>90995</v>
+        <v>86995</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9381,21 +9366,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>720</v>
+        <v>248934</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Knölfotad bananspindling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Cortinarius stjernegaardii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>Brandrud &amp; Frøslev</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9408,10 +9393,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>717267</v>
+        <v>717020</v>
       </c>
       <c r="R88" t="n">
-        <v>6374381</v>
+        <v>6374147</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9438,12 +9423,27 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Bilddokumentation av Ullas fynd. Uppsvullen bulb och orange basalmycel. Ek fanss på fyndplatsen som domineras av kalktallskog.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9459,12 +9459,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -9474,7 +9474,7 @@
         <v>128738885</v>
       </c>
       <c r="B89" t="n">
-        <v>86822</v>
+        <v>86825</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9578,10 +9578,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128805996</v>
+        <v>128806494</v>
       </c>
       <c r="B90" t="n">
-        <v>87020</v>
+        <v>87000</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9589,21 +9589,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9613,10 +9613,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>717308</v>
+        <v>717333</v>
       </c>
       <c r="R90" t="n">
-        <v>6374239</v>
+        <v>6374180</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9663,22 +9663,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128806494</v>
+        <v>128806493</v>
       </c>
       <c r="B91" t="n">
-        <v>86997</v>
+        <v>87000</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9710,10 +9710,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>717333</v>
+        <v>717133</v>
       </c>
       <c r="R91" t="n">
-        <v>6374180</v>
+        <v>6374199</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9772,10 +9772,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128806493</v>
+        <v>128805996</v>
       </c>
       <c r="B92" t="n">
-        <v>86997</v>
+        <v>87023</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9783,21 +9783,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9807,10 +9807,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>717133</v>
+        <v>717308</v>
       </c>
       <c r="R92" t="n">
-        <v>6374199</v>
+        <v>6374239</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9857,44 +9857,44 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128738839</v>
+        <v>128738846</v>
       </c>
       <c r="B93" t="n">
-        <v>87020</v>
+        <v>91032</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3767</v>
+        <v>5741</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9904,10 +9904,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>717039</v>
+        <v>717037</v>
       </c>
       <c r="R93" t="n">
-        <v>6374168</v>
+        <v>6374226</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9976,10 +9976,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128738846</v>
+        <v>128815850</v>
       </c>
       <c r="B94" t="n">
-        <v>91029</v>
+        <v>89501</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9987,21 +9987,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5741</v>
+        <v>236437</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Brun klibbskivling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Limacella glioderma</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Fr.) Maire</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10011,10 +10011,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>717037</v>
+        <v>716975</v>
       </c>
       <c r="R94" t="n">
-        <v>6374226</v>
+        <v>6374071</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10046,7 +10046,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10083,10 +10083,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128806044</v>
+        <v>128738839</v>
       </c>
       <c r="B95" t="n">
-        <v>86997</v>
+        <v>87023</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10094,21 +10094,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10118,10 +10118,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>717148</v>
+        <v>717039</v>
       </c>
       <c r="R95" t="n">
-        <v>6374175</v>
+        <v>6374168</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10148,12 +10148,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10168,44 +10178,44 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128806038</v>
+        <v>128806044</v>
       </c>
       <c r="B96" t="n">
-        <v>98673</v>
+        <v>87000</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>219862</v>
+        <v>449</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10215,10 +10225,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>717113</v>
+        <v>717148</v>
       </c>
       <c r="R96" t="n">
-        <v>6374105</v>
+        <v>6374175</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10277,10 +10287,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128815850</v>
+        <v>128806038</v>
       </c>
       <c r="B97" t="n">
-        <v>89498</v>
+        <v>98678</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10288,21 +10298,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>236437</v>
+        <v>219862</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Brun klibbskivling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Limacella glioderma</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Maire</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10312,10 +10322,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>716975</v>
+        <v>717113</v>
       </c>
       <c r="R97" t="n">
-        <v>6374071</v>
+        <v>6374105</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10342,22 +10352,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>09:13</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>09:13</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10372,12 +10372,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -10387,7 +10387,7 @@
         <v>128806004</v>
       </c>
       <c r="B98" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>128806484</v>
       </c>
       <c r="B99" t="n">
-        <v>90995</v>
+        <v>90998</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>128738866</v>
       </c>
       <c r="B100" t="n">
-        <v>90261</v>
+        <v>90264</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>128738897</v>
       </c>
       <c r="B101" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10801,7 +10801,7 @@
         <v>128806005</v>
       </c>
       <c r="B102" t="n">
-        <v>91029</v>
+        <v>91032</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>128806009</v>
       </c>
       <c r="B103" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>128738875</v>
       </c>
       <c r="B104" t="n">
-        <v>87032</v>
+        <v>87035</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11099,7 +11099,7 @@
         <v>128738842</v>
       </c>
       <c r="B105" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>128805993</v>
       </c>
       <c r="B106" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11300,32 +11300,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128806056</v>
+        <v>128738843</v>
       </c>
       <c r="B107" t="n">
-        <v>106977</v>
+        <v>87023</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221849</v>
+        <v>3767</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11335,10 +11335,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>717370</v>
+        <v>716967</v>
       </c>
       <c r="R107" t="n">
-        <v>6374168</v>
+        <v>6374084</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11365,12 +11365,22 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11385,22 +11395,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128806010</v>
+        <v>128806056</v>
       </c>
       <c r="B108" t="n">
-        <v>86975</v>
+        <v>106982</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11408,21 +11418,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6003295</v>
+        <v>221849</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11432,10 +11442,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>717186</v>
+        <v>717370</v>
       </c>
       <c r="R108" t="n">
-        <v>6374253</v>
+        <v>6374168</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11476,7 +11486,6 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11488,17 +11497,17 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128806023</v>
+        <v>128806010</v>
       </c>
       <c r="B109" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11530,10 +11539,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>717360</v>
+        <v>717186</v>
       </c>
       <c r="R109" t="n">
-        <v>6374214</v>
+        <v>6374253</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11593,32 +11602,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128738843</v>
+        <v>128806023</v>
       </c>
       <c r="B110" t="n">
-        <v>87020</v>
+        <v>86978</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11628,10 +11637,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>716967</v>
+        <v>717360</v>
       </c>
       <c r="R110" t="n">
-        <v>6374084</v>
+        <v>6374214</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11658,22 +11667,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>09:26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>09:26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11682,50 +11681,51 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128738840</v>
+        <v>128806497</v>
       </c>
       <c r="B111" t="n">
-        <v>87020</v>
+        <v>86803</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>3767</v>
+        <v>3712</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11735,10 +11735,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>717020</v>
+        <v>717273</v>
       </c>
       <c r="R111" t="n">
-        <v>6374147</v>
+        <v>6374182</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11765,22 +11765,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>10:06</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>10:06</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11795,44 +11785,44 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128806497</v>
+        <v>128806022</v>
       </c>
       <c r="B112" t="n">
-        <v>86800</v>
+        <v>86978</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11842,10 +11832,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>717273</v>
+        <v>717284</v>
       </c>
       <c r="R112" t="n">
-        <v>6374182</v>
+        <v>6374309</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11886,50 +11876,51 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128806022</v>
+        <v>128738840</v>
       </c>
       <c r="B113" t="n">
-        <v>86975</v>
+        <v>87023</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11939,10 +11930,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>717284</v>
+        <v>717020</v>
       </c>
       <c r="R113" t="n">
-        <v>6374309</v>
+        <v>6374147</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11969,12 +11960,22 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11983,51 +11984,50 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128738886</v>
+        <v>128738893</v>
       </c>
       <c r="B114" t="n">
-        <v>86822</v>
+        <v>86978</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12037,10 +12037,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>716990</v>
+        <v>717000</v>
       </c>
       <c r="R114" t="n">
-        <v>6374260</v>
+        <v>6374121</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12072,7 +12072,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12091,6 +12091,7 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12109,32 +12110,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128738893</v>
+        <v>128806495</v>
       </c>
       <c r="B115" t="n">
-        <v>86975</v>
+        <v>86865</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6003295</v>
+        <v>442</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12144,10 +12145,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>717000</v>
+        <v>717357</v>
       </c>
       <c r="R115" t="n">
-        <v>6374121</v>
+        <v>6374169</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12174,22 +12175,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>10:04</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>10:04</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12198,29 +12189,28 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128806495</v>
+        <v>128806049</v>
       </c>
       <c r="B116" t="n">
-        <v>86862</v>
+        <v>87035</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12228,23 +12218,19 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -12252,10 +12238,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>717357</v>
+        <v>717128</v>
       </c>
       <c r="R116" t="n">
-        <v>6374169</v>
+        <v>6374123</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12302,42 +12288,46 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128806049</v>
+        <v>128806043</v>
       </c>
       <c r="B117" t="n">
-        <v>87032</v>
+        <v>75155</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>433</v>
+        <v>6426</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr"/>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -12345,10 +12335,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>717128</v>
+        <v>717359</v>
       </c>
       <c r="R117" t="n">
-        <v>6374123</v>
+        <v>6374214</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12410,7 +12400,7 @@
         <v>128806064</v>
       </c>
       <c r="B118" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12504,32 +12494,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128806043</v>
+        <v>128806050</v>
       </c>
       <c r="B119" t="n">
-        <v>75155</v>
+        <v>86944</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6426</v>
+        <v>6037417</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12539,10 +12529,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>717359</v>
+        <v>717311</v>
       </c>
       <c r="R119" t="n">
-        <v>6374214</v>
+        <v>6374287</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12583,6 +12573,7 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -12601,32 +12592,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128806050</v>
+        <v>128738886</v>
       </c>
       <c r="B120" t="n">
-        <v>86941</v>
+        <v>86825</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6037417</v>
+        <v>424</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12636,10 +12627,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>717311</v>
+        <v>716990</v>
       </c>
       <c r="R120" t="n">
-        <v>6374287</v>
+        <v>6374260</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12666,12 +12657,22 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12680,19 +12681,18 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -12702,7 +12702,7 @@
         <v>128738892</v>
       </c>
       <c r="B121" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>128806052</v>
       </c>
       <c r="B122" t="n">
-        <v>86800</v>
+        <v>86803</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12904,32 +12904,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128806051</v>
+        <v>128806045</v>
       </c>
       <c r="B123" t="n">
-        <v>86800</v>
+        <v>87000</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>3712</v>
+        <v>449</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12939,10 +12939,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>717327</v>
+        <v>717324</v>
       </c>
       <c r="R123" t="n">
-        <v>6374171</v>
+        <v>6374179</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13004,7 +13004,7 @@
         <v>128738882</v>
       </c>
       <c r="B124" t="n">
-        <v>87102</v>
+        <v>87105</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         <v>128738894</v>
       </c>
       <c r="B125" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13220,32 +13220,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128806011</v>
+        <v>128806051</v>
       </c>
       <c r="B126" t="n">
-        <v>86975</v>
+        <v>86803</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13255,10 +13255,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>717367</v>
+        <v>717327</v>
       </c>
       <c r="R126" t="n">
-        <v>6374231</v>
+        <v>6374171</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13299,7 +13299,6 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13311,39 +13310,39 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128806045</v>
+        <v>128806011</v>
       </c>
       <c r="B127" t="n">
-        <v>86997</v>
+        <v>86978</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13353,10 +13352,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>717324</v>
+        <v>717367</v>
       </c>
       <c r="R127" t="n">
-        <v>6374179</v>
+        <v>6374231</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13397,6 +13396,7 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13408,7 +13408,7 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
@@ -13418,7 +13418,7 @@
         <v>128806485</v>
       </c>
       <c r="B128" t="n">
-        <v>86800</v>
+        <v>86803</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13513,32 +13513,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128806492</v>
+        <v>128806491</v>
       </c>
       <c r="B129" t="n">
-        <v>91055</v>
+        <v>86978</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13548,10 +13548,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>717146</v>
+        <v>717324</v>
       </c>
       <c r="R129" t="n">
-        <v>6374178</v>
+        <v>6374171</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13592,6 +13592,7 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13610,32 +13611,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128806491</v>
+        <v>128806492</v>
       </c>
       <c r="B130" t="n">
-        <v>86975</v>
+        <v>91058</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6003295</v>
+        <v>5747</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13645,10 +13646,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>717324</v>
+        <v>717146</v>
       </c>
       <c r="R130" t="n">
-        <v>6374171</v>
+        <v>6374178</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13689,7 +13690,6 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13711,7 +13711,7 @@
         <v>128806057</v>
       </c>
       <c r="B131" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13805,32 +13805,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128738847</v>
+        <v>128806058</v>
       </c>
       <c r="B132" t="n">
-        <v>86891</v>
+        <v>86941</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>248956</v>
+        <v>3674</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13840,10 +13840,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>716980</v>
+        <v>717196</v>
       </c>
       <c r="R132" t="n">
-        <v>6374264</v>
+        <v>6374281</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13870,22 +13870,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13900,12 +13890,12 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
@@ -13915,7 +13905,7 @@
         <v>128806487</v>
       </c>
       <c r="B133" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14012,7 +14002,7 @@
         <v>128806490</v>
       </c>
       <c r="B134" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14107,32 +14097,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128806058</v>
+        <v>128738847</v>
       </c>
       <c r="B135" t="n">
-        <v>86938</v>
+        <v>86894</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3674</v>
+        <v>248956</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14142,10 +14132,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>717196</v>
+        <v>716980</v>
       </c>
       <c r="R135" t="n">
-        <v>6374281</v>
+        <v>6374264</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14172,12 +14162,22 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14192,12 +14192,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -14207,7 +14207,7 @@
         <v>128806013</v>
       </c>
       <c r="B136" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14302,32 +14302,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128806486</v>
+        <v>128806065</v>
       </c>
       <c r="B137" t="n">
-        <v>87020</v>
+        <v>86941</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14337,10 +14337,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>717170</v>
+        <v>717316</v>
       </c>
       <c r="R137" t="n">
-        <v>6374288</v>
+        <v>6374280</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14387,44 +14387,44 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128806065</v>
+        <v>128806486</v>
       </c>
       <c r="B138" t="n">
-        <v>86938</v>
+        <v>87023</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14434,10 +14434,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>717316</v>
+        <v>717170</v>
       </c>
       <c r="R138" t="n">
-        <v>6374280</v>
+        <v>6374288</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14484,44 +14484,44 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128806496</v>
+        <v>128738883</v>
       </c>
       <c r="B139" t="n">
-        <v>96247</v>
+        <v>86841</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2180</v>
+        <v>3561</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blåbandad spindling</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cortinarius borgsjoeensis</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14531,10 +14531,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>717337</v>
+        <v>716993</v>
       </c>
       <c r="R139" t="n">
-        <v>6374082</v>
+        <v>6374384</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14561,12 +14561,22 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14575,50 +14585,51 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128805991</v>
+        <v>128806496</v>
       </c>
       <c r="B140" t="n">
-        <v>87020</v>
+        <v>96252</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>3767</v>
+        <v>2180</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14628,10 +14639,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>717147</v>
+        <v>717337</v>
       </c>
       <c r="R140" t="n">
-        <v>6374164</v>
+        <v>6374082</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14678,44 +14689,44 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128806024</v>
+        <v>128805991</v>
       </c>
       <c r="B141" t="n">
-        <v>86975</v>
+        <v>87023</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14725,10 +14736,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>717366</v>
+        <v>717147</v>
       </c>
       <c r="R141" t="n">
-        <v>6374150</v>
+        <v>6374164</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14769,7 +14780,6 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -14781,39 +14791,39 @@
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128738883</v>
+        <v>128806024</v>
       </c>
       <c r="B142" t="n">
-        <v>86838</v>
+        <v>86978</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>3561</v>
+        <v>6003295</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Blåbandad spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cortinarius borgsjoeensis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14823,10 +14833,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>716993</v>
+        <v>717366</v>
       </c>
       <c r="R142" t="n">
-        <v>6374384</v>
+        <v>6374150</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14853,22 +14863,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -14884,12 +14884,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
@@ -14899,7 +14899,7 @@
         <v>128738867</v>
       </c>
       <c r="B143" t="n">
-        <v>86997</v>
+        <v>87000</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>128742275</v>
       </c>
       <c r="B144" t="n">
-        <v>86926</v>
+        <v>86929</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 42607-2025 artfynd.xlsx
+++ b/artfynd/A 42607-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128738845</v>
       </c>
       <c r="B2" t="n">
-        <v>86779</v>
+        <v>86782</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128740514</v>
+        <v>128738831</v>
       </c>
       <c r="B3" t="n">
-        <v>86803</v>
+        <v>87026</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3712</v>
+        <v>3767</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717295</v>
+        <v>717030</v>
       </c>
       <c r="R3" t="n">
-        <v>6374249</v>
+        <v>6374429</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,9 +850,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128738831</v>
+        <v>128742256</v>
       </c>
       <c r="B4" t="n">
-        <v>87023</v>
+        <v>87026</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717030</v>
+        <v>717053</v>
       </c>
       <c r="R4" t="n">
-        <v>6374429</v>
+        <v>6374253</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -947,19 +957,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,44 +974,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128742256</v>
+        <v>128740514</v>
       </c>
       <c r="B5" t="n">
-        <v>87023</v>
+        <v>86806</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3767</v>
+        <v>3712</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717053</v>
+        <v>717295</v>
       </c>
       <c r="R5" t="n">
-        <v>6374253</v>
+        <v>6374249</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,12 +1071,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1086,7 +1086,7 @@
         <v>128740505</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>98681</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128740487</v>
+        <v>128738854</v>
       </c>
       <c r="B7" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717292</v>
+        <v>716967</v>
       </c>
       <c r="R7" t="n">
-        <v>6374265</v>
+        <v>6374338</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1248,9 +1248,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1266,22 +1276,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128738854</v>
+        <v>128740487</v>
       </c>
       <c r="B8" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1313,10 +1323,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716967</v>
+        <v>717292</v>
       </c>
       <c r="R8" t="n">
-        <v>6374338</v>
+        <v>6374265</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,19 +1356,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,12 +1374,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1389,7 +1389,7 @@
         <v>128738853</v>
       </c>
       <c r="B9" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>128738834</v>
       </c>
       <c r="B10" t="n">
-        <v>87023</v>
+        <v>87026</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>128742266</v>
       </c>
       <c r="B11" t="n">
-        <v>86779</v>
+        <v>86782</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>128738837</v>
       </c>
       <c r="B12" t="n">
-        <v>87023</v>
+        <v>87026</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,32 +1805,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128742285</v>
+        <v>128740482</v>
       </c>
       <c r="B13" t="n">
-        <v>86978</v>
+        <v>87026</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716995</v>
+        <v>717057</v>
       </c>
       <c r="R13" t="n">
-        <v>6374141</v>
+        <v>6374457</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1884,51 +1884,50 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128740482</v>
+        <v>128742285</v>
       </c>
       <c r="B14" t="n">
-        <v>87023</v>
+        <v>86981</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1938,10 +1937,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>717057</v>
+        <v>716995</v>
       </c>
       <c r="R14" t="n">
-        <v>6374457</v>
+        <v>6374141</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1982,18 +1981,19 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2003,7 +2003,7 @@
         <v>128740504</v>
       </c>
       <c r="B15" t="n">
-        <v>98678</v>
+        <v>98681</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>128742286</v>
       </c>
       <c r="B16" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>128740498</v>
       </c>
       <c r="B17" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>128738857</v>
       </c>
       <c r="B18" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2401,32 +2401,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128738856</v>
+        <v>128738898</v>
       </c>
       <c r="B19" t="n">
-        <v>86978</v>
+        <v>86944</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2436,10 +2436,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716986</v>
+        <v>716960</v>
       </c>
       <c r="R19" t="n">
-        <v>6374339</v>
+        <v>6374150</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2490,7 +2490,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2509,32 +2508,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128738898</v>
+        <v>128738832</v>
       </c>
       <c r="B20" t="n">
-        <v>86941</v>
+        <v>87026</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2544,10 +2543,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>716960</v>
+        <v>717000</v>
       </c>
       <c r="R20" t="n">
-        <v>6374150</v>
+        <v>6374409</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2579,7 +2578,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2589,7 +2588,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2616,32 +2615,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128738832</v>
+        <v>128738859</v>
       </c>
       <c r="B21" t="n">
-        <v>87023</v>
+        <v>98693</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3767</v>
+        <v>219874</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2651,10 +2650,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>717000</v>
+        <v>716963</v>
       </c>
       <c r="R21" t="n">
-        <v>6374409</v>
+        <v>6374082</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2686,7 +2685,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2696,7 +2695,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2723,32 +2722,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128738859</v>
+        <v>128738856</v>
       </c>
       <c r="B22" t="n">
-        <v>98690</v>
+        <v>86981</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219874</v>
+        <v>6003295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2758,10 +2757,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>716963</v>
+        <v>716986</v>
       </c>
       <c r="R22" t="n">
-        <v>6374082</v>
+        <v>6374339</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2793,7 +2792,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2803,7 +2802,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2812,6 +2811,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2833,7 +2833,7 @@
         <v>128742257</v>
       </c>
       <c r="B23" t="n">
-        <v>87023</v>
+        <v>87026</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>128740485</v>
       </c>
       <c r="B24" t="n">
-        <v>87023</v>
+        <v>87026</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>128742258</v>
       </c>
       <c r="B25" t="n">
-        <v>87023</v>
+        <v>87026</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3121,32 +3121,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128742273</v>
+        <v>128742283</v>
       </c>
       <c r="B26" t="n">
-        <v>86954</v>
+        <v>86981</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1988</v>
+        <v>6003295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>717014</v>
+        <v>717040</v>
       </c>
       <c r="R26" t="n">
-        <v>6374164</v>
+        <v>6374195</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3200,6 +3200,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3218,32 +3219,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128740489</v>
+        <v>128742281</v>
       </c>
       <c r="B27" t="n">
-        <v>91032</v>
+        <v>86981</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5741</v>
+        <v>6003295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3253,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>717220</v>
+        <v>717039</v>
       </c>
       <c r="R27" t="n">
-        <v>6374302</v>
+        <v>6374227</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3297,50 +3298,51 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128742281</v>
+        <v>128742273</v>
       </c>
       <c r="B28" t="n">
-        <v>86978</v>
+        <v>86957</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6003295</v>
+        <v>1988</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3350,10 +3352,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>717039</v>
+        <v>717014</v>
       </c>
       <c r="R28" t="n">
-        <v>6374227</v>
+        <v>6374164</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3394,7 +3396,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3413,32 +3414,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128742283</v>
+        <v>128740489</v>
       </c>
       <c r="B29" t="n">
-        <v>86978</v>
+        <v>91035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6003295</v>
+        <v>5741</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3448,10 +3449,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>717040</v>
+        <v>717220</v>
       </c>
       <c r="R29" t="n">
-        <v>6374195</v>
+        <v>6374302</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3492,19 +3493,18 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3514,7 +3514,7 @@
         <v>128740500</v>
       </c>
       <c r="B30" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>128740499</v>
       </c>
       <c r="B31" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>128740502</v>
       </c>
       <c r="B32" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3805,32 +3805,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128742254</v>
+        <v>128742293</v>
       </c>
       <c r="B33" t="n">
-        <v>87023</v>
+        <v>86944</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>717285</v>
+        <v>717094</v>
       </c>
       <c r="R33" t="n">
-        <v>6374272</v>
+        <v>6374468</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3902,32 +3902,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128742293</v>
+        <v>128742254</v>
       </c>
       <c r="B34" t="n">
-        <v>86941</v>
+        <v>87026</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>717094</v>
+        <v>717285</v>
       </c>
       <c r="R34" t="n">
-        <v>6374468</v>
+        <v>6374272</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4002,7 +4002,7 @@
         <v>128742272</v>
       </c>
       <c r="B35" t="n">
-        <v>91058</v>
+        <v>91061</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4096,32 +4096,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128740521</v>
+        <v>128742267</v>
       </c>
       <c r="B36" t="n">
-        <v>86941</v>
+        <v>86981</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4131,10 +4131,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>717216</v>
+        <v>717105</v>
       </c>
       <c r="R36" t="n">
-        <v>6374357</v>
+        <v>6374393</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4175,50 +4175,51 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128738900</v>
+        <v>128738858</v>
       </c>
       <c r="B37" t="n">
-        <v>86941</v>
+        <v>86981</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4228,10 +4229,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>716960</v>
+        <v>717003</v>
       </c>
       <c r="R37" t="n">
-        <v>6374079</v>
+        <v>6374177</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4263,7 +4264,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4273,7 +4274,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4282,6 +4283,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4300,32 +4302,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128742267</v>
+        <v>128740521</v>
       </c>
       <c r="B38" t="n">
-        <v>86978</v>
+        <v>86944</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4335,10 +4337,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>717105</v>
+        <v>717216</v>
       </c>
       <c r="R38" t="n">
-        <v>6374393</v>
+        <v>6374357</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4379,51 +4381,50 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128738858</v>
+        <v>128738900</v>
       </c>
       <c r="B39" t="n">
-        <v>86978</v>
+        <v>86944</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4433,10 +4434,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>717003</v>
+        <v>716960</v>
       </c>
       <c r="R39" t="n">
-        <v>6374177</v>
+        <v>6374079</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4468,7 +4469,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4478,7 +4479,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4487,7 +4488,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4509,7 +4509,7 @@
         <v>128740509</v>
       </c>
       <c r="B40" t="n">
-        <v>87000</v>
+        <v>87003</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>128738887</v>
       </c>
       <c r="B41" t="n">
-        <v>86825</v>
+        <v>86828</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>128742259</v>
       </c>
       <c r="B42" t="n">
-        <v>87023</v>
+        <v>87026</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>128738895</v>
       </c>
       <c r="B43" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>128742268</v>
       </c>
       <c r="B44" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>128742280</v>
       </c>
       <c r="B45" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5111,32 +5111,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128738880</v>
+        <v>128742289</v>
       </c>
       <c r="B46" t="n">
-        <v>86803</v>
+        <v>86981</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>716983</v>
+        <v>716965</v>
       </c>
       <c r="R46" t="n">
-        <v>6374266</v>
+        <v>6374079</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5179,71 +5179,62 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128738838</v>
+        <v>128742269</v>
       </c>
       <c r="B47" t="n">
-        <v>87023</v>
+        <v>86981</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5253,10 +5244,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>717020</v>
+        <v>717186</v>
       </c>
       <c r="R47" t="n">
-        <v>6374199</v>
+        <v>6374129</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5286,49 +5277,40 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128742269</v>
+        <v>128742279</v>
       </c>
       <c r="B48" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5360,10 +5342,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>717186</v>
+        <v>717013</v>
       </c>
       <c r="R48" t="n">
-        <v>6374129</v>
+        <v>6374176</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5426,7 +5408,7 @@
         <v>128742288</v>
       </c>
       <c r="B49" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5521,32 +5503,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128742289</v>
+        <v>128738880</v>
       </c>
       <c r="B50" t="n">
-        <v>86978</v>
+        <v>86806</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5556,10 +5538,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>716965</v>
+        <v>716983</v>
       </c>
       <c r="R50" t="n">
-        <v>6374079</v>
+        <v>6374266</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5589,62 +5571,71 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128742279</v>
+        <v>128738838</v>
       </c>
       <c r="B51" t="n">
-        <v>86978</v>
+        <v>87026</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5654,10 +5645,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>717013</v>
+        <v>717020</v>
       </c>
       <c r="R51" t="n">
-        <v>6374176</v>
+        <v>6374199</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5687,30 +5678,39 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5720,7 +5720,7 @@
         <v>128738896</v>
       </c>
       <c r="B52" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>128742291</v>
       </c>
       <c r="B53" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>128742284</v>
       </c>
       <c r="B54" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>128738841</v>
       </c>
       <c r="B55" t="n">
-        <v>87023</v>
+        <v>87026</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>128738835</v>
       </c>
       <c r="B56" t="n">
-        <v>87023</v>
+        <v>87026</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>128742252</v>
       </c>
       <c r="B57" t="n">
-        <v>87023</v>
+        <v>87026</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>128740522</v>
       </c>
       <c r="B58" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>128742263</v>
       </c>
       <c r="B59" t="n">
-        <v>91032</v>
+        <v>91035</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>128742282</v>
       </c>
       <c r="B60" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6624,32 +6624,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128742276</v>
+        <v>128740491</v>
       </c>
       <c r="B61" t="n">
-        <v>87000</v>
+        <v>86782</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6659,10 +6659,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>717269</v>
+        <v>717281</v>
       </c>
       <c r="R61" t="n">
-        <v>6374317</v>
+        <v>6374215</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6709,22 +6709,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128738884</v>
+        <v>128742255</v>
       </c>
       <c r="B62" t="n">
-        <v>86825</v>
+        <v>87026</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6732,21 +6732,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>424</v>
+        <v>3767</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6756,10 +6756,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>716969</v>
+        <v>717059</v>
       </c>
       <c r="R62" t="n">
-        <v>6374310</v>
+        <v>6374329</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6789,19 +6789,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>14:32</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6816,12 +6806,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -6935,32 +6925,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128740491</v>
+        <v>128742276</v>
       </c>
       <c r="B64" t="n">
-        <v>86779</v>
+        <v>87003</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3762</v>
+        <v>449</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6970,10 +6960,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>717281</v>
+        <v>717269</v>
       </c>
       <c r="R64" t="n">
-        <v>6374215</v>
+        <v>6374317</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7020,22 +7010,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128742255</v>
+        <v>128738884</v>
       </c>
       <c r="B65" t="n">
-        <v>87023</v>
+        <v>86828</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7043,21 +7033,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3767</v>
+        <v>424</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7067,10 +7057,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>717059</v>
+        <v>716969</v>
       </c>
       <c r="R65" t="n">
-        <v>6374329</v>
+        <v>6374310</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7100,9 +7090,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7117,22 +7117,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128740512</v>
+        <v>128738851</v>
       </c>
       <c r="B66" t="n">
-        <v>86803</v>
+        <v>86782</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7140,21 +7140,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3712</v>
+        <v>3762</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7164,10 +7164,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>717079</v>
+        <v>717040</v>
       </c>
       <c r="R66" t="n">
-        <v>6374436</v>
+        <v>6374229</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7197,9 +7197,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7214,22 +7224,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128738851</v>
+        <v>128740512</v>
       </c>
       <c r="B67" t="n">
-        <v>86779</v>
+        <v>86806</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7237,21 +7247,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7261,10 +7271,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>717040</v>
+        <v>717079</v>
       </c>
       <c r="R67" t="n">
-        <v>6374229</v>
+        <v>6374436</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7294,19 +7304,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7321,44 +7321,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128738836</v>
+        <v>128738855</v>
       </c>
       <c r="B68" t="n">
-        <v>87023</v>
+        <v>86981</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7368,10 +7368,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>717056</v>
+        <v>716966</v>
       </c>
       <c r="R68" t="n">
-        <v>6374262</v>
+        <v>6374312</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7403,7 +7403,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7422,6 +7422,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7440,32 +7441,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128738855</v>
+        <v>128738836</v>
       </c>
       <c r="B69" t="n">
-        <v>86978</v>
+        <v>87026</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7475,10 +7476,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>716966</v>
+        <v>717056</v>
       </c>
       <c r="R69" t="n">
-        <v>6374312</v>
+        <v>6374262</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7510,7 +7511,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7520,7 +7521,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7529,7 +7530,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7551,7 +7551,7 @@
         <v>128738852</v>
       </c>
       <c r="B70" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7656,10 +7656,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128740508</v>
+        <v>128742251</v>
       </c>
       <c r="B71" t="n">
-        <v>87000</v>
+        <v>87026</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7667,21 +7667,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7691,10 +7691,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>717063</v>
+        <v>717106</v>
       </c>
       <c r="R71" t="n">
-        <v>6374397</v>
+        <v>6374415</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7741,44 +7741,44 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128740519</v>
+        <v>128738833</v>
       </c>
       <c r="B72" t="n">
-        <v>86941</v>
+        <v>87026</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7788,10 +7788,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>717067</v>
+        <v>716976</v>
       </c>
       <c r="R72" t="n">
-        <v>6374399</v>
+        <v>6374331</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7821,9 +7821,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7838,44 +7848,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128742251</v>
+        <v>128740519</v>
       </c>
       <c r="B73" t="n">
-        <v>87023</v>
+        <v>86944</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7885,10 +7895,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>717106</v>
+        <v>717067</v>
       </c>
       <c r="R73" t="n">
-        <v>6374415</v>
+        <v>6374399</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7935,22 +7945,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128738833</v>
+        <v>128740508</v>
       </c>
       <c r="B74" t="n">
-        <v>87023</v>
+        <v>87003</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7958,21 +7968,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7982,10 +7992,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>716976</v>
+        <v>717063</v>
       </c>
       <c r="R74" t="n">
-        <v>6374331</v>
+        <v>6374397</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8015,19 +8025,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8042,12 +8042,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8057,7 +8057,7 @@
         <v>128742287</v>
       </c>
       <c r="B75" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>128742270</v>
       </c>
       <c r="B76" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>128742290</v>
       </c>
       <c r="B77" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8348,32 +8348,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128740516</v>
+        <v>128738891</v>
       </c>
       <c r="B78" t="n">
-        <v>92158</v>
+        <v>86981</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6031</v>
+        <v>6003295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8383,10 +8383,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>717218</v>
+        <v>717025</v>
       </c>
       <c r="R78" t="n">
-        <v>6374124</v>
+        <v>6374225</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8416,61 +8416,72 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128738891</v>
+        <v>128740516</v>
       </c>
       <c r="B79" t="n">
-        <v>86978</v>
+        <v>92161</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6003295</v>
+        <v>6031</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8480,10 +8491,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>717025</v>
+        <v>717218</v>
       </c>
       <c r="R79" t="n">
-        <v>6374225</v>
+        <v>6374124</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8513,40 +8524,29 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -8556,7 +8556,7 @@
         <v>128738890</v>
       </c>
       <c r="B80" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>128740484</v>
       </c>
       <c r="B81" t="n">
-        <v>87023</v>
+        <v>87026</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>128740518</v>
       </c>
       <c r="B82" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>128740503</v>
       </c>
       <c r="B83" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>128740510</v>
       </c>
       <c r="B84" t="n">
-        <v>86944</v>
+        <v>86947</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
         <v>128738899</v>
       </c>
       <c r="B85" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>128806499</v>
       </c>
       <c r="B86" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9254,10 +9254,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128806483</v>
+        <v>128815957</v>
       </c>
       <c r="B87" t="n">
-        <v>90998</v>
+        <v>86998</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9265,21 +9265,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>720</v>
+        <v>248934</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Knölfotad bananspindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Cortinarius stjernegaardii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>Brandrud &amp; Frøslev</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9292,10 +9292,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>717267</v>
+        <v>717020</v>
       </c>
       <c r="R87" t="n">
-        <v>6374381</v>
+        <v>6374147</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9322,12 +9322,27 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Bilddokumentation av Ullas fynd. Uppsvullen bulb och orange basalmycel. Ek fanss på fyndplatsen som domineras av kalktallskog.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9343,22 +9358,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128815957</v>
+        <v>128806483</v>
       </c>
       <c r="B88" t="n">
-        <v>86995</v>
+        <v>91001</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9366,21 +9381,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>248934</v>
+        <v>720</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knölfotad bananspindling</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cortinarius stjernegaardii</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Brandrud &amp; Frøslev</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9393,10 +9408,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>717020</v>
+        <v>717267</v>
       </c>
       <c r="R88" t="n">
-        <v>6374147</v>
+        <v>6374381</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9423,27 +9438,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>10:37</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Bilddokumentation av Ullas fynd. Uppsvullen bulb och orange basalmycel. Ek fanss på fyndplatsen som domineras av kalktallskog.</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9459,12 +9459,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -9474,7 +9474,7 @@
         <v>128738885</v>
       </c>
       <c r="B89" t="n">
-        <v>86825</v>
+        <v>86828</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
         <v>128806494</v>
       </c>
       <c r="B90" t="n">
-        <v>87000</v>
+        <v>87003</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>128806493</v>
       </c>
       <c r="B91" t="n">
-        <v>87000</v>
+        <v>87003</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         <v>128805996</v>
       </c>
       <c r="B92" t="n">
-        <v>87023</v>
+        <v>87026</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9869,32 +9869,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128738846</v>
+        <v>128738839</v>
       </c>
       <c r="B93" t="n">
-        <v>91032</v>
+        <v>87026</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5741</v>
+        <v>3767</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9904,10 +9904,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>717037</v>
+        <v>717039</v>
       </c>
       <c r="R93" t="n">
-        <v>6374226</v>
+        <v>6374168</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9976,10 +9976,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128815850</v>
+        <v>128738846</v>
       </c>
       <c r="B94" t="n">
-        <v>89501</v>
+        <v>91035</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9987,21 +9987,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>236437</v>
+        <v>5741</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Brun klibbskivling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Limacella glioderma</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Maire</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10011,10 +10011,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>716975</v>
+        <v>717037</v>
       </c>
       <c r="R94" t="n">
-        <v>6374071</v>
+        <v>6374226</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10046,7 +10046,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10083,32 +10083,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128738839</v>
+        <v>128806038</v>
       </c>
       <c r="B95" t="n">
-        <v>87023</v>
+        <v>98681</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3767</v>
+        <v>219862</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10118,10 +10118,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>717039</v>
+        <v>717113</v>
       </c>
       <c r="R95" t="n">
-        <v>6374168</v>
+        <v>6374105</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10148,22 +10148,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>10:24</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>10:24</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10178,12 +10168,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -10193,7 +10183,7 @@
         <v>128806044</v>
       </c>
       <c r="B96" t="n">
-        <v>87000</v>
+        <v>87003</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10287,10 +10277,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128806038</v>
+        <v>128815850</v>
       </c>
       <c r="B97" t="n">
-        <v>98678</v>
+        <v>89504</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10298,21 +10288,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>219862</v>
+        <v>236437</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Brun klibbskivling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Limacella glioderma</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Maire</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10322,10 +10312,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>717113</v>
+        <v>716975</v>
       </c>
       <c r="R97" t="n">
-        <v>6374105</v>
+        <v>6374071</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10352,12 +10342,22 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10372,12 +10372,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -10387,7 +10387,7 @@
         <v>128806004</v>
       </c>
       <c r="B98" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>128806484</v>
       </c>
       <c r="B99" t="n">
-        <v>90998</v>
+        <v>91001</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10582,10 +10582,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128738866</v>
+        <v>128806009</v>
       </c>
       <c r="B100" t="n">
-        <v>90264</v>
+        <v>86981</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10593,21 +10593,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>970</v>
+        <v>6003295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10617,10 +10617,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>717039</v>
+        <v>717132</v>
       </c>
       <c r="R100" t="n">
-        <v>6374321</v>
+        <v>6374140</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10647,22 +10647,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>13:50</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>13:50</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10678,12 +10668,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -10693,7 +10683,7 @@
         <v>128738897</v>
       </c>
       <c r="B101" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10798,32 +10788,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128806005</v>
+        <v>128738866</v>
       </c>
       <c r="B102" t="n">
-        <v>91032</v>
+        <v>90267</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5741</v>
+        <v>970</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10833,10 +10823,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>717142</v>
+        <v>717039</v>
       </c>
       <c r="R102" t="n">
-        <v>6374197</v>
+        <v>6374321</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10863,12 +10853,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10877,50 +10877,51 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128806009</v>
+        <v>128806005</v>
       </c>
       <c r="B103" t="n">
-        <v>86978</v>
+        <v>91035</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6003295</v>
+        <v>5741</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10930,10 +10931,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>717132</v>
+        <v>717142</v>
       </c>
       <c r="R103" t="n">
-        <v>6374140</v>
+        <v>6374197</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10974,7 +10975,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -10986,17 +10986,17 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128738875</v>
+        <v>128805993</v>
       </c>
       <c r="B104" t="n">
-        <v>87035</v>
+        <v>87026</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11004,19 +11004,23 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>433</v>
+        <v>3767</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr"/>
+          <t>Cortinarius violaceomaculatus</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -11024,10 +11028,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>716968</v>
+        <v>717148</v>
       </c>
       <c r="R104" t="n">
-        <v>6374251</v>
+        <v>6374174</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11054,22 +11058,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>12:41</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>12:41</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11084,22 +11078,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128738842</v>
+        <v>128738875</v>
       </c>
       <c r="B105" t="n">
-        <v>87023</v>
+        <v>87038</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11107,23 +11101,19 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>3767</v>
+        <v>433</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Brandrud</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
@@ -11131,10 +11121,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>716981</v>
+        <v>716968</v>
       </c>
       <c r="R105" t="n">
-        <v>6374088</v>
+        <v>6374251</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11166,7 +11156,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11176,7 +11166,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11203,10 +11193,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128805993</v>
+        <v>128738842</v>
       </c>
       <c r="B106" t="n">
-        <v>87023</v>
+        <v>87026</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11238,10 +11228,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>717148</v>
+        <v>716981</v>
       </c>
       <c r="R106" t="n">
-        <v>6374174</v>
+        <v>6374088</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11268,12 +11258,22 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11288,44 +11288,44 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128738843</v>
+        <v>128806010</v>
       </c>
       <c r="B107" t="n">
-        <v>87023</v>
+        <v>86981</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11335,10 +11335,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>716967</v>
+        <v>717186</v>
       </c>
       <c r="R107" t="n">
-        <v>6374084</v>
+        <v>6374253</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11365,22 +11365,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>09:26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>09:26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11389,28 +11379,29 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128806056</v>
+        <v>128806023</v>
       </c>
       <c r="B108" t="n">
-        <v>106982</v>
+        <v>86981</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11418,21 +11409,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221849</v>
+        <v>6003295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11442,10 +11433,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>717370</v>
+        <v>717360</v>
       </c>
       <c r="R108" t="n">
-        <v>6374168</v>
+        <v>6374214</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11486,6 +11477,7 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11497,39 +11489,39 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128806010</v>
+        <v>128738843</v>
       </c>
       <c r="B109" t="n">
-        <v>86978</v>
+        <v>87026</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11539,10 +11531,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>717186</v>
+        <v>716967</v>
       </c>
       <c r="R109" t="n">
-        <v>6374253</v>
+        <v>6374084</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11569,12 +11561,22 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11583,29 +11585,28 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128806023</v>
+        <v>128806056</v>
       </c>
       <c r="B110" t="n">
-        <v>86978</v>
+        <v>106985</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11613,21 +11614,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6003295</v>
+        <v>221849</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11637,10 +11638,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>717360</v>
+        <v>717370</v>
       </c>
       <c r="R110" t="n">
-        <v>6374214</v>
+        <v>6374168</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11681,7 +11682,6 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
@@ -11703,7 +11703,7 @@
         <v>128806497</v>
       </c>
       <c r="B111" t="n">
-        <v>86803</v>
+        <v>86806</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11800,7 +11800,7 @@
         <v>128806022</v>
       </c>
       <c r="B112" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>128738840</v>
       </c>
       <c r="B113" t="n">
-        <v>87023</v>
+        <v>87026</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12002,32 +12002,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128738893</v>
+        <v>128738886</v>
       </c>
       <c r="B114" t="n">
-        <v>86978</v>
+        <v>86828</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12037,10 +12037,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>717000</v>
+        <v>716990</v>
       </c>
       <c r="R114" t="n">
-        <v>6374121</v>
+        <v>6374260</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12072,7 +12072,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12091,7 +12091,6 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12110,32 +12109,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128806495</v>
+        <v>128738893</v>
       </c>
       <c r="B115" t="n">
-        <v>86865</v>
+        <v>86981</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>442</v>
+        <v>6003295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12145,10 +12144,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>717357</v>
+        <v>717000</v>
       </c>
       <c r="R115" t="n">
-        <v>6374169</v>
+        <v>6374121</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12175,12 +12174,22 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12189,48 +12198,53 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128806049</v>
+        <v>128806043</v>
       </c>
       <c r="B116" t="n">
-        <v>87035</v>
+        <v>75155</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>433</v>
+        <v>6426</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -12238,10 +12252,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>717128</v>
+        <v>717359</v>
       </c>
       <c r="R116" t="n">
-        <v>6374123</v>
+        <v>6374214</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12300,32 +12314,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128806043</v>
+        <v>128806495</v>
       </c>
       <c r="B117" t="n">
-        <v>75155</v>
+        <v>86868</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6426</v>
+        <v>442</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12335,10 +12349,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>717359</v>
+        <v>717357</v>
       </c>
       <c r="R117" t="n">
-        <v>6374214</v>
+        <v>6374169</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12385,46 +12399,42 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128806064</v>
+        <v>128806049</v>
       </c>
       <c r="B118" t="n">
-        <v>86941</v>
+        <v>87038</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3674</v>
+        <v>433</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
@@ -12432,10 +12442,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>717299</v>
+        <v>717128</v>
       </c>
       <c r="R118" t="n">
-        <v>6374300</v>
+        <v>6374123</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12494,32 +12504,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128806050</v>
+        <v>128806064</v>
       </c>
       <c r="B119" t="n">
         <v>86944</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6037417</v>
+        <v>3674</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12529,10 +12539,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>717311</v>
+        <v>717299</v>
       </c>
       <c r="R119" t="n">
-        <v>6374287</v>
+        <v>6374300</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12573,7 +12583,6 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -12592,32 +12601,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128738886</v>
+        <v>128806050</v>
       </c>
       <c r="B120" t="n">
-        <v>86825</v>
+        <v>86947</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>424</v>
+        <v>6037417</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12627,10 +12636,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>716990</v>
+        <v>717311</v>
       </c>
       <c r="R120" t="n">
-        <v>6374260</v>
+        <v>6374287</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12657,22 +12666,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12681,18 +12680,19 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -12702,7 +12702,7 @@
         <v>128738892</v>
       </c>
       <c r="B121" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>128806052</v>
       </c>
       <c r="B122" t="n">
-        <v>86803</v>
+        <v>86806</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12904,10 +12904,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128806045</v>
+        <v>128738882</v>
       </c>
       <c r="B123" t="n">
-        <v>87000</v>
+        <v>87108</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12915,34 +12915,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>449</v>
+        <v>3563</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Stor granspindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius bovinus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Fr. sl.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>717324</v>
+        <v>717013</v>
       </c>
       <c r="R123" t="n">
-        <v>6374179</v>
+        <v>6374226</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12969,12 +12972,22 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -12983,66 +12996,64 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128738882</v>
+        <v>128806011</v>
       </c>
       <c r="B124" t="n">
-        <v>87105</v>
+        <v>86981</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>3563</v>
+        <v>6003295</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Stor granspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cortinarius bovinus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Fr. sl.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>717013</v>
+        <v>717367</v>
       </c>
       <c r="R124" t="n">
-        <v>6374226</v>
+        <v>6374231</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13069,22 +13080,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>13:07</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>13:07</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13100,12 +13101,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -13115,7 +13116,7 @@
         <v>128738894</v>
       </c>
       <c r="B125" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13220,32 +13221,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128806051</v>
+        <v>128806045</v>
       </c>
       <c r="B126" t="n">
-        <v>86803</v>
+        <v>87003</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>3712</v>
+        <v>449</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13255,10 +13256,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>717327</v>
+        <v>717324</v>
       </c>
       <c r="R126" t="n">
-        <v>6374171</v>
+        <v>6374179</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13317,32 +13318,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128806011</v>
+        <v>128806051</v>
       </c>
       <c r="B127" t="n">
-        <v>86978</v>
+        <v>86806</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13352,10 +13353,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>717367</v>
+        <v>717327</v>
       </c>
       <c r="R127" t="n">
-        <v>6374231</v>
+        <v>6374171</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13396,7 +13397,6 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13408,7 +13408,7 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
@@ -13418,7 +13418,7 @@
         <v>128806485</v>
       </c>
       <c r="B128" t="n">
-        <v>86803</v>
+        <v>86806</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13513,32 +13513,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128806491</v>
+        <v>128806492</v>
       </c>
       <c r="B129" t="n">
-        <v>86978</v>
+        <v>91061</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6003295</v>
+        <v>5747</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13548,10 +13548,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>717324</v>
+        <v>717146</v>
       </c>
       <c r="R129" t="n">
-        <v>6374171</v>
+        <v>6374178</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13592,7 +13592,6 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13611,32 +13610,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128806492</v>
+        <v>128806491</v>
       </c>
       <c r="B130" t="n">
-        <v>91058</v>
+        <v>86981</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13646,10 +13645,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>717146</v>
+        <v>717324</v>
       </c>
       <c r="R130" t="n">
-        <v>6374178</v>
+        <v>6374171</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13690,6 +13689,7 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13711,7 +13711,7 @@
         <v>128806057</v>
       </c>
       <c r="B131" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13805,32 +13805,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128806058</v>
+        <v>128806487</v>
       </c>
       <c r="B132" t="n">
-        <v>86941</v>
+        <v>87026</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13840,10 +13840,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>717196</v>
+        <v>717275</v>
       </c>
       <c r="R132" t="n">
-        <v>6374281</v>
+        <v>6374183</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13890,22 +13890,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128806487</v>
+        <v>128738847</v>
       </c>
       <c r="B133" t="n">
-        <v>87023</v>
+        <v>86897</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13913,21 +13913,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>3767</v>
+        <v>248956</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13937,10 +13937,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>717275</v>
+        <v>716980</v>
       </c>
       <c r="R133" t="n">
-        <v>6374183</v>
+        <v>6374264</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13967,12 +13967,22 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -13987,44 +13997,44 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128806490</v>
+        <v>128806058</v>
       </c>
       <c r="B134" t="n">
-        <v>86978</v>
+        <v>86944</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14034,10 +14044,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>717333</v>
+        <v>717196</v>
       </c>
       <c r="R134" t="n">
-        <v>6374202</v>
+        <v>6374281</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14078,51 +14088,50 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128738847</v>
+        <v>128806490</v>
       </c>
       <c r="B135" t="n">
-        <v>86894</v>
+        <v>86981</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14132,10 +14141,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>716980</v>
+        <v>717333</v>
       </c>
       <c r="R135" t="n">
-        <v>6374264</v>
+        <v>6374202</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14162,22 +14171,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14186,18 +14185,19 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -14207,7 +14207,7 @@
         <v>128806013</v>
       </c>
       <c r="B136" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14305,7 +14305,7 @@
         <v>128806065</v>
       </c>
       <c r="B137" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14402,7 +14402,7 @@
         <v>128806486</v>
       </c>
       <c r="B138" t="n">
-        <v>87023</v>
+        <v>87026</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         <v>128738883</v>
       </c>
       <c r="B139" t="n">
-        <v>86841</v>
+        <v>86844</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14604,32 +14604,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128806496</v>
+        <v>128805991</v>
       </c>
       <c r="B140" t="n">
-        <v>96252</v>
+        <v>87026</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2180</v>
+        <v>3767</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14639,10 +14639,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>717337</v>
+        <v>717147</v>
       </c>
       <c r="R140" t="n">
-        <v>6374082</v>
+        <v>6374164</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14689,44 +14689,44 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128805991</v>
+        <v>128806496</v>
       </c>
       <c r="B141" t="n">
-        <v>87023</v>
+        <v>96255</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3767</v>
+        <v>2180</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14736,10 +14736,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>717147</v>
+        <v>717337</v>
       </c>
       <c r="R141" t="n">
-        <v>6374164</v>
+        <v>6374082</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14786,12 +14786,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
@@ -14801,7 +14801,7 @@
         <v>128806024</v>
       </c>
       <c r="B142" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14899,7 +14899,7 @@
         <v>128738867</v>
       </c>
       <c r="B143" t="n">
-        <v>87000</v>
+        <v>87003</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>128742275</v>
       </c>
       <c r="B144" t="n">
-        <v>86929</v>
+        <v>86932</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 42607-2025 artfynd.xlsx
+++ b/artfynd/A 42607-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128738845</v>
+        <v>128738854</v>
       </c>
       <c r="B2" t="n">
-        <v>86782</v>
+        <v>86981</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716961</v>
+        <v>716967</v>
       </c>
       <c r="R2" t="n">
-        <v>6374255</v>
+        <v>6374338</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,6 +764,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,32 +783,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128738831</v>
+        <v>128740487</v>
       </c>
       <c r="B3" t="n">
-        <v>87026</v>
+        <v>86981</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717030</v>
+        <v>717292</v>
       </c>
       <c r="R3" t="n">
-        <v>6374429</v>
+        <v>6374265</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,71 +851,62 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128742256</v>
+        <v>128738845</v>
       </c>
       <c r="B4" t="n">
-        <v>87026</v>
+        <v>86782</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717053</v>
+        <v>716961</v>
       </c>
       <c r="R4" t="n">
-        <v>6374253</v>
+        <v>6374255</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,9 +949,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,44 +976,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128740514</v>
+        <v>128738831</v>
       </c>
       <c r="B5" t="n">
-        <v>86806</v>
+        <v>87026</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3712</v>
+        <v>3767</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717295</v>
+        <v>717030</v>
       </c>
       <c r="R5" t="n">
-        <v>6374249</v>
+        <v>6374429</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,9 +1056,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,44 +1083,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128740505</v>
+        <v>128742256</v>
       </c>
       <c r="B6" t="n">
-        <v>98681</v>
+        <v>87026</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219862</v>
+        <v>3767</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717182</v>
+        <v>717053</v>
       </c>
       <c r="R6" t="n">
-        <v>6374336</v>
+        <v>6374253</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,44 +1180,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128738854</v>
+        <v>128740514</v>
       </c>
       <c r="B7" t="n">
-        <v>86981</v>
+        <v>86806</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1227,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716967</v>
+        <v>717295</v>
       </c>
       <c r="R7" t="n">
-        <v>6374338</v>
+        <v>6374249</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1248,72 +1260,61 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128740487</v>
+        <v>128740505</v>
       </c>
       <c r="B8" t="n">
-        <v>86981</v>
+        <v>98681</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6003295</v>
+        <v>219862</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1323,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717292</v>
+        <v>717182</v>
       </c>
       <c r="R8" t="n">
-        <v>6374265</v>
+        <v>6374336</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,7 +1368,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1805,32 +1805,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128740482</v>
+        <v>128740504</v>
       </c>
       <c r="B13" t="n">
-        <v>87026</v>
+        <v>98681</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3767</v>
+        <v>219862</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>717057</v>
+        <v>717091</v>
       </c>
       <c r="R13" t="n">
-        <v>6374457</v>
+        <v>6374400</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2000,32 +2000,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128740504</v>
+        <v>128740482</v>
       </c>
       <c r="B15" t="n">
-        <v>98681</v>
+        <v>87026</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219862</v>
+        <v>3767</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2035,10 +2035,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>717091</v>
+        <v>717057</v>
       </c>
       <c r="R15" t="n">
-        <v>6374400</v>
+        <v>6374457</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -3121,32 +3121,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128742283</v>
+        <v>128742273</v>
       </c>
       <c r="B26" t="n">
-        <v>86981</v>
+        <v>86957</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6003295</v>
+        <v>1988</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>717040</v>
+        <v>717014</v>
       </c>
       <c r="R26" t="n">
-        <v>6374195</v>
+        <v>6374164</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3200,7 +3200,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3219,32 +3218,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128742281</v>
+        <v>128740489</v>
       </c>
       <c r="B27" t="n">
-        <v>86981</v>
+        <v>91035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6003295</v>
+        <v>5741</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3254,10 +3253,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>717039</v>
+        <v>717220</v>
       </c>
       <c r="R27" t="n">
-        <v>6374227</v>
+        <v>6374302</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3298,51 +3297,50 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128742273</v>
+        <v>128742283</v>
       </c>
       <c r="B28" t="n">
-        <v>86957</v>
+        <v>86981</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1988</v>
+        <v>6003295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3352,10 +3350,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>717014</v>
+        <v>717040</v>
       </c>
       <c r="R28" t="n">
-        <v>6374164</v>
+        <v>6374195</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3396,6 +3394,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3414,32 +3413,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128740489</v>
+        <v>128742281</v>
       </c>
       <c r="B29" t="n">
-        <v>91035</v>
+        <v>86981</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5741</v>
+        <v>6003295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3449,10 +3448,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>717220</v>
+        <v>717039</v>
       </c>
       <c r="R29" t="n">
-        <v>6374302</v>
+        <v>6374227</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3493,50 +3492,51 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128740500</v>
+        <v>128742293</v>
       </c>
       <c r="B30" t="n">
-        <v>86981</v>
+        <v>86944</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3546,10 +3546,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>717281</v>
+        <v>717094</v>
       </c>
       <c r="R30" t="n">
-        <v>6374283</v>
+        <v>6374468</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3590,51 +3590,50 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128740499</v>
+        <v>128742254</v>
       </c>
       <c r="B31" t="n">
-        <v>86981</v>
+        <v>87026</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3644,10 +3643,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>717145</v>
+        <v>717285</v>
       </c>
       <c r="R31" t="n">
-        <v>6374308</v>
+        <v>6374272</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3688,51 +3687,50 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128740502</v>
+        <v>128742272</v>
       </c>
       <c r="B32" t="n">
-        <v>86981</v>
+        <v>91061</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6003295</v>
+        <v>5747</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3742,10 +3740,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>717282</v>
+        <v>717018</v>
       </c>
       <c r="R32" t="n">
-        <v>6374266</v>
+        <v>6374179</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3786,51 +3784,50 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128742293</v>
+        <v>128740500</v>
       </c>
       <c r="B33" t="n">
-        <v>86944</v>
+        <v>86981</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3840,10 +3837,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>717094</v>
+        <v>717281</v>
       </c>
       <c r="R33" t="n">
-        <v>6374468</v>
+        <v>6374283</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3884,50 +3881,51 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128742254</v>
+        <v>128740499</v>
       </c>
       <c r="B34" t="n">
-        <v>87026</v>
+        <v>86981</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3937,10 +3935,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>717285</v>
+        <v>717145</v>
       </c>
       <c r="R34" t="n">
-        <v>6374272</v>
+        <v>6374308</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3981,50 +3979,51 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128742272</v>
+        <v>128740502</v>
       </c>
       <c r="B35" t="n">
-        <v>91061</v>
+        <v>86981</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4034,10 +4033,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>717018</v>
+        <v>717282</v>
       </c>
       <c r="R35" t="n">
-        <v>6374179</v>
+        <v>6374266</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4078,18 +4077,19 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -5111,7 +5111,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128742289</v>
+        <v>128738896</v>
       </c>
       <c r="B46" t="n">
         <v>86981</v>
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>716965</v>
+        <v>717038</v>
       </c>
       <c r="R46" t="n">
-        <v>6374079</v>
+        <v>6374195</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5179,9 +5179,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5197,44 +5207,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128742269</v>
+        <v>128738880</v>
       </c>
       <c r="B47" t="n">
-        <v>86981</v>
+        <v>86806</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5244,10 +5254,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>717186</v>
+        <v>716983</v>
       </c>
       <c r="R47" t="n">
-        <v>6374129</v>
+        <v>6374266</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5277,62 +5287,71 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128742279</v>
+        <v>128738838</v>
       </c>
       <c r="B48" t="n">
-        <v>86981</v>
+        <v>87026</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5342,10 +5361,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>717013</v>
+        <v>717020</v>
       </c>
       <c r="R48" t="n">
-        <v>6374176</v>
+        <v>6374199</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5375,37 +5394,46 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128742288</v>
+        <v>128742289</v>
       </c>
       <c r="B49" t="n">
         <v>86981</v>
@@ -5440,10 +5468,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>716995</v>
+        <v>716965</v>
       </c>
       <c r="R49" t="n">
-        <v>6374147</v>
+        <v>6374079</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5503,32 +5531,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128738880</v>
+        <v>128742269</v>
       </c>
       <c r="B50" t="n">
-        <v>86806</v>
+        <v>86981</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5538,10 +5566,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>716983</v>
+        <v>717186</v>
       </c>
       <c r="R50" t="n">
-        <v>6374266</v>
+        <v>6374129</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5571,71 +5599,62 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128738838</v>
+        <v>128742279</v>
       </c>
       <c r="B51" t="n">
-        <v>87026</v>
+        <v>86981</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5645,10 +5664,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>717020</v>
+        <v>717013</v>
       </c>
       <c r="R51" t="n">
-        <v>6374199</v>
+        <v>6374176</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5678,46 +5697,37 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128738896</v>
+        <v>128742288</v>
       </c>
       <c r="B52" t="n">
         <v>86981</v>
@@ -5752,10 +5762,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>717038</v>
+        <v>716995</v>
       </c>
       <c r="R52" t="n">
-        <v>6374195</v>
+        <v>6374147</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5785,19 +5795,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>10:50</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5813,12 +5813,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6021,32 +6021,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128738841</v>
+        <v>128742282</v>
       </c>
       <c r="B55" t="n">
-        <v>87026</v>
+        <v>86981</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6056,10 +6056,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>716992</v>
+        <v>717040</v>
       </c>
       <c r="R55" t="n">
-        <v>6374116</v>
+        <v>6374212</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6089,46 +6089,37 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128738835</v>
+        <v>128738841</v>
       </c>
       <c r="B56" t="n">
         <v>87026</v>
@@ -6163,10 +6154,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>716983</v>
+        <v>716992</v>
       </c>
       <c r="R56" t="n">
-        <v>6374357</v>
+        <v>6374116</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6198,7 +6189,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6208,7 +6199,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6235,7 +6226,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128742252</v>
+        <v>128738835</v>
       </c>
       <c r="B57" t="n">
         <v>87026</v>
@@ -6270,10 +6261,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>717146</v>
+        <v>716983</v>
       </c>
       <c r="R57" t="n">
-        <v>6374313</v>
+        <v>6374357</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6303,9 +6294,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6320,44 +6321,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128740522</v>
+        <v>128742252</v>
       </c>
       <c r="B58" t="n">
-        <v>86944</v>
+        <v>87026</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6367,10 +6368,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>717274</v>
+        <v>717146</v>
       </c>
       <c r="R58" t="n">
-        <v>6374210</v>
+        <v>6374313</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6417,22 +6418,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128742263</v>
+        <v>128740522</v>
       </c>
       <c r="B59" t="n">
-        <v>91035</v>
+        <v>86944</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6440,21 +6441,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5741</v>
+        <v>3674</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6464,10 +6465,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>717281</v>
+        <v>717274</v>
       </c>
       <c r="R59" t="n">
-        <v>6374199</v>
+        <v>6374210</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6514,44 +6515,44 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128742282</v>
+        <v>128742263</v>
       </c>
       <c r="B60" t="n">
-        <v>86981</v>
+        <v>91035</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6003295</v>
+        <v>5741</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6561,10 +6562,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>717040</v>
+        <v>717281</v>
       </c>
       <c r="R60" t="n">
-        <v>6374212</v>
+        <v>6374199</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6605,7 +6606,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6624,32 +6624,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128740491</v>
+        <v>128742276</v>
       </c>
       <c r="B61" t="n">
-        <v>86782</v>
+        <v>87003</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3762</v>
+        <v>449</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6659,10 +6659,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>717281</v>
+        <v>717269</v>
       </c>
       <c r="R61" t="n">
-        <v>6374215</v>
+        <v>6374317</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6709,22 +6709,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128742255</v>
+        <v>128738884</v>
       </c>
       <c r="B62" t="n">
-        <v>87026</v>
+        <v>86828</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6732,21 +6732,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3767</v>
+        <v>424</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6756,10 +6756,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>717059</v>
+        <v>716969</v>
       </c>
       <c r="R62" t="n">
-        <v>6374329</v>
+        <v>6374310</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6789,9 +6789,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6806,44 +6816,44 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128738848</v>
+        <v>128740491</v>
       </c>
       <c r="B63" t="n">
-        <v>57720</v>
+        <v>86782</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>3762</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6853,10 +6863,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>717165</v>
+        <v>717281</v>
       </c>
       <c r="R63" t="n">
-        <v>6374351</v>
+        <v>6374215</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6886,19 +6896,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>10:25</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6913,22 +6913,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128742276</v>
+        <v>128742255</v>
       </c>
       <c r="B64" t="n">
-        <v>87003</v>
+        <v>87026</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6936,21 +6936,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6960,10 +6960,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>717269</v>
+        <v>717059</v>
       </c>
       <c r="R64" t="n">
-        <v>6374317</v>
+        <v>6374329</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7022,32 +7022,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128738884</v>
+        <v>128738848</v>
       </c>
       <c r="B65" t="n">
-        <v>86828</v>
+        <v>57720</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>424</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>716969</v>
+        <v>717165</v>
       </c>
       <c r="R65" t="n">
-        <v>6374310</v>
+        <v>6374351</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7092,7 +7092,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9578,10 +9578,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128806494</v>
+        <v>128805996</v>
       </c>
       <c r="B90" t="n">
-        <v>87003</v>
+        <v>87026</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9589,21 +9589,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9613,10 +9613,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>717333</v>
+        <v>717308</v>
       </c>
       <c r="R90" t="n">
-        <v>6374180</v>
+        <v>6374239</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9663,19 +9663,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128806493</v>
+        <v>128806494</v>
       </c>
       <c r="B91" t="n">
         <v>87003</v>
@@ -9710,10 +9710,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>717133</v>
+        <v>717333</v>
       </c>
       <c r="R91" t="n">
-        <v>6374199</v>
+        <v>6374180</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9772,10 +9772,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128805996</v>
+        <v>128806493</v>
       </c>
       <c r="B92" t="n">
-        <v>87026</v>
+        <v>87003</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9783,21 +9783,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9807,10 +9807,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>717308</v>
+        <v>717133</v>
       </c>
       <c r="R92" t="n">
-        <v>6374239</v>
+        <v>6374199</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9857,44 +9857,44 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128738839</v>
+        <v>128806038</v>
       </c>
       <c r="B93" t="n">
-        <v>87026</v>
+        <v>98681</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3767</v>
+        <v>219862</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9904,10 +9904,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>717039</v>
+        <v>717113</v>
       </c>
       <c r="R93" t="n">
-        <v>6374168</v>
+        <v>6374105</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9934,22 +9934,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>10:24</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>10:24</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9964,44 +9954,44 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128738846</v>
+        <v>128738839</v>
       </c>
       <c r="B94" t="n">
-        <v>91035</v>
+        <v>87026</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5741</v>
+        <v>3767</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10011,10 +10001,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>717037</v>
+        <v>717039</v>
       </c>
       <c r="R94" t="n">
-        <v>6374226</v>
+        <v>6374168</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10046,7 +10036,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10056,7 +10046,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10083,10 +10073,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128806038</v>
+        <v>128738846</v>
       </c>
       <c r="B95" t="n">
-        <v>98681</v>
+        <v>91035</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10094,21 +10084,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>219862</v>
+        <v>5741</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10118,10 +10108,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>717113</v>
+        <v>717037</v>
       </c>
       <c r="R95" t="n">
-        <v>6374105</v>
+        <v>6374226</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10148,12 +10138,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10168,12 +10168,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -10582,10 +10582,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128806009</v>
+        <v>128738866</v>
       </c>
       <c r="B100" t="n">
-        <v>86981</v>
+        <v>90267</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10593,21 +10593,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6003295</v>
+        <v>970</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10617,10 +10617,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>717132</v>
+        <v>717039</v>
       </c>
       <c r="R100" t="n">
-        <v>6374140</v>
+        <v>6374321</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10647,12 +10647,22 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10668,12 +10678,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -10788,10 +10798,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128738866</v>
+        <v>128806009</v>
       </c>
       <c r="B102" t="n">
-        <v>90267</v>
+        <v>86981</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10799,21 +10809,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>970</v>
+        <v>6003295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10823,10 +10833,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>717039</v>
+        <v>717132</v>
       </c>
       <c r="R102" t="n">
-        <v>6374321</v>
+        <v>6374140</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10853,22 +10863,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>13:50</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>13:50</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10884,12 +10884,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -10993,10 +10993,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128805993</v>
+        <v>128738875</v>
       </c>
       <c r="B104" t="n">
-        <v>87026</v>
+        <v>87038</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11004,23 +11004,19 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>3767</v>
+        <v>433</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Brandrud</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -11028,10 +11024,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>717148</v>
+        <v>716968</v>
       </c>
       <c r="R104" t="n">
-        <v>6374174</v>
+        <v>6374251</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11058,12 +11054,22 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11078,22 +11084,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128738875</v>
+        <v>128738842</v>
       </c>
       <c r="B105" t="n">
-        <v>87038</v>
+        <v>87026</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11101,19 +11107,23 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>433</v>
+        <v>3767</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr"/>
+          <t>Cortinarius violaceomaculatus</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
@@ -11121,10 +11131,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>716968</v>
+        <v>716981</v>
       </c>
       <c r="R105" t="n">
-        <v>6374251</v>
+        <v>6374088</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11156,7 +11166,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11166,7 +11176,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11193,7 +11203,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128738842</v>
+        <v>128805993</v>
       </c>
       <c r="B106" t="n">
         <v>87026</v>
@@ -11228,10 +11238,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>716981</v>
+        <v>717148</v>
       </c>
       <c r="R106" t="n">
-        <v>6374088</v>
+        <v>6374174</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11258,22 +11268,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>09:31</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>09:31</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11288,22 +11288,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128806010</v>
+        <v>128806056</v>
       </c>
       <c r="B107" t="n">
-        <v>86981</v>
+        <v>106985</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11311,21 +11311,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6003295</v>
+        <v>221849</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11335,10 +11335,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>717186</v>
+        <v>717370</v>
       </c>
       <c r="R107" t="n">
-        <v>6374253</v>
+        <v>6374168</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11379,7 +11379,6 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11391,14 +11390,14 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128806023</v>
+        <v>128806010</v>
       </c>
       <c r="B108" t="n">
         <v>86981</v>
@@ -11433,10 +11432,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>717360</v>
+        <v>717186</v>
       </c>
       <c r="R108" t="n">
-        <v>6374214</v>
+        <v>6374253</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11496,32 +11495,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128738843</v>
+        <v>128806023</v>
       </c>
       <c r="B109" t="n">
-        <v>87026</v>
+        <v>86981</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H109" t=